--- a/data/Olahan Data Sampel.xlsx
+++ b/data/Olahan Data Sampel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F9D784-0D54-45EC-BDEC-3A3C7A9E0C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B2E681-E6A1-4438-A421-887FF3D4F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Original" sheetId="1" r:id="rId1"/>
@@ -376,16 +376,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -966,27 +962,27 @@
       <c r="G9" s="2">
         <v>1057465</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <f>(C9-'2. Statistika Deskriptif'!B9)^3</f>
         <v>-41.511587890625044</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <f>(D9-'2. Statistika Deskriptif'!B10)^3</f>
         <v>4.0386695781250088</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <f>(E9-'2. Statistika Deskriptif'!B11)^3</f>
         <v>-3.7058852968749956</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9">
         <f>(C9-'2. Statistika Deskriptif'!B9)^4</f>
         <v>143.73387307128925</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9">
         <f>(D9-'2. Statistika Deskriptif'!B10)^4</f>
         <v>6.4315813031640809</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9">
         <f>(E9-'2. Statistika Deskriptif'!B11)^4</f>
         <v>5.7348574969140538</v>
       </c>
@@ -1013,27 +1009,27 @@
       <c r="G10" s="2">
         <v>1808420</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <f>(C10-'2. Statistika Deskriptif'!B9)^3</f>
         <v>24.325979359374976</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10">
         <f>(D10-'2. Statistika Deskriptif'!B10)^3</f>
         <v>-4.0768299843750011</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <f>(E10-'2. Statistika Deskriptif'!B11)^3</f>
         <v>13.019337828125016</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10">
         <f>(C10-'2. Statistika Deskriptif'!B9)^4</f>
         <v>70.484525193788983</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10">
         <f>(D10-'2. Statistika Deskriptif'!B10)^4</f>
         <v>6.5127359000390639</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10">
         <f>(E10-'2. Statistika Deskriptif'!B11)^4</f>
         <v>30.627992240664117</v>
       </c>
@@ -1060,27 +1056,27 @@
       <c r="G11" s="2">
         <v>723100</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <f>(C11-'2. Statistika Deskriptif'!B9)^3</f>
         <v>105.65610892187495</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11">
         <f>(D11-'2. Statistika Deskriptif'!B10)^3</f>
         <v>-2.1369234374999966E-2</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <f>(E11-'2. Statistika Deskriptif'!B11)^3</f>
         <v>-4.3908027343749945</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11">
         <f>(C11-'2. Statistika Deskriptif'!B9)^4</f>
         <v>499.48925492816375</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11">
         <f>(D11-'2. Statistika Deskriptif'!B10)^4</f>
         <v>5.9299625390624869E-3</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11">
         <f>(E11-'2. Statistika Deskriptif'!B11)^4</f>
         <v>7.1899394775390491</v>
       </c>
@@ -1107,27 +1103,27 @@
       <c r="G12" s="2">
         <v>439.48</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12">
         <f>(C12-'2. Statistika Deskriptif'!B9)^3</f>
         <v>-72.121166015625079</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12">
         <f>(D12-'2. Statistika Deskriptif'!B10)^3</f>
         <v>2.2545265625000151E-2</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12">
         <f>(E12-'2. Statistika Deskriptif'!B11)^3</f>
         <v>0.57696932812500279</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12">
         <f>(C12-'2. Statistika Deskriptif'!B9)^4</f>
         <v>300.20435354003951</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12">
         <f>(D12-'2. Statistika Deskriptif'!B10)^4</f>
         <v>6.3690375390625569E-3</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12">
         <f>(E12-'2. Statistika Deskriptif'!B11)^4</f>
         <v>0.48032696566406563</v>
       </c>
@@ -1182,27 +1178,27 @@
       <c r="G15" s="2">
         <v>1053482</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15">
         <f>(C15-'2. Statistika Deskriptif'!B14)^3</f>
         <v>-30.371327999999977</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15">
         <f>(D15-'2. Statistika Deskriptif'!B15)^3</f>
         <v>4.2910156249999858</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15">
         <f>(E15-'2. Statistika Deskriptif'!B16)^3</f>
         <v>-4.7204954843750091</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15">
         <f>(C15-'2. Statistika Deskriptif'!B14)^4</f>
         <v>94.758543359999919</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15">
         <f>(D15-'2. Statistika Deskriptif'!B15)^4</f>
         <v>6.9729003906249698</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15">
         <f>(E15-'2. Statistika Deskriptif'!B16)^4</f>
         <v>7.9186311750390841</v>
       </c>
@@ -1229,27 +1225,27 @@
       <c r="G16" s="2">
         <v>1834230</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16">
         <f>(C16-'2. Statistika Deskriptif'!B14)^3</f>
         <v>21.952000000000016</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16">
         <f>(D16-'2. Statistika Deskriptif'!B15)^3</f>
         <v>-4.7840941250000046</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16">
         <f>(E16-'2. Statistika Deskriptif'!B16)^3</f>
         <v>8.9019185781249988</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16">
         <f>(C16-'2. Statistika Deskriptif'!B14)^4</f>
         <v>61.465600000000066</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16">
         <f>(D16-'2. Statistika Deskriptif'!B15)^4</f>
         <v>8.0611986006250103</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16">
         <f>(E16-'2. Statistika Deskriptif'!B16)^4</f>
         <v>18.44922625316406</v>
       </c>
@@ -1276,27 +1272,27 @@
       <c r="G17" s="2">
         <v>732480</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17">
         <f>(C17-'2. Statistika Deskriptif'!B14)^3</f>
         <v>103.82300000000008</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17">
         <f>(D17-'2. Statistika Deskriptif'!B15)^3</f>
         <v>-5.2734375000000749E-2</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17">
         <f>(E17-'2. Statistika Deskriptif'!B16)^3</f>
         <v>-0.82397460937500233</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17">
         <f>(C17-'2. Statistika Deskriptif'!B14)^4</f>
         <v>487.96810000000045</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17">
         <f>(D17-'2. Statistika Deskriptif'!B15)^4</f>
         <v>1.9775390625000375E-2</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17">
         <f>(E17-'2. Statistika Deskriptif'!B16)^4</f>
         <v>0.77247619628906539</v>
       </c>
@@ -1323,124 +1319,124 @@
       <c r="G18" s="2">
         <v>445.06</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18">
         <f>(C18-'2. Statistika Deskriptif'!B14)^3</f>
         <v>-84.027671999999953</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18">
         <f>(D18-'2. Statistika Deskriptif'!B15)^3</f>
         <v>8.2312874999999272E-2</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18">
         <f>(E18-'2. Statistika Deskriptif'!B16)^3</f>
         <v>0.15966114062499881</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18">
         <f>(C18-'2. Statistika Deskriptif'!B14)^4</f>
         <v>368.04120335999971</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18">
         <f>(D18-'2. Statistika Deskriptif'!B15)^4</f>
         <v>3.580610062499958E-2</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18">
         <f>(E18-'2. Statistika Deskriptif'!B16)^4</f>
         <v>8.6616168789061643E-2</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="2">
         <f>(G3+G9+G15)/3</f>
         <v>1055947.6666666667</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="2">
         <f>C21/C$25</f>
         <v>0.29432026733409078</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="2">
         <f>SQRT(D21)</f>
         <v>0.54251291904810039</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="2">
         <f>(G4+G10+G16)/3</f>
         <v>1808280</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="2">
         <f t="shared" ref="D22:D24" si="0">C22/C$25</f>
         <v>0.50401499034032582</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="2">
         <f t="shared" ref="E22:E24" si="1">SQRT(D22)</f>
         <v>0.70994013151837376</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="2">
         <f>(G5+G11+G17)/3</f>
         <v>723083.33333333337</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="2">
         <f t="shared" si="0"/>
         <v>0.20154226074792103</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="2">
         <f t="shared" si="1"/>
         <v>0.44893458404083886</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="2">
         <f>(G6+G12+G18)/3</f>
         <v>439.43333333333334</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="2">
         <f t="shared" si="0"/>
         <v>1.2248157766231845E-4</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="2">
         <f t="shared" si="1"/>
         <v>1.1067139542913447E-2</v>
       </c>
@@ -1452,63 +1448,57 @@
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="2">
         <f>C3*$D21</f>
         <v>1.3273844056767494</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="2">
         <f t="shared" ref="D29:G29" si="2">D3*$D21</f>
         <v>3.3493646422619534</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="2">
         <f t="shared" si="2"/>
         <v>3.2286933326549758</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="2">
         <f t="shared" si="2"/>
         <v>23.954726558321649</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="2">
         <f t="shared" si="2"/>
         <v>311065.91326433123</v>
       </c>
@@ -1550,29 +1540,29 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="2">
         <f t="shared" ref="C30:G30" si="3">C4*$D22</f>
         <v>5.2871172486700182</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="2">
         <f t="shared" si="3"/>
         <v>4.1278827708872683</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="2">
         <f t="shared" si="3"/>
         <v>6.1741836316689911</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="2">
         <f t="shared" si="3"/>
         <v>34.313340542369382</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="2">
         <f t="shared" si="3"/>
         <v>898250.4756346253</v>
       </c>
@@ -1584,59 +1574,59 @@
         <f>((D4-'2. Statistika Deskriptif'!B$22)^2)*$D22</f>
         <v>0.68858529720798056</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30">
         <f>((E4-'2. Statistika Deskriptif'!B$23)^2)*$D22</f>
         <v>0.76904264468871986</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30">
         <f>((C4-'2. Statistika Deskriptif'!B$21)^3)*$D22</f>
         <v>1.0107259498557426</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30">
         <f>((D4-'2. Statistika Deskriptif'!B$22)^3)*$D22</f>
         <v>-0.80484989424572395</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30">
         <f>((E4-'2. Statistika Deskriptif'!B$23)^3)*$D22</f>
         <v>0.9499569130348392</v>
       </c>
-      <c r="N30" s="5">
+      <c r="N30">
         <f>((C4-'2. Statistika Deskriptif'!B$21)^4)*$D22</f>
         <v>1.2745691535760033</v>
       </c>
-      <c r="O30" s="5">
+      <c r="O30">
         <f>((D4-'2. Statistika Deskriptif'!B$22)^4)*$D22</f>
         <v>0.94074525682429211</v>
       </c>
-      <c r="P30" s="5">
+      <c r="P30">
         <f>((E4-'2. Statistika Deskriptif'!B$23)^4)*$D22</f>
         <v>1.1734305540207679</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="2">
         <f t="shared" ref="C31:G31" si="4">C5*$D23</f>
         <v>2.6140031219005357</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="2">
         <f t="shared" si="4"/>
         <v>1.8803892927781032</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="2">
         <f t="shared" si="4"/>
         <v>1.6103226633758891</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="2">
         <f t="shared" si="4"/>
         <v>14.706538766775797</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="2">
         <f t="shared" si="4"/>
         <v>143834.6652279688</v>
       </c>
@@ -1648,59 +1638,59 @@
         <f>((D5-'2. Statistika Deskriptif'!B$22)^2)*$D23</f>
         <v>1.6769698419622853E-4</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31">
         <f>((E5-'2. Statistika Deskriptif'!B$23)^2)*$D23</f>
         <v>1.8439376077514917</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31">
         <f>((C5-'2. Statistika Deskriptif'!B$21)^3)*$D23</f>
         <v>10.552231706655755</v>
       </c>
-      <c r="L31" s="5">
+      <c r="L31">
         <f>((D5-'2. Statistika Deskriptif'!B$22)^3)*$D23</f>
         <v>-4.8373199762110559E-6</v>
       </c>
-      <c r="M31" s="5">
+      <c r="M31">
         <f>((E5-'2. Statistika Deskriptif'!B$23)^3)*$D23</f>
         <v>-5.5774575052910151</v>
       </c>
-      <c r="N31" s="5">
+      <c r="N31">
         <f>((C5-'2. Statistika Deskriptif'!B$21)^4)*$D23</f>
         <v>39.476355375171188</v>
       </c>
-      <c r="O31" s="5">
+      <c r="O31">
         <f>((D5-'2. Statistika Deskriptif'!B$22)^4)*$D23</f>
         <v>1.3953539274665605E-7</v>
       </c>
-      <c r="P31" s="5">
+      <c r="P31">
         <f>((E5-'2. Statistika Deskriptif'!B$23)^4)*$D23</f>
         <v>16.870436446740946</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="2">
         <f t="shared" ref="C32:G32" si="5">C6*$D24</f>
         <v>4.5195702157395503E-4</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="2">
         <f t="shared" si="5"/>
         <v>1.2088931715270831E-3</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="2">
         <f t="shared" si="5"/>
         <v>1.5542912205348211E-3</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="2">
         <f t="shared" si="5"/>
         <v>8.9472792482323624E-3</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="2">
         <f t="shared" si="5"/>
         <v>5.3127609126807251E-2</v>
       </c>
@@ -1712,93 +1702,87 @@
         <f>((D6-'2. Statistika Deskriptif'!B$22)^2)*$D24</f>
         <v>3.2001842274494881E-5</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32">
         <f>((E6-'2. Statistika Deskriptif'!B$23)^2)*$D24</f>
         <v>3.437383540820161E-4</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32">
         <f>((C6-'2. Statistika Deskriptif'!B$21)^3)*$D24</f>
         <v>-2.0813958772531206E-2</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32">
         <f>((D6-'2. Statistika Deskriptif'!B$22)^3)*$D24</f>
         <v>1.6357882515552413E-5</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32">
         <f>((E6-'2. Statistika Deskriptif'!B$23)^3)*$D24</f>
         <v>5.758463305926523E-4</v>
       </c>
-      <c r="N32" s="5">
+      <c r="N32">
         <f>((C6-'2. Statistika Deskriptif'!B$21)^4)*$D24</f>
         <v>0.11528761708909256</v>
       </c>
-      <c r="O32" s="5">
+      <c r="O32">
         <f>((D6-'2. Statistika Deskriptif'!B$22)^4)*$D24</f>
         <v>8.3614036372485301E-6</v>
       </c>
-      <c r="P32" s="5">
+      <c r="P32">
         <f>((E6-'2. Statistika Deskriptif'!B$23)^4)*$D24</f>
         <v>9.6468430862941331E-4</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="2">
         <f>C9*$D21</f>
         <v>1.4539421206304086</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="2">
         <f t="shared" ref="D35:G35" si="6">D9*$D21</f>
         <v>3.3523078449352943</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="2">
         <f t="shared" si="6"/>
         <v>2.2809820718392038</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="2">
         <f t="shared" si="6"/>
         <v>24.072454665255286</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="2">
         <f t="shared" si="6"/>
         <v>311233.38149644429</v>
       </c>
@@ -1810,7 +1794,7 @@
         <f>((D9-'2. Statistika Deskriptif'!B$27)^2)*$D21</f>
         <v>1.1595154987518137</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35">
         <f>((E9-'2. Statistika Deskriptif'!B$28)^2)*$D21</f>
         <v>1.1166417744836827</v>
       </c>
@@ -1840,29 +1824,29 @@
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="2">
         <f t="shared" ref="C36:G36" si="7">C10*$D22</f>
         <v>5.6953693908456824</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="2">
         <f t="shared" si="7"/>
         <v>4.132922920790671</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="2">
         <f t="shared" si="7"/>
         <v>5.8717746374647959</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="2">
         <f t="shared" si="7"/>
         <v>34.424223840244252</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="2">
         <f t="shared" si="7"/>
         <v>911470.78883125202</v>
       </c>
@@ -1874,59 +1858,59 @@
         <f>((D10-'2. Statistika Deskriptif'!B$27)^2)*$D22</f>
         <v>0.7320217878616988</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36">
         <f>((E10-'2. Statistika Deskriptif'!B$28)^2)*$D22</f>
         <v>1.9208219175155063</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36">
         <f>((C10-'2. Statistika Deskriptif'!B$26)^3)*$D22</f>
         <v>1.7144192594125898</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36">
         <f>((D10-'2. Statistika Deskriptif'!B$27)^3)*$D22</f>
         <v>-0.88219437571094161</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36">
         <f>((E10-'2. Statistika Deskriptif'!B$28)^3)*$D22</f>
         <v>3.7498071013686456</v>
       </c>
-      <c r="N36" s="5">
+      <c r="N36">
         <f>((C10-'2. Statistika Deskriptif'!B$26)^4)*$D22</f>
         <v>2.5783481834018929</v>
       </c>
-      <c r="O36" s="5">
+      <c r="O36">
         <f>((D10-'2. Statistika Deskriptif'!B$27)^4)*$D22</f>
         <v>1.0631745249132614</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36">
         <f>((E10-'2. Statistika Deskriptif'!B$28)^4)*$D22</f>
         <v>7.3203315566401077</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="2">
         <f t="shared" ref="C37:G37" si="8">C11*$D23</f>
         <v>2.6462498836202033</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="2">
         <f t="shared" si="8"/>
         <v>1.9186823223202081</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="2">
         <f t="shared" si="8"/>
         <v>1.5438137173290751</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="2">
         <f t="shared" si="8"/>
         <v>14.752893486747819</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="2">
         <f t="shared" si="8"/>
         <v>145735.20874682171</v>
       </c>
@@ -1938,59 +1922,59 @@
         <f>((D11-'2. Statistika Deskriptif'!B$27)^2)*$D23</f>
         <v>2.6585540942063637E-3</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37">
         <f>((E11-'2. Statistika Deskriptif'!B$28)^2)*$D23</f>
         <v>0.83693937549183994</v>
       </c>
-      <c r="K37" s="5">
+      <c r="K37">
         <f>((C11-'2. Statistika Deskriptif'!B$26)^3)*$D23</f>
         <v>7.4684653219723662</v>
       </c>
-      <c r="L37" s="5">
+      <c r="L37">
         <f>((D11-'2. Statistika Deskriptif'!B$27)^3)*$D23</f>
         <v>3.0534104614904513E-4</v>
       </c>
-      <c r="M37" s="5">
+      <c r="M37">
         <f>((E11-'2. Statistika Deskriptif'!B$28)^3)*$D23</f>
         <v>-1.7055244038177808</v>
       </c>
-      <c r="N37" s="5">
+      <c r="N37">
         <f>((C11-'2. Statistika Deskriptif'!B$26)^4)*$D23</f>
         <v>24.899260551448165</v>
       </c>
-      <c r="O37" s="5">
+      <c r="O37">
         <f>((D11-'2. Statistika Deskriptif'!B$27)^4)*$D23</f>
         <v>3.5069120717374545E-5</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P37">
         <f>((E11-'2. Statistika Deskriptif'!B$28)^4)*$D23</f>
         <v>3.4755366723050742</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="2">
         <f t="shared" ref="C38:G38" si="9">C12*$D24</f>
         <v>5.1932188928823029E-4</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="2">
         <f t="shared" si="9"/>
         <v>1.23461430283617E-3</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="2">
         <f t="shared" si="9"/>
         <v>1.2407383817192859E-3</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="2">
         <f t="shared" si="9"/>
         <v>8.9778996426479411E-3</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="2">
         <f t="shared" si="9"/>
         <v>5.3828203751035711E-2</v>
       </c>
@@ -2002,93 +1986,87 @@
         <f>((D12-'2. Statistika Deskriptif'!B$27)^2)*$D24</f>
         <v>5.5781248891862822E-5</v>
       </c>
-      <c r="J38" s="5">
+      <c r="J38">
         <f>((E12-'2. Statistika Deskriptif'!B$28)^2)*$D24</f>
         <v>2.2877989606347136E-5</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K38">
         <f>((C12-'2. Statistika Deskriptif'!B$26)^3)*$D24</f>
         <v>-2.1007598619696685E-2</v>
       </c>
-      <c r="L38" s="5">
+      <c r="L38">
         <f>((D12-'2. Statistika Deskriptif'!B$27)^3)*$D24</f>
         <v>3.7644103980515347E-5</v>
       </c>
-      <c r="M38" s="5">
+      <c r="M38">
         <f>((E12-'2. Statistika Deskriptif'!B$28)^3)*$D24</f>
         <v>9.8876116747708269E-6</v>
       </c>
-      <c r="N38" s="5">
+      <c r="N38">
         <f>((C12-'2. Statistika Deskriptif'!B$26)^4)*$D24</f>
         <v>0.11671991360106967</v>
       </c>
-      <c r="O38" s="5">
+      <c r="O38">
         <f>((D12-'2. Statistika Deskriptif'!B$27)^4)*$D24</f>
         <v>2.5404210064263547E-5</v>
       </c>
-      <c r="P38" s="5">
+      <c r="P38">
         <f>((E12-'2. Statistika Deskriptif'!B$28)^4)*$D24</f>
         <v>4.2733153705053287E-6</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="2">
         <f>C15*$D21</f>
         <v>1.442169309937045</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="2">
         <f t="shared" ref="D41:G41" si="10">D15*$D21</f>
         <v>3.3935126823620667</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="2">
         <f t="shared" si="10"/>
         <v>1.7306031719244537</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="2">
         <f t="shared" si="10"/>
         <v>24.172523556148874</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="2">
         <f t="shared" si="10"/>
         <v>310061.10387165262</v>
       </c>
@@ -2130,29 +2108,29 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="2">
         <f t="shared" ref="C42:G42" si="11">C16*$D22</f>
         <v>5.4534421954823253</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="2">
         <f t="shared" si="11"/>
         <v>4.1430032205974783</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="2">
         <f t="shared" si="11"/>
         <v>4.8536643569773377</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="2">
         <f t="shared" si="11"/>
         <v>34.797194933096101</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="2">
         <f t="shared" si="11"/>
         <v>924479.41573193588</v>
       </c>
@@ -2168,55 +2146,55 @@
         <f>((E16-'2. Statistika Deskriptif'!B$33)^2)*$D22</f>
         <v>1.4747049941495245</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42">
         <f>((C16-'2. Statistika Deskriptif'!B$31)^3)*$D22</f>
         <v>1.2687369628171024</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42">
         <f>((D16-'2. Statistika Deskriptif'!B$32)^3)*$D22</f>
         <v>-0.957437777181394</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42">
         <f>((E16-'2. Statistika Deskriptif'!B$33)^3)*$D22</f>
         <v>2.5225280246120163</v>
       </c>
-      <c r="N42" s="5">
+      <c r="N42">
         <f>((C16-'2. Statistika Deskriptif'!B$31)^4)*$D22</f>
         <v>1.7258947420656205</v>
       </c>
-      <c r="O42" s="5">
+      <c r="O42">
         <f>((D16-'2. Statistika Deskriptif'!B$32)^4)*$D22</f>
         <v>1.1857676411126792</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42">
         <f>((E16-'2. Statistika Deskriptif'!B$33)^4)*$D22</f>
         <v>4.3148613859700697</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="2">
         <f t="shared" ref="C43:G43" si="12">C17*$D23</f>
         <v>2.5636175567135555</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="2">
         <f t="shared" si="12"/>
         <v>1.9206977449276874</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="2">
         <f t="shared" si="12"/>
         <v>1.3342097661512373</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="2">
         <f t="shared" si="12"/>
         <v>14.87986511101901</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="2">
         <f t="shared" si="12"/>
         <v>147625.67515263721</v>
       </c>
@@ -2232,55 +2210,55 @@
         <f>((E17-'2. Statistika Deskriptif'!B$33)^2)*$D23</f>
         <v>0.34032843558109088</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K43">
         <f>((C17-'2. Statistika Deskriptif'!B$31)^3)*$D23</f>
         <v>6.984717574178271</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43">
         <f>((D17-'2. Statistika Deskriptif'!B$32)^3)*$D23</f>
         <v>7.3730416408844228E-5</v>
       </c>
-      <c r="M43" s="5">
+      <c r="M43">
         <f>((E17-'2. Statistika Deskriptif'!B$33)^3)*$D23</f>
         <v>-0.44224638656904169</v>
       </c>
-      <c r="N43" s="5">
+      <c r="N43">
         <f>((C17-'2. Statistika Deskriptif'!B$31)^4)*$D23</f>
         <v>22.772450057899967</v>
       </c>
-      <c r="O43" s="5">
+      <c r="O43">
         <f>((D17-'2. Statistika Deskriptif'!B$32)^4)*$D23</f>
         <v>5.2731914628945332E-6</v>
       </c>
-      <c r="P43" s="5">
+      <c r="P43">
         <f>((E17-'2. Statistika Deskriptif'!B$33)^4)*$D23</f>
         <v>0.57468564476379913</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="2">
         <f t="shared" ref="C44:G44" si="13">C18*$D24</f>
         <v>4.4583294269083914E-4</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="2">
         <f t="shared" si="13"/>
         <v>1.2664595130283728E-3</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="2">
         <f t="shared" si="13"/>
         <v>9.9210077906477937E-4</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="2">
         <f t="shared" si="13"/>
         <v>9.0575126681284486E-3</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="2">
         <f t="shared" si="13"/>
         <v>5.451165095439145E-2</v>
       </c>
@@ -2296,27 +2274,27 @@
         <f>((E18-'2. Statistika Deskriptif'!B$33)^2)*$D24</f>
         <v>3.9918337246341545E-6</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K44">
         <f>((C18-'2. Statistika Deskriptif'!B$31)^3)*$D24</f>
         <v>-2.4141649742580786E-2</v>
       </c>
-      <c r="L44" s="5">
+      <c r="L44">
         <f>((D18-'2. Statistika Deskriptif'!B$32)^3)*$D24</f>
         <v>8.3900997313364047E-5</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44">
         <f>((E18-'2. Statistika Deskriptif'!B$33)^3)*$D24</f>
         <v>7.2064815404602641E-7</v>
       </c>
-      <c r="N44" s="5">
+      <c r="N44">
         <f>((C18-'2. Statistika Deskriptif'!B$31)^4)*$D24</f>
         <v>0.14049655293260607</v>
       </c>
-      <c r="O44" s="5">
+      <c r="O44">
         <f>((D18-'2. Statistika Deskriptif'!B$32)^4)*$D24</f>
         <v>7.3960398140687658E-5</v>
       </c>
-      <c r="P44" s="5">
+      <c r="P44">
         <f>((E18-'2. Statistika Deskriptif'!B$33)^4)*$D24</f>
         <v>1.3009904664241537E-7</v>
       </c>
@@ -2551,13 +2529,13 @@
       <c r="H8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2593,11 +2571,11 @@
         <f>MAX('1. Data Original'!C9:C12)</f>
         <v>13.13</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="2">
         <f>((1/4)*SUM('1. Data Original'!H9:H12))/(C9^3)</f>
         <v>7.0250798738267298E-2</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="2">
         <f>((1/4)*SUM('1. Data Original'!K9:K12))/(C9^4)-3</f>
         <v>-1.8756836742009684</v>
       </c>
@@ -2638,11 +2616,11 @@
         <f>MAX('1. Data Original'!D9:D12)</f>
         <v>11.39</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="2">
         <f>((1/4)*SUM('1. Data Original'!I9:I12))/(C10^3)</f>
         <v>-6.1580833995721817E-3</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="2">
         <f>((1/4)*SUM('1. Data Original'!L9:L12))/(C10^4)-3</f>
         <v>-1.1159982522379579</v>
       </c>
@@ -2683,11 +2661,11 @@
         <f>MAX('1. Data Original'!E9:E12)</f>
         <v>11.65</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="2">
         <f>((1/4)*SUM('1. Data Original'!J9:J12))/(C11^3)</f>
         <v>0.28943073137805847</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="2">
         <f>((1/4)*SUM('1. Data Original'!M9:M12))/(C11^4)-3</f>
         <v>-1.6214724299958387</v>
       </c>
@@ -2726,13 +2704,13 @@
       <c r="H13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2768,11 +2746,11 @@
         <f>MAX('1. Data Original'!C15:C18)</f>
         <v>12.72</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="2">
         <f>((1/4)*SUM('1. Data Original'!H15:H18))/(C14^3)</f>
         <v>5.0397983713451562E-2</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="2">
         <f>((1/4)*SUM('1. Data Original'!K15:K18))/(C14^4)-3</f>
         <v>-1.8308628739818147</v>
       </c>
@@ -2813,11 +2791,11 @@
         <f>MAX('1. Data Original'!D15:D18)</f>
         <v>11.53</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="2">
         <f>((1/4)*SUM('1. Data Original'!I15:I18))/(C15^3)</f>
         <v>-6.6198656219491364E-2</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="2">
         <f>((1/4)*SUM('1. Data Original'!L15:L18))/(C15^4)-3</f>
         <v>-1.2117319337382952</v>
       </c>
@@ -2858,11 +2836,11 @@
         <f>MAX('1. Data Original'!E15:E18)</f>
         <v>9.6300000000000008</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="2">
         <f>((1/4)*SUM('1. Data Original'!J15:J18))/(C16^3)</f>
         <v>0.29510441044055769</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="2">
         <f>((1/4)*SUM('1. Data Original'!M15:M18))/(C16^4)-3</f>
         <v>-1.4124086847054669</v>
       </c>
@@ -2872,571 +2850,531 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="2">
         <f>SUM('1. Data Original'!C29:C32)</f>
         <v>9.2289567332688769</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="2">
         <f>SQRT(SUM('1. Data Original'!H29:H32))</f>
         <v>3.1906127054315507</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="2">
         <f>D4</f>
         <v>3.69</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="2">
         <f t="shared" ref="E21:H21" si="0">E4</f>
         <v>4.3049999999999997</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="2">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="2">
         <f t="shared" si="0"/>
         <v>11.11</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="2">
         <f t="shared" si="0"/>
         <v>12.97</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="2">
         <f>(SUM('1. Data Original'!K29:K32))/(C21^3)</f>
         <v>-0.59686044653529424</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="2">
         <f>(SUM('1. Data Original'!N29:N32))/(C21^4)-3</f>
         <v>-1.1973216560923112</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="2">
         <f>C21/B21*100</f>
         <v>34.571759275129274</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="2">
         <f>SUM('1. Data Original'!D29:D32)</f>
         <v>9.3588455990988528</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="2">
         <f>SQRT(SUM('1. Data Original'!I29:I32))</f>
         <v>1.3751736079340964</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="2">
         <f t="shared" ref="D22:H22" si="1">D5</f>
         <v>8.19</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="2">
         <f t="shared" si="1"/>
         <v>9.0449999999999999</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="2">
         <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="2">
         <f t="shared" si="1"/>
         <v>10.247499999999999</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="2">
         <f t="shared" si="1"/>
         <v>11.38</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="2">
         <f>(SUM('1. Data Original'!L29:L32))/(C22^3)</f>
         <v>0.6249459661916813</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="2">
         <f>(SUM('1. Data Original'!O29:O32))/(C22^4)-3</f>
         <v>-1.3635739661742687</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="2">
         <f>C22/B22*100</f>
         <v>14.693837967222256</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="2">
         <f>SUM('1. Data Original'!E29:E32)</f>
         <v>11.014753918920391</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="2">
         <f>SQRT(SUM('1. Data Original'!J29:J32))</f>
         <v>1.6167601828224403</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="2">
         <f t="shared" ref="D23:H23" si="2">D6</f>
         <v>7.99</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="2">
         <f t="shared" si="2"/>
         <v>10.225000000000001</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="2">
         <f t="shared" si="2"/>
         <v>11.61</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="2">
         <f t="shared" si="2"/>
         <v>12.36</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="2">
         <f t="shared" si="2"/>
         <v>12.69</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="2">
         <f>(SUM('1. Data Original'!M29:M32))/(C23^3)</f>
         <v>-1.0948587599659791</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="2">
         <f>(SUM('1. Data Original'!P29:P32))/(C23^4)-3</f>
         <v>-0.35898757658715086</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="2">
         <f>C23/B23*100</f>
         <v>14.678132573123401</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="2">
         <f>SUM('1. Data Original'!C35:C38)</f>
         <v>9.7960807169855819</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="2">
         <f>SQRT(SUM('1. Data Original'!H35:H38))</f>
         <v>3.2131625659959258</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="2">
         <f>D9</f>
         <v>4.24</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="2">
         <f t="shared" ref="E26:H26" si="3">E9</f>
         <v>4.7650000000000006</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="2">
         <f t="shared" si="3"/>
         <v>8.120000000000001</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="2">
         <f t="shared" si="3"/>
         <v>11.7575</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="2">
         <f t="shared" si="3"/>
         <v>13.13</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="2">
         <f>(SUM('1. Data Original'!K35:K38))/(C26^3)</f>
         <v>-0.73979110925758917</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="2">
         <f>(SUM('1. Data Original'!N35:N38))/(C26^4)-3</f>
         <v>-1.2056852450954711</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="2">
         <f>C26/B26*100</f>
         <v>32.800490919032256</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="2">
         <f>SUM('1. Data Original'!D35:D38)</f>
         <v>9.4051477023490104</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="2">
         <f>SQRT(SUM('1. Data Original'!I35:I38))</f>
         <v>1.3763181398051145</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="2">
         <f t="shared" ref="D27:H27" si="4">D10</f>
         <v>8.1999999999999993</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="2">
         <f t="shared" si="4"/>
         <v>9.19</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="2">
         <f t="shared" si="4"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="2">
         <f t="shared" si="4"/>
         <v>10.407500000000001</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="2">
         <f t="shared" si="4"/>
         <v>11.39</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="2">
         <f>(SUM('1. Data Original'!L35:L38))/(C27^3)</f>
         <v>0.5445205379398339</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="2">
         <f>(SUM('1. Data Original'!O35:O38))/(C27^4)-3</f>
         <v>-1.4305991853999025</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="2">
         <f>C27/B27*100</f>
         <v>14.633668533045666</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="2">
         <f>SUM('1. Data Original'!E35:E38)</f>
         <v>9.6978111650147945</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="2">
         <f>SQRT(SUM('1. Data Original'!J35:J38))</f>
         <v>1.968356153108638</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="2">
         <f t="shared" ref="D28:H28" si="5">D11</f>
         <v>7.66</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="2">
         <f t="shared" si="5"/>
         <v>7.7275</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="2">
         <f t="shared" si="5"/>
         <v>8.9400000000000013</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="2">
         <f t="shared" si="5"/>
         <v>10.510000000000002</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="2">
         <f t="shared" si="5"/>
         <v>11.65</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="2">
         <f>(SUM('1. Data Original'!M35:M38))/(C28^3)</f>
         <v>-1.7140105285742942E-2</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="2">
         <f>(SUM('1. Data Original'!P35:P38))/(C28^4)-3</f>
         <v>-1.998587743684701</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="2">
         <f>C28/B28*100</f>
         <v>20.29691153617792</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="2">
         <f>SUM('1. Data Original'!C41:C44)</f>
         <v>9.4596748950756151</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="2">
         <f>SQRT(SUM('1. Data Original'!H41:H44))</f>
         <v>3.0328638621926665</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="2">
         <f>D14</f>
         <v>3.64</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="2">
         <f t="shared" ref="E31:H31" si="6">E14</f>
         <v>4.585</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="2">
         <f t="shared" si="6"/>
         <v>7.86</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="2">
         <f t="shared" si="6"/>
         <v>11.295</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="2">
         <f t="shared" si="6"/>
         <v>12.72</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="2">
         <f>(SUM('1. Data Original'!K41:K44))/(C31^3)</f>
         <v>-0.7051568785876513</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="2">
         <f>(SUM('1. Data Original'!N41:N44))/(C31^4)-3</f>
         <v>-1.2051479247370764</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="2">
         <f>C31/B31*100</f>
         <v>32.060973509475176</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="2">
         <f>SUM('1. Data Original'!D41:D44)</f>
         <v>9.4584801074002609</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="2">
         <f>SQRT(SUM('1. Data Original'!I41:I44))</f>
         <v>1.4273004096492865</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="2">
         <f t="shared" ref="D32:H32" si="7">D15</f>
         <v>8.2200000000000006</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="2">
         <f t="shared" si="7"/>
         <v>9.2025000000000006</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="2">
         <f t="shared" si="7"/>
         <v>9.9349999999999987</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="2">
         <f t="shared" si="7"/>
         <v>10.637499999999999</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="2">
         <f t="shared" si="7"/>
         <v>11.53</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="2">
         <f>(SUM('1. Data Original'!L41:L44))/(C32^3)</f>
         <v>0.57056527576500127</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="2">
         <f>(SUM('1. Data Original'!O41:O44))/(C32^4)-3</f>
         <v>-1.4083472340636569</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="2">
         <f>C32/B32*100</f>
         <v>15.090166638216798</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="2">
         <f>SUM('1. Data Original'!E41:E44)</f>
         <v>7.9194693958320936</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="2">
         <f>SQRT(SUM('1. Data Original'!J41:J44))</f>
         <v>1.7433426413984199</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="2">
         <f t="shared" ref="D33:H33" si="8">D16</f>
         <v>5.88</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="2">
         <f t="shared" si="8"/>
         <v>6.4350000000000005</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="2">
         <f t="shared" si="8"/>
         <v>7.3599999999999994</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="2">
         <f t="shared" si="8"/>
         <v>8.4824999999999999</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="2">
         <f t="shared" si="8"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="2">
         <f>(SUM('1. Data Original'!M41:M44))/(C33^3)</f>
         <v>-7.859830013266382E-2</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="2">
         <f>(SUM('1. Data Original'!P41:P44))/(C33^4)-3</f>
         <v>-1.9193946101383521</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="2">
         <f>C33/B33*100</f>
         <v>22.013376834512634</v>
       </c>
@@ -3448,7 +3386,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -3767,16 +3705,16 @@
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="2">
         <v>-0.86747510051361965</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="2">
         <v>0.65602008335464623</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="2">
         <v>1.2878374840224223</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="2">
         <v>-1.0763824668634485</v>
       </c>
     </row>
@@ -3784,16 +3722,16 @@
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="2">
         <v>1.470441673732648</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="2">
         <v>-1.3092376976493632</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="2">
         <v>-0.31587265583886387</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="2">
         <v>0.15466867975558224</v>
       </c>
     </row>
@@ -3801,16 +3739,16 @@
       <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="2">
         <v>-2.7239665775486309E-3</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="2">
         <v>0.69461147727503925</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="2">
         <v>-1.6262080467968558</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="2">
         <v>0.93432053609936616</v>
       </c>
     </row>
@@ -3840,16 +3778,16 @@
       <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="2">
         <v>-0.89356642597673686</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="2">
         <v>0.74775703083540601</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="2">
         <v>1.2200246292577679</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="2">
         <v>-1.0742152341164382</v>
       </c>
     </row>
@@ -3857,16 +3795,16 @@
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="2">
         <v>1.3907269337392965</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="2">
         <v>-1.3950934233271741</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="2">
         <v>-0.24234017212725545</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="2">
         <v>0.24670666171513458</v>
       </c>
     </row>
@@ -3874,16 +3812,16 @@
       <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="2">
         <v>-0.92056543529687862</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="2">
         <v>1.3994379234480829</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="2">
         <v>-0.97410397434483909</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="2">
         <v>0.49523148619363677</v>
       </c>
     </row>
@@ -3913,16 +3851,16 @@
       <c r="A33" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="2">
         <v>-0.81342175593733446</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="2">
         <v>0.72999388353350569</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="2">
         <v>1.2253468759312416</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="2">
         <v>-1.1419190035274118</v>
       </c>
     </row>
@@ -3930,16 +3868,16 @@
       <c r="A34" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="2">
         <v>1.3483620090341482</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="2">
         <v>-1.3981476832138724</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="2">
         <v>-0.31116046362326677</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="2">
         <v>0.36094613780298668</v>
       </c>
     </row>
@@ -3947,839 +3885,1019 @@
       <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="2">
         <v>-1.1657688798586363</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="2">
         <v>1.4402718351755721</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="2">
         <v>-0.65151017875855255</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="2">
         <v>0.37700722344161447</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="str">
+      <c r="A39" s="1" t="str">
         <f>A2</f>
         <v>Data Tahun 2020</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="str">
+      <c r="A40" s="1" t="str">
         <f t="shared" ref="A40:A72" si="0">A3</f>
         <v>Kabupaten/Kota</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="str">
+      <c r="A41" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Jakarta Pusat</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="2">
         <f>('1. Data Original'!C3 - '2. Statistika Deskriptif'!B21) / '2. Statistika Deskriptif'!C21</f>
         <v>-1.4790127066301544</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="2">
         <f>('1. Data Original'!D3 - '2. Statistika Deskriptif'!B22) / '2. Statistika Deskriptif'!C22</f>
         <v>1.4697449029272016</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="2">
         <f>('1. Data Original'!E3 - '2. Statistika Deskriptif'!B23) / '2. Statistika Deskriptif'!C23</f>
         <v>-2.7681235223310521E-2</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="G41">
-        <f>'1. Data Original'!$E21*B41</f>
-        <v>-0.80238350078315679</v>
-      </c>
-      <c r="H41" s="5">
-        <f>'1. Data Original'!$E21*C41</f>
-        <v>0.79735559754310315</v>
-      </c>
-      <c r="I41" s="5">
-        <f>'1. Data Original'!$E21*D41</f>
-        <v>-1.5017427723855286E-2</v>
-      </c>
-      <c r="K41" s="5">
-        <v>-0.80238350078315679</v>
-      </c>
-      <c r="L41" s="5">
-        <v>0.28059351143101624</v>
-      </c>
-      <c r="M41" s="5">
-        <v>0.52638281668271525</v>
-      </c>
-      <c r="N41" s="5">
-        <v>-1.9212738351129775E-2</v>
+      <c r="G41" cm="1">
+        <f t="array" ref="G41:J43">TRANSPOSE(B41:D44)</f>
+        <v>-1.4790127066301544</v>
+      </c>
+      <c r="H41">
+        <v>0.39523545574314989</v>
+      </c>
+      <c r="I41">
+        <v>1.172515630105323</v>
+      </c>
+      <c r="J41">
+        <v>-1.7360166352499051</v>
+      </c>
+      <c r="L41">
+        <f>B41*'1. Data Original'!$D21</f>
+        <v>-0.43530341520590421</v>
+      </c>
+      <c r="M41">
+        <f>C41*'1. Data Original'!$D21</f>
+        <v>0.43257571274245127</v>
+      </c>
+      <c r="N41">
+        <f>D41*'1. Data Original'!$D21</f>
+        <v>-8.1471485510626034E-3</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="str">
+      <c r="A42" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="2">
         <f>('1. Data Original'!C4 - '2. Statistika Deskriptif'!B21) / '2. Statistika Deskriptif'!C21</f>
         <v>0.39523545574314989</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="2">
         <f>('1. Data Original'!D4 - '2. Statistika Deskriptif'!B22) / '2. Statistika Deskriptif'!C22</f>
         <v>-0.84996221012035955</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="2">
         <f>('1. Data Original'!E4 - '2. Statistika Deskriptif'!B23) / '2. Statistika Deskriptif'!C23</f>
         <v>0.76402554578205428</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="G42" s="5">
-        <f>'1. Data Original'!$E22*B42</f>
-        <v>0.28059351143101624</v>
-      </c>
-      <c r="H42" s="5">
-        <f>'1. Data Original'!$E22*C42</f>
-        <v>-0.60342228323849567</v>
-      </c>
-      <c r="I42" s="5">
-        <f>'1. Data Original'!$E22*D42</f>
-        <v>0.54241239645590889</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0.79735559754310315</v>
-      </c>
-      <c r="L42" s="5">
-        <v>-0.60342228323849567</v>
-      </c>
-      <c r="M42" s="5">
-        <v>-9.4168379600496691E-3</v>
-      </c>
-      <c r="N42" s="5">
-        <v>4.1136748481130072E-3</v>
+      <c r="G42">
+        <v>1.4697449029272016</v>
+      </c>
+      <c r="H42">
+        <v>-0.84996221012035955</v>
+      </c>
+      <c r="I42">
+        <v>-2.0975969093958317E-2</v>
+      </c>
+      <c r="J42">
+        <v>0.37170172402380985</v>
+      </c>
+      <c r="L42">
+        <f>B42*'1. Data Original'!$D22</f>
+        <v>0.19920459440853797</v>
+      </c>
+      <c r="M42">
+        <f>C42*'1. Data Original'!$D22</f>
+        <v>-0.42839369512345499</v>
+      </c>
+      <c r="N42">
+        <f>D42*'1. Data Original'!$D22</f>
+        <v>0.38508032807710424</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="str">
+      <c r="A43" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="2">
         <f>('1. Data Original'!C5 - '2. Statistika Deskriptif'!B21) / '2. Statistika Deskriptif'!C21</f>
         <v>1.172515630105323</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="2">
         <f>('1. Data Original'!D5 - '2. Statistika Deskriptif'!B22) / '2. Statistika Deskriptif'!C22</f>
         <v>-2.0975969093958317E-2</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="2">
         <f>('1. Data Original'!E5 - '2. Statistika Deskriptif'!B23) / '2. Statistika Deskriptif'!C23</f>
         <v>-1.8708735847514268</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="G43" s="5">
-        <f>'1. Data Original'!$E23*B43</f>
-        <v>0.52638281668271525</v>
-      </c>
-      <c r="H43" s="5">
-        <f>'1. Data Original'!$E23*C43</f>
-        <v>-9.4168379600496691E-3</v>
-      </c>
-      <c r="I43" s="5">
-        <f>'1. Data Original'!$E23*D43</f>
-        <v>-0.8398998545633749</v>
-      </c>
-      <c r="K43" s="5">
-        <v>-1.5017427723855286E-2</v>
-      </c>
-      <c r="L43" s="5">
-        <v>0.54241239645590889</v>
-      </c>
-      <c r="M43" s="5">
-        <v>-0.8398998545633749</v>
-      </c>
-      <c r="N43" s="5">
-        <v>1.1467490568490259E-2</v>
+      <c r="G43">
+        <v>-2.7681235223310521E-2</v>
+      </c>
+      <c r="H43">
+        <v>0.76402554578205428</v>
+      </c>
+      <c r="I43">
+        <v>-1.8708735847514268</v>
+      </c>
+      <c r="J43">
+        <v>1.0361747517526483</v>
+      </c>
+      <c r="L43">
+        <f>B43*'1. Data Original'!$D23</f>
+        <v>0.23631145085369992</v>
+      </c>
+      <c r="M43">
+        <f>C43*'1. Data Original'!$D23</f>
+        <v>-4.2275442325748801E-3</v>
+      </c>
+      <c r="N43">
+        <f>D43*'1. Data Original'!$D23</f>
+        <v>-0.37706009184436978</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="str">
+      <c r="A44" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="2">
         <f>('1. Data Original'!C6 - '2. Statistika Deskriptif'!B21) / '2. Statistika Deskriptif'!C21</f>
         <v>-1.7360166352499051</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="2">
         <f>('1. Data Original'!D6 - '2. Statistika Deskriptif'!B22) / '2. Statistika Deskriptif'!C22</f>
         <v>0.37170172402380985</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="2">
         <f>('1. Data Original'!E6 - '2. Statistika Deskriptif'!B23) / '2. Statistika Deskriptif'!C23</f>
         <v>1.0361747517526483</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="G44" s="5">
-        <f>'1. Data Original'!$E24*B44</f>
-        <v>-1.9212738351129775E-2</v>
-      </c>
-      <c r="H44" s="5">
-        <f>'1. Data Original'!$E24*C44</f>
-        <v>4.1136748481130072E-3</v>
-      </c>
-      <c r="I44" s="5">
-        <f>'1. Data Original'!$E24*D44</f>
-        <v>1.1467490568490259E-2</v>
+      <c r="L44">
+        <f>B44*'1. Data Original'!$D24</f>
+        <v>-2.12630056333438E-4</v>
+      </c>
+      <c r="M44">
+        <f>C44*'1. Data Original'!$D24</f>
+        <v>4.5526613578239924E-5</v>
+      </c>
+      <c r="N44">
+        <f>D44*'1. Data Original'!$D24</f>
+        <v>1.2691231832852553E-4</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="str">
+      <c r="A45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Data Tahun 2021</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="str">
+      <c r="A46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Kabupaten/Kota</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="str">
+      <c r="A47" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Jakarta Pusat</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="2">
         <f>('1. Data Original'!C9 - '2. Statistika Deskriptif'!B26) / '2. Statistika Deskriptif'!C26</f>
         <v>-1.5113087549245832</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="2">
         <f>('1. Data Original'!D9 - '2. Statistika Deskriptif'!B27) / '2. Statistika Deskriptif'!C27</f>
         <v>1.4421464342045536</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="2">
         <f>('1. Data Original'!E9 - '2. Statistika Deskriptif'!B28) / '2. Statistika Deskriptif'!C28</f>
         <v>-0.98956236245082141</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="G47" s="5">
-        <f>'1. Data Original'!$E21*B47</f>
-        <v>-0.81990452421708582</v>
-      </c>
-      <c r="H47" s="5">
-        <f>'1. Data Original'!$E21*C47</f>
-        <v>0.78238307171512167</v>
-      </c>
-      <c r="I47" s="5">
-        <f>'1. Data Original'!$E21*D47</f>
-        <v>-0.53685036583332946</v>
-      </c>
-      <c r="K47" s="5">
-        <v>-0.81990452421708582</v>
-      </c>
-      <c r="L47" s="5">
-        <v>0.33228715685766791</v>
-      </c>
-      <c r="M47" s="5">
-        <v>0.46580639348445207</v>
-      </c>
-      <c r="N47" s="5">
-        <v>-1.9136884407064261E-2</v>
+      <c r="G47" cm="1">
+        <f t="array" ref="G47:J49">TRANSPOSE(B47:D50)</f>
+        <v>-1.5113087549245832</v>
+      </c>
+      <c r="H47">
+        <v>0.46804954686389366</v>
+      </c>
+      <c r="I47">
+        <v>1.0375818884162384</v>
+      </c>
+      <c r="J47">
+        <v>-1.7291626560648243</v>
+      </c>
+      <c r="L47">
+        <f>B47*'1. Data Original'!$D21</f>
+        <v>-0.44480879677375518</v>
+      </c>
+      <c r="M47">
+        <f>C47*'1. Data Original'!$D21</f>
+        <v>0.42445292404998997</v>
+      </c>
+      <c r="N47">
+        <f>D47*'1. Data Original'!$D21</f>
+        <v>-0.29124825906028018</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="str">
+      <c r="A48" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="2">
         <f>('1. Data Original'!C10 - '2. Statistika Deskriptif'!B26) / '2. Statistika Deskriptif'!C26</f>
         <v>0.46804954686389366</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="2">
         <f>('1. Data Original'!D10 - '2. Statistika Deskriptif'!B27) / '2. Statistika Deskriptif'!C27</f>
         <v>-0.87563163449960701</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="2">
         <f>('1. Data Original'!E10 - '2. Statistika Deskriptif'!B28) / '2. Statistika Deskriptif'!C28</f>
         <v>0.99178638576260758</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="G48" s="5">
-        <f>'1. Data Original'!$E22*B48</f>
-        <v>0.33228715685766791</v>
-      </c>
-      <c r="H48" s="5">
-        <f>'1. Data Original'!$E22*C48</f>
-        <v>-0.62164603775829963</v>
-      </c>
-      <c r="I48" s="5">
-        <f>'1. Data Original'!$E22*D48</f>
-        <v>0.70410895714643817</v>
-      </c>
-      <c r="K48" s="5">
-        <v>0.78238307171512167</v>
-      </c>
-      <c r="L48" s="5">
-        <v>-0.62164603775829963</v>
-      </c>
-      <c r="M48" s="5">
-        <v>3.7463117705752572E-2</v>
-      </c>
-      <c r="N48" s="5">
-        <v>5.4265684168173659E-3</v>
+      <c r="G48">
+        <v>1.4421464342045536</v>
+      </c>
+      <c r="H48">
+        <v>-0.87563163449960701</v>
+      </c>
+      <c r="I48">
+        <v>8.3448945653838535E-2</v>
+      </c>
+      <c r="J48">
+        <v>0.49033161602196723</v>
+      </c>
+      <c r="L48">
+        <f>B48*'1. Data Original'!$D22</f>
+        <v>0.23590398784139924</v>
+      </c>
+      <c r="M48">
+        <f>C48*'1. Data Original'!$D22</f>
+        <v>-0.44133146980400312</v>
+      </c>
+      <c r="N48">
+        <f>D48*'1. Data Original'!$D22</f>
+        <v>0.49987520563980731</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="str">
+      <c r="A49" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="2">
         <f>('1. Data Original'!C11 - '2. Statistika Deskriptif'!B26) / '2. Statistika Deskriptif'!C26</f>
         <v>1.0375818884162384</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="2">
         <f>('1. Data Original'!D11 - '2. Statistika Deskriptif'!B27) / '2. Statistika Deskriptif'!C27</f>
         <v>8.3448945653838535E-2</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="2">
         <f>('1. Data Original'!E11 - '2. Statistika Deskriptif'!B28) / '2. Statistika Deskriptif'!C28</f>
         <v>-1.0352857951019003</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="G49" s="5">
-        <f>'1. Data Original'!$E23*B49</f>
-        <v>0.46580639348445207</v>
-      </c>
-      <c r="H49" s="5">
-        <f>'1. Data Original'!$E23*C49</f>
-        <v>3.7463117705752572E-2</v>
-      </c>
-      <c r="I49" s="5">
-        <f>'1. Data Original'!$E23*D49</f>
-        <v>-0.46477559778746075</v>
-      </c>
-      <c r="K49" s="5">
-        <v>-0.53685036583332946</v>
-      </c>
-      <c r="L49" s="5">
-        <v>0.70410895714643817</v>
-      </c>
-      <c r="M49" s="5">
-        <v>-0.46477559778746075</v>
-      </c>
-      <c r="N49" s="5">
-        <v>2.4299942559259406E-3</v>
+      <c r="G49">
+        <v>-0.98956236245082141</v>
+      </c>
+      <c r="H49">
+        <v>0.99178638576260758</v>
+      </c>
+      <c r="I49">
+        <v>-1.0352857951019003</v>
+      </c>
+      <c r="J49">
+        <v>0.21956841209993813</v>
+      </c>
+      <c r="L49">
+        <f>B49*'1. Data Original'!$D23</f>
+        <v>0.20911659950250583</v>
+      </c>
+      <c r="M49">
+        <f>C49*'1. Data Original'!$D23</f>
+        <v>1.6818489164105017E-2</v>
+      </c>
+      <c r="N49">
+        <f>D49*'1. Data Original'!$D23</f>
+        <v>-0.20865383966504594</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="str">
+      <c r="A50" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="2">
         <f>('1. Data Original'!C12 - '2. Statistika Deskriptif'!B26) / '2. Statistika Deskriptif'!C26</f>
         <v>-1.7291626560648243</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="2">
         <f>('1. Data Original'!D12 - '2. Statistika Deskriptif'!B27) / '2. Statistika Deskriptif'!C27</f>
         <v>0.49033161602196723</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="2">
         <f>('1. Data Original'!E12 - '2. Statistika Deskriptif'!B28) / '2. Statistika Deskriptif'!C28</f>
         <v>0.21956841209993813</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="G50" s="5">
-        <f>'1. Data Original'!$E24*B50</f>
-        <v>-1.9136884407064261E-2</v>
-      </c>
-      <c r="H50" s="5">
-        <f>'1. Data Original'!$E24*C50</f>
-        <v>5.4265684168173659E-3</v>
-      </c>
-      <c r="I50" s="5">
-        <f>'1. Data Original'!$E24*D50</f>
-        <v>2.4299942559259406E-3</v>
+      <c r="L50">
+        <f>B50*'1. Data Original'!$D24</f>
+        <v>-2.1179057014958461E-4</v>
+      </c>
+      <c r="M50">
+        <f>C50*'1. Data Original'!$D24</f>
+        <v>6.005658990808469E-5</v>
+      </c>
+      <c r="N50">
+        <f>D50*'1. Data Original'!$D24</f>
+        <v>2.6893085518810513E-5</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="str">
+      <c r="A51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Data Tahun 2022</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="str">
+      <c r="A52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Kabupaten/Kota</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="str">
+      <c r="A53" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Jakarta Pusat</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="2">
         <f>('1. Data Original'!C15 - '2. Statistika Deskriptif'!B31) / '2. Statistika Deskriptif'!C31</f>
         <v>-1.5034222115657745</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="2">
         <f>('1. Data Original'!D15 - '2. Statistika Deskriptif'!B32) / '2. Statistika Deskriptif'!C32</f>
         <v>1.45135521477833</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="2">
         <f>('1. Data Original'!E15 - '2. Statistika Deskriptif'!B33) / '2. Statistika Deskriptif'!C33</f>
         <v>-1.1698614761101329</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="G53" s="5">
-        <f>'1. Data Original'!$E21*B53</f>
-        <v>-0.81562597255829905</v>
-      </c>
-      <c r="H53" s="5">
-        <f>'1. Data Original'!$E21*C53</f>
-        <v>0.78737895414507453</v>
-      </c>
-      <c r="I53" s="5">
-        <f>'1. Data Original'!$E21*D53</f>
-        <v>-0.63466496428642782</v>
-      </c>
-      <c r="K53" s="5">
-        <v>-0.81562597255829905</v>
-      </c>
-      <c r="L53" s="5">
-        <v>0.31842820112590109</v>
-      </c>
-      <c r="M53" s="5">
-        <v>0.48260415281513602</v>
-      </c>
-      <c r="N53" s="5">
-        <v>-2.1236414519320901E-2</v>
+      <c r="G53" cm="1">
+        <f t="array" ref="G53:J55">TRANSPOSE(B53:D56)</f>
+        <v>-1.5034222115657745</v>
+      </c>
+      <c r="H53">
+        <v>0.44852824483223336</v>
+      </c>
+      <c r="I53">
+        <v>1.0749988305005129</v>
+      </c>
+      <c r="J53">
+        <v>-1.9188711262721072</v>
+      </c>
+      <c r="L53">
+        <f>B53*'1. Data Original'!$D21</f>
+        <v>-0.44248762722404872</v>
+      </c>
+      <c r="M53">
+        <f>C53*'1. Data Original'!$D21</f>
+        <v>0.42716325481028483</v>
+      </c>
+      <c r="N53">
+        <f>D53*'1. Data Original'!$D21</f>
+        <v>-0.34431394239258839</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="str">
+      <c r="A54" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="2">
         <f>('1. Data Original'!C16 - '2. Statistika Deskriptif'!B31) / '2. Statistika Deskriptif'!C31</f>
         <v>0.44852824483223336</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="2">
         <f>('1. Data Original'!D16 - '2. Statistika Deskriptif'!B32) / '2. Statistika Deskriptif'!C32</f>
         <v>-0.86770808655801979</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="2">
         <f>('1. Data Original'!E16 - '2. Statistika Deskriptif'!B33) / '2. Statistika Deskriptif'!C33</f>
         <v>0.98117866422162847</v>
       </c>
-      <c r="E54" s="5"/>
-      <c r="G54" s="5">
-        <f>'1. Data Original'!$E22*B54</f>
-        <v>0.31842820112590109</v>
-      </c>
-      <c r="H54" s="5">
-        <f>'1. Data Original'!$E22*C54</f>
-        <v>-0.61602079309055702</v>
-      </c>
-      <c r="I54" s="5">
-        <f>'1. Data Original'!$E22*D54</f>
-        <v>0.69657810992052516</v>
-      </c>
-      <c r="K54" s="5">
-        <v>0.78737895414507453</v>
-      </c>
-      <c r="L54" s="5">
-        <v>-0.61602079309055702</v>
-      </c>
-      <c r="M54" s="5">
-        <v>2.2495441756930839E-2</v>
-      </c>
-      <c r="N54" s="5">
-        <v>6.83521394325991E-3</v>
+      <c r="G54">
+        <v>1.45135521477833</v>
+      </c>
+      <c r="H54">
+        <v>-0.86770808655801979</v>
+      </c>
+      <c r="I54">
+        <v>5.0108507022226793E-2</v>
+      </c>
+      <c r="J54">
+        <v>0.61761342366344885</v>
+      </c>
+      <c r="L54">
+        <f>B54*'1. Data Original'!$D22</f>
+        <v>0.22606495898648138</v>
+      </c>
+      <c r="M54">
+        <f>C54*'1. Data Original'!$D22</f>
+        <v>-0.43733788286476294</v>
+      </c>
+      <c r="N54">
+        <f>D54*'1. Data Original'!$D22</f>
+        <v>0.49452875496979787</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="str">
+      <c r="A55" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="2">
         <f>('1. Data Original'!C17 - '2. Statistika Deskriptif'!B31) / '2. Statistika Deskriptif'!C31</f>
         <v>1.0749988305005129</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="2">
         <f>('1. Data Original'!D17 - '2. Statistika Deskriptif'!B32) / '2. Statistika Deskriptif'!C32</f>
         <v>5.0108507022226793E-2</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="2">
         <f>('1. Data Original'!E17 - '2. Statistika Deskriptif'!B33) / '2. Statistika Deskriptif'!C33</f>
         <v>-0.74538955508466542</v>
       </c>
-      <c r="E55" s="5"/>
-      <c r="G55" s="5">
-        <f>'1. Data Original'!$E23*B55</f>
-        <v>0.48260415281513602</v>
-      </c>
-      <c r="H55" s="5">
-        <f>'1. Data Original'!$E23*C55</f>
-        <v>2.2495441756930839E-2</v>
-      </c>
-      <c r="I55" s="5">
-        <f>'1. Data Original'!$E23*D55</f>
-        <v>-0.33463114986032022</v>
-      </c>
-      <c r="K55" s="5">
-        <v>-0.63466496428642782</v>
-      </c>
-      <c r="L55" s="5">
-        <v>0.69657810992052516</v>
-      </c>
-      <c r="M55" s="5">
-        <v>-0.33463114986032022</v>
-      </c>
-      <c r="N55" s="5">
-        <v>1.1460497441226063E-3</v>
+      <c r="G55">
+        <v>-1.1698614761101329</v>
+      </c>
+      <c r="H55">
+        <v>0.98117866422162847</v>
+      </c>
+      <c r="I55">
+        <v>-0.74538955508466542</v>
+      </c>
+      <c r="J55">
+        <v>0.10355428696626937</v>
+      </c>
+      <c r="L55">
+        <f>B55*'1. Data Original'!$D23</f>
+        <v>0.21665769460044454</v>
+      </c>
+      <c r="M55">
+        <f>C55*'1. Data Original'!$D23</f>
+        <v>1.0098981787962664E-2</v>
+      </c>
+      <c r="N55">
+        <f>D55*'1. Data Original'!$D23</f>
+        <v>-0.1502274960696505</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="str">
+      <c r="A56" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="2">
         <f>('1. Data Original'!C18 - '2. Statistika Deskriptif'!B31) / '2. Statistika Deskriptif'!C31</f>
         <v>-1.9188711262721072</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="2">
         <f>('1. Data Original'!D18 - '2. Statistika Deskriptif'!B32) / '2. Statistika Deskriptif'!C32</f>
         <v>0.61761342366344885</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="2">
         <f>('1. Data Original'!E18 - '2. Statistika Deskriptif'!B33) / '2. Statistika Deskriptif'!C33</f>
         <v>0.10355428696626937</v>
       </c>
-      <c r="E56" s="5"/>
-      <c r="G56" s="5">
-        <f>'1. Data Original'!$E24*B56</f>
-        <v>-2.1236414519320901E-2</v>
-      </c>
-      <c r="H56" s="5">
-        <f>'1. Data Original'!$E24*C56</f>
-        <v>6.83521394325991E-3</v>
-      </c>
-      <c r="I56" s="5">
-        <f>'1. Data Original'!$E24*D56</f>
-        <v>1.1460497441226063E-3</v>
+      <c r="L56">
+        <f>B56*'1. Data Original'!$D24</f>
+        <v>-2.3502636287647756E-4</v>
+      </c>
+      <c r="M56">
+        <f>C56*'1. Data Original'!$D24</f>
+        <v>7.5646266515725098E-5</v>
+      </c>
+      <c r="N56">
+        <f>D56*'1. Data Original'!$D24</f>
+        <v>1.2683492441325133E-5</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="str">
+      <c r="A57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Z-Score transpose</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="str">
+      <c r="A58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Data Tahun 2020</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="str">
+      <c r="A59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Variabel</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="str">
+      <c r="A60" s="2" t="str">
         <f t="shared" si="0"/>
         <v>PPM</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="2">
         <v>-1.4790127066301544</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="2">
         <v>0.39523545574314989</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="2">
         <v>1.172515630105323</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="2">
         <v>-1.7360166352499051</v>
       </c>
+      <c r="G60" cm="1">
+        <f t="array" ref="G60:J62">TRANSPOSE(L41:N44)</f>
+        <v>-0.43530341520590421</v>
+      </c>
+      <c r="H60">
+        <v>0.19920459440853797</v>
+      </c>
+      <c r="I60">
+        <v>0.23631145085369992</v>
+      </c>
+      <c r="J60">
+        <v>-2.12630056333438E-4</v>
+      </c>
+      <c r="L60" cm="1">
+        <f t="array" ref="L60:N63">TRANSPOSE(B60:E62)</f>
+        <v>-1.4790127066301544</v>
+      </c>
+      <c r="M60">
+        <v>1.4697449029272016</v>
+      </c>
+      <c r="N60">
+        <v>-2.7681235223310521E-2</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="str">
+      <c r="A61" s="2" t="str">
         <f t="shared" si="0"/>
         <v>RLS</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="2">
         <v>1.4697449029272016</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="2">
         <v>-0.84996221012035955</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="2">
         <v>-2.0975969093958317E-2</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="2">
         <v>0.37170172402380985</v>
       </c>
+      <c r="G61">
+        <v>0.43257571274245127</v>
+      </c>
+      <c r="H61">
+        <v>-0.42839369512345499</v>
+      </c>
+      <c r="I61">
+        <v>-4.2275442325748801E-3</v>
+      </c>
+      <c r="J61">
+        <v>4.5526613578239924E-5</v>
+      </c>
+      <c r="L61">
+        <v>0.39523545574314989</v>
+      </c>
+      <c r="M61">
+        <v>-0.84996221012035955</v>
+      </c>
+      <c r="N61">
+        <v>0.76402554578205428</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="str">
+      <c r="A62" s="2" t="str">
         <f t="shared" si="0"/>
         <v>TPT</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="2">
         <v>-2.7681235223310521E-2</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="2">
         <v>0.76402554578205428</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="2">
         <v>-1.8708735847514268</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="2">
         <v>1.0361747517526483</v>
       </c>
+      <c r="G62">
+        <v>-8.1471485510626034E-3</v>
+      </c>
+      <c r="H62">
+        <v>0.38508032807710424</v>
+      </c>
+      <c r="I62">
+        <v>-0.37706009184436978</v>
+      </c>
+      <c r="J62">
+        <v>1.2691231832852553E-4</v>
+      </c>
+      <c r="L62">
+        <v>1.172515630105323</v>
+      </c>
+      <c r="M62">
+        <v>-2.0975969093958317E-2</v>
+      </c>
+      <c r="N62">
+        <v>-1.8708735847514268</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="str">
+      <c r="A63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Data Tahun 2021</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
+      <c r="L63">
+        <v>-1.7360166352499051</v>
+      </c>
+      <c r="M63">
+        <v>0.37170172402380985</v>
+      </c>
+      <c r="N63">
+        <v>1.0361747517526483</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="str">
+      <c r="A64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Kabupaten/Kota</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="str">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="str">
         <f t="shared" si="0"/>
         <v>PPM</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="2">
         <v>-1.5113087549245832</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="2">
         <v>0.46804954686389366</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="2">
         <v>1.0375818884162384</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="2">
         <v>-1.7291626560648243</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="str">
+      <c r="G65" cm="1">
+        <f t="array" ref="G65:J67">TRANSPOSE(L47:N50)</f>
+        <v>-0.44480879677375518</v>
+      </c>
+      <c r="H65">
+        <v>0.23590398784139924</v>
+      </c>
+      <c r="I65">
+        <v>0.20911659950250583</v>
+      </c>
+      <c r="J65">
+        <v>-2.1179057014958461E-4</v>
+      </c>
+      <c r="L65" cm="1">
+        <f t="array" ref="L65:N68">TRANSPOSE(B65:E67)</f>
+        <v>-1.5113087549245832</v>
+      </c>
+      <c r="M65">
+        <v>1.4421464342045536</v>
+      </c>
+      <c r="N65">
+        <v>-0.98956236245082141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="str">
         <f t="shared" si="0"/>
         <v>RLS</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="2">
         <v>1.4421464342045536</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="2">
         <v>-0.87563163449960701</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="2">
         <v>8.3448945653838535E-2</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="2">
         <v>0.49033161602196723</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="str">
+      <c r="G66">
+        <v>0.42445292404998997</v>
+      </c>
+      <c r="H66">
+        <v>-0.44133146980400312</v>
+      </c>
+      <c r="I66">
+        <v>1.6818489164105017E-2</v>
+      </c>
+      <c r="J66">
+        <v>6.005658990808469E-5</v>
+      </c>
+      <c r="L66">
+        <v>0.46804954686389366</v>
+      </c>
+      <c r="M66">
+        <v>-0.87563163449960701</v>
+      </c>
+      <c r="N66">
+        <v>0.99178638576260758</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="str">
         <f t="shared" si="0"/>
         <v>TPT</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="2">
         <v>-0.98956236245082141</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="2">
         <v>0.99178638576260758</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="2">
         <v>-1.0352857951019003</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="2">
         <v>0.21956841209993813</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="str">
+      <c r="G67">
+        <v>-0.29124825906028018</v>
+      </c>
+      <c r="H67">
+        <v>0.49987520563980731</v>
+      </c>
+      <c r="I67">
+        <v>-0.20865383966504594</v>
+      </c>
+      <c r="J67">
+        <v>2.6893085518810513E-5</v>
+      </c>
+      <c r="L67">
+        <v>1.0375818884162384</v>
+      </c>
+      <c r="M67">
+        <v>8.3448945653838535E-2</v>
+      </c>
+      <c r="N67">
+        <v>-1.0352857951019003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Data Tahun 2022</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="str">
+      <c r="L68">
+        <v>-1.7291626560648243</v>
+      </c>
+      <c r="M68">
+        <v>0.49033161602196723</v>
+      </c>
+      <c r="N68">
+        <v>0.21956841209993813</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Kabupaten/Kota</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="str">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="str">
         <f t="shared" si="0"/>
         <v>PPM</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="2">
         <v>-1.5034222115657745</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="2">
         <v>0.44852824483223336</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="2">
         <v>1.0749988305005129</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="2">
         <v>-1.9188711262721072</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="str">
+      <c r="G70" cm="1">
+        <f t="array" ref="G70:J72">TRANSPOSE(L53:N56)</f>
+        <v>-0.44248762722404872</v>
+      </c>
+      <c r="H70">
+        <v>0.22606495898648138</v>
+      </c>
+      <c r="I70">
+        <v>0.21665769460044454</v>
+      </c>
+      <c r="J70">
+        <v>-2.3502636287647756E-4</v>
+      </c>
+      <c r="L70" cm="1">
+        <f t="array" ref="L70:N73">TRANSPOSE(B70:E72)</f>
+        <v>-1.5034222115657745</v>
+      </c>
+      <c r="M70">
+        <v>1.45135521477833</v>
+      </c>
+      <c r="N70">
+        <v>-1.1698614761101329</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="str">
         <f t="shared" si="0"/>
         <v>RLS</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="2">
         <v>1.45135521477833</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="2">
         <v>-0.86770808655801979</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="2">
         <v>5.0108507022226793E-2</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="2">
         <v>0.61761342366344885</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="str">
+      <c r="G71">
+        <v>0.42716325481028483</v>
+      </c>
+      <c r="H71">
+        <v>-0.43733788286476294</v>
+      </c>
+      <c r="I71">
+        <v>1.0098981787962664E-2</v>
+      </c>
+      <c r="J71">
+        <v>7.5646266515725098E-5</v>
+      </c>
+      <c r="L71">
+        <v>0.44852824483223336</v>
+      </c>
+      <c r="M71">
+        <v>-0.86770808655801979</v>
+      </c>
+      <c r="N71">
+        <v>0.98117866422162847</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="str">
         <f t="shared" si="0"/>
         <v>TPT</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="2">
         <v>-1.1698614761101329</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="2">
         <v>0.98117866422162847</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="2">
         <v>-0.74538955508466542</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="2">
+        <v>0.10355428696626937</v>
+      </c>
+      <c r="G72">
+        <v>-0.34431394239258839</v>
+      </c>
+      <c r="H72">
+        <v>0.49452875496979787</v>
+      </c>
+      <c r="I72">
+        <v>-0.1502274960696505</v>
+      </c>
+      <c r="J72">
+        <v>1.2683492441325133E-5</v>
+      </c>
+      <c r="L72">
+        <v>1.0749988305005129</v>
+      </c>
+      <c r="M72">
+        <v>5.0108507022226793E-2</v>
+      </c>
+      <c r="N72">
+        <v>-0.74538955508466542</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L73">
+        <v>-1.9188711262721072</v>
+      </c>
+      <c r="M73">
+        <v>0.61761342366344885</v>
+      </c>
+      <c r="N73">
         <v>0.10355428696626937</v>
       </c>
     </row>
@@ -5711,1060 +5829,853 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="str">
+      <c r="A37" s="1" t="str">
         <f>A1</f>
         <v>Matriks W (Produk Skalar antar Wilayah)</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="str">
+      <c r="A38" s="1" t="str">
         <f t="shared" ref="A38:E71" si="21">A2</f>
         <v>Data Tahun 2020</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="str">
+      <c r="A39" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Score</v>
       </c>
-      <c r="B39" s="6" t="str">
+      <c r="B39" s="1" t="str">
         <f>B3</f>
         <v>Kota Jakarta Pusat</v>
       </c>
-      <c r="C39" s="6" t="str">
+      <c r="C39" s="1" t="str">
         <f t="shared" ref="C39:E39" si="22">C3</f>
         <v>Bandung Barat</v>
       </c>
-      <c r="D39" s="6" t="str">
+      <c r="D39" s="1" t="str">
         <f t="shared" si="22"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="E39" s="6" t="str">
+      <c r="E39" s="1" t="str">
         <f t="shared" si="22"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="str">
+      <c r="A40" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Jakarta Pusat</v>
       </c>
       <c r="B40" cm="1">
-        <f t="array" ref="B40:E43">MMULT('3. Standardisasi Z-Score'!G41:I44,'3. Standardisasi Z-Score'!K41:N43)</f>
-        <v>1.2798207543977944</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-0.71443137818181157</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-0.41725632029939569</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.852383371363921E-2</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5">
+        <f t="array" ref="B40:E43">MMULT('3. Standardisasi Z-Score'!B41:D44,_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!G41))</f>
+        <v>4.3483949168374334</v>
+      </c>
+      <c r="C40" s="2">
+        <v>-1.8549350580094275</v>
+      </c>
+      <c r="D40" s="2">
+        <v>-1.7132067475354562</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3.0852147797134633</v>
+      </c>
+      <c r="G40">
         <f>B40*B40</f>
-        <v>1.6379411633873395</v>
-      </c>
-      <c r="H40" s="5">
+        <v>18.908538352777629</v>
+      </c>
+      <c r="H40">
         <f t="shared" ref="H40:H43" si="23">C40*C40</f>
-        <v>0.51041219413076266</v>
-      </c>
-      <c r="I40" s="5">
+        <v>3.4407840694324383</v>
+      </c>
+      <c r="I40">
         <f t="shared" ref="I40:I43" si="24">D40*D40</f>
-        <v>0.17410283682979188</v>
-      </c>
-      <c r="J40" s="5">
+        <v>2.9350773598010163</v>
+      </c>
+      <c r="J40">
         <f t="shared" ref="J40:J43" si="25">E40*E40</f>
-        <v>3.4313241545055661E-4</v>
-      </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
+        <v>9.518550236962394</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="str">
+      <c r="A41" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="B41" s="7">
-        <v>-0.71443137818181157</v>
-      </c>
-      <c r="C41" s="7">
-        <v>0.73706237839498923</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-0.30219016014399747</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.6531437469076453E-3</v>
-      </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5">
+      <c r="B41" s="2">
+        <v>-1.8549350580094275</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1.4623818587167476</v>
+      </c>
+      <c r="D41" s="2">
+        <v>-0.94814668119777612</v>
+      </c>
+      <c r="E41" s="2">
+        <v>-0.21040376463410959</v>
+      </c>
+      <c r="G41">
         <f t="shared" ref="G41:G43" si="26">B41*B41</f>
-        <v>0.51041219413076266</v>
-      </c>
-      <c r="H41" s="5">
+        <v>3.4407840694324383</v>
+      </c>
+      <c r="H41">
         <f t="shared" si="23"/>
-        <v>0.54326094964527827</v>
-      </c>
-      <c r="I41" s="5">
+        <v>2.1385607007038496</v>
+      </c>
+      <c r="I41">
         <f t="shared" si="24"/>
-        <v>9.131889288785483E-2</v>
-      </c>
-      <c r="J41" s="5">
+        <v>0.89898212906635733</v>
+      </c>
+      <c r="J41">
         <f t="shared" si="25"/>
-        <v>2.7328842479398485E-6</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
+        <v>4.4269744172205784E-2</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="str">
+      <c r="A42" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="B42" s="7">
-        <v>-0.41725632029939569</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-0.30219016014399747</v>
-      </c>
-      <c r="D42" s="7">
-        <v>0.98259931223157315</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.9783536799602573E-2</v>
-      </c>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5">
+      <c r="B42" s="2">
+        <v>-1.7132067475354562</v>
+      </c>
+      <c r="C42" s="2">
+        <v>-0.94814668119777612</v>
+      </c>
+      <c r="D42" s="2">
+        <v>4.8754008642413673</v>
+      </c>
+      <c r="E42" s="2">
+        <v>-3.9818554150690564</v>
+      </c>
+      <c r="G42">
         <f t="shared" si="26"/>
-        <v>0.17410283682979188</v>
-      </c>
-      <c r="H42" s="5">
+        <v>2.9350773598010163</v>
+      </c>
+      <c r="H42">
         <f t="shared" si="23"/>
-        <v>9.131889288785483E-2</v>
-      </c>
-      <c r="I42" s="5">
+        <v>0.89898212906635733</v>
+      </c>
+      <c r="I42">
         <f t="shared" si="24"/>
-        <v>0.96550140839796061</v>
-      </c>
-      <c r="J42" s="5">
+        <v>23.769533587045473</v>
+      </c>
+      <c r="J42">
         <f t="shared" si="25"/>
-        <v>3.9138832830122919E-4</v>
-      </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
+        <v>15.855172546514767</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="str">
+      <c r="A43" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="B43" s="7">
-        <v>1.852383371363921E-2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-1.6531437469076453E-3</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-1.9783536799602573E-2</v>
-      </c>
-      <c r="E43" s="7">
-        <v>5.175549756433835E-4</v>
-      </c>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5">
+      <c r="B43" s="2">
+        <v>3.0852147797134633</v>
+      </c>
+      <c r="C43" s="2">
+        <v>-0.21040376463410959</v>
+      </c>
+      <c r="D43" s="2">
+        <v>-3.9818554150690564</v>
+      </c>
+      <c r="E43" s="2">
+        <v>4.2255740456763373</v>
+      </c>
+      <c r="G43">
         <f t="shared" si="26"/>
-        <v>3.4313241545055661E-4</v>
-      </c>
-      <c r="H43" s="5">
+        <v>9.518550236962394</v>
+      </c>
+      <c r="H43">
         <f t="shared" si="23"/>
-        <v>2.7328842479398485E-6</v>
-      </c>
-      <c r="I43" s="5">
+        <v>4.4269744172205784E-2</v>
+      </c>
+      <c r="I43">
         <f t="shared" si="24"/>
-        <v>3.9138832830122919E-4</v>
-      </c>
-      <c r="J43" s="5">
+        <v>15.855172546514767</v>
+      </c>
+      <c r="J43">
         <f t="shared" si="25"/>
-        <v>2.6786315281322327E-7</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5">
+        <v>17.85547601549349</v>
+      </c>
+      <c r="L43">
         <f>SUM(G40:J43)</f>
-        <v>4.6998461442465507</v>
+        <v>128.0577808279188</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="str">
+      <c r="A44" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Data Tahun 2021</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="str">
+      <c r="A45" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Score</v>
       </c>
-      <c r="B45" s="6" t="str">
+      <c r="B45" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Jakarta Pusat</v>
       </c>
-      <c r="C45" s="6" t="str">
+      <c r="C45" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="D45" s="6" t="str">
+      <c r="D45" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="E45" s="6" t="str">
+      <c r="E45" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="str">
+      <c r="A46" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Jakarta Pusat</v>
       </c>
       <c r="B46" cm="1">
-        <f t="array" ref="B46:E49">MMULT('3. Standardisasi Z-Score'!G47:I50,'3. Standardisasi Z-Score'!K47:N49)</f>
-        <v>1.5725750150334146</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-1.1368102310182968</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-0.10309131061789184</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.8631530066326497E-2</v>
-      </c>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5">
+        <f t="array" ref="B46:E49">MMULT('3. Standardisasi Z-Score'!B47:D50,_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!G47))</f>
+        <v>5.343074159579853</v>
+      </c>
+      <c r="C46" s="2">
+        <v>-2.9515908962260076</v>
+      </c>
+      <c r="D46" s="2">
+        <v>-0.42328113528901667</v>
+      </c>
+      <c r="E46" s="2">
+        <v>3.1031520158260615</v>
+      </c>
+      <c r="G46">
         <f>B46*B46</f>
-        <v>2.472992177907344</v>
-      </c>
-      <c r="H46" s="5">
+        <v>28.548441474769952</v>
+      </c>
+      <c r="H46">
         <f t="shared" ref="H46:H49" si="27">C46*C46</f>
-        <v>1.2923375013478733</v>
-      </c>
-      <c r="I46" s="5">
+        <v>8.7118888186842458</v>
+      </c>
+      <c r="I46">
         <f t="shared" ref="I46:I49" si="28">D46*D46</f>
-        <v>1.0627818324914658E-2</v>
-      </c>
-      <c r="J46" s="5">
+        <v>0.17916691949155883</v>
+      </c>
+      <c r="J46">
         <f t="shared" ref="J46:J49" si="29">E46*E46</f>
-        <v>3.4713391261242824E-4</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
+        <v>9.6295524333253493</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="str">
+      <c r="A47" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="B47" s="7">
-        <v>-1.1368102310182968</v>
-      </c>
-      <c r="C47" s="7">
-        <v>0.99262797440699035</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-0.19575997801202258</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-8.0213649442642167E-3</v>
-      </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5">
+      <c r="B47" s="2">
+        <v>-2.9515908962260076</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1.9694413726400053</v>
+      </c>
+      <c r="D47" s="2">
+        <v>-0.61421316092821732</v>
+      </c>
+      <c r="E47" s="2">
+        <v>-1.0209187101450241</v>
+      </c>
+      <c r="G47">
         <f t="shared" ref="G47:G49" si="30">B47*B47</f>
-        <v>1.2923375013478733</v>
-      </c>
-      <c r="H47" s="5">
+        <v>8.7118888186842458</v>
+      </c>
+      <c r="H47">
         <f t="shared" si="27"/>
-        <v>0.98531029557532468</v>
-      </c>
-      <c r="I47" s="5">
+        <v>3.8786993202661484</v>
+      </c>
+      <c r="I47">
         <f t="shared" si="28"/>
-        <v>3.8321968991267566E-2</v>
-      </c>
-      <c r="J47" s="5">
+        <v>0.37725780705743217</v>
+      </c>
+      <c r="J47">
         <f t="shared" si="29"/>
-        <v>6.4342295569070875E-5</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
+        <v>1.0422750127241798</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="str">
+      <c r="A48" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="B48" s="7">
-        <v>-0.10309131061789184</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-0.19575997801202258</v>
-      </c>
-      <c r="D48" s="7">
-        <v>0.43439543769791877</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-9.8401889697639754E-3</v>
-      </c>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5">
+      <c r="B48" s="2">
+        <v>-0.42328113528901667</v>
+      </c>
+      <c r="C48" s="2">
+        <v>-0.61421316092821732</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2.1553565792399185</v>
+      </c>
+      <c r="E48" s="2">
+        <v>-1.9805462557809492</v>
+      </c>
+      <c r="G48">
         <f t="shared" si="30"/>
-        <v>1.0627818324914658E-2</v>
-      </c>
-      <c r="H48" s="5">
+        <v>0.17916691949155883</v>
+      </c>
+      <c r="H48">
         <f t="shared" si="27"/>
-        <v>3.8321968991267566E-2</v>
-      </c>
-      <c r="I48" s="5">
+        <v>0.37725780705743217</v>
+      </c>
+      <c r="I48">
         <f t="shared" si="28"/>
-        <v>0.18869939629276644</v>
-      </c>
-      <c r="J48" s="5">
+        <v>4.6455619836728035</v>
+      </c>
+      <c r="J48">
         <f t="shared" si="29"/>
-        <v>9.6829318960664607E-5</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
+        <v>3.9225634712879374</v>
+      </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="str">
+      <c r="A49" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="B49" s="7">
-        <v>1.8631530066326497E-2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-8.0213649442642167E-3</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-9.8401889697639754E-3</v>
-      </c>
-      <c r="E49" s="7">
-        <v>4.0157286167557204E-4</v>
-      </c>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5">
+      <c r="B49" s="2">
+        <v>3.1031520158260615</v>
+      </c>
+      <c r="C49" s="2">
+        <v>-1.0209187101450241</v>
+      </c>
+      <c r="D49" s="2">
+        <v>-1.9805462557809492</v>
+      </c>
+      <c r="E49" s="2">
+        <v>3.2786388723919604</v>
+      </c>
+      <c r="G49">
         <f t="shared" si="30"/>
-        <v>3.4713391261242824E-4</v>
-      </c>
-      <c r="H49" s="5">
+        <v>9.6295524333253493</v>
+      </c>
+      <c r="H49">
         <f t="shared" si="27"/>
-        <v>6.4342295569070875E-5</v>
-      </c>
-      <c r="I49" s="5">
+        <v>1.0422750127241798</v>
+      </c>
+      <c r="I49">
         <f t="shared" si="28"/>
-        <v>9.6829318960664607E-5</v>
-      </c>
-      <c r="J49" s="5">
+        <v>3.9225634712879374</v>
+      </c>
+      <c r="J49">
         <f t="shared" si="29"/>
-        <v>1.6126076323430812E-7</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5">
+        <v>10.749472855559626</v>
+      </c>
+      <c r="L49">
         <f>SUM(G46:J49)</f>
-        <v>6.3305932194185912</v>
+        <v>95.547584559409941</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="str">
+      <c r="A50" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Data Tahun 2022</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="str">
+      <c r="A51" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Score</v>
       </c>
-      <c r="B51" s="6" t="str">
+      <c r="B51" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Jakarta Pusat</v>
       </c>
-      <c r="C51" s="6" t="str">
+      <c r="C51" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="D51" s="6" t="str">
+      <c r="D51" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="E51" s="6" t="str">
+      <c r="E51" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="str">
+      <c r="A52" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Jakarta Pusat</v>
       </c>
       <c r="B52" cm="1">
-        <f t="array" ref="B52:E55">MMULT('3. Standardisasi Z-Score'!G53:I56,'3. Standardisasi Z-Score'!K53:N55)</f>
-        <v>1.6880109614349554</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-1.1868538402839823</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-0.16353337732168929</v>
-      </c>
-      <c r="E52" s="7">
-        <v>2.1975517232050067E-2</v>
-      </c>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5">
+        <f t="array" ref="B52:E55">MMULT('3. Standardisasi Z-Score'!B53:D56,_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!G53))</f>
+        <v>5.7352861789801555</v>
+      </c>
+      <c r="C52" s="2">
+        <v>-3.0815231025807828</v>
+      </c>
+      <c r="D52" s="2">
+        <v>-0.67144935102181502</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3.6601057645128727</v>
+      </c>
+      <c r="G52">
         <f>B52*B52</f>
-        <v>2.8493810059245628</v>
-      </c>
-      <c r="H52" s="5">
+        <v>32.893507554800792</v>
+      </c>
+      <c r="H52">
         <f t="shared" ref="H52:H55" si="31">C52*C52</f>
-        <v>1.4086220381968366</v>
-      </c>
-      <c r="I52" s="5">
+        <v>9.4957846317390935</v>
+      </c>
+      <c r="I52">
         <f t="shared" ref="I52:I55" si="32">D52*D52</f>
-        <v>2.6743165498238002E-2</v>
-      </c>
-      <c r="J52" s="5">
+        <v>0.45084423098761656</v>
+      </c>
+      <c r="J52">
         <f t="shared" ref="J52:J55" si="33">E52*E52</f>
-        <v>4.8292335761612943E-4</v>
-      </c>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
+        <v>13.39637420742036</v>
+      </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="str">
+      <c r="A53" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Bandung Barat</v>
       </c>
-      <c r="B53" s="7">
-        <v>-1.1868538402839823</v>
-      </c>
-      <c r="C53" s="7">
-        <v>0.96609920001264737</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-9.3279621525447581E-2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.0174594023386099E-2</v>
-      </c>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5">
+      <c r="B53" s="2">
+        <v>-3.0815231025807828</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1.9168064810142029</v>
+      </c>
+      <c r="D53" s="2">
+        <v>-0.29267254609016291</v>
+      </c>
+      <c r="E53" s="2">
+        <v>-1.2949708034456504</v>
+      </c>
+      <c r="G53">
         <f t="shared" ref="G53:G55" si="34">B53*B53</f>
-        <v>1.4086220381968366</v>
-      </c>
-      <c r="H53" s="5">
+        <v>9.4957846317390935</v>
+      </c>
+      <c r="H53">
         <f t="shared" si="31"/>
-        <v>0.9333476642650772</v>
-      </c>
-      <c r="I53" s="5">
+        <v>3.6741470856580518</v>
+      </c>
+      <c r="I53">
         <f t="shared" si="32"/>
-        <v>8.7010877919307429E-3</v>
-      </c>
-      <c r="J53" s="5">
+        <v>8.5657219234898538E-2</v>
+      </c>
+      <c r="J53">
         <f t="shared" si="33"/>
-        <v>1.0352236354072412E-4</v>
-      </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
+        <v>1.6769493817766734</v>
+      </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="str">
+      <c r="A54" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Tasikmalaya</v>
       </c>
-      <c r="B54" s="7">
-        <v>-0.16353337732168929</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-9.3279621525447581E-2</v>
-      </c>
-      <c r="D54" s="7">
-        <v>0.34539081967109475</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.0478524624444025E-2</v>
-      </c>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5">
+      <c r="B54" s="2">
+        <v>-0.67144935102181502</v>
+      </c>
+      <c r="C54" s="2">
+        <v>-0.29267254609016291</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1.7137389368827827</v>
+      </c>
+      <c r="E54" s="2">
+        <v>-2.1090248139359531</v>
+      </c>
+      <c r="G54">
         <f t="shared" si="34"/>
-        <v>2.6743165498238002E-2</v>
-      </c>
-      <c r="H54" s="5">
+        <v>0.45084423098761656</v>
+      </c>
+      <c r="H54">
         <f t="shared" si="31"/>
-        <v>8.7010877919307429E-3</v>
-      </c>
-      <c r="I54" s="5">
+        <v>8.5657219234898538E-2</v>
+      </c>
+      <c r="I54">
         <f t="shared" si="32"/>
-        <v>0.11929481831307069</v>
-      </c>
-      <c r="J54" s="5">
+        <v>2.9369011437881301</v>
+      </c>
+      <c r="J54">
         <f t="shared" si="33"/>
-        <v>1.0979947830507981E-4</v>
-      </c>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
+        <v>4.4479856657975816</v>
+      </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="str">
+      <c r="A55" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Kota Cilegon</v>
       </c>
-      <c r="B55" s="7">
-        <v>2.1975517232050067E-2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-1.0174594023386099E-2</v>
-      </c>
-      <c r="D55" s="7">
-        <v>-1.0478524624444025E-2</v>
-      </c>
-      <c r="E55" s="7">
-        <v>4.9901888130256169E-4</v>
-      </c>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5">
+      <c r="B55" s="2">
+        <v>3.6601057645128727</v>
+      </c>
+      <c r="C55" s="2">
+        <v>-1.2949708034456504</v>
+      </c>
+      <c r="D55" s="2">
+        <v>-2.1090248139359531</v>
+      </c>
+      <c r="E55" s="2">
+        <v>4.0742362306791646</v>
+      </c>
+      <c r="G55">
         <f t="shared" si="34"/>
-        <v>4.8292335761612943E-4</v>
-      </c>
-      <c r="H55" s="5">
+        <v>13.39637420742036</v>
+      </c>
+      <c r="H55">
         <f t="shared" si="31"/>
-        <v>1.0352236354072412E-4</v>
-      </c>
-      <c r="I55" s="5">
+        <v>1.6769493817766734</v>
+      </c>
+      <c r="I55">
         <f t="shared" si="32"/>
-        <v>1.0979947830507981E-4</v>
-      </c>
-      <c r="J55" s="5">
+        <v>4.4479856657975816</v>
+      </c>
+      <c r="J55">
         <f t="shared" si="33"/>
-        <v>2.4901984389646013E-7</v>
-      </c>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5">
+        <v>16.599400863378769</v>
+      </c>
+      <c r="L55">
         <f>SUM(G52:J55)</f>
-        <v>6.7915488108954891</v>
+        <v>115.21114732153822</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="str">
+      <c r="A56" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Matriks S (Produk Skalar antar Variabel)</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="str">
+      <c r="A57" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Data Tahun 2020</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="str">
+      <c r="A58" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Loadings</v>
       </c>
-      <c r="B58" s="6" t="str">
+      <c r="B58" s="1" t="str">
         <f t="shared" si="21"/>
         <v>PPM</v>
       </c>
-      <c r="C58" s="6" t="str">
+      <c r="C58" s="1" t="str">
         <f t="shared" si="21"/>
         <v>RLS</v>
       </c>
-      <c r="D58" s="6" t="str">
+      <c r="D58" s="1" t="str">
         <f t="shared" si="21"/>
         <v>TPT</v>
       </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="str">
+      <c r="A59" s="1" t="str">
         <f t="shared" si="21"/>
         <v>PPM</v>
       </c>
       <c r="B59" cm="1">
-        <f t="array" ref="B59:D61">MMULT('3. Standardisasi Z-Score'!K41:N43,'3. Standardisasi Z-Score'!G41:I44)</f>
-        <v>1</v>
-      </c>
-      <c r="C59" s="7">
+        <f t="array" ref="B59:D61">MMULT(_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!G60),_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!L60))</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="C59" s="2">
         <v>-0.8141372497034659</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="2">
         <v>-0.27808203787720759</v>
       </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5">
+      <c r="G59">
         <f>B59*B59</f>
-        <v>1</v>
-      </c>
-      <c r="H59" s="5">
+        <v>1.0000000000000004</v>
+      </c>
+      <c r="H59">
         <f t="shared" ref="H59:H61" si="35">C59*C59</f>
         <v>0.66281946135472358</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59">
         <f t="shared" ref="I59:I61" si="36">D59*D59</f>
         <v>7.7329619789940712E-2</v>
       </c>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="str">
+      <c r="A60" s="1" t="str">
         <f t="shared" si="21"/>
         <v>RLS</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="2">
         <v>-0.8141372497034659</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="2">
         <v>1.0000000000000002</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="2">
         <v>-0.33132158242198845</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5">
+      <c r="G60">
         <f t="shared" ref="G60:G61" si="37">B60*B60</f>
         <v>0.66281946135472358</v>
       </c>
-      <c r="H60" s="5">
+      <c r="H60">
         <f t="shared" si="35"/>
         <v>1.0000000000000004</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60">
         <f t="shared" si="36"/>
         <v>0.10977399097861049</v>
       </c>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="str">
+      <c r="A61" s="1" t="str">
         <f t="shared" si="21"/>
         <v>TPT</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="2">
         <v>-0.27808203787720759</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="2">
         <v>-0.33132158242198845</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="2">
         <v>1</v>
       </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5">
+      <c r="G61">
         <f t="shared" si="37"/>
         <v>7.7329619789940712E-2</v>
       </c>
-      <c r="H61" s="5">
+      <c r="H61">
         <f t="shared" si="35"/>
         <v>0.10977399097861049</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61">
         <f t="shared" si="36"/>
         <v>1</v>
       </c>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5">
+      <c r="L61">
         <f>SUM(G59:I61)</f>
         <v>4.6998461442465498</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="str">
+      <c r="A62" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Data Tahun 2021</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="str">
+      <c r="A63" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Loadings</v>
       </c>
-      <c r="B63" s="6" t="str">
+      <c r="B63" s="1" t="str">
         <f t="shared" si="21"/>
         <v>PPM</v>
       </c>
-      <c r="C63" s="6" t="str">
+      <c r="C63" s="1" t="str">
         <f t="shared" si="21"/>
         <v>RLS</v>
       </c>
-      <c r="D63" s="6" t="str">
+      <c r="D63" s="1" t="str">
         <f t="shared" si="21"/>
         <v>TPT</v>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="str">
+      <c r="A64" s="1" t="str">
         <f t="shared" si="21"/>
         <v>PPM</v>
       </c>
       <c r="B64" cm="1">
-        <f t="array" ref="B64:D66">MMULT('3. Standardisasi Z-Score'!K47:N49,'3. Standardisasi Z-Score'!G47:I50)</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="C64" s="7">
+        <f t="array" ref="B64:D66">MMULT(_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!G65),_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!L65))</f>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="C64" s="2">
         <v>-0.83069770249394836</v>
       </c>
-      <c r="D64" s="7">
-        <v>0.45759045975840901</v>
-      </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5">
+      <c r="D64" s="2">
+        <v>0.45759045975840906</v>
+      </c>
+      <c r="G64">
         <f>B64*B64</f>
-        <v>0.99999999999999978</v>
-      </c>
-      <c r="H64" s="5">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="H64">
         <f t="shared" ref="H64:H66" si="38">C64*C64</f>
         <v>0.69005867292872436</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64">
         <f t="shared" ref="I64:I66" si="39">D64*D64</f>
-        <v>0.20938902886191213</v>
-      </c>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
+        <v>0.20938902886191219</v>
+      </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="str">
+      <c r="A65" s="1" t="str">
         <f t="shared" si="21"/>
         <v>RLS</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="2">
         <v>-0.83069770249394836</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="2">
         <v>0.99999999999999989</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="2">
         <v>-0.87512793802886957</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5">
+      <c r="G65">
         <f t="shared" ref="G65:G66" si="40">B65*B65</f>
         <v>0.69005867292872436</v>
       </c>
-      <c r="H65" s="5">
+      <c r="H65">
         <f t="shared" si="38"/>
         <v>0.99999999999999978</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I65">
         <f t="shared" si="39"/>
         <v>0.765848907918661</v>
       </c>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="str">
+      <c r="A66" s="1" t="str">
         <f t="shared" si="21"/>
         <v>TPT</v>
       </c>
-      <c r="B66" s="7">
-        <v>0.45759045975840901</v>
-      </c>
-      <c r="C66" s="7">
+      <c r="B66" s="2">
+        <v>0.45759045975840906</v>
+      </c>
+      <c r="C66" s="2">
         <v>-0.87512793802886957</v>
       </c>
-      <c r="D66" s="7">
-        <v>0.99999999999999967</v>
-      </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5">
+      <c r="D66" s="2">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="G66">
         <f t="shared" si="40"/>
-        <v>0.20938902886191213</v>
-      </c>
-      <c r="H66" s="5">
+        <v>0.20938902886191219</v>
+      </c>
+      <c r="H66">
         <f t="shared" si="38"/>
         <v>0.765848907918661</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I66">
         <f t="shared" si="39"/>
-        <v>0.99999999999999933</v>
-      </c>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5">
+        <v>0.99999999999999956</v>
+      </c>
+      <c r="L66">
         <f>SUM(G64:I66)</f>
         <v>6.3305932194185939</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="str">
+      <c r="A67" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Data Tahun 2022</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="str">
+      <c r="A68" s="1" t="str">
         <f t="shared" si="21"/>
         <v>Loadings</v>
       </c>
-      <c r="B68" s="6" t="str">
+      <c r="B68" s="1" t="str">
         <f t="shared" si="21"/>
         <v>PPM</v>
       </c>
-      <c r="C68" s="6" t="str">
+      <c r="C68" s="1" t="str">
         <f t="shared" si="21"/>
         <v>RLS</v>
       </c>
-      <c r="D68" s="6" t="str">
+      <c r="D68" s="1" t="str">
         <f t="shared" si="21"/>
         <v>TPT</v>
       </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="str">
+      <c r="A69" s="1" t="str">
         <f t="shared" si="21"/>
         <v>PPM</v>
       </c>
       <c r="B69" cm="1">
-        <f t="array" ref="B69:D71">MMULT('3. Standardisasi Z-Score'!K53:N55,'3. Standardisasi Z-Score'!G53:I56)</f>
-        <v>1</v>
-      </c>
-      <c r="C69" s="7">
+        <f t="array" ref="B69:D71">MMULT(_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!G70),_xlfn.ANCHORARRAY('3. Standardisasi Z-Score'!L70))</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="C69" s="2">
         <v>-0.82765388007181118</v>
       </c>
-      <c r="D69" s="7">
-        <v>0.57794062265914814</v>
-      </c>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5">
+      <c r="D69" s="2">
+        <v>0.57794062265914825</v>
+      </c>
+      <c r="G69">
         <f>B69*B69</f>
-        <v>1</v>
-      </c>
-      <c r="H69" s="5">
+        <v>1.0000000000000004</v>
+      </c>
+      <c r="H69">
         <f t="shared" ref="H69:H71" si="41">C69*C69</f>
         <v>0.68501094519792405</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I69">
         <f t="shared" ref="I69:I71" si="42">D69*D69</f>
-        <v>0.33401536331964388</v>
-      </c>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
+        <v>0.33401536331964399</v>
+      </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="str">
+      <c r="A70" s="1" t="str">
         <f t="shared" si="21"/>
         <v>RLS</v>
       </c>
-      <c r="B70" s="7">
-        <v>-0.82765388007181118</v>
-      </c>
-      <c r="C70" s="7">
-        <v>1</v>
-      </c>
-      <c r="D70" s="7">
+      <c r="B70" s="2">
+        <v>-0.82765388007181129</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="D70" s="2">
         <v>-0.9363482775816786</v>
       </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5">
+      <c r="G70">
         <f t="shared" ref="G70:G71" si="43">B70*B70</f>
-        <v>0.68501094519792405</v>
-      </c>
-      <c r="H70" s="5">
+        <v>0.68501094519792416</v>
+      </c>
+      <c r="H70">
         <f t="shared" si="41"/>
-        <v>1</v>
-      </c>
-      <c r="I70" s="5">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="I70">
         <f t="shared" si="42"/>
         <v>0.87674809693017619</v>
       </c>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="str">
+      <c r="A71" s="1" t="str">
         <f t="shared" si="21"/>
         <v>TPT</v>
       </c>
-      <c r="B71" s="7">
-        <v>0.57794062265914814</v>
-      </c>
-      <c r="C71" s="7">
+      <c r="B71" s="2">
+        <v>0.57794062265914825</v>
+      </c>
+      <c r="C71" s="2">
         <v>-0.9363482775816786</v>
       </c>
-      <c r="D71" s="7">
-        <v>1</v>
-      </c>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5">
+      <c r="D71" s="2">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="G71">
         <f t="shared" si="43"/>
-        <v>0.33401536331964388</v>
-      </c>
-      <c r="H71" s="5">
+        <v>0.33401536331964399</v>
+      </c>
+      <c r="H71">
         <f t="shared" si="41"/>
         <v>0.87674809693017619</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I71">
         <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5">
+        <v>1.0000000000000004</v>
+      </c>
+      <c r="L71">
         <f>SUM(G69:I71)</f>
         <v>6.7915488108954882</v>
       </c>

--- a/data/Olahan Data Sampel.xlsx
+++ b/data/Olahan Data Sampel.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B2E681-E6A1-4438-A421-887FF3D4F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F46061-333D-45A3-AB5C-040F5F482227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Original" sheetId="1" r:id="rId1"/>
-    <sheet name="2. Statistika Deskriptif" sheetId="2" r:id="rId2"/>
-    <sheet name="3. Standardisasi Z-Score" sheetId="3" r:id="rId3"/>
-    <sheet name="4. STATIS Intra-struktur" sheetId="4" r:id="rId4"/>
-    <sheet name="5. STATIS Inter-struktur" sheetId="5" r:id="rId5"/>
+    <sheet name="Lembar1" sheetId="6" r:id="rId2"/>
+    <sheet name="2. Statistika Deskriptif" sheetId="2" r:id="rId3"/>
+    <sheet name="3. Standardisasi Z-Score" sheetId="3" r:id="rId4"/>
+    <sheet name="4. STATIS Intra-struktur" sheetId="4" r:id="rId5"/>
+    <sheet name="5. STATIS Inter-struktur" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="203">
   <si>
     <t>Data Tahun 2020</t>
   </si>
@@ -292,14 +293,389 @@
     <t>Bobot^(1/2)</t>
   </si>
   <si>
-    <t>W1 =(D^(1/2) * Z1) * (D^(1/2) * Z1)^T</t>
+    <t>W1 = Z1 * Z1^T (terbobot)</t>
+  </si>
+  <si>
+    <t>terbobot</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>w*d</t>
+  </si>
+  <si>
+    <t>w*d*w</t>
+  </si>
+  <si>
+    <t>w1*d*w1</t>
+  </si>
+  <si>
+    <t>w1*d*w2</t>
+  </si>
+  <si>
+    <t>w1*d*w3</t>
+  </si>
+  <si>
+    <t>w2*d*w2</t>
+  </si>
+  <si>
+    <t>w1*d</t>
+  </si>
+  <si>
+    <t>w3*d</t>
+  </si>
+  <si>
+    <t>w1</t>
+  </si>
+  <si>
+    <t>w2</t>
+  </si>
+  <si>
+    <t>w3</t>
+  </si>
+  <si>
+    <t>w2*d*w3</t>
+  </si>
+  <si>
+    <t>w3*d*w3</t>
+  </si>
+  <si>
+    <t>w2*d*w1</t>
+  </si>
+  <si>
+    <t>w3*d*w1</t>
+  </si>
+  <si>
+    <t>w3*d*w2</t>
+  </si>
+  <si>
+    <t>w2*d</t>
+  </si>
+  <si>
+    <t>tr</t>
+  </si>
+  <si>
+    <t>rv</t>
+  </si>
+  <si>
+    <t>w*d*w*d</t>
+  </si>
+  <si>
+    <t>w1*d*w1*d</t>
+  </si>
+  <si>
+    <t>w1*d*w2*d</t>
+  </si>
+  <si>
+    <t>w1*d*w3*d</t>
+  </si>
+  <si>
+    <t>w2*d*w1*d</t>
+  </si>
+  <si>
+    <t>w2*d*w2*d</t>
+  </si>
+  <si>
+    <t>w2*d*w3*d</t>
+  </si>
+  <si>
+    <t>w3*d*w1*d</t>
+  </si>
+  <si>
+    <t>w3*d*w2*d</t>
+  </si>
+  <si>
+    <t>w3*d*w3*d</t>
+  </si>
+  <si>
+    <t>alpha V</t>
+  </si>
+  <si>
+    <t>alpha W</t>
+  </si>
+  <si>
+    <t>Vc</t>
+  </si>
+  <si>
+    <t>rvw</t>
+  </si>
+  <si>
+    <t>trv atau hv</t>
+  </si>
+  <si>
+    <t>trw atau hw</t>
+  </si>
+  <si>
+    <t>rvv</t>
+  </si>
+  <si>
+    <t>hw</t>
+  </si>
+  <si>
+    <t>hv</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>mean tanpa bobot</t>
+  </si>
+  <si>
+    <t>wc skenario1</t>
+  </si>
+  <si>
+    <t>wc skenario2</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>Fc skenario1</t>
+  </si>
+  <si>
+    <t>Fc skenario2</t>
+  </si>
+  <si>
+    <t>Skenario2</t>
+  </si>
+  <si>
+    <t>Skenario1</t>
+  </si>
+  <si>
+    <t>Gc skenario1</t>
+  </si>
+  <si>
+    <t>Gc skenario2</t>
+  </si>
+  <si>
+    <t>Dim</t>
+  </si>
+  <si>
+    <t>Eigen</t>
+  </si>
+  <si>
+    <t>Akar Ciri</t>
+  </si>
+  <si>
+    <t>Var (%)</t>
+  </si>
+  <si>
+    <t>Kum (%)</t>
+  </si>
+  <si>
+    <t>Dim 1</t>
+  </si>
+  <si>
+    <t>Dim 2</t>
+  </si>
+  <si>
+    <t>Dim 3</t>
+  </si>
+  <si>
+    <t>Dim 4</t>
+  </si>
+  <si>
+    <t>Awalan Fc skenario1</t>
+  </si>
+  <si>
+    <t>Awalan Fc skenario2</t>
+  </si>
+  <si>
+    <t>D^(-1/2)</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>zc</t>
+  </si>
+  <si>
+    <t>zc^T</t>
+  </si>
+  <si>
+    <t>Λ^(-1/2)</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Fk</t>
+  </si>
+  <si>
+    <t>wk</t>
+  </si>
+  <si>
+    <t>z1</t>
+  </si>
+  <si>
+    <t>z2</t>
+  </si>
+  <si>
+    <t>zk</t>
+  </si>
+  <si>
+    <t>skenario1</t>
+  </si>
+  <si>
+    <t>skenario2</t>
+  </si>
+  <si>
+    <t>P Λ^(1/2)</t>
+  </si>
+  <si>
+    <t>D^(-1/2) P Λ^(1/2)</t>
+  </si>
+  <si>
+    <t>Vc Λ^(1/2)</t>
+  </si>
+  <si>
+    <t>Gk=Zk^T D (Fc Λ^(-1/2))</t>
+  </si>
+  <si>
+    <t>Gk=Sk (Vc Λ^(-1/2))</t>
+  </si>
+  <si>
+    <t>Fk=Zk (Gc Λ^(-1/2))</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>D^(1/2)</t>
+  </si>
+  <si>
+    <t>Pteori = D(-1/2) P</t>
+  </si>
+  <si>
+    <t>sq_s</t>
+  </si>
+  <si>
+    <t>P_svd</t>
+  </si>
+  <si>
+    <t>P_teori</t>
+  </si>
+  <si>
+    <t>Sc skenario1</t>
+  </si>
+  <si>
+    <t>Sc skenario2</t>
+  </si>
+  <si>
+    <t>Gk</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Sk</t>
+  </si>
+  <si>
+    <t>Sk*Sk</t>
+  </si>
+  <si>
+    <t>S1*S1</t>
+  </si>
+  <si>
+    <t>S2*S1</t>
+  </si>
+  <si>
+    <t>S3*S1</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>S1*S2</t>
+  </si>
+  <si>
+    <t>S2*S2</t>
+  </si>
+  <si>
+    <t>S3*S2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S1*S3</t>
+  </si>
+  <si>
+    <t>S2*S3</t>
+  </si>
+  <si>
+    <t>S3*S3</t>
+  </si>
+  <si>
+    <t>Fk=Wk D (P_teori Λ^(-1/2)) atau Fk=Wk D^(1/2) (P_svd Λ^(-1/2))</t>
+  </si>
+  <si>
+    <t>Fc=∑αFk</t>
+  </si>
+  <si>
+    <t>Gc=∑αGk</t>
+  </si>
+  <si>
+    <t>scaleG1</t>
+  </si>
+  <si>
+    <t>Kuantitas</t>
+  </si>
+  <si>
+    <t>Nilai</t>
+  </si>
+  <si>
+    <t>λ₁ (Nilai Eigen Dominan)</t>
+  </si>
+  <si>
+    <t>‖H‖_F² (Frobenius²)</t>
+  </si>
+  <si>
+    <t>V (SS Residual)</t>
+  </si>
+  <si>
+    <t>V / ‖H‖_F² (Rasio Sisa)</t>
+  </si>
+  <si>
+    <t>Inertia₁ (Dominansi %)</t>
+  </si>
+  <si>
+    <t>96.43%</t>
+  </si>
+  <si>
+    <t>λ₁ / λ₂ (Rasio Kegentingan)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,8 +699,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA9B1D6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,8 +719,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -372,16 +772,110 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2305,6 +2799,7578 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE09AFDF-31FA-40C7-B91C-9F3ECBF96D71}">
+  <dimension ref="A1:CD171"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="43" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="15" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="12" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A1" s="2">
+        <v>4.51</v>
+      </c>
+      <c r="B1" s="2">
+        <v>11.38</v>
+      </c>
+      <c r="C1" s="2">
+        <v>10.97</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="F1" s="2">
+        <v>11.39</v>
+      </c>
+      <c r="G1" s="2">
+        <v>7.75</v>
+      </c>
+      <c r="I1" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J1" s="2">
+        <v>11.53</v>
+      </c>
+      <c r="K1" s="2">
+        <v>5.88</v>
+      </c>
+      <c r="M1">
+        <v>0.29432026733409078</v>
+      </c>
+      <c r="N1">
+        <v>0.29432026733409078</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <v>0</v>
+      </c>
+      <c r="Q1">
+        <v>0</v>
+      </c>
+      <c r="S1" t="s">
+        <v>130</v>
+      </c>
+      <c r="U1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BE1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
+      <c r="BH1" s="7"/>
+      <c r="BI1" s="7"/>
+      <c r="BJ1" s="7"/>
+      <c r="BK1" s="7"/>
+      <c r="BL1" s="7"/>
+      <c r="BM1" s="7"/>
+      <c r="BN1" s="7"/>
+      <c r="BO1" s="7"/>
+      <c r="BP1" s="8"/>
+    </row>
+    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>10.49</v>
+      </c>
+      <c r="B2" s="2">
+        <v>8.19</v>
+      </c>
+      <c r="C2" s="2">
+        <v>12.25</v>
+      </c>
+      <c r="E2" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="F2" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G2" s="2">
+        <v>11.65</v>
+      </c>
+      <c r="I2" s="2">
+        <v>10.82</v>
+      </c>
+      <c r="J2" s="2">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="K2" s="2">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="M2">
+        <v>0.50401499034032582</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0.50401499034032582</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>133</v>
+      </c>
+      <c r="T2" t="s">
+        <v>134</v>
+      </c>
+      <c r="U2" t="s">
+        <v>135</v>
+      </c>
+      <c r="V2" t="s">
+        <v>136</v>
+      </c>
+      <c r="W2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AQ2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AR2" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="AS2" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="BE2" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="BP2" s="10"/>
+    </row>
+    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>12.97</v>
+      </c>
+      <c r="B3" s="2">
+        <v>9.33</v>
+      </c>
+      <c r="C3" s="2">
+        <v>7.99</v>
+      </c>
+      <c r="E3" s="2">
+        <v>13.13</v>
+      </c>
+      <c r="F3" s="2">
+        <v>9.52</v>
+      </c>
+      <c r="G3" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="I3" s="2">
+        <v>12.72</v>
+      </c>
+      <c r="J3" s="2">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="K3" s="2">
+        <v>6.62</v>
+      </c>
+      <c r="M3">
+        <v>0.20154226074792103</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0.20154226074792103</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
+        <v>138</v>
+      </c>
+      <c r="T3">
+        <v>2.3008000000000002</v>
+      </c>
+      <c r="U3">
+        <v>1.5167999999999999</v>
+      </c>
+      <c r="V3">
+        <v>76.69</v>
+      </c>
+      <c r="W3">
+        <v>76.69</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z3">
+        <v>2.2692000000000001</v>
+      </c>
+      <c r="AA3">
+        <v>1.5064</v>
+      </c>
+      <c r="AB3">
+        <v>75.64</v>
+      </c>
+      <c r="AC3">
+        <v>75.64</v>
+      </c>
+      <c r="AJ3" s="9"/>
+      <c r="AK3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL3">
+        <v>-0.56493890526314894</v>
+      </c>
+      <c r="AM3">
+        <v>0.61515382688380837</v>
+      </c>
+      <c r="AN3" s="9"/>
+      <c r="AO3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP3">
+        <v>-0.80458077944986472</v>
+      </c>
+      <c r="AQ3" s="10">
+        <v>-0.24085077570699526</v>
+      </c>
+      <c r="AR3" s="9"/>
+      <c r="AS3" cm="1">
+        <f t="array" ref="AS3:AT6">MMULT(N5:Q8,AP3:AQ6)</f>
+        <v>-1.4830628934359602</v>
+      </c>
+      <c r="AT3" s="10">
+        <v>-0.44395399123323159</v>
+      </c>
+      <c r="AV3" cm="1">
+        <f t="array" ref="AV3:AW4">MMULT(MMULT(TRANSPOSE(AS3:AT6),N1:Q4),AS3:AT6)</f>
+        <v>1.0000000000000007</v>
+      </c>
+      <c r="AW3">
+        <v>-3.7676025493871279E-18</v>
+      </c>
+      <c r="AY3" cm="1">
+        <f t="array" ref="AY3:AZ4">MMULT(TRANSPOSE(AP3:AQ6),AP3:AQ6)</f>
+        <v>1.0000000000000004</v>
+      </c>
+      <c r="AZ3">
+        <v>-3.1496073110703904E-17</v>
+      </c>
+      <c r="BE3" s="9">
+        <v>-0.86747510051361965</v>
+      </c>
+      <c r="BF3">
+        <v>1.470441673732648</v>
+      </c>
+      <c r="BG3">
+        <v>-2.7239665775486309E-3</v>
+      </c>
+      <c r="BI3">
+        <v>-0.89356642597673686</v>
+      </c>
+      <c r="BJ3">
+        <v>1.3907269337392965</v>
+      </c>
+      <c r="BK3">
+        <v>-0.92056543529687862</v>
+      </c>
+      <c r="BM3">
+        <v>-0.81342175593733446</v>
+      </c>
+      <c r="BN3">
+        <v>1.3483620090341482</v>
+      </c>
+      <c r="BO3">
+        <v>-1.1657688798586363</v>
+      </c>
+      <c r="BP3" s="10"/>
+    </row>
+    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3.69</v>
+      </c>
+      <c r="B4" s="2">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="C4" s="2">
+        <v>12.69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4.24</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10.08</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3.64</v>
+      </c>
+      <c r="J4" s="2">
+        <v>10.34</v>
+      </c>
+      <c r="K4" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="M4">
+        <v>1.2248157766231845E-4</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1.2248157766231845E-4</v>
+      </c>
+      <c r="S4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T4">
+        <v>0.69920000000000004</v>
+      </c>
+      <c r="U4">
+        <v>0.83620000000000005</v>
+      </c>
+      <c r="V4">
+        <v>23.31</v>
+      </c>
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z4">
+        <v>0.70579999999999998</v>
+      </c>
+      <c r="AA4">
+        <v>0.84009999999999996</v>
+      </c>
+      <c r="AB4">
+        <v>23.53</v>
+      </c>
+      <c r="AC4">
+        <v>99.17</v>
+      </c>
+      <c r="AJ4" s="9"/>
+      <c r="AK4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL4">
+        <v>0.65792355248264001</v>
+      </c>
+      <c r="AM4">
+        <v>7.1896747227522664E-2</v>
+      </c>
+      <c r="AN4" s="9"/>
+      <c r="AO4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP4">
+        <v>0.59273374911162502</v>
+      </c>
+      <c r="AQ4" s="10">
+        <v>-0.38019927591285807</v>
+      </c>
+      <c r="AR4" s="9"/>
+      <c r="AS4">
+        <v>0.83490666719167528</v>
+      </c>
+      <c r="AT4" s="10">
+        <v>-0.53553709536001659</v>
+      </c>
+      <c r="AV4">
+        <v>-3.7676025493871279E-18</v>
+      </c>
+      <c r="AW4">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="AY4">
+        <v>-3.1496073110703904E-17</v>
+      </c>
+      <c r="AZ4">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="9">
+        <v>0.65602008335464623</v>
+      </c>
+      <c r="BF4">
+        <v>-1.3092376976493632</v>
+      </c>
+      <c r="BG4">
+        <v>0.69461147727503925</v>
+      </c>
+      <c r="BI4">
+        <v>0.74775703083540601</v>
+      </c>
+      <c r="BJ4">
+        <v>-1.3950934233271741</v>
+      </c>
+      <c r="BK4">
+        <v>1.3994379234480829</v>
+      </c>
+      <c r="BM4">
+        <v>0.72999388353350569</v>
+      </c>
+      <c r="BN4">
+        <v>-1.3981476832138724</v>
+      </c>
+      <c r="BO4">
+        <v>1.4402718351755721</v>
+      </c>
+      <c r="BP4" s="10"/>
+    </row>
+    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="M5" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="N5" s="7">
+        <f>1/SQRT(N1)</f>
+        <v>1.8432740767807185</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>140</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AA5">
+        <v>0.15820000000000001</v>
+      </c>
+      <c r="AB5">
+        <v>0.83</v>
+      </c>
+      <c r="AC5">
+        <v>100</v>
+      </c>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="12">
+        <v>-0.46744904459427966</v>
+      </c>
+      <c r="AM5" s="12">
+        <v>-0.73769148968266962</v>
+      </c>
+      <c r="AN5" s="9"/>
+      <c r="AO5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP5">
+        <v>3.5169323102582056E-2</v>
+      </c>
+      <c r="AQ5" s="10">
+        <v>0.89278024371047693</v>
+      </c>
+      <c r="AR5" s="9"/>
+      <c r="AS5">
+        <v>7.8339527300446868E-2</v>
+      </c>
+      <c r="AT5" s="10">
+        <v>1.9886644412079024</v>
+      </c>
+      <c r="BE5" s="9">
+        <v>1.2878374840224223</v>
+      </c>
+      <c r="BF5">
+        <v>-0.31587265583886387</v>
+      </c>
+      <c r="BG5">
+        <v>-1.6262080467968558</v>
+      </c>
+      <c r="BI5">
+        <v>1.2200246292577679</v>
+      </c>
+      <c r="BJ5">
+        <v>-0.24234017212725545</v>
+      </c>
+      <c r="BK5">
+        <v>-0.97410397434483909</v>
+      </c>
+      <c r="BM5">
+        <v>1.2253468759312416</v>
+      </c>
+      <c r="BN5">
+        <v>-0.31116046362326677</v>
+      </c>
+      <c r="BO5">
+        <v>-0.65151017875855255</v>
+      </c>
+      <c r="BP5" s="10"/>
+    </row>
+    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A6" cm="1">
+        <f t="array" ref="A6:D9">MMULT(A1:C4,TRANSPOSE(A1:C4))</f>
+        <v>270.18540000000002</v>
+      </c>
+      <c r="B6">
+        <v>274.89460000000003</v>
+      </c>
+      <c r="C6">
+        <v>252.32040000000001</v>
+      </c>
+      <c r="D6">
+        <v>268.17180000000002</v>
+      </c>
+      <c r="M6" s="9"/>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>1/SQRT(O2)</f>
+        <v>1.4085694773463011</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
+        <v>141</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>100</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA6">
+        <f>1/AA3</f>
+        <v>0.66383430695698353</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP6" s="12">
+        <v>-8.9213629245830997E-3</v>
+      </c>
+      <c r="AQ6" s="13">
+        <v>-1.9566575503614427E-2</v>
+      </c>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="12">
+        <v>-0.8061128071973811</v>
+      </c>
+      <c r="AT6" s="13">
+        <v>-1.7679885057691689</v>
+      </c>
+      <c r="BE6" s="9">
+        <v>-1.0763824668634485</v>
+      </c>
+      <c r="BF6">
+        <v>0.15466867975558224</v>
+      </c>
+      <c r="BG6">
+        <v>0.93432053609936616</v>
+      </c>
+      <c r="BI6">
+        <v>-1.0742152341164382</v>
+      </c>
+      <c r="BJ6">
+        <v>0.24670666171513458</v>
+      </c>
+      <c r="BK6">
+        <v>0.49523148619363677</v>
+      </c>
+      <c r="BM6">
+        <v>-1.1419190035274118</v>
+      </c>
+      <c r="BN6">
+        <v>0.36094613780298668</v>
+      </c>
+      <c r="BO6">
+        <v>0.37700722344161447</v>
+      </c>
+      <c r="BP6" s="10"/>
+    </row>
+    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>274.89460000000003</v>
+      </c>
+      <c r="B7">
+        <v>327.17869999999999</v>
+      </c>
+      <c r="C7">
+        <v>310.34550000000002</v>
+      </c>
+      <c r="D7">
+        <v>274.99590000000001</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f>1/SQRT(P3)</f>
+        <v>2.2274960218013224</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>148</v>
+      </c>
+      <c r="U7">
+        <f>1/U3</f>
+        <v>0.65928270042194093</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f>1/AA4</f>
+        <v>1.1903344839900012</v>
+      </c>
+      <c r="BE7" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP7" s="10"/>
+    </row>
+    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>252.32040000000001</v>
+      </c>
+      <c r="B8">
+        <v>310.34550000000002</v>
+      </c>
+      <c r="C8">
+        <v>319.10990000000004</v>
+      </c>
+      <c r="D8">
+        <v>241.33949999999999</v>
+      </c>
+      <c r="M8" s="11"/>
+      <c r="N8" s="12">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <f>1/SQRT(Q4)</f>
+        <v>90.35758482329102</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f>1/U4</f>
+        <v>1.1958861516383639</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BE8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>90</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BP8" s="10"/>
+    </row>
+    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>268.17180000000002</v>
+      </c>
+      <c r="B9">
+        <v>274.99590000000001</v>
+      </c>
+      <c r="C9">
+        <v>241.33949999999999</v>
+      </c>
+      <c r="D9">
+        <v>272.06909999999993</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9">
+        <f>SQRT(N1)</f>
+        <v>0.54251291904810039</v>
+      </c>
+      <c r="O9">
+        <f t="shared" ref="O9:Q9" si="0">SQRT(O1)</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN9" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AO9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AP9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AQ9" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AR9" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="AS9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT9" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="BE9" s="9" cm="1">
+        <f t="array" ref="BE9:BH12">MMULT(BE3:BG6,TRANSPOSE(BE3:BG6))</f>
+        <v>2.9147191858547012</v>
+      </c>
+      <c r="BF9">
+        <v>-2.496130857640912</v>
+      </c>
+      <c r="BG9">
+        <v>-1.5772095312680179</v>
+      </c>
+      <c r="BH9">
+        <v>1.1586212030542331</v>
+      </c>
+      <c r="BI9" cm="1">
+        <f t="array" ref="BI9:BL12">MMULT(BI3:BK6,TRANSPOSE(BI3:BK6))</f>
+        <v>3.5800230825240762</v>
+      </c>
+      <c r="BJ9">
+        <v>-3.8966387576161736</v>
+      </c>
+      <c r="BK9">
+        <v>-0.53047560290667217</v>
+      </c>
+      <c r="BL9">
+        <v>0.84709127799877093</v>
+      </c>
+      <c r="BM9" cm="1">
+        <f t="array" ref="BM9:BP12">MMULT(BM3:BO6,TRANSPOSE(BM3:BO6))</f>
+        <v>3.8387521416856405</v>
+      </c>
+      <c r="BN9">
+        <v>-4.1580262096166045</v>
+      </c>
+      <c r="BO9">
+        <v>-0.65677046400752492</v>
+      </c>
+      <c r="BP9" s="10">
+        <v>0.97604453193848451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>154</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ref="N10:Q10" si="1">SQRT(N2)</f>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>0.70994013151837376</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="9"/>
+      <c r="AK10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL10">
+        <v>-0.54836231261667567</v>
+      </c>
+      <c r="AM10">
+        <v>-0.66400609366274088</v>
+      </c>
+      <c r="AN10" s="9"/>
+      <c r="AO10" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP10">
+        <v>0.78683961169459982</v>
+      </c>
+      <c r="AQ10" s="10">
+        <v>0.2927388759123461</v>
+      </c>
+      <c r="AR10" s="9"/>
+      <c r="AS10" cm="1">
+        <f t="array" ref="AS10:AT13">MMULT(N5:Q8,AP10:AQ13)</f>
+        <v>1.4503610588208626</v>
+      </c>
+      <c r="AT10" s="10">
+        <v>0.53959798123515512</v>
+      </c>
+      <c r="BE10" s="9">
+        <v>-2.496130857640912</v>
+      </c>
+      <c r="BF10">
+        <v>2.6269508030730546</v>
+      </c>
+      <c r="BG10">
+        <v>0.12881686855437091</v>
+      </c>
+      <c r="BH10">
+        <v>-0.25963681398651706</v>
+      </c>
+      <c r="BI10">
+        <v>-3.8966387576161736</v>
+      </c>
+      <c r="BJ10">
+        <v>4.4638527385591988</v>
+      </c>
+      <c r="BK10">
+        <v>-0.11282886841710127</v>
+      </c>
+      <c r="BL10">
+        <v>-0.45438511252592362</v>
+      </c>
+      <c r="BM10">
+        <v>-4.1580262096166045</v>
+      </c>
+      <c r="BN10">
+        <v>4.5620909732726584</v>
+      </c>
+      <c r="BO10">
+        <v>0.39119224516317508</v>
+      </c>
+      <c r="BP10" s="10">
+        <v>-0.79525700881922623</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11">
+        <f t="shared" ref="N11:Q11" si="2">SQRT(N3)</f>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="2"/>
+        <v>0.44893458404083886</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ11" s="9"/>
+      <c r="AK11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL11">
+        <v>0.65890515900708024</v>
+      </c>
+      <c r="AM11">
+        <v>3.1215730045989265E-2</v>
+      </c>
+      <c r="AN11" s="9"/>
+      <c r="AO11" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP11">
+        <v>-0.60695123135633677</v>
+      </c>
+      <c r="AQ11" s="10">
+        <v>0.31345803658474986</v>
+      </c>
+      <c r="AR11" s="9"/>
+      <c r="AS11">
+        <v>-0.85493297872628915</v>
+      </c>
+      <c r="AT11" s="10">
+        <v>0.44152742276217882</v>
+      </c>
+      <c r="BE11" s="9">
+        <v>-1.5772095312680179</v>
+      </c>
+      <c r="BF11">
+        <v>0.12881686855437091</v>
+      </c>
+      <c r="BG11">
+        <v>4.4028535314267447</v>
+      </c>
+      <c r="BH11">
+        <v>-2.9544608687130998</v>
+      </c>
+      <c r="BI11">
+        <v>-0.53047560290667217</v>
+      </c>
+      <c r="BJ11">
+        <v>-0.11282886841710127</v>
+      </c>
+      <c r="BK11">
+        <v>2.4960674078566329</v>
+      </c>
+      <c r="BL11">
+        <v>-1.8527629365328628</v>
+      </c>
+      <c r="BM11">
+        <v>-0.65677046400752492</v>
+      </c>
+      <c r="BN11">
+        <v>0.39119224516317508</v>
+      </c>
+      <c r="BO11">
+        <v>2.0227613135027012</v>
+      </c>
+      <c r="BP11" s="10">
+        <v>-1.7571830946583471</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>-1.4790127066301544</v>
+      </c>
+      <c r="B12">
+        <v>1.4697449029272016</v>
+      </c>
+      <c r="C12">
+        <v>-2.7681235223310521E-2</v>
+      </c>
+      <c r="E12">
+        <v>-1.5113087549245832</v>
+      </c>
+      <c r="F12">
+        <v>1.4421464342045536</v>
+      </c>
+      <c r="G12">
+        <v>-0.98956236245082141</v>
+      </c>
+      <c r="I12">
+        <v>-1.5034222115657745</v>
+      </c>
+      <c r="J12">
+        <v>1.45135521477833</v>
+      </c>
+      <c r="K12">
+        <v>-1.1698614761101329</v>
+      </c>
+      <c r="N12">
+        <f t="shared" ref="N12:Q12" si="3">SQRT(N4)</f>
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="3"/>
+        <v>1.1067139542913447E-2</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" ref="AA12:AC15" si="4">$M1*A12+$M1*E12+$M1*I12</f>
+        <v>-1.3225998392037082</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="4"/>
+        <v>1.2841918916027262</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="4"/>
+        <v>-0.64370935000393115</v>
+      </c>
+      <c r="AE12" cm="1">
+        <f t="array" ref="AE12:AH14">TRANSPOSE(AA12:AC15)</f>
+        <v>-1.3225998392037082</v>
+      </c>
+      <c r="AF12">
+        <v>0.66117354123641858</v>
+      </c>
+      <c r="AG12">
+        <v>0.66208574495665029</v>
+      </c>
+      <c r="AH12">
+        <v>-6.5944698935950009E-4</v>
+      </c>
+      <c r="AJ12" s="11"/>
+      <c r="AK12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL12" s="12">
+        <v>-0.51492015452451023</v>
+      </c>
+      <c r="AM12" s="12">
+        <v>0.74707528789034605</v>
+      </c>
+      <c r="AN12" s="9"/>
+      <c r="AO12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP12">
+        <v>8.7721081210509078E-3</v>
+      </c>
+      <c r="AQ12" s="10">
+        <v>-0.84994964490900216</v>
+      </c>
+      <c r="AR12" s="9"/>
+      <c r="AS12">
+        <v>1.9539835942451969E-2</v>
+      </c>
+      <c r="AT12" s="10">
+        <v>-1.893259452766249</v>
+      </c>
+      <c r="BE12" s="9">
+        <v>1.1586212030542331</v>
+      </c>
+      <c r="BF12">
+        <v>-0.25963681398651706</v>
+      </c>
+      <c r="BG12">
+        <v>-2.9544608687130998</v>
+      </c>
+      <c r="BH12">
+        <v>2.0554764796453848</v>
+      </c>
+      <c r="BI12">
+        <v>0.84709127799877093</v>
+      </c>
+      <c r="BJ12">
+        <v>-0.45438511252592362</v>
+      </c>
+      <c r="BK12">
+        <v>-1.8527629365328628</v>
+      </c>
+      <c r="BL12">
+        <v>1.4600567710600181</v>
+      </c>
+      <c r="BM12">
+        <v>0.97604453193848451</v>
+      </c>
+      <c r="BN12">
+        <v>-0.79525700881922623</v>
+      </c>
+      <c r="BO12">
+        <v>-1.7571830946583471</v>
+      </c>
+      <c r="BP12" s="10">
+        <v>1.5763955715390854</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.39523545574314989</v>
+      </c>
+      <c r="B13">
+        <v>-0.84996221012035955</v>
+      </c>
+      <c r="C13">
+        <v>0.76402554578205428</v>
+      </c>
+      <c r="E13">
+        <v>0.46804954686389366</v>
+      </c>
+      <c r="F13">
+        <v>-0.87563163449960701</v>
+      </c>
+      <c r="G13">
+        <v>0.99178638576260758</v>
+      </c>
+      <c r="I13">
+        <v>0.44852824483223336</v>
+      </c>
+      <c r="J13">
+        <v>-0.86770808655801979</v>
+      </c>
+      <c r="K13">
+        <v>0.98117866422162847</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="4"/>
+        <v>0.66117354123641858</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="4"/>
+        <v>-1.3070630477922212</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="4"/>
+        <v>1.3794842886867094</v>
+      </c>
+      <c r="AE13">
+        <v>1.2841918916027262</v>
+      </c>
+      <c r="AF13">
+        <v>-1.3070630477922212</v>
+      </c>
+      <c r="AG13">
+        <v>2.2689926719492801E-2</v>
+      </c>
+      <c r="AH13">
+        <v>1.8122947000204971E-4</v>
+      </c>
+      <c r="AN13" s="11"/>
+      <c r="AO13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP13" s="12">
+        <v>8.1574593335531926E-3</v>
+      </c>
+      <c r="AQ13" s="13">
+        <v>1.9944492747264331E-2</v>
+      </c>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="12">
+        <v>0.73708832367407962</v>
+      </c>
+      <c r="AT13" s="13">
+        <v>1.8021361951684494</v>
+      </c>
+      <c r="BE13" s="9"/>
+      <c r="BP13" s="10"/>
+    </row>
+    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1.172515630105323</v>
+      </c>
+      <c r="B14">
+        <v>-2.0975969093958317E-2</v>
+      </c>
+      <c r="C14">
+        <v>-1.8708735847514268</v>
+      </c>
+      <c r="E14">
+        <v>1.0375818884162384</v>
+      </c>
+      <c r="F14">
+        <v>8.3448945653838535E-2</v>
+      </c>
+      <c r="G14">
+        <v>-1.0352857951019003</v>
+      </c>
+      <c r="I14">
+        <v>1.0749988305005129</v>
+      </c>
+      <c r="J14">
+        <v>5.0108507022226793E-2</v>
+      </c>
+      <c r="K14">
+        <v>-0.74538955508466542</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="4"/>
+        <v>0.66208574495665029</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="4"/>
+        <v>2.2689926719492801E-2</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="4"/>
+        <v>-0.73594142757906622</v>
+      </c>
+      <c r="AE14">
+        <v>-0.64370935000393115</v>
+      </c>
+      <c r="AF14">
+        <v>1.3794842886867094</v>
+      </c>
+      <c r="AG14">
+        <v>-0.73594142757906622</v>
+      </c>
+      <c r="AH14">
+        <v>1.6648889628866119E-4</v>
+      </c>
+      <c r="BE14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP14" s="10"/>
+    </row>
+    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>-1.7360166352499051</v>
+      </c>
+      <c r="B15">
+        <v>0.37170172402380985</v>
+      </c>
+      <c r="C15">
+        <v>1.0361747517526483</v>
+      </c>
+      <c r="E15">
+        <v>-1.7291626560648243</v>
+      </c>
+      <c r="F15">
+        <v>0.49033161602196723</v>
+      </c>
+      <c r="G15">
+        <v>0.21956841209993813</v>
+      </c>
+      <c r="I15">
+        <v>-1.9188711262721072</v>
+      </c>
+      <c r="J15">
+        <v>0.61761342366344885</v>
+      </c>
+      <c r="K15">
+        <v>0.10355428696626937</v>
+      </c>
+      <c r="N15" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="4"/>
+        <v>-6.5944698935950009E-4</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="4"/>
+        <v>1.8122947000204971E-4</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="4"/>
+        <v>1.6648889628866119E-4</v>
+      </c>
+      <c r="BE15" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>97</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>88</v>
+      </c>
+      <c r="BP15" s="10"/>
+    </row>
+    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>151</v>
+      </c>
+      <c r="N16" t="s">
+        <v>155</v>
+      </c>
+      <c r="O16" t="s">
+        <v>190</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>157</v>
+      </c>
+      <c r="BE16" s="9" cm="1">
+        <f t="array" ref="BE16:BH19">MMULT(_xlfn.ANCHORARRAY(BE9),$N1:$Q4)</f>
+        <v>0.8578609299845591</v>
+      </c>
+      <c r="BF16">
+        <v>-1.2580873701020734</v>
+      </c>
+      <c r="BG16">
+        <v>-0.31787437460492518</v>
+      </c>
+      <c r="BH16">
+        <v>1.4190975286309588E-4</v>
+      </c>
+      <c r="BI16" cm="1">
+        <f t="array" ref="BI16:BL19">MMULT(_xlfn.ANCHORARRAY(BI9),$N1:$Q4)</f>
+        <v>1.0536733507107019</v>
+      </c>
+      <c r="BJ16">
+        <v>-1.963964345779655</v>
+      </c>
+      <c r="BK16">
+        <v>-0.10691325228142713</v>
+      </c>
+      <c r="BL16">
+        <v>1.0375307615327904E-4</v>
+      </c>
+      <c r="BM16" cm="1">
+        <f t="array" ref="BM16:BP19">MMULT(_xlfn.ANCHORARRAY(BM9),$N1:$Q4)</f>
+        <v>1.1298225565702313</v>
+      </c>
+      <c r="BN16">
+        <v>-2.0957075398747347</v>
+      </c>
+      <c r="BO16">
+        <v>-0.13236700410853766</v>
+      </c>
+      <c r="BP16" s="10">
+        <v>1.1954747414050474E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>163</v>
+      </c>
+      <c r="T17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE17" s="9">
+        <v>-0.73466190132174647</v>
+      </c>
+      <c r="BF17">
+        <v>1.3240225836353767</v>
+      </c>
+      <c r="BG17">
+        <v>2.5962042910915691E-2</v>
+      </c>
+      <c r="BH17">
+        <v>-3.1800726596286515E-5</v>
+      </c>
+      <c r="BI17">
+        <v>-1.1468597608459716</v>
+      </c>
+      <c r="BJ17">
+        <v>2.2498486949055514</v>
+      </c>
+      <c r="BK17">
+        <v>-2.2739785218412297E-2</v>
+      </c>
+      <c r="BL17">
+        <v>-5.5653805448445222E-5</v>
+      </c>
+      <c r="BM17">
+        <v>-1.2237913855965152</v>
+      </c>
+      <c r="BN17">
+        <v>2.2993622378257066</v>
+      </c>
+      <c r="BO17">
+        <v>7.884176947724128E-2</v>
+      </c>
+      <c r="BP17" s="10">
+        <v>-9.7404333087195119E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" cm="1">
+        <f t="array" ref="A18:D21">MMULT(A12:C15,TRANSPOSE(A12:C15))</f>
+        <v>4.3483949168374334</v>
+      </c>
+      <c r="B18" s="15">
+        <v>-1.8549350580094275</v>
+      </c>
+      <c r="C18" s="15">
+        <v>-1.7132067475354562</v>
+      </c>
+      <c r="D18" s="15">
+        <v>3.0852147797134633</v>
+      </c>
+      <c r="E18" s="15" cm="1">
+        <f t="array" ref="E18:H21">MMULT(E12:G15,TRANSPOSE(E12:G15))</f>
+        <v>5.343074159579853</v>
+      </c>
+      <c r="F18" s="15">
+        <v>-2.9515908962260076</v>
+      </c>
+      <c r="G18" s="15">
+        <v>-0.42328113528901667</v>
+      </c>
+      <c r="H18" s="15">
+        <v>3.1031520158260615</v>
+      </c>
+      <c r="I18" s="15" cm="1">
+        <f t="array" ref="I18:L21">MMULT(I12:K15,TRANSPOSE(I12:K15))</f>
+        <v>5.7352861789801555</v>
+      </c>
+      <c r="J18" s="15">
+        <v>-3.0815231025807828</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-0.67144935102181502</v>
+      </c>
+      <c r="L18" s="15">
+        <v>3.6601057645128727</v>
+      </c>
+      <c r="N18" s="14" cm="1">
+        <f t="array" ref="N18:O21">MMULT(MMULT(_xlfn.ANCHORARRAY(A18),N9:Q12),MMULT(AP3:AQ6,U7:V8))</f>
+        <v>-1.7840028133002299</v>
+      </c>
+      <c r="O18" s="14">
+        <v>-0.90268005148704777</v>
+      </c>
+      <c r="Q18" s="14" cm="1">
+        <f t="array" ref="Q18:R21">MMULT(_xlfn.ANCHORARRAY(E18),MMULT(N9:Q12,MMULT(AP3:AQ6,U7:V8)))</f>
+        <v>-2.361064556654942</v>
+      </c>
+      <c r="R18" s="14">
+        <v>-8.5845885693585491E-2</v>
+      </c>
+      <c r="T18" s="14" cm="1">
+        <f t="array" ref="T18:U21">MMULT(_xlfn.ANCHORARRAY(I18),MMULT(N9:Q12,MMULT(AP3:AQ6,U7:V8)))</f>
+        <v>-2.5125995003970916</v>
+      </c>
+      <c r="U18" s="14">
+        <v>-0.22428587941860292</v>
+      </c>
+      <c r="AA18" s="14">
+        <f>$AC$152*A18+$AC$153*E18+$AC$154*I18</f>
+        <v>5.1983647840595868</v>
+      </c>
+      <c r="AB18" s="14">
+        <f t="shared" ref="AB18:AB21" si="5">$AC$152*B18+$AC$153*F18+$AC$154*J18</f>
+        <v>-2.6826662967097858</v>
+      </c>
+      <c r="AC18" s="14">
+        <f t="shared" ref="AC18:AC21" si="6">$AC$152*C18+$AC$153*G18+$AC$154*K18</f>
+        <v>-0.88459957528567312</v>
+      </c>
+      <c r="AD18" s="14">
+        <f t="shared" ref="AD18:AD21" si="7">$AC$152*D18+$AC$153*H18+$AC$154*L18</f>
+        <v>3.2993773055271287</v>
+      </c>
+      <c r="AF18">
+        <f>$AC$140*A18+$AC$141*E18+$AC$142*I18</f>
+        <v>5.2082977427754162</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" ref="AG18:AG21" si="8">$AC$140*B18+$AC$141*F18+$AC$142*J18</f>
+        <v>-2.6925882969022874</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" ref="AH18:AH21" si="9">$AC$140*C18+$AC$141*G18+$AC$142*K18</f>
+        <v>-0.87429347550452297</v>
+      </c>
+      <c r="AI18">
+        <f t="shared" ref="AI18:AI21" si="10">$AC$140*D18+$AC$141*H18+$AC$142*L18</f>
+        <v>3.3014275496303838</v>
+      </c>
+      <c r="AK18">
+        <f>AP3*$U$3</f>
+        <v>-1.2203881262695548</v>
+      </c>
+      <c r="AL18">
+        <f>AQ3*$U$4</f>
+        <v>-0.20139941864618946</v>
+      </c>
+      <c r="AN18" s="16">
+        <f>AP10*$AA$3</f>
+        <v>1.1852951910567451</v>
+      </c>
+      <c r="AO18" s="16">
+        <f>AQ10*$AA$4</f>
+        <v>0.24592992965396193</v>
+      </c>
+      <c r="BE18" s="9">
+        <v>-0.46420473088467901</v>
+      </c>
+      <c r="BF18">
+        <v>6.492563276010227E-2</v>
+      </c>
+      <c r="BG18">
+        <v>0.88736105446571389</v>
+      </c>
+      <c r="BH18">
+        <v>-3.6186702834156438E-4</v>
+      </c>
+      <c r="BI18">
+        <v>-0.15612972126170474</v>
+      </c>
+      <c r="BJ18">
+        <v>-5.6867441025355188E-2</v>
+      </c>
+      <c r="BK18">
+        <v>0.50306306835862891</v>
+      </c>
+      <c r="BL18">
+        <v>-2.2692932750081502E-4</v>
+      </c>
+      <c r="BM18">
+        <v>-0.19330085854382958</v>
+      </c>
+      <c r="BN18">
+        <v>0.19716675566712805</v>
+      </c>
+      <c r="BO18">
+        <v>0.40767188807676863</v>
+      </c>
+      <c r="BP18" s="10">
+        <v>-2.1522255767530941E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>-1.8549350580094275</v>
+      </c>
+      <c r="B19" s="15">
+        <v>1.4623818587167476</v>
+      </c>
+      <c r="C19" s="15">
+        <v>-0.94814668119777612</v>
+      </c>
+      <c r="D19" s="15">
+        <v>-0.21040376463410959</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-2.9515908962260076</v>
+      </c>
+      <c r="F19" s="15">
+        <v>1.9694413726400053</v>
+      </c>
+      <c r="G19" s="15">
+        <v>-0.61421316092821732</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-1.0209187101450241</v>
+      </c>
+      <c r="I19" s="15">
+        <v>-3.0815231025807828</v>
+      </c>
+      <c r="J19" s="15">
+        <v>1.9168064810142029</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-0.29267254609016291</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-1.2949708034456504</v>
+      </c>
+      <c r="N19" s="14">
+        <v>0.92965439420652174</v>
+      </c>
+      <c r="O19" s="14">
+        <v>-0.63659573097812883</v>
+      </c>
+      <c r="Q19" s="14">
+        <v>1.3894454889944623</v>
+      </c>
+      <c r="R19" s="14">
+        <v>-0.46863908560994427</v>
+      </c>
+      <c r="T19" s="14">
+        <v>1.4155989325911693</v>
+      </c>
+      <c r="U19" s="14">
+        <v>-0.27715679672362903</v>
+      </c>
+      <c r="AA19" s="14">
+        <f t="shared" ref="AA19:AA21" si="11">$AC$152*A19+$AC$153*E19+$AC$154*I19</f>
+        <v>-2.6826662967097858</v>
+      </c>
+      <c r="AB19" s="14">
+        <f t="shared" si="5"/>
+        <v>1.8043429593760623</v>
+      </c>
+      <c r="AC19" s="14">
+        <f t="shared" si="6"/>
+        <v>-0.59413967599270268</v>
+      </c>
+      <c r="AD19" s="14">
+        <f t="shared" si="7"/>
+        <v>-0.88653434456733526</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" ref="AF19:AF21" si="12">$AC$140*A19+$AC$141*E19+$AC$142*I19</f>
+        <v>-2.6925882969022874</v>
+      </c>
+      <c r="AG19">
+        <f t="shared" si="8"/>
+        <v>1.8085470514279762</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="9"/>
+        <v>-0.59015890937257376</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="10"/>
+        <v>-0.89447325210375794</v>
+      </c>
+      <c r="AK19">
+        <f>AP4*$U$3</f>
+        <v>0.89905855065251283</v>
+      </c>
+      <c r="AL19">
+        <f>AQ4*$U$4</f>
+        <v>-0.31792263451833191</v>
+      </c>
+      <c r="AN19" s="16">
+        <f>AP11*$AA$3</f>
+        <v>-0.91431133491518568</v>
+      </c>
+      <c r="AO19" s="16">
+        <f>AQ11*$AA$4</f>
+        <v>0.26333609653484835</v>
+      </c>
+      <c r="BE19" s="9">
+        <v>0.34100570222186777</v>
+      </c>
+      <c r="BF19">
+        <v>-0.13086084629340736</v>
+      </c>
+      <c r="BG19">
+        <v>-0.5954487227717048</v>
+      </c>
+      <c r="BH19">
+        <v>2.5175800207475512E-4</v>
+      </c>
+      <c r="BI19">
+        <v>0.24931613139697487</v>
+      </c>
+      <c r="BJ19">
+        <v>-0.22901690810054126</v>
+      </c>
+      <c r="BK19">
+        <v>-0.3734100308587901</v>
+      </c>
+      <c r="BL19">
+        <v>1.7883005679598151E-4</v>
+      </c>
+      <c r="BM19">
+        <v>0.28726968757011229</v>
+      </c>
+      <c r="BN19">
+        <v>-0.40082145361809873</v>
+      </c>
+      <c r="BO19">
+        <v>-0.35414665344547142</v>
+      </c>
+      <c r="BP19" s="10">
+        <v>1.9307941662199935E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>-1.7132067475354562</v>
+      </c>
+      <c r="B20" s="15">
+        <v>-0.94814668119777612</v>
+      </c>
+      <c r="C20" s="15">
+        <v>4.8754008642413673</v>
+      </c>
+      <c r="D20" s="15">
+        <v>-3.9818554150690564</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-0.42328113528901667</v>
+      </c>
+      <c r="F20" s="15">
+        <v>-0.61421316092821732</v>
+      </c>
+      <c r="G20" s="15">
+        <v>2.1553565792399185</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-1.9805462557809492</v>
+      </c>
+      <c r="I20" s="15">
+        <v>-0.67144935102181502</v>
+      </c>
+      <c r="J20" s="15">
+        <v>-0.29267254609016291</v>
+      </c>
+      <c r="K20" s="15">
+        <v>1.7137389368827827</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-2.1090248139359531</v>
+      </c>
+      <c r="N20" s="14">
+        <v>0.28098046843212232</v>
+      </c>
+      <c r="O20" s="14">
+        <v>2.9116248291487659</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>-2.6027217860227585E-2</v>
+      </c>
+      <c r="R20" s="14">
+        <v>1.2980042536859864</v>
+      </c>
+      <c r="T20" s="14">
+        <v>0.130005520930424</v>
+      </c>
+      <c r="U20" s="14">
+        <v>1.0213533148868346</v>
+      </c>
+      <c r="AA20" s="14">
+        <f t="shared" si="11"/>
+        <v>-0.88459957528567312</v>
+      </c>
+      <c r="AB20" s="14">
+        <f t="shared" si="5"/>
+        <v>-0.59413967599270268</v>
+      </c>
+      <c r="AC20" s="14">
+        <f t="shared" si="6"/>
+        <v>2.779217452631674</v>
+      </c>
+      <c r="AD20" s="14">
+        <f t="shared" si="7"/>
+        <v>-2.6035096998491403</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="12"/>
+        <v>-0.87429347550452297</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="8"/>
+        <v>-0.59015890937257376</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="9"/>
+        <v>2.7542017290879865</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="10"/>
+        <v>-2.5866468791064463</v>
+      </c>
+      <c r="AK20">
+        <f>AP5*$U$3</f>
+        <v>5.3344829281996457E-2</v>
+      </c>
+      <c r="AL20">
+        <f>AQ5*$U$4</f>
+        <v>0.74654283979070091</v>
+      </c>
+      <c r="AN20" s="16">
+        <f>AP12*$AA$3</f>
+        <v>1.3214303673551087E-2</v>
+      </c>
+      <c r="AO20" s="16">
+        <f>AQ12*$AA$4</f>
+        <v>-0.71404269668805265</v>
+      </c>
+      <c r="BE20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP20" s="10"/>
+    </row>
+    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>3.0852147797134633</v>
+      </c>
+      <c r="B21" s="15">
+        <v>-0.21040376463410959</v>
+      </c>
+      <c r="C21" s="15">
+        <v>-3.9818554150690564</v>
+      </c>
+      <c r="D21" s="15">
+        <v>4.2255740456763373</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3.1031520158260615</v>
+      </c>
+      <c r="F21" s="15">
+        <v>-1.0209187101450241</v>
+      </c>
+      <c r="G21" s="15">
+        <v>-1.9805462557809492</v>
+      </c>
+      <c r="H21" s="15">
+        <v>3.2786388723919604</v>
+      </c>
+      <c r="I21" s="15">
+        <v>3.6601057645128727</v>
+      </c>
+      <c r="J21" s="15">
+        <v>-1.2949708034456504</v>
+      </c>
+      <c r="K21" s="15">
+        <v>-2.1090248139359531</v>
+      </c>
+      <c r="L21" s="15">
+        <v>4.0742362306791646</v>
+      </c>
+      <c r="N21" s="14">
+        <v>-0.98793971041736861</v>
+      </c>
+      <c r="O21" s="14">
+        <v>-2.3238208667897333</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>-1.1970688204165938</v>
+      </c>
+      <c r="R21" s="14">
+        <v>-1.1055010656519457</v>
+      </c>
+      <c r="T21" s="14">
+        <v>-1.4347649395223094</v>
+      </c>
+      <c r="U21" s="14">
+        <v>-1.1658560759962251</v>
+      </c>
+      <c r="AA21" s="14">
+        <f t="shared" si="11"/>
+        <v>3.2993773055271287</v>
+      </c>
+      <c r="AB21" s="14">
+        <f t="shared" si="5"/>
+        <v>-0.88653434456733526</v>
+      </c>
+      <c r="AC21" s="14">
+        <f t="shared" si="6"/>
+        <v>-2.6035096998491403</v>
+      </c>
+      <c r="AD21" s="14">
+        <f t="shared" si="7"/>
+        <v>3.8391022585355761</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="12"/>
+        <v>3.3014275496303838</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="8"/>
+        <v>-0.89447325210375794</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="9"/>
+        <v>-2.5866468791064463</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="10"/>
+        <v>3.833623864399482</v>
+      </c>
+      <c r="AK21">
+        <f>AP6*$U$3</f>
+        <v>-1.3531923284007645E-2</v>
+      </c>
+      <c r="AL21">
+        <f>AQ6*$U$4</f>
+        <v>-1.6361570436122384E-2</v>
+      </c>
+      <c r="AN21" s="16">
+        <f>AP13*$AA$3</f>
+        <v>1.2288396740064529E-2</v>
+      </c>
+      <c r="AO21" s="16">
+        <f>AQ13*$AA$4</f>
+        <v>1.6755368356976764E-2</v>
+      </c>
+      <c r="BE21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>84</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>85</v>
+      </c>
+      <c r="BP21" s="10"/>
+    </row>
+    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="N22" t="s">
+        <v>156</v>
+      </c>
+      <c r="O22" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>158</v>
+      </c>
+      <c r="BE22" s="9" cm="1">
+        <f t="array" ref="BE22:BH25">MMULT(_xlfn.ANCHORARRAY(BE16),_xlfn.ANCHORARRAY(BE9))</f>
+        <v>6.1422933305625751</v>
+      </c>
+      <c r="BF22">
+        <v>-5.4872511926510885</v>
+      </c>
+      <c r="BG22">
+        <v>-2.9150628902495308</v>
+      </c>
+      <c r="BH22">
+        <v>2.2600207523380544</v>
+      </c>
+      <c r="BI22" cm="1">
+        <f t="array" ref="BI22:BL25">MMULT(_xlfn.ANCHORARRAY(BE16),_xlfn.ANCHORARRAY(BI9))</f>
+        <v>8.1422187487784772</v>
+      </c>
+      <c r="BJ22">
+        <v>-8.9228899764929253</v>
+      </c>
+      <c r="BK22">
+        <v>-1.106824511079775</v>
+      </c>
+      <c r="BL22">
+        <v>1.8874957387942237</v>
+      </c>
+      <c r="BM22" cm="1">
+        <f t="array" ref="BM22:BP25">MMULT(_xlfn.ANCHORARRAY(BE16),_xlfn.ANCHORARRAY(BM9))</f>
+        <v>8.733184751862396</v>
+      </c>
+      <c r="BN22">
+        <v>-9.4309801108200038</v>
+      </c>
+      <c r="BO22">
+        <v>-1.6988050928849565</v>
+      </c>
+      <c r="BP22" s="10">
+        <v>2.3966004518425543</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" t="s">
+        <v>88</v>
+      </c>
+      <c r="N23" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>163</v>
+      </c>
+      <c r="T23" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA23" cm="1">
+        <f t="array" ref="AA23:AB25">MMULT(MMULT(MMULT(_xlfn.ANCHORARRAY(AE12),N1:Q4),_xlfn.ANCHORARRAY(AK24)),U7:V8)</f>
+        <v>0.86598783658312273</v>
+      </c>
+      <c r="AB23">
+        <v>0.25971799756759339</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE23" s="9">
+        <v>-5.4872511926510894</v>
+      </c>
+      <c r="BF23">
+        <v>5.3153070368985622</v>
+      </c>
+      <c r="BG23">
+        <v>1.4436732224590227</v>
+      </c>
+      <c r="BH23">
+        <v>-1.2717290667065031</v>
+      </c>
+      <c r="BI23">
+        <v>-7.8031434484195774</v>
+      </c>
+      <c r="BJ23">
+        <v>8.7700390561626076</v>
+      </c>
+      <c r="BK23">
+        <v>0.30519417352485362</v>
+      </c>
+      <c r="BL23">
+        <v>-1.272089781267882</v>
+      </c>
+      <c r="BM23">
+        <v>-8.3425876938883796</v>
+      </c>
+      <c r="BN23">
+        <v>9.1052363577207398</v>
+      </c>
+      <c r="BO23">
+        <v>1.0530225006776746</v>
+      </c>
+      <c r="BP23" s="10">
+        <v>-1.8156711645100283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A24" cm="1">
+        <f t="array" ref="A24:D27">MMULT(_xlfn.ANCHORARRAY(A18),$N$1:$Q$4)</f>
+        <v>1.2798207543977949</v>
+      </c>
+      <c r="B24">
+        <v>-0.93491507534455331</v>
+      </c>
+      <c r="C24">
+        <v>-0.34528356102688862</v>
+      </c>
+      <c r="D24">
+        <v>3.7788197364640726E-4</v>
+      </c>
+      <c r="E24" cm="1">
+        <f t="array" ref="E24:H27">MMULT(_xlfn.ANCHORARRAY(E18),$N$1:$Q$4)</f>
+        <v>1.5725750150334148</v>
+      </c>
+      <c r="F24">
+        <v>-1.4876460570499448</v>
+      </c>
+      <c r="G24">
+        <v>-8.5309036938095037E-2</v>
+      </c>
+      <c r="H24">
+        <v>3.8007895462437976E-4</v>
+      </c>
+      <c r="I24" cm="1">
+        <f t="array" ref="I24:L27">MMULT(_xlfn.ANCHORARRAY(I18),$N$1:$Q$4)</f>
+        <v>1.6880109614349554</v>
+      </c>
+      <c r="J24">
+        <v>-1.5531338367807441</v>
+      </c>
+      <c r="K24">
+        <v>-0.135325420182661</v>
+      </c>
+      <c r="L24">
+        <v>4.4829552844848287E-4</v>
+      </c>
+      <c r="N24" s="14" cm="1">
+        <f t="array" ref="N24:O27">MMULT(A12:C15,MMULT(X103:Y105,AA6:AB7))</f>
+        <v>1.7937109530788702</v>
+      </c>
+      <c r="O24" s="14">
+        <v>1.0072726431596752</v>
+      </c>
+      <c r="Q24" s="14" cm="1">
+        <f t="array" ref="Q24:R27">MMULT(E12:G15,MMULT(X103:Y105,AA6:AB7))</f>
+        <v>2.2885280940541346</v>
+      </c>
+      <c r="R24" s="14">
+        <v>0.30925828963928981</v>
+      </c>
+      <c r="T24" s="14" cm="1">
+        <f t="array" ref="T24:U27">MMULT(I12:K15,MMULT(X103:Y105,AA6:AB7))</f>
+        <v>2.3831107713936572</v>
+      </c>
+      <c r="U24" s="14">
+        <v>0.169612023356145</v>
+      </c>
+      <c r="AA24">
+        <v>-1.1102050003853463</v>
+      </c>
+      <c r="AB24">
+        <v>0.19409637818033543</v>
+      </c>
+      <c r="AK24" s="14" cm="1">
+        <f t="array" ref="AK24:AL27">MMULT(N5:Q8,AK18:AL21)</f>
+        <v>-2.2495097967636646</v>
+      </c>
+      <c r="AL24" s="14">
+        <v>-0.3712343274692283</v>
+      </c>
+      <c r="AN24" s="16" cm="1">
+        <f t="array" ref="AN24:AO27">MMULT(N5:Q8,AN18:AO21)</f>
+        <v>2.1848238990077471</v>
+      </c>
+      <c r="AO24" s="16">
+        <v>0.45331626403565373</v>
+      </c>
+      <c r="BE24" s="9">
+        <v>-2.9150628902495308</v>
+      </c>
+      <c r="BF24">
+        <v>1.4436732224590227</v>
+      </c>
+      <c r="BG24">
+        <v>4.6485015169919297</v>
+      </c>
+      <c r="BH24">
+        <v>-3.1771118492014256</v>
+      </c>
+      <c r="BI24">
+        <v>-2.3858853133269</v>
+      </c>
+      <c r="BJ24">
+        <v>1.9987010927705173</v>
+      </c>
+      <c r="BK24">
+        <v>2.4545072596838207</v>
+      </c>
+      <c r="BL24">
+        <v>-2.0673230391274409</v>
+      </c>
+      <c r="BM24">
+        <v>-2.6350751173745706</v>
+      </c>
+      <c r="BN24">
+        <v>2.5737886212527505</v>
+      </c>
+      <c r="BO24">
+        <v>2.1258298392526083</v>
+      </c>
+      <c r="BP24" s="10">
+        <v>-2.064543343130782</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>-0.54594498216071186</v>
+      </c>
+      <c r="B25">
+        <v>0.73706237839498923</v>
+      </c>
+      <c r="C25">
+        <v>-0.19109162564923815</v>
+      </c>
+      <c r="D25">
+        <v>-2.5770585038476864E-5</v>
+      </c>
+      <c r="E25">
+        <v>-0.86871302163810715</v>
+      </c>
+      <c r="F25">
+        <v>0.99262797440699024</v>
+      </c>
+      <c r="G25">
+        <v>-0.12378990903459956</v>
+      </c>
+      <c r="H25">
+        <v>-1.2504373428354174E-4</v>
+      </c>
+      <c r="I25">
+        <v>-0.90695470334775286</v>
+      </c>
+      <c r="J25">
+        <v>0.96609920001264737</v>
+      </c>
+      <c r="K25">
+        <v>-5.8985886597861546E-2</v>
+      </c>
+      <c r="L25">
+        <v>-1.5861006703266336E-4</v>
+      </c>
+      <c r="N25" s="14">
+        <v>-1.1701888658435529</v>
+      </c>
+      <c r="O25" s="14">
+        <v>0.28181366262527546</v>
+      </c>
+      <c r="Q25" s="14">
+        <v>-1.3443097323112525</v>
+      </c>
+      <c r="R25" s="14">
+        <v>0.40281786769334793</v>
+      </c>
+      <c r="T25" s="14">
+        <v>-1.3229219897524969</v>
+      </c>
+      <c r="U25" s="14">
+        <v>0.40810270390806452</v>
+      </c>
+      <c r="AA25">
+        <v>0.84985116239796643</v>
+      </c>
+      <c r="AB25">
+        <v>-0.58320388399123901</v>
+      </c>
+      <c r="AK25" s="14">
+        <v>1.266386432796333</v>
+      </c>
+      <c r="AL25" s="14">
+        <v>-0.44781611914004588</v>
+      </c>
+      <c r="AN25" s="16">
+        <v>-1.2878710391532819</v>
+      </c>
+      <c r="AO25" s="16">
+        <v>0.37092718786250645</v>
+      </c>
+      <c r="BE25" s="9">
+        <v>2.260020752338054</v>
+      </c>
+      <c r="BF25">
+        <v>-1.2717290667065031</v>
+      </c>
+      <c r="BG25">
+        <v>-3.1771118492014256</v>
+      </c>
+      <c r="BH25">
+        <v>2.1888201635698774</v>
+      </c>
+      <c r="BI25">
+        <v>2.046810012968014</v>
+      </c>
+      <c r="BJ25">
+        <v>-1.8458501724402128</v>
+      </c>
+      <c r="BK25">
+        <v>-1.6528769221289008</v>
+      </c>
+      <c r="BL25">
+        <v>1.451917081601102</v>
+      </c>
+      <c r="BM25">
+        <v>2.2444780594005658</v>
+      </c>
+      <c r="BN25">
+        <v>-2.2480448681535004</v>
+      </c>
+      <c r="BO25">
+        <v>-1.4800472470453292</v>
+      </c>
+      <c r="BP25" s="10">
+        <v>1.4836140557982596</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>-0.50423146793320361</v>
+      </c>
+      <c r="B26">
+        <v>-0.47788014036510912</v>
+      </c>
+      <c r="C26">
+        <v>0.98259931223157315</v>
+      </c>
+      <c r="D26">
+        <v>-4.8770393326090386E-4</v>
+      </c>
+      <c r="E26">
+        <v>-0.12458021689574084</v>
+      </c>
+      <c r="F26">
+        <v>-0.30957264037213644</v>
+      </c>
+      <c r="G26">
+        <v>0.43439543769791877</v>
+      </c>
+      <c r="H26">
+        <v>-2.4258043004124835E-4</v>
+      </c>
+      <c r="I26">
+        <v>-0.19762115249404236</v>
+      </c>
+      <c r="J26">
+        <v>-0.14751135049051203</v>
+      </c>
+      <c r="K26">
+        <v>0.34539081967109475</v>
+      </c>
+      <c r="L26">
+        <v>-2.5831668653985315E-4</v>
+      </c>
+      <c r="N26" s="14">
+        <v>0.30656595860109326</v>
+      </c>
+      <c r="O26" s="14">
+        <v>-2.1768957254280483</v>
+      </c>
+      <c r="Q26" s="14">
+        <v>1.9103658534810664E-2</v>
+      </c>
+      <c r="R26" s="14">
+        <v>-1.4597922102468617</v>
+      </c>
+      <c r="T26" s="14">
+        <v>-0.17265598608124344</v>
+      </c>
+      <c r="U26" s="14">
+        <v>-1.2691037169597803</v>
+      </c>
+      <c r="AK26" s="14">
+        <v>0.11882539500931781</v>
+      </c>
+      <c r="AL26" s="14">
+        <v>1.6629212057380482</v>
+      </c>
+      <c r="AN26" s="16">
+        <v>2.9434808863709645E-2</v>
+      </c>
+      <c r="AO26" s="16">
+        <v>-1.5905272662689256</v>
+      </c>
+      <c r="BE26" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI26" t="s">
+        <v>86</v>
+      </c>
+      <c r="BM26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BP26" s="10"/>
+    </row>
+    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>0.90804123874835452</v>
+      </c>
+      <c r="B27">
+        <v>-0.10604665139962893</v>
+      </c>
+      <c r="C27">
+        <v>-0.80251214232436907</v>
+      </c>
+      <c r="D27">
+        <v>5.175549756433835E-4</v>
+      </c>
+      <c r="E27">
+        <v>0.91332053087624909</v>
+      </c>
+      <c r="F27">
+        <v>-0.51455833383200222</v>
+      </c>
+      <c r="G27">
+        <v>-0.39916376990592278</v>
+      </c>
+      <c r="H27">
+        <v>4.0157286167557209E-4</v>
+      </c>
+      <c r="I27">
+        <v>1.0772433070824754</v>
+      </c>
+      <c r="J27">
+        <v>-0.65268469698966347</v>
+      </c>
+      <c r="K27">
+        <v>-0.42505762897411548</v>
+      </c>
+      <c r="L27">
+        <v>4.9901888130256169E-4</v>
+      </c>
+      <c r="N27" s="14">
+        <v>0.66333501713090248</v>
+      </c>
+      <c r="O27" s="14">
+        <v>1.9384291161508982</v>
+      </c>
+      <c r="Q27" s="14">
+        <v>1.158229463704052</v>
+      </c>
+      <c r="R27" s="14">
+        <v>1.3275147346010359</v>
+      </c>
+      <c r="T27" s="14">
+        <v>1.4058630900934628</v>
+      </c>
+      <c r="U27" s="14">
+        <v>1.3707842234516285</v>
+      </c>
+      <c r="AK27" s="14">
+        <v>-1.2227119059569875</v>
+      </c>
+      <c r="AL27" s="14">
+        <v>-1.478391988524179</v>
+      </c>
+      <c r="AN27" s="16">
+        <v>1.1103498507826335</v>
+      </c>
+      <c r="AO27" s="16">
+        <v>1.5139746175610143</v>
+      </c>
+      <c r="BE27" s="9" cm="1">
+        <f t="array" ref="BE27:BH30">MMULT(_xlfn.ANCHORARRAY(BI16),_xlfn.ANCHORARRAY(BE9))</f>
+        <v>8.1422187487784772</v>
+      </c>
+      <c r="BF27">
+        <v>-7.8031434484195783</v>
+      </c>
+      <c r="BG27">
+        <v>-2.3858853133269</v>
+      </c>
+      <c r="BH27">
+        <v>2.046810012968014</v>
+      </c>
+      <c r="BI27" cm="1">
+        <f t="array" ref="BI27:BL30">MMULT(_xlfn.ANCHORARRAY(BI16),_xlfn.ANCHORARRAY(BI9))</f>
+        <v>11.481837265614674</v>
+      </c>
+      <c r="BJ27">
+        <v>-12.860616282167234</v>
+      </c>
+      <c r="BK27">
+        <v>-0.60441104558077408</v>
+      </c>
+      <c r="BL27">
+        <v>1.983190062133338</v>
+      </c>
+      <c r="BM27" cm="1">
+        <f t="array" ref="BM27:BP30">MMULT(_xlfn.ANCHORARRAY(BI16),_xlfn.ANCHORARRAY(BM9))</f>
+        <v>12.281324790114203</v>
+      </c>
+      <c r="BN27">
+        <v>-13.382891567899017</v>
+      </c>
+      <c r="BO27">
+        <v>-1.6767514610716614</v>
+      </c>
+      <c r="BP27" s="10">
+        <v>2.7783182388564667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>191</v>
+      </c>
+      <c r="BE28" s="9">
+        <v>-8.9228899764929253</v>
+      </c>
+      <c r="BF28">
+        <v>8.7700390561626076</v>
+      </c>
+      <c r="BG28">
+        <v>1.9987010927705173</v>
+      </c>
+      <c r="BH28">
+        <v>-1.8458501724402128</v>
+      </c>
+      <c r="BI28">
+        <v>-12.860616282167234</v>
+      </c>
+      <c r="BJ28">
+        <v>14.514482444255707</v>
+      </c>
+      <c r="BK28">
+        <v>0.29787631729095615</v>
+      </c>
+      <c r="BL28">
+        <v>-1.9517424793794282</v>
+      </c>
+      <c r="BM28">
+        <v>-13.742559705552711</v>
+      </c>
+      <c r="BN28">
+        <v>15.023835998054798</v>
+      </c>
+      <c r="BO28">
+        <v>1.5874476156288322</v>
+      </c>
+      <c r="BP28" s="10">
+        <v>-2.8687239081309097</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA29" s="5"/>
+      <c r="AN29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE29" s="9">
+        <v>-1.106824511079775</v>
+      </c>
+      <c r="BF29">
+        <v>0.30519417352485362</v>
+      </c>
+      <c r="BG29">
+        <v>2.4545072596838207</v>
+      </c>
+      <c r="BH29">
+        <v>-1.652876922128901</v>
+      </c>
+      <c r="BI29">
+        <v>-0.60441104558077419</v>
+      </c>
+      <c r="BJ29">
+        <v>0.29787631729095609</v>
+      </c>
+      <c r="BK29">
+        <v>1.3453390723121537</v>
+      </c>
+      <c r="BL29">
+        <v>-1.0388043440223371</v>
+      </c>
+      <c r="BM29">
+        <v>-0.69350544957708737</v>
+      </c>
+      <c r="BN29">
+        <v>0.58673187203950439</v>
+      </c>
+      <c r="BO29">
+        <v>1.0982705568527882</v>
+      </c>
+      <c r="BP29" s="10">
+        <v>-0.99149697931520275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A30" cm="1">
+        <f t="array" ref="A30:D33">MMULT(_xlfn.ANCHORARRAY(A24),_xlfn.ANCHORARRAY(A18))</f>
+        <v>7.8920807860189752</v>
+      </c>
+      <c r="B30">
+        <v>-3.413887276255267</v>
+      </c>
+      <c r="C30">
+        <v>-2.9910613694023636</v>
+      </c>
+      <c r="D30">
+        <v>5.5216975437871998</v>
+      </c>
+      <c r="E30" cm="1">
+        <f t="array" ref="E30:H33">MMULT(_xlfn.ANCHORARRAY(A24),_xlfn.ANCHORARRAY(E18))</f>
+        <v>9.7449886697646484</v>
+      </c>
+      <c r="F30">
+        <v>-5.4070757961122897</v>
+      </c>
+      <c r="G30">
+        <v>-0.71244444595184864</v>
+      </c>
+      <c r="H30">
+        <v>5.6110396492239376</v>
+      </c>
+      <c r="I30" cm="1">
+        <f t="array" ref="I30:L33">MMULT(_xlfn.ANCHORARRAY(A24),_xlfn.ANCHORARRAY(I18))</f>
+        <v>10.454324198854978</v>
+      </c>
+      <c r="J30">
+        <v>-5.6352828246516955</v>
+      </c>
+      <c r="K30">
+        <v>-1.178233684741963</v>
+      </c>
+      <c r="L30">
+        <v>6.6247182254647967</v>
+      </c>
+      <c r="AN30" s="14">
+        <f t="shared" ref="AN30:AO33" si="13">$AC$140*N24+$AC$141*Q24+$AC$142*T24</f>
+        <v>2.1847888031448481</v>
+      </c>
+      <c r="AO30" s="14">
+        <f t="shared" si="13"/>
+        <v>0.45332680873979336</v>
+      </c>
+      <c r="BE30" s="9">
+        <v>1.8874957387942239</v>
+      </c>
+      <c r="BF30">
+        <v>-1.272089781267882</v>
+      </c>
+      <c r="BG30">
+        <v>-2.0673230391274409</v>
+      </c>
+      <c r="BH30">
+        <v>1.451917081601102</v>
+      </c>
+      <c r="BI30">
+        <v>1.9831900621333378</v>
+      </c>
+      <c r="BJ30">
+        <v>-1.9517424793794285</v>
+      </c>
+      <c r="BK30">
+        <v>-1.0388043440223371</v>
+      </c>
+      <c r="BL30">
+        <v>1.0073567612684293</v>
+      </c>
+      <c r="BM30">
+        <v>2.1547403650155972</v>
+      </c>
+      <c r="BN30">
+        <v>-2.2276763021952872</v>
+      </c>
+      <c r="BO30">
+        <v>-1.0089667114099607</v>
+      </c>
+      <c r="BP30" s="10">
+        <v>1.0819026485896468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>-3.413887276255267</v>
+      </c>
+      <c r="B31">
+        <v>2.2717474509538089</v>
+      </c>
+      <c r="C31">
+        <v>-0.69507228278609112</v>
+      </c>
+      <c r="D31">
+        <v>-1.0786478982066203</v>
+      </c>
+      <c r="E31">
+        <v>-5.0117256225504008</v>
+      </c>
+      <c r="F31">
+        <v>3.1804046825027292</v>
+      </c>
+      <c r="G31">
+        <v>-0.6334447541259578</v>
+      </c>
+      <c r="H31">
+        <v>-2.0682497333207501</v>
+      </c>
+      <c r="I31">
+        <v>-5.2742114327761662</v>
+      </c>
+      <c r="J31">
+        <v>3.1511086638560286</v>
+      </c>
+      <c r="K31">
+        <v>-0.17657032753071852</v>
+      </c>
+      <c r="L31">
+        <v>-2.5497786518746666</v>
+      </c>
+      <c r="AN31" s="14">
+        <f t="shared" si="13"/>
+        <v>-1.2878503514697393</v>
+      </c>
+      <c r="AO31" s="14">
+        <f t="shared" si="13"/>
+        <v>0.3709358160935271</v>
+      </c>
+      <c r="BE31" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BI31" t="s">
+        <v>96</v>
+      </c>
+      <c r="BM31" t="s">
+        <v>93</v>
+      </c>
+      <c r="BP31" s="10"/>
+    </row>
+    <row r="32" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>-2.9910613694023636</v>
+      </c>
+      <c r="B32">
+        <v>-0.69507228278609123</v>
+      </c>
+      <c r="C32">
+        <v>6.1094607248847677</v>
+      </c>
+      <c r="D32">
+        <v>-5.3697438180222203</v>
+      </c>
+      <c r="E32">
+        <v>-1.7010686268312669</v>
+      </c>
+      <c r="F32">
+        <v>-5.5899432676908681E-2</v>
+      </c>
+      <c r="G32">
+        <v>2.6257697523275771</v>
+      </c>
+      <c r="H32">
+        <v>-3.0245125135013704</v>
+      </c>
+      <c r="I32">
+        <v>-2.0808637947344222</v>
+      </c>
+      <c r="J32">
+        <v>0.35084888714161089</v>
+      </c>
+      <c r="K32">
+        <v>2.1633755697376986</v>
+      </c>
+      <c r="L32">
+        <v>-3.301013025799306</v>
+      </c>
+      <c r="AN32" s="14">
+        <f t="shared" si="13"/>
+        <v>2.9434336038411016E-2</v>
+      </c>
+      <c r="AO32" s="14">
+        <f t="shared" si="13"/>
+        <v>-1.5905642639254738</v>
+      </c>
+      <c r="BE32" s="9" cm="1">
+        <f t="array" ref="BE32:BH35">MMULT(_xlfn.ANCHORARRAY(BM16),_xlfn.ANCHORARRAY(BE9))</f>
+        <v>8.7331847518623977</v>
+      </c>
+      <c r="BF32">
+        <v>-8.3425876938883796</v>
+      </c>
+      <c r="BG32">
+        <v>-2.635075117374571</v>
+      </c>
+      <c r="BH32">
+        <v>2.2444780594005662</v>
+      </c>
+      <c r="BI32" cm="1">
+        <f t="array" ref="BI32:BL35">MMULT(_xlfn.ANCHORARRAY(BM16),_xlfn.ANCHORARRAY(BI9))</f>
+        <v>12.281324790114205</v>
+      </c>
+      <c r="BJ32">
+        <v>-13.742559705552713</v>
+      </c>
+      <c r="BK32">
+        <v>-0.69350544957708737</v>
+      </c>
+      <c r="BL32">
+        <v>2.1547403650155972</v>
+      </c>
+      <c r="BM32" cm="1">
+        <f t="array" ref="BM32:BP35">MMULT(_xlfn.ANCHORARRAY(BM16),_xlfn.ANCHORARRAY(BM9))</f>
+        <v>13.138167059615098</v>
+      </c>
+      <c r="BN32">
+        <v>-14.310516269206476</v>
+      </c>
+      <c r="BO32">
+        <v>-1.8298155443493627</v>
+      </c>
+      <c r="BP32" s="10">
+        <v>3.0021647539407326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>5.5216975437871998</v>
+      </c>
+      <c r="B33">
+        <v>-1.0786478982066208</v>
+      </c>
+      <c r="C33">
+        <v>-5.3697438180222212</v>
+      </c>
+      <c r="D33">
+        <v>6.0214891515023155</v>
+      </c>
+      <c r="E33">
+        <v>5.5060323118878589</v>
+      </c>
+      <c r="F33">
+        <v>-2.396633778321628</v>
+      </c>
+      <c r="G33">
+        <v>-2.0499463449125521</v>
+      </c>
+      <c r="H33">
+        <v>4.5171643055982793</v>
+      </c>
+      <c r="I33">
+        <v>6.0754021358773729</v>
+      </c>
+      <c r="J33">
+        <v>-2.7672179106120818</v>
+      </c>
+      <c r="K33">
+        <v>-1.9550545988978589</v>
+      </c>
+      <c r="L33">
+        <v>5.1554809526040906</v>
+      </c>
+      <c r="AN33" s="14">
+        <f t="shared" si="13"/>
+        <v>1.1103320147061626</v>
+      </c>
+      <c r="AO33" s="14">
+        <f t="shared" si="13"/>
+        <v>1.5140098345070605</v>
+      </c>
+      <c r="BE33" s="9">
+        <v>-9.4309801108200038</v>
+      </c>
+      <c r="BF33">
+        <v>9.1052363577207416</v>
+      </c>
+      <c r="BG33">
+        <v>2.5737886212527505</v>
+      </c>
+      <c r="BH33">
+        <v>-2.2480448681535004</v>
+      </c>
+      <c r="BI33">
+        <v>-13.382891567899017</v>
+      </c>
+      <c r="BJ33">
+        <v>15.0238359980548</v>
+      </c>
+      <c r="BK33">
+        <v>0.58673187203950439</v>
+      </c>
+      <c r="BL33">
+        <v>-2.2276763021952872</v>
+      </c>
+      <c r="BM33">
+        <v>-14.310516269206476</v>
+      </c>
+      <c r="BN33">
+        <v>15.609376116175021</v>
+      </c>
+      <c r="BO33">
+        <v>1.8628919508592048</v>
+      </c>
+      <c r="BP33" s="10">
+        <v>-3.1617517978277401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" t="s">
+        <v>86</v>
+      </c>
+      <c r="I34" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE34" s="9">
+        <v>-1.6988050928849565</v>
+      </c>
+      <c r="BF34">
+        <v>1.0530225006776748</v>
+      </c>
+      <c r="BG34">
+        <v>2.1258298392526083</v>
+      </c>
+      <c r="BH34">
+        <v>-1.4800472470453292</v>
+      </c>
+      <c r="BI34">
+        <v>-1.6767514610716612</v>
+      </c>
+      <c r="BJ34">
+        <v>1.5874476156288322</v>
+      </c>
+      <c r="BK34">
+        <v>1.098270556852788</v>
+      </c>
+      <c r="BL34">
+        <v>-1.0089667114099607</v>
+      </c>
+      <c r="BM34">
+        <v>-1.8298155443493622</v>
+      </c>
+      <c r="BN34">
+        <v>1.8628919508592048</v>
+      </c>
+      <c r="BO34">
+        <v>1.0290855096240739</v>
+      </c>
+      <c r="BP34" s="10">
+        <v>-1.0621619161339129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A35" cm="1">
+        <f t="array" ref="A35:D38">MMULT(_xlfn.ANCHORARRAY(E24),_xlfn.ANCHORARRAY(A18))</f>
+        <v>9.7449886697646484</v>
+      </c>
+      <c r="B35">
+        <v>-5.0117256225504008</v>
+      </c>
+      <c r="C35">
+        <v>-1.7010686268312671</v>
+      </c>
+      <c r="D35">
+        <v>5.5060323118878589</v>
+      </c>
+      <c r="E35" cm="1">
+        <f t="array" ref="E35:H38">MMULT(_xlfn.ANCHORARRAY(E24),_xlfn.ANCHORARRAY(E18))</f>
+        <v>12.830596634400857</v>
+      </c>
+      <c r="F35">
+        <v>-7.5194198870866575</v>
+      </c>
+      <c r="G35">
+        <v>6.3466291368932601E-2</v>
+      </c>
+      <c r="H35">
+        <v>6.5689096569816332</v>
+      </c>
+      <c r="I35" cm="1">
+        <f t="array" ref="I35:L38">MMULT(_xlfn.ANCHORARRAY(E24),_xlfn.ANCHORARRAY(I18))</f>
+        <v>13.66205526905444</v>
+      </c>
+      <c r="J35">
+        <v>-7.6729804210794184</v>
+      </c>
+      <c r="K35">
+        <v>-0.767510328294851</v>
+      </c>
+      <c r="L35">
+        <v>7.8637164945963098</v>
+      </c>
+      <c r="BE35" s="9">
+        <v>2.3966004518425543</v>
+      </c>
+      <c r="BF35">
+        <v>-1.8156711645100287</v>
+      </c>
+      <c r="BG35">
+        <v>-2.0645433431307825</v>
+      </c>
+      <c r="BH35">
+        <v>1.4836140557982596</v>
+      </c>
+      <c r="BI35">
+        <v>2.7783182388564667</v>
+      </c>
+      <c r="BJ35">
+        <v>-2.8687239081309097</v>
+      </c>
+      <c r="BK35">
+        <v>-0.99149697931520275</v>
+      </c>
+      <c r="BL35">
+        <v>1.081902648589647</v>
+      </c>
+      <c r="BM35">
+        <v>3.0021647539407326</v>
+      </c>
+      <c r="BN35">
+        <v>-3.1617517978277401</v>
+      </c>
+      <c r="BO35">
+        <v>-1.0621619161339131</v>
+      </c>
+      <c r="BP35" s="10">
+        <v>1.2217489600209173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>-5.4070757961122888</v>
+      </c>
+      <c r="B36">
+        <v>3.1804046825027292</v>
+      </c>
+      <c r="C36">
+        <v>-5.5899432676908459E-2</v>
+      </c>
+      <c r="D36">
+        <v>-2.396633778321628</v>
+      </c>
+      <c r="E36">
+        <v>-7.5194198870866575</v>
+      </c>
+      <c r="F36">
+        <v>4.59516909734407</v>
+      </c>
+      <c r="G36">
+        <v>-0.50853907172845203</v>
+      </c>
+      <c r="H36">
+        <v>-3.4643793679621244</v>
+      </c>
+      <c r="I36">
+        <v>-7.9584628411125671</v>
+      </c>
+      <c r="J36">
+        <v>4.6160268161123827</v>
+      </c>
+      <c r="K36">
+        <v>8.0901971245752283E-2</v>
+      </c>
+      <c r="L36">
+        <v>-4.2044392515892737</v>
+      </c>
+      <c r="BE36" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BP36" s="10"/>
+    </row>
+    <row r="37" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>-0.71244444595184864</v>
+      </c>
+      <c r="B37">
+        <v>-0.6334447541259578</v>
+      </c>
+      <c r="C37">
+        <v>2.6257697523275771</v>
+      </c>
+      <c r="D37">
+        <v>-2.0499463449125521</v>
+      </c>
+      <c r="E37">
+        <v>6.3466291368932601E-2</v>
+      </c>
+      <c r="F37">
+        <v>-0.50853907172845203</v>
+      </c>
+      <c r="G37">
+        <v>1.1796335520185026</v>
+      </c>
+      <c r="H37">
+        <v>-0.93167844177570946</v>
+      </c>
+      <c r="I37">
+        <v>-5.3110357662278534E-2</v>
+      </c>
+      <c r="J37">
+        <v>-0.33631551110785002</v>
+      </c>
+      <c r="K37">
+        <v>0.91920470237586427</v>
+      </c>
+      <c r="L37">
+        <v>-0.97222832631927592</v>
+      </c>
+      <c r="BE37" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI37" t="s">
+        <v>102</v>
+      </c>
+      <c r="BM37" t="s">
+        <v>103</v>
+      </c>
+      <c r="BP37" s="10"/>
+    </row>
+    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>5.6110396492239376</v>
+      </c>
+      <c r="B38">
+        <v>-2.0682497333207506</v>
+      </c>
+      <c r="C38">
+        <v>-3.0245125135013708</v>
+      </c>
+      <c r="D38">
+        <v>4.5171643055982802</v>
+      </c>
+      <c r="E38">
+        <v>6.5689096569816332</v>
+      </c>
+      <c r="F38">
+        <v>-3.464379367962124</v>
+      </c>
+      <c r="G38">
+        <v>-0.93167844177570958</v>
+      </c>
+      <c r="H38">
+        <v>4.1513735992790721</v>
+      </c>
+      <c r="I38">
+        <v>7.0932660644428038</v>
+      </c>
+      <c r="J38">
+        <v>-3.6844228133915697</v>
+      </c>
+      <c r="K38">
+        <v>-1.1475608018678098</v>
+      </c>
+      <c r="L38">
+        <v>4.8526701571483075</v>
+      </c>
+      <c r="BE38" s="9" cm="1">
+        <f t="array" ref="BE38:BH41">MMULT(_xlfn.ANCHORARRAY(BE22),$N$1:$Q$4)</f>
+        <v>1.8078014150955799</v>
+      </c>
+      <c r="BF38">
+        <v>-2.7656568568589797</v>
+      </c>
+      <c r="BG38">
+        <v>-0.58750836512325921</v>
+      </c>
+      <c r="BH38">
+        <v>2.7681090729594476E-4</v>
+      </c>
+      <c r="BI38" cm="1">
+        <f t="array" ref="BI38:BL41">MMULT(_xlfn.ANCHORARRAY(BI22),$N$1:$Q$4)</f>
+        <v>2.3964199988331276</v>
+      </c>
+      <c r="BJ38">
+        <v>-4.4972703053098719</v>
+      </c>
+      <c r="BK38">
+        <v>-0.22307191421423023</v>
+      </c>
+      <c r="BL38">
+        <v>2.3118345591841984E-4</v>
+      </c>
+      <c r="BM38" cm="1">
+        <f t="array" ref="BM38:BP41">MMULT(_xlfn.ANCHORARRAY(BM22),$N$1:$Q$4)</f>
+        <v>2.5703532708461458</v>
+      </c>
+      <c r="BN38">
+        <v>-4.7533553494547487</v>
+      </c>
+      <c r="BO38">
+        <v>-0.34238101899011614</v>
+      </c>
+      <c r="BP38" s="10">
+        <v>2.935394043679013E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" t="s">
+        <v>96</v>
+      </c>
+      <c r="I39" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE39" s="9">
+        <v>-1.6150092379503771</v>
+      </c>
+      <c r="BF39">
+        <v>2.6789944248582946</v>
+      </c>
+      <c r="BG39">
+        <v>0.29096116503562774</v>
+      </c>
+      <c r="BH39">
+        <v>-1.5576338244924031E-4</v>
+      </c>
+      <c r="BI39">
+        <v>-2.2966232657851089</v>
+      </c>
+      <c r="BJ39">
+        <v>4.4202311501760772</v>
+      </c>
+      <c r="BK39">
+        <v>6.1509523699292308E-2</v>
+      </c>
+      <c r="BL39">
+        <v>-1.5580756333780378E-4</v>
+      </c>
+      <c r="BM39">
+        <v>-2.4553926403233239</v>
+      </c>
+      <c r="BN39">
+        <v>4.5891756148830023</v>
+      </c>
+      <c r="BO39">
+        <v>0.21222853540500775</v>
+      </c>
+      <c r="BP39" s="10">
+        <v>-2.2238626874516721E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A40" cm="1">
+        <f t="array" ref="A40:D43">MMULT(_xlfn.ANCHORARRAY(I24),_xlfn.ANCHORARRAY(A18))</f>
+        <v>10.454324198854978</v>
+      </c>
+      <c r="B40">
+        <v>-5.2742114327761662</v>
+      </c>
+      <c r="C40">
+        <v>-2.0808637947344226</v>
+      </c>
+      <c r="D40">
+        <v>6.0754021358773729</v>
+      </c>
+      <c r="E40" cm="1">
+        <f t="array" ref="E40:H43">MMULT(_xlfn.ANCHORARRAY(I24),_xlfn.ANCHORARRAY(E18))</f>
+        <v>13.66205526905444</v>
+      </c>
+      <c r="F40">
+        <v>-7.9584628411125689</v>
+      </c>
+      <c r="G40">
+        <v>-5.3110357662278534E-2</v>
+      </c>
+      <c r="H40">
+        <v>7.0932660644428038</v>
+      </c>
+      <c r="I40" cm="1">
+        <f t="array" ref="I40:L43">MMULT(_xlfn.ANCHORARRAY(I24),_xlfn.ANCHORARRAY(I18))</f>
+        <v>14.559748711130979</v>
+      </c>
+      <c r="J40">
+        <v>-8.1396762736402746</v>
+      </c>
+      <c r="K40">
+        <v>-0.91171213825433062</v>
+      </c>
+      <c r="L40">
+        <v>8.4767927539891801</v>
+      </c>
+      <c r="BE40" s="9">
+        <v>-0.85796208915392924</v>
+      </c>
+      <c r="BF40">
+        <v>0.7276329452722714</v>
+      </c>
+      <c r="BG40">
+        <v>0.936869504824694</v>
+      </c>
+      <c r="BH40">
+        <v>-3.8913767169983661E-4</v>
+      </c>
+      <c r="BI40">
+        <v>-0.70221440324685414</v>
+      </c>
+      <c r="BJ40">
+        <v>1.007375311965931</v>
+      </c>
+      <c r="BK40">
+        <v>0.49468694213886172</v>
+      </c>
+      <c r="BL40">
+        <v>-2.5320898736998785E-4</v>
+      </c>
+      <c r="BM40">
+        <v>-0.77555601299109422</v>
+      </c>
+      <c r="BN40">
+        <v>1.2972280470787456</v>
+      </c>
+      <c r="BO40">
+        <v>0.42844455176836022</v>
+      </c>
+      <c r="BP40" s="10">
+        <v>-2.5286852581889543E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>-5.6352828246516964</v>
+      </c>
+      <c r="B41">
+        <v>3.1511086638560286</v>
+      </c>
+      <c r="C41">
+        <v>0.35084888714161111</v>
+      </c>
+      <c r="D41">
+        <v>-2.7672179106120818</v>
+      </c>
+      <c r="E41">
+        <v>-7.6729804210794192</v>
+      </c>
+      <c r="F41">
+        <v>4.6160268161123827</v>
+      </c>
+      <c r="G41">
+        <v>-0.33631551110784991</v>
+      </c>
+      <c r="H41">
+        <v>-3.6844228133915697</v>
+      </c>
+      <c r="I41">
+        <v>-8.1396762736402746</v>
+      </c>
+      <c r="J41">
+        <v>4.6640960242672014</v>
+      </c>
+      <c r="K41">
+        <v>0.22547153630346467</v>
+      </c>
+      <c r="L41">
+        <v>-4.4468639114985038</v>
+      </c>
+      <c r="BE41" s="9">
+        <v>0.66516991200872899</v>
+      </c>
+      <c r="BF41">
+        <v>-0.64097051327158971</v>
+      </c>
+      <c r="BG41">
+        <v>-0.64032230473706331</v>
+      </c>
+      <c r="BH41">
+        <v>2.6809014685313248E-4</v>
+      </c>
+      <c r="BI41">
+        <v>0.60241767019883974</v>
+      </c>
+      <c r="BJ41">
+        <v>-0.93033615683214255</v>
+      </c>
+      <c r="BK41">
+        <v>-0.33312455162392407</v>
+      </c>
+      <c r="BL41">
+        <v>1.7783309478937211E-4</v>
+      </c>
+      <c r="BM41">
+        <v>0.66059538246827576</v>
+      </c>
+      <c r="BN41">
+        <v>-1.1330483125070054</v>
+      </c>
+      <c r="BO41">
+        <v>-0.29829206818325243</v>
+      </c>
+      <c r="BP41" s="10">
+        <v>1.8171539019616178E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>-1.1782336847419628</v>
+      </c>
+      <c r="B42">
+        <v>-0.1765703275307185</v>
+      </c>
+      <c r="C42">
+        <v>2.1633755697376986</v>
+      </c>
+      <c r="D42">
+        <v>-1.9550545988978587</v>
+      </c>
+      <c r="E42">
+        <v>-0.767510328294851</v>
+      </c>
+      <c r="F42">
+        <v>8.090197124575231E-2</v>
+      </c>
+      <c r="G42">
+        <v>0.91920470237586427</v>
+      </c>
+      <c r="H42">
+        <v>-1.1475608018678096</v>
+      </c>
+      <c r="I42">
+        <v>-0.91171213825433062</v>
+      </c>
+      <c r="J42">
+        <v>0.22547153630346461</v>
+      </c>
+      <c r="K42">
+        <v>0.76831960952954548</v>
+      </c>
+      <c r="L42">
+        <v>-1.2617816797663772</v>
+      </c>
+      <c r="BE42" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI42" t="s">
+        <v>105</v>
+      </c>
+      <c r="BM42" t="s">
+        <v>106</v>
+      </c>
+      <c r="BP42" s="10"/>
+    </row>
+    <row r="43" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>6.6247182254647967</v>
+      </c>
+      <c r="B43">
+        <v>-2.5497786518746666</v>
+      </c>
+      <c r="C43">
+        <v>-3.3010130257993064</v>
+      </c>
+      <c r="D43">
+        <v>5.1554809526040906</v>
+      </c>
+      <c r="E43">
+        <v>7.8637164945963098</v>
+      </c>
+      <c r="F43">
+        <v>-4.2044392515892737</v>
+      </c>
+      <c r="G43">
+        <v>-0.9722283263192758</v>
+      </c>
+      <c r="H43">
+        <v>4.8526701571483075</v>
+      </c>
+      <c r="I43">
+        <v>8.4767927539891801</v>
+      </c>
+      <c r="J43">
+        <v>-4.4468639114985038</v>
+      </c>
+      <c r="K43">
+        <v>-1.2617816797663772</v>
+      </c>
+      <c r="L43">
+        <v>5.6865222721580517</v>
+      </c>
+      <c r="BE43" s="9" cm="1">
+        <f t="array" ref="BE43:BH46">MMULT(_xlfn.ANCHORARRAY(BE27),$N$1:$Q$4)</f>
+        <v>2.3964199988331276</v>
+      </c>
+      <c r="BF43">
+        <v>-3.9329012697793706</v>
+      </c>
+      <c r="BG43">
+        <v>-0.48085671993316537</v>
+      </c>
+      <c r="BH43">
+        <v>2.5069651956335286E-4</v>
+      </c>
+      <c r="BI43" cm="1">
+        <f t="array" ref="BI43:BL46">MMULT(_xlfn.ANCHORARRAY(BI27),$N$1:$Q$4)</f>
+        <v>3.3793374135022365</v>
+      </c>
+      <c r="BJ43">
+        <v>-6.4819433912271549</v>
+      </c>
+      <c r="BK43">
+        <v>-0.12181436854736395</v>
+      </c>
+      <c r="BL43">
+        <v>2.4290424761432258E-4</v>
+      </c>
+      <c r="BM43" cm="1">
+        <f t="array" ref="BM43:BP46">MMULT(_xlfn.ANCHORARRAY(BM27),$N$1:$Q$4)</f>
+        <v>3.6146427954432085</v>
+      </c>
+      <c r="BN43">
+        <v>-6.7451779643202512</v>
+      </c>
+      <c r="BO43">
+        <v>-0.33793628017676236</v>
+      </c>
+      <c r="BP43" s="10">
+        <v>3.4029280114313416E-4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>100</v>
+      </c>
+      <c r="BE44" s="9">
+        <v>-2.6261873632740769</v>
+      </c>
+      <c r="BF44">
+        <v>4.4202311501760772</v>
+      </c>
+      <c r="BG44">
+        <v>0.40282273679631031</v>
+      </c>
+      <c r="BH44">
+        <v>-2.2608264124873983E-4</v>
+      </c>
+      <c r="BI44">
+        <v>-3.7851400222486209</v>
+      </c>
+      <c r="BJ44">
+        <v>7.3155167289363687</v>
+      </c>
+      <c r="BK44">
+        <v>6.0034666410084342E-2</v>
+      </c>
+      <c r="BL44">
+        <v>-2.390524980649574E-4</v>
+      </c>
+      <c r="BM44">
+        <v>-4.0447138463929777</v>
+      </c>
+      <c r="BN44">
+        <v>7.572238555434228</v>
+      </c>
+      <c r="BO44">
+        <v>0.31993778127273159</v>
+      </c>
+      <c r="BP44" s="10">
+        <v>-3.5136583014548569E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" t="s">
+        <v>102</v>
+      </c>
+      <c r="I45" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE45" s="9">
+        <v>-0.32576088599292369</v>
+      </c>
+      <c r="BF45">
+        <v>0.15382243842105281</v>
+      </c>
+      <c r="BG45">
+        <v>0.49468694213886172</v>
+      </c>
+      <c r="BH45">
+        <v>-2.0244697310398488E-4</v>
+      </c>
+      <c r="BI45">
+        <v>-0.17789042051501078</v>
+      </c>
+      <c r="BJ45">
+        <v>0.15013412918201308</v>
+      </c>
+      <c r="BK45">
+        <v>0.27114267810630227</v>
+      </c>
+      <c r="BL45">
+        <v>-1.2723439493832566E-4</v>
+      </c>
+      <c r="BM45">
+        <v>-0.20411270931717718</v>
+      </c>
+      <c r="BN45">
+        <v>0.29572165881835211</v>
+      </c>
+      <c r="BO45">
+        <v>0.22134793094098906</v>
+      </c>
+      <c r="BP45" s="10">
+        <v>-1.2144011427394915E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A46" cm="1">
+        <f t="array" ref="A46:D49">MMULT(_xlfn.ANCHORARRAY(A30),$N$1:$Q$4)</f>
+        <v>2.322799326763346</v>
+      </c>
+      <c r="B46">
+        <v>-1.7206503625647596</v>
+      </c>
+      <c r="C46">
+        <v>-0.6028252704251249</v>
+      </c>
+      <c r="D46">
+        <v>6.763062265372049E-4</v>
+      </c>
+      <c r="E46" cm="1">
+        <f t="array" ref="E46:H49">MMULT(_xlfn.ANCHORARRAY(E30),$N$1:$Q$4)</f>
+        <v>2.8681476704528168</v>
+      </c>
+      <c r="F46">
+        <v>-2.7252472551469453</v>
+      </c>
+      <c r="G46">
+        <v>-0.14358766429443562</v>
+      </c>
+      <c r="H46">
+        <v>6.8724898856276973E-4</v>
+      </c>
+      <c r="I46" cm="1">
+        <f t="array" ref="I46:L49">MMULT(_xlfn.ANCHORARRAY(I30),$N$1:$Q$4)</f>
+        <v>3.0769194930042518</v>
+      </c>
+      <c r="J46">
+        <v>-2.8402670184318284</v>
+      </c>
+      <c r="K46">
+        <v>-0.23746388051224848</v>
+      </c>
+      <c r="L46">
+        <v>8.1140593982324295E-4</v>
+      </c>
+      <c r="BE46" s="9">
+        <v>0.55552825043387322</v>
+      </c>
+      <c r="BF46">
+        <v>-0.64115231881775869</v>
+      </c>
+      <c r="BG46">
+        <v>-0.41665295900200722</v>
+      </c>
+      <c r="BH46">
+        <v>1.7783309478937211E-4</v>
+      </c>
+      <c r="BI46">
+        <v>0.5836930292613961</v>
+      </c>
+      <c r="BJ46">
+        <v>-0.98370746689122623</v>
+      </c>
+      <c r="BK46">
+        <v>-0.20936297596902292</v>
+      </c>
+      <c r="BL46">
+        <v>1.233826453889607E-4</v>
+      </c>
+      <c r="BM46">
+        <v>0.63418376026694689</v>
+      </c>
+      <c r="BN46">
+        <v>-1.1227822499323303</v>
+      </c>
+      <c r="BO46">
+        <v>-0.20334943203695871</v>
+      </c>
+      <c r="BP46" s="10">
+        <v>1.3251314327630085E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>-1.0047762157959013</v>
+      </c>
+      <c r="B47">
+        <v>1.1449947695481437</v>
+      </c>
+      <c r="C47">
+        <v>-0.14008643925592709</v>
+      </c>
+      <c r="D47">
+        <v>-1.3211449631449074E-4</v>
+      </c>
+      <c r="E47">
+        <v>-1.4750524250341466</v>
+      </c>
+      <c r="F47">
+        <v>1.6029716353299401</v>
+      </c>
+      <c r="G47">
+        <v>-0.12766588780545651</v>
+      </c>
+      <c r="H47">
+        <v>-2.5332249033679487E-4</v>
+      </c>
+      <c r="I47">
+        <v>-1.5523073188711991</v>
+      </c>
+      <c r="J47">
+        <v>1.5882060027747134</v>
+      </c>
+      <c r="K47">
+        <v>-3.558638299154189E-2</v>
+      </c>
+      <c r="L47">
+        <v>-3.1230091197130858E-4</v>
+      </c>
+      <c r="BE47" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="BI47" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM47" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP47" s="10"/>
+    </row>
+    <row r="48" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>-0.8803299818551753</v>
+      </c>
+      <c r="B48">
+        <v>-0.35032684989426</v>
+      </c>
+      <c r="C48">
+        <v>1.2313145264439085</v>
+      </c>
+      <c r="D48">
+        <v>-6.5769469447384292E-4</v>
+      </c>
+      <c r="E48">
+        <v>-0.50065897300261319</v>
+      </c>
+      <c r="F48">
+        <v>-2.8174152020681822E-2</v>
+      </c>
+      <c r="G48">
+        <v>0.5292035720876086</v>
+      </c>
+      <c r="H48">
+        <v>-3.7044706431307205E-4</v>
+      </c>
+      <c r="I48">
+        <v>-0.61244038835206571</v>
+      </c>
+      <c r="J48">
+        <v>0.17683309846359307</v>
+      </c>
+      <c r="K48">
+        <v>0.43601160317175747</v>
+      </c>
+      <c r="L48">
+        <v>-4.043132832837625E-4</v>
+      </c>
+      <c r="BE48" s="9" cm="1">
+        <f t="array" ref="BE48:BH51">MMULT(_xlfn.ANCHORARRAY(BE32),$N$1:$Q$4)</f>
+        <v>2.5703532708461463</v>
+      </c>
+      <c r="BF48">
+        <v>-4.204789255948473</v>
+      </c>
+      <c r="BG48">
+        <v>-0.53107899639626444</v>
+      </c>
+      <c r="BH48">
+        <v>2.7490721374384024E-4</v>
+      </c>
+      <c r="BI48" cm="1">
+        <f t="array" ref="BI48:BL51">MMULT(_xlfn.ANCHORARRAY(BI32),$N$1:$Q$4)</f>
+        <v>3.614642795443209</v>
+      </c>
+      <c r="BJ48">
+        <v>-6.9264560972455014</v>
+      </c>
+      <c r="BK48">
+        <v>-0.13977065614876955</v>
+      </c>
+      <c r="BL48">
+        <v>2.6391599935979027E-4</v>
+      </c>
+      <c r="BM48" cm="1">
+        <f t="array" ref="BM48:BP51">MMULT(_xlfn.ANCHORARRAY(BM32),$N$1:$Q$4)</f>
+        <v>3.8668288412658609</v>
+      </c>
+      <c r="BN48">
+        <v>-7.2127147191891776</v>
+      </c>
+      <c r="BO48">
+        <v>-0.3687851615598583</v>
+      </c>
+      <c r="BP48" s="10">
+        <v>3.6770987546486697E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1.6251474972254412</v>
+      </c>
+      <c r="B49">
+        <v>-0.5436547099952227</v>
+      </c>
+      <c r="C49">
+        <v>-1.0822303087213716</v>
+      </c>
+      <c r="D49">
+        <v>7.3752149115253888E-4</v>
+      </c>
+      <c r="E49">
+        <v>1.6205369019849765</v>
+      </c>
+      <c r="F49">
+        <v>-1.207939350630074</v>
+      </c>
+      <c r="G49">
+        <v>-0.41315082076561327</v>
+      </c>
+      <c r="H49">
+        <v>5.5326941070958841E-4</v>
+      </c>
+      <c r="I49">
+        <v>1.7881139807935345</v>
+      </c>
+      <c r="J49">
+        <v>-1.3947193084867251</v>
+      </c>
+      <c r="K49">
+        <v>-0.39402612374749446</v>
+      </c>
+      <c r="L49">
+        <v>6.3145144068298142E-4</v>
+      </c>
+      <c r="BE49" s="9">
+        <v>-2.7757285874390365</v>
+      </c>
+      <c r="BF49">
+        <v>4.5891756148830032</v>
+      </c>
+      <c r="BG49">
+        <v>0.51872717741455399</v>
+      </c>
+      <c r="BH49">
+        <v>-2.753440821071194E-4</v>
+      </c>
+      <c r="BI49">
+        <v>-3.9388562239671883</v>
+      </c>
+      <c r="BJ49">
+        <v>7.5722385554342289</v>
+      </c>
+      <c r="BK49">
+        <v>0.11825126794370162</v>
+      </c>
+      <c r="BL49">
+        <v>-2.7284930801383842E-4</v>
+      </c>
+      <c r="BM49">
+        <v>-4.211874974041705</v>
+      </c>
+      <c r="BN49">
+        <v>7.8673595524124655</v>
+      </c>
+      <c r="BO49">
+        <v>0.37545145530526913</v>
+      </c>
+      <c r="BP49" s="10">
+        <v>-3.8725634837461333E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" t="s">
+        <v>105</v>
+      </c>
+      <c r="I50" t="s">
+        <v>106</v>
+      </c>
+      <c r="BE50" s="9">
+        <v>-0.49999276908641532</v>
+      </c>
+      <c r="BF50">
+        <v>0.53073912550720403</v>
+      </c>
+      <c r="BG50">
+        <v>0.42844455176836022</v>
+      </c>
+      <c r="BH50">
+        <v>-1.8127852183288311E-4</v>
+      </c>
+      <c r="BI50">
+        <v>-0.49350193827543865</v>
+      </c>
+      <c r="BJ50">
+        <v>0.80009739465693908</v>
+      </c>
+      <c r="BK50">
+        <v>0.22134793094098901</v>
+      </c>
+      <c r="BL50">
+        <v>-1.2357983462225316E-4</v>
+      </c>
+      <c r="BM50">
+        <v>-0.53855180018497917</v>
+      </c>
+      <c r="BN50">
+        <v>0.9389254686173728</v>
+      </c>
+      <c r="BO50">
+        <v>0.20740422011256229</v>
+      </c>
+      <c r="BP50" s="10">
+        <v>-1.3009526722091282E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A51" cm="1">
+        <f t="array" ref="A51:D54">MMULT(_xlfn.ANCHORARRAY(A35),$N$1:$Q$4)</f>
+        <v>2.8681476704528168</v>
+      </c>
+      <c r="B51">
+        <v>-2.5259848412381039</v>
+      </c>
+      <c r="C51">
+        <v>-0.34283721673893525</v>
+      </c>
+      <c r="D51">
+        <v>6.7438752421972756E-4</v>
+      </c>
+      <c r="E51" cm="1">
+        <f t="array" ref="E51:H54">MMULT(_xlfn.ANCHORARRAY(E35),$N$1:$Q$4)</f>
+        <v>3.7763046314927458</v>
+      </c>
+      <c r="F51">
+        <v>-3.7899003417548354</v>
+      </c>
+      <c r="G51">
+        <v>1.2791139843780944E-2</v>
+      </c>
+      <c r="H51">
+        <v>8.0457041830834955E-4</v>
+      </c>
+      <c r="I51" cm="1">
+        <f t="array" ref="I51:L54">MMULT(_xlfn.ANCHORARRAY(I35),$N$1:$Q$4)</f>
+        <v>4.0210197591212262</v>
+      </c>
+      <c r="J51">
+        <v>-3.8672971528118523</v>
+      </c>
+      <c r="K51">
+        <v>-0.15468576671192333</v>
+      </c>
+      <c r="L51">
+        <v>9.6316040254735245E-4</v>
+      </c>
+      <c r="BE51" s="9">
+        <v>0.70536808567930331</v>
+      </c>
+      <c r="BF51">
+        <v>-0.91512548444173025</v>
+      </c>
+      <c r="BG51">
+        <v>-0.41609273278664877</v>
+      </c>
+      <c r="BH51">
+        <v>1.8171539019616178E-4</v>
+      </c>
+      <c r="BI51">
+        <v>0.81771536679941559</v>
+      </c>
+      <c r="BJ51">
+        <v>-1.4458798528456622</v>
+      </c>
+      <c r="BK51">
+        <v>-0.19982854273592066</v>
+      </c>
+      <c r="BL51">
+        <v>1.3251314327630088E-4</v>
+      </c>
+      <c r="BM51">
+        <v>0.88359793296082123</v>
+      </c>
+      <c r="BN51">
+        <v>-1.5935703018406562</v>
+      </c>
+      <c r="BO51">
+        <v>-0.21407051385797254</v>
+      </c>
+      <c r="BP51" s="10">
+        <v>1.4964174013065877E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>-1.5914119938074607</v>
+      </c>
+      <c r="B52">
+        <v>1.6029716353299401</v>
+      </c>
+      <c r="C52">
+        <v>-1.1266098036230342E-2</v>
+      </c>
+      <c r="D52">
+        <v>-2.9354348624763618E-4</v>
+      </c>
+      <c r="E52">
+        <v>-2.2131176713646239</v>
+      </c>
+      <c r="F52">
+        <v>2.3160341082100353</v>
+      </c>
+      <c r="G52">
+        <v>-0.10249211419480139</v>
+      </c>
+      <c r="H52">
+        <v>-4.2432265060878666E-4</v>
+      </c>
+      <c r="I52">
+        <v>-2.3423369109646783</v>
+      </c>
+      <c r="J52">
+        <v>2.3265467111335676</v>
+      </c>
+      <c r="K52">
+        <v>1.6305166183832216E-2</v>
+      </c>
+      <c r="L52">
+        <v>-5.1496635272003162E-4</v>
+      </c>
+      <c r="BE52" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP52" s="10"/>
+    </row>
+    <row r="53" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>-0.20968683979323627</v>
+      </c>
+      <c r="B53">
+        <v>-0.31926565163192466</v>
+      </c>
+      <c r="C53">
+        <v>0.5292035720876086</v>
+      </c>
+      <c r="D53">
+        <v>-2.5108066244799261E-4</v>
+      </c>
+      <c r="E53">
+        <v>1.8679415842407541E-2</v>
+      </c>
+      <c r="F53">
+        <v>-0.25631131532489398</v>
+      </c>
+      <c r="G53">
+        <v>0.23774601292790931</v>
+      </c>
+      <c r="H53">
+        <v>-1.1411344542265939E-4</v>
+      </c>
+      <c r="I53">
+        <v>-1.5631454665370994E-2</v>
+      </c>
+      <c r="J53">
+        <v>-0.16950805908232477</v>
+      </c>
+      <c r="K53">
+        <v>0.18525859380695159</v>
+      </c>
+      <c r="L53">
+        <v>-1.1908005925558028E-4</v>
+      </c>
+      <c r="BE53" s="9">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4))</f>
+        <v>5.4239334349254209</v>
+      </c>
+      <c r="BI53">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BI38),_xlfn.MUNIT(4))</f>
+        <v>7.3115159242428565</v>
+      </c>
+      <c r="BM53">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BM38),_xlfn.MUNIT(4))</f>
+        <v>7.5881551528877056</v>
+      </c>
+      <c r="BP53" s="10"/>
+    </row>
+    <row r="54" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1.6514426895817722</v>
+      </c>
+      <c r="B54">
+        <v>-1.0424288693610395</v>
+      </c>
+      <c r="C54">
+        <v>-0.60956708963144335</v>
+      </c>
+      <c r="D54">
+        <v>5.5326941070958852E-4</v>
+      </c>
+      <c r="E54">
+        <v>1.9333632463363248</v>
+      </c>
+      <c r="F54">
+        <v>-1.746099133678654</v>
+      </c>
+      <c r="G54">
+        <v>-0.18777257944557682</v>
+      </c>
+      <c r="H54">
+        <v>5.084667879053981E-4</v>
+      </c>
+      <c r="I54">
+        <v>2.08769196435864</v>
+      </c>
+      <c r="J54">
+        <v>-1.8570043287012281</v>
+      </c>
+      <c r="K54">
+        <v>-0.23128199835413549</v>
+      </c>
+      <c r="L54">
+        <v>5.9436269672237551E-4</v>
+      </c>
+      <c r="BE54" s="9"/>
+      <c r="BP54" s="10"/>
+    </row>
+    <row r="55" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E55" t="s">
+        <v>108</v>
+      </c>
+      <c r="I55" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE55" s="9"/>
+      <c r="BP55" s="10"/>
+    </row>
+    <row r="56" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A56" cm="1">
+        <f t="array" ref="A56:D59">MMULT(_xlfn.ANCHORARRAY(A40),$N$1:$Q$4)</f>
+        <v>3.0769194930042518</v>
+      </c>
+      <c r="B56">
+        <v>-2.6582816243435152</v>
+      </c>
+      <c r="C56">
+        <v>-0.41938199349927341</v>
+      </c>
+      <c r="D56">
+        <v>7.4412483853527982E-4</v>
+      </c>
+      <c r="E56" cm="1">
+        <f t="array" ref="E56:H59">MMULT(_xlfn.ANCHORARRAY(E40),$N$1:$Q$4)</f>
+        <v>4.0210197591212262</v>
+      </c>
+      <c r="F56">
+        <v>-4.0111845719871937</v>
+      </c>
+      <c r="G56">
+        <v>-1.0703981552386286E-2</v>
+      </c>
+      <c r="H56">
+        <v>8.6879441835153916E-4</v>
+      </c>
+      <c r="I56" cm="1">
+        <f t="array" ref="I56:L59">MMULT(_xlfn.ANCHORARRAY(I40),$N$1:$Q$4)</f>
+        <v>4.2852291329772534</v>
+      </c>
+      <c r="J56">
+        <v>-4.1025188584321821</v>
+      </c>
+      <c r="K56">
+        <v>-0.18374852549509893</v>
+      </c>
+      <c r="L56">
+        <v>1.0382509500251041E-3</v>
+      </c>
+      <c r="BE56" s="9"/>
+      <c r="BP56" s="10"/>
+    </row>
+    <row r="57" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>-1.6585779474546976</v>
+      </c>
+      <c r="B57">
+        <v>1.5882060027747134</v>
+      </c>
+      <c r="C57">
+        <v>7.0710877895412499E-2</v>
+      </c>
+      <c r="D57">
+        <v>-3.3893321542719228E-4</v>
+      </c>
+      <c r="E57">
+        <v>-2.2583136487813391</v>
+      </c>
+      <c r="F57">
+        <v>2.3265467111335676</v>
+      </c>
+      <c r="G57">
+        <v>-6.7781788433268625E-2</v>
+      </c>
+      <c r="H57">
+        <v>-4.512739189592374E-4</v>
+      </c>
+      <c r="I57">
+        <v>-2.3956716968707616</v>
+      </c>
+      <c r="J57">
+        <v>2.3507743126173857</v>
+      </c>
+      <c r="K57">
+        <v>4.544204316090722E-2</v>
+      </c>
+      <c r="L57">
+        <v>-5.4465890752996519E-4</v>
+      </c>
+      <c r="BE57" s="9"/>
+      <c r="BP57" s="10"/>
+    </row>
+    <row r="58" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>-0.34677805307528531</v>
+      </c>
+      <c r="B58">
+        <v>-8.8994091924783247E-2</v>
+      </c>
+      <c r="C58">
+        <v>0.43601160317175747</v>
+      </c>
+      <c r="D58">
+        <v>-2.3945817168898091E-4</v>
+      </c>
+      <c r="E58">
+        <v>-0.22589384500541632</v>
+      </c>
+      <c r="F58">
+        <v>4.0775806255941169E-2</v>
+      </c>
+      <c r="G58">
+        <v>0.18525859380695159</v>
+      </c>
+      <c r="H58">
+        <v>-1.4055505747620457E-4</v>
+      </c>
+      <c r="I58">
+        <v>-0.26833536026275012</v>
+      </c>
+      <c r="J58">
+        <v>0.11364103419200915</v>
+      </c>
+      <c r="K58">
+        <v>0.15484887108154452</v>
+      </c>
+      <c r="L58">
+        <v>-1.5454501080319617E-4</v>
+      </c>
+      <c r="BE58" s="9">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BE43),_xlfn.MUNIT(4))</f>
+        <v>7.3115159242428565</v>
+      </c>
+      <c r="BI58">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4))</f>
+        <v>10.966120203190297</v>
+      </c>
+      <c r="BM58">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BM43),_xlfn.MUNIT(4))</f>
+        <v>11.408361794961703</v>
+      </c>
+      <c r="BP58" s="10"/>
+    </row>
+    <row r="59" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1.9497888391318225</v>
+      </c>
+      <c r="B59">
+        <v>-1.285126662594579</v>
+      </c>
+      <c r="C59">
+        <v>-0.66529362797792757</v>
+      </c>
+      <c r="D59">
+        <v>6.3145144068298142E-4</v>
+      </c>
+      <c r="E59">
+        <v>2.3144511409290853</v>
+      </c>
+      <c r="F59">
+        <v>-2.1191004087762546</v>
+      </c>
+      <c r="G59">
+        <v>-0.19594509484955433</v>
+      </c>
+      <c r="H59">
+        <v>5.9436269672237551E-4</v>
+      </c>
+      <c r="I59">
+        <v>2.494891909489779</v>
+      </c>
+      <c r="J59">
+        <v>-2.2412860713986618</v>
+      </c>
+      <c r="K59">
+        <v>-0.25430233231042498</v>
+      </c>
+      <c r="L59">
+        <v>6.9649421930582998E-4</v>
+      </c>
+      <c r="BE59" s="9"/>
+      <c r="BP59" s="10"/>
+    </row>
+    <row r="60" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="BE60" s="9"/>
+      <c r="BP60" s="10"/>
+    </row>
+    <row r="61" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))</f>
+        <v>4.6998461442465507</v>
+      </c>
+      <c r="E61">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E46),_xlfn.MUNIT(4))</f>
+        <v>5.0008761472810752</v>
+      </c>
+      <c r="I61">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I46),_xlfn.MUNIT(4))</f>
+        <v>5.1017685503914061</v>
+      </c>
+      <c r="BE61" s="9"/>
+      <c r="BP61" s="10"/>
+    </row>
+    <row r="62" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE62" s="9"/>
+      <c r="BP62" s="10"/>
+    </row>
+    <row r="63" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE63" s="9">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BE48),_xlfn.MUNIT(4))</f>
+        <v>7.5881551528877065</v>
+      </c>
+      <c r="BI63">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BI48),_xlfn.MUNIT(4))</f>
+        <v>11.408361794961705</v>
+      </c>
+      <c r="BM63">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4))</f>
+        <v>11.941742255531018</v>
+      </c>
+      <c r="BP63" s="10"/>
+    </row>
+    <row r="64" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE64" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP64" s="10"/>
+    </row>
+    <row r="65" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE65" s="9">
+        <f>BE53/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4))))</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="BI65">
+        <f>BI53/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4))))</f>
+        <v>0.94803365219272517</v>
+      </c>
+      <c r="BM65">
+        <f>BM53/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4))))</f>
+        <v>0.94285558947372838</v>
+      </c>
+      <c r="BP65" s="10"/>
+    </row>
+    <row r="66" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A51),_xlfn.MUNIT(4))</f>
+        <v>5.0008761472810752</v>
+      </c>
+      <c r="E66">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))</f>
+        <v>6.3305932194185948</v>
+      </c>
+      <c r="I66">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I51),_xlfn.MUNIT(4))</f>
+        <v>6.5334194267584671</v>
+      </c>
+      <c r="BE66" s="9"/>
+      <c r="BP66" s="10"/>
+    </row>
+    <row r="67" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE67" s="9"/>
+      <c r="BP67" s="10"/>
+    </row>
+    <row r="68" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE68" s="9"/>
+      <c r="BP68" s="10"/>
+    </row>
+    <row r="69" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE69" s="9"/>
+      <c r="BP69" s="10"/>
+    </row>
+    <row r="70" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE70" s="9">
+        <f>BE58/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4))))</f>
+        <v>0.94803365219272517</v>
+      </c>
+      <c r="BI70">
+        <f>BI58/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4))))</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="BM70">
+        <f>BM58/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4))))</f>
+        <v>0.99692603503181465</v>
+      </c>
+      <c r="BP70" s="10"/>
+    </row>
+    <row r="71" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A56),_xlfn.MUNIT(4))</f>
+        <v>5.1017685503914061</v>
+      </c>
+      <c r="E71">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E56),_xlfn.MUNIT(4))</f>
+        <v>6.5334194267584671</v>
+      </c>
+      <c r="I71">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4))</f>
+        <v>6.7915488108954891</v>
+      </c>
+      <c r="BE71" s="9"/>
+      <c r="BP71" s="10"/>
+    </row>
+    <row r="72" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE72" s="9"/>
+      <c r="BP72" s="10"/>
+    </row>
+    <row r="73" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <f>A61/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="E73">
+        <f>E61/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))))</f>
+        <v>0.91681576858937075</v>
+      </c>
+      <c r="I73">
+        <f>I61/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4))))</f>
+        <v>0.90301407305509662</v>
+      </c>
+      <c r="BE73" s="9"/>
+      <c r="BP73" s="10"/>
+    </row>
+    <row r="74" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE74" s="9"/>
+      <c r="BP74" s="10"/>
+    </row>
+    <row r="75" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BE75" s="11">
+        <f>BE63/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BE38),_xlfn.MUNIT(4))))</f>
+        <v>0.94285558947372849</v>
+      </c>
+      <c r="BF75" s="12"/>
+      <c r="BG75" s="12"/>
+      <c r="BH75" s="12"/>
+      <c r="BI75" s="12">
+        <f>BI63/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BI43),_xlfn.MUNIT(4))))</f>
+        <v>0.99692603503181476</v>
+      </c>
+      <c r="BJ75" s="12"/>
+      <c r="BK75" s="12"/>
+      <c r="BL75" s="12"/>
+      <c r="BM75" s="12">
+        <f>BM63/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(BM48),_xlfn.MUNIT(4))))</f>
+        <v>1</v>
+      </c>
+      <c r="BN75" s="12"/>
+      <c r="BO75" s="12"/>
+      <c r="BP75" s="13"/>
+    </row>
+    <row r="78" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <f>A66/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
+        <v>0.91681576858937075</v>
+      </c>
+      <c r="E78">
+        <f>E66/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))))</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="I78">
+        <f>I66/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4))))</f>
+        <v>0.99640046664270443</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <f>A71/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
+        <v>0.90301407305509662</v>
+      </c>
+      <c r="E83">
+        <f>E71/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))))</f>
+        <v>0.99640046664270443</v>
+      </c>
+      <c r="I83">
+        <f>I71/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>-1.4790127066301544</v>
+      </c>
+      <c r="B87">
+        <v>1.4697449029272016</v>
+      </c>
+      <c r="C87">
+        <v>-2.7681235223310521E-2</v>
+      </c>
+      <c r="E87">
+        <v>-1.5113087549245832</v>
+      </c>
+      <c r="F87">
+        <v>1.4421464342045536</v>
+      </c>
+      <c r="G87">
+        <v>-0.98956236245082141</v>
+      </c>
+      <c r="I87">
+        <v>-1.5034222115657745</v>
+      </c>
+      <c r="J87">
+        <v>1.45135521477833</v>
+      </c>
+      <c r="K87">
+        <v>-1.1698614761101329</v>
+      </c>
+      <c r="V87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>0.39523545574314989</v>
+      </c>
+      <c r="B88">
+        <v>-0.84996221012035955</v>
+      </c>
+      <c r="C88">
+        <v>0.76402554578205428</v>
+      </c>
+      <c r="E88">
+        <v>0.46804954686389366</v>
+      </c>
+      <c r="F88">
+        <v>-0.87563163449960701</v>
+      </c>
+      <c r="G88">
+        <v>0.99178638576260758</v>
+      </c>
+      <c r="I88">
+        <v>0.44852824483223336</v>
+      </c>
+      <c r="J88">
+        <v>-0.86770808655801979</v>
+      </c>
+      <c r="K88">
+        <v>0.98117866422162847</v>
+      </c>
+      <c r="V88" cm="1">
+        <f t="array" ref="V88">MAX(ABS(_xlfn.ANCHORARRAY(N18)))</f>
+        <v>2.9116248291487659</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1.172515630105323</v>
+      </c>
+      <c r="B89">
+        <v>-2.0975969093958317E-2</v>
+      </c>
+      <c r="C89">
+        <v>-1.8708735847514268</v>
+      </c>
+      <c r="E89">
+        <v>1.0375818884162384</v>
+      </c>
+      <c r="F89">
+        <v>8.3448945653838535E-2</v>
+      </c>
+      <c r="G89">
+        <v>-1.0352857951019003</v>
+      </c>
+      <c r="I89">
+        <v>1.0749988305005129</v>
+      </c>
+      <c r="J89">
+        <v>5.0108507022226793E-2</v>
+      </c>
+      <c r="K89">
+        <v>-0.74538955508466542</v>
+      </c>
+      <c r="V89" cm="1">
+        <f t="array" ref="V89">MAX(ABS(_xlfn.ANCHORARRAY(M93)))</f>
+        <v>0.99957362381448844</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>-1.7360166352499051</v>
+      </c>
+      <c r="B90">
+        <v>0.37170172402380985</v>
+      </c>
+      <c r="C90">
+        <v>1.0361747517526483</v>
+      </c>
+      <c r="E90">
+        <v>-1.7291626560648243</v>
+      </c>
+      <c r="F90">
+        <v>0.49033161602196723</v>
+      </c>
+      <c r="G90">
+        <v>0.21956841209993813</v>
+      </c>
+      <c r="I90">
+        <v>-1.9188711262721072</v>
+      </c>
+      <c r="J90">
+        <v>0.61761342366344885</v>
+      </c>
+      <c r="K90">
+        <v>0.10355428696626937</v>
+      </c>
+      <c r="M90" t="s">
+        <v>172</v>
+      </c>
+      <c r="V90">
+        <f>V88/V89</f>
+        <v>2.9128668061864911</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>176</v>
+      </c>
+      <c r="M91" t="s">
+        <v>155</v>
+      </c>
+      <c r="N91" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" t="s">
+        <v>182</v>
+      </c>
+      <c r="I92" t="s">
+        <v>186</v>
+      </c>
+      <c r="M92" t="s">
+        <v>173</v>
+      </c>
+      <c r="P92" t="s">
+        <v>174</v>
+      </c>
+      <c r="S92" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="15" cm="1">
+        <f t="array" ref="A93:C95">MMULT(MMULT(TRANSPOSE(A87:C90), $N$1:$Q$4), A87:C90)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="B93" s="15">
+        <v>-0.8141372497034659</v>
+      </c>
+      <c r="C93" s="15">
+        <v>-0.27808203787720759</v>
+      </c>
+      <c r="E93" s="15" cm="1">
+        <f t="array" ref="E93:G95">MMULT(MMULT(TRANSPOSE(E87:G90), $N$1:$Q$4),E87:G90)</f>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="F93" s="15">
+        <v>-0.83069770249394836</v>
+      </c>
+      <c r="G93" s="15">
+        <v>0.45759045975840906</v>
+      </c>
+      <c r="I93" s="15" cm="1">
+        <f t="array" ref="I93:K95">MMULT(MMULT(TRANSPOSE(I87:K90),$N$1:$Q$4),I87:K90)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="J93" s="15">
+        <v>-0.82765388007181118</v>
+      </c>
+      <c r="K93" s="15">
+        <v>0.57794062265914825</v>
+      </c>
+      <c r="M93" s="14" cm="1">
+        <f t="array" ref="M93:N95">MMULT(TRANSPOSE(A12:C15),MMULT(N1:Q4,MMULT(_xlfn.ANCHORARRAY(AK24),U7:V8)))</f>
+        <v>0.83058351765189253</v>
+      </c>
+      <c r="N93" s="14">
+        <v>0.55689334556477954</v>
+      </c>
+      <c r="P93" s="14" cm="1">
+        <f t="array" ref="P93:Q95">MMULT(TRANSPOSE(E12:G15),MMULT(N1:Q4,MMULT(_xlfn.ANCHORARRAY(AK24),U7:V8)))</f>
+        <v>0.87319005608168598</v>
+      </c>
+      <c r="Q93" s="14">
+        <v>0.48737649302153463</v>
+      </c>
+      <c r="S93" s="14" cm="1">
+        <f t="array" ref="S93:T95">MMULT(TRANSPOSE(I12:K15),MMULT(N1:Q4,MMULT(_xlfn.ANCHORARRAY(AK24),U7:V8)))</f>
+        <v>0.8621424413588834</v>
+      </c>
+      <c r="T93" s="14">
+        <v>0.50665295375324104</v>
+      </c>
+      <c r="V93">
+        <f>M93*$V$90</f>
+        <v>2.4193791583338093</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="15">
+        <v>-0.8141372497034659</v>
+      </c>
+      <c r="B94" s="15">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="C94" s="15">
+        <v>-0.33132158242198845</v>
+      </c>
+      <c r="E94" s="15">
+        <v>-0.83069770249394836</v>
+      </c>
+      <c r="F94" s="15">
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="G94" s="15">
+        <v>-0.87512793802886957</v>
+      </c>
+      <c r="I94" s="15">
+        <v>-0.82765388007181129</v>
+      </c>
+      <c r="J94" s="15">
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="K94" s="15">
+        <v>-0.9363482775816786</v>
+      </c>
+      <c r="M94" s="14">
+        <v>-0.99957362381448844</v>
+      </c>
+      <c r="N94" s="14">
+        <v>2.8889343555920287E-2</v>
+      </c>
+      <c r="P94" s="14">
+        <v>-0.99669182814505353</v>
+      </c>
+      <c r="Q94" s="14">
+        <v>8.1251955702036804E-2</v>
+      </c>
+      <c r="S94" s="14">
+        <v>-0.99791611683251613</v>
+      </c>
+      <c r="T94" s="14">
+        <v>6.4519571843513826E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="15">
+        <v>-0.27808203787720759</v>
+      </c>
+      <c r="B95" s="15">
+        <v>-0.33132158242198845</v>
+      </c>
+      <c r="C95" s="15">
+        <v>1</v>
+      </c>
+      <c r="E95" s="15">
+        <v>0.45759045975840906</v>
+      </c>
+      <c r="F95" s="15">
+        <v>-0.87512793802886957</v>
+      </c>
+      <c r="G95" s="15">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="I95" s="15">
+        <v>0.57794062265914825</v>
+      </c>
+      <c r="J95" s="15">
+        <v>-0.9363482775816786</v>
+      </c>
+      <c r="K95" s="15">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="M95" s="14">
+        <v>0.30394785201517671</v>
+      </c>
+      <c r="N95" s="14">
+        <v>-0.95267821763180971</v>
+      </c>
+      <c r="P95" s="14">
+        <v>0.83292110571316547</v>
+      </c>
+      <c r="Q95" s="14">
+        <v>-0.55339090675074554</v>
+      </c>
+      <c r="S95" s="14">
+        <v>0.91174561094205409</v>
+      </c>
+      <c r="T95" s="14">
+        <v>-0.41075344784035539</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>177</v>
+      </c>
+      <c r="M96" t="s">
+        <v>156</v>
+      </c>
+      <c r="N96" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>178</v>
+      </c>
+      <c r="E97" t="s">
+        <v>183</v>
+      </c>
+      <c r="I97" t="s">
+        <v>187</v>
+      </c>
+      <c r="M97" t="s">
+        <v>173</v>
+      </c>
+      <c r="P97" t="s">
+        <v>174</v>
+      </c>
+      <c r="S97" t="s">
+        <v>175</v>
+      </c>
+      <c r="V97" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A98" cm="1">
+        <f t="array" ref="A98:C100">MMULT(_xlfn.ANCHORARRAY(A93),_xlfn.ANCHORARRAY(A93))</f>
+        <v>1.7401490811446647</v>
+      </c>
+      <c r="B98">
+        <v>-1.5361399185743245</v>
+      </c>
+      <c r="C98">
+        <v>-0.28642283387397738</v>
+      </c>
+      <c r="E98" cm="1">
+        <f t="array" ref="E98:G100">MMULT(_xlfn.ANCHORARRAY(A93),_xlfn.ANCHORARRAY(E93))</f>
+        <v>1.5490542552806241</v>
+      </c>
+      <c r="F98">
+        <v>-1.4014775917870677</v>
+      </c>
+      <c r="G98">
+        <v>0.89198267448669055</v>
+      </c>
+      <c r="I98" cm="1">
+        <f t="array" ref="I98:K100">MMULT(_xlfn.ANCHORARRAY(A93),_xlfn.ANCHORARRAY(I93))</f>
+        <v>1.5131089475069888</v>
+      </c>
+      <c r="J98">
+        <v>-1.3814094925825509</v>
+      </c>
+      <c r="K98">
+        <v>1.0621745962568658</v>
+      </c>
+      <c r="M98" s="14" cm="1">
+        <f t="array" ref="M98:N100">MMULT(_xlfn.ANCHORARRAY(A93),MMULT(AL10:AM12,AA6:AB7))</f>
+        <v>-0.62507401797125761</v>
+      </c>
+      <c r="N98" s="14">
+        <v>-1.0679302473206969</v>
+      </c>
+      <c r="P98" s="14" cm="1">
+        <f t="array" ref="P98:Q100">MMULT(_xlfn.ANCHORARRAY(E93),MMULT(AL10:AM12,AA6:AB7))</f>
+        <v>-0.88378642101235305</v>
+      </c>
+      <c r="Q98" s="14">
+        <v>-0.41433448926761818</v>
+      </c>
+      <c r="S98" s="14" cm="1">
+        <f t="array" ref="S98:T100">MMULT(_xlfn.ANCHORARRAY(I93),MMULT(AL10:AM12,AA6:AB7))</f>
+        <v>-0.92359333430288082</v>
+      </c>
+      <c r="T98" s="14">
+        <v>-0.30719766301389029</v>
+      </c>
+      <c r="V98" cm="1">
+        <f t="array" ref="V98">M98/SUM(ABS(M98:M100))</f>
+        <v>-0.33649376690928745</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>-1.5361399185743245</v>
+      </c>
+      <c r="B99">
+        <v>1.7725934523333344</v>
+      </c>
+      <c r="C99">
+        <v>-0.4362462193346921</v>
+      </c>
+      <c r="E99">
+        <v>-1.7964445474257755</v>
+      </c>
+      <c r="F99">
+        <v>1.9662507160928278</v>
+      </c>
+      <c r="G99">
+        <v>-1.5789909588491138</v>
+      </c>
+      <c r="I99">
+        <v>-1.833275331420656</v>
+      </c>
+      <c r="J99">
+        <v>1.9840562466545315</v>
+      </c>
+      <c r="K99">
+        <v>-1.7381928490272949</v>
+      </c>
+      <c r="M99" s="14">
+        <v>0.8470203826738506</v>
+      </c>
+      <c r="N99" s="14">
+        <v>0.38600840180302703</v>
+      </c>
+      <c r="P99" s="14">
+        <v>1.038933540434521</v>
+      </c>
+      <c r="Q99" s="14">
+        <v>-8.4492786275673248E-2</v>
+      </c>
+      <c r="S99" s="14">
+        <v>1.058751961305457</v>
+      </c>
+      <c r="T99" s="14">
+        <v>-0.14133997045908686</v>
+      </c>
+      <c r="V99" cm="1">
+        <f t="array" ref="V99">M99/SUM(ABS(M99:M101))</f>
+        <v>0.68721784913291939</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>-0.28642283387397738</v>
+      </c>
+      <c r="B100">
+        <v>-0.4362462193346921</v>
+      </c>
+      <c r="C100">
+        <v>1.1871036107685513</v>
+      </c>
+      <c r="E100">
+        <v>0.45473649918580666</v>
+      </c>
+      <c r="F100">
+        <v>-0.97544741048142647</v>
+      </c>
+      <c r="G100">
+        <v>1.16270108568663</v>
+      </c>
+      <c r="I100">
+        <v>0.57407817802503169</v>
+      </c>
+      <c r="J100">
+        <v>-1.0375141823763196</v>
+      </c>
+      <c r="K100">
+        <v>1.149517486905387</v>
+      </c>
+      <c r="M100" s="14">
+        <v>-0.38551509896789987</v>
+      </c>
+      <c r="N100" s="14">
+        <v>1.0967515896960722</v>
+      </c>
+      <c r="P100" s="14">
+        <v>-0.89117885716105261</v>
+      </c>
+      <c r="Q100" s="14">
+        <v>0.49507758212071729</v>
+      </c>
+      <c r="S100" s="14">
+        <v>-0.96176694214482472</v>
+      </c>
+      <c r="T100" s="14">
+        <v>0.39767932104203829</v>
+      </c>
+      <c r="V100" t="e" cm="1">
+        <f t="array" ref="V100">M100/SUM(ABS(M100:M102))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="X101" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>179</v>
+      </c>
+      <c r="E102" t="s">
+        <v>184</v>
+      </c>
+      <c r="I102" t="s">
+        <v>188</v>
+      </c>
+      <c r="M102" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>171</v>
+      </c>
+      <c r="U102" t="s">
+        <v>131</v>
+      </c>
+      <c r="X102" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A103" cm="1">
+        <f t="array" ref="A103:C105">MMULT(_xlfn.ANCHORARRAY(E93),_xlfn.ANCHORARRAY(A93))</f>
+        <v>1.5490542552806241</v>
+      </c>
+      <c r="B103">
+        <v>-1.7964445474257755</v>
+      </c>
+      <c r="C103">
+        <v>0.45473649918580666</v>
+      </c>
+      <c r="E103" cm="1">
+        <f t="array" ref="E103:G105">MMULT(_xlfn.ANCHORARRAY(E93),_xlfn.ANCHORARRAY(E93))</f>
+        <v>1.8994477017906362</v>
+      </c>
+      <c r="F103">
+        <v>-2.0618456004979553</v>
+      </c>
+      <c r="G103">
+        <v>1.6421476870256662</v>
+      </c>
+      <c r="I103" cm="1">
+        <f t="array" ref="I103:K105">MMULT(_xlfn.ANCHORARRAY(E93),_xlfn.ANCHORARRAY(I93))</f>
+        <v>1.9519902918715164</v>
+      </c>
+      <c r="J103">
+        <v>-2.0868156213983542</v>
+      </c>
+      <c r="K103">
+        <v>1.8133534453388238</v>
+      </c>
+      <c r="M103" s="14">
+        <f t="shared" ref="M103:O105" si="14">$AC$152*A93+$AC$153*E93+$AC$154*I93</f>
+        <v>1</v>
+      </c>
+      <c r="N103" s="14">
+        <f t="shared" si="14"/>
+        <v>-0.82482658958326938</v>
+      </c>
+      <c r="O103" s="14">
+        <f t="shared" si="14"/>
+        <v>0.28918750798290105</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" ref="Q103:S105" si="15">$AC$140*A93+$AC$141*E93+$AC$142*I93</f>
+        <v>1</v>
+      </c>
+      <c r="R103">
+        <f t="shared" si="15"/>
+        <v>-0.82495938638675614</v>
+      </c>
+      <c r="S103">
+        <f t="shared" si="15"/>
+        <v>0.29595643853495757</v>
+      </c>
+      <c r="U103" s="16">
+        <f>AL3*$U$3</f>
+        <v>-0.85689933150314423</v>
+      </c>
+      <c r="V103" s="16">
+        <f>AM3*$U$4</f>
+        <v>0.51439163004024058</v>
+      </c>
+      <c r="X103" s="14">
+        <f>AL10*$AA$3</f>
+        <v>-0.82605298772576019</v>
+      </c>
+      <c r="Y103" s="14">
+        <f>AM10*$AA$4</f>
+        <v>-0.55783151928606856</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>-1.4014775917870677</v>
+      </c>
+      <c r="B104">
+        <v>1.9662507160928278</v>
+      </c>
+      <c r="C104">
+        <v>-0.97544741048142647</v>
+      </c>
+      <c r="E104">
+        <v>-2.0618456004979553</v>
+      </c>
+      <c r="F104">
+        <v>2.4559075808473851</v>
+      </c>
+      <c r="G104">
+        <v>-2.1303752196621986</v>
+      </c>
+      <c r="I104">
+        <v>-2.1641235679765813</v>
+      </c>
+      <c r="J104">
+        <v>2.5069547140727932</v>
+      </c>
+      <c r="K104">
+        <v>-2.2915701630314245</v>
+      </c>
+      <c r="M104" s="14">
+        <f t="shared" si="14"/>
+        <v>-0.82482658958326938</v>
+      </c>
+      <c r="N104" s="14">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="O104" s="14">
+        <f t="shared" si="14"/>
+        <v>-0.74061368614327683</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="15"/>
+        <v>-0.82495938638675614</v>
+      </c>
+      <c r="R104">
+        <f t="shared" si="15"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="S104">
+        <f t="shared" si="15"/>
+        <v>-0.74552285429814225</v>
+      </c>
+      <c r="U104" s="16">
+        <f>AL4*$U$3</f>
+        <v>0.99793844440566837</v>
+      </c>
+      <c r="V104" s="16">
+        <f>AM4*$U$4</f>
+        <v>6.0120060031654453E-2</v>
+      </c>
+      <c r="X104" s="14">
+        <f>AL11*$AA$3</f>
+        <v>0.9925747315282657</v>
+      </c>
+      <c r="Y104" s="14">
+        <f>AM11*$AA$4</f>
+        <v>2.622433481163558E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>0.89198267448669055</v>
+      </c>
+      <c r="B105">
+        <v>-1.5789909588491138</v>
+      </c>
+      <c r="C105">
+        <v>1.16270108568663</v>
+      </c>
+      <c r="E105">
+        <v>1.6421476870256662</v>
+      </c>
+      <c r="F105">
+        <v>-2.1303752196621986</v>
+      </c>
+      <c r="G105">
+        <v>1.9752379367805728</v>
+      </c>
+      <c r="I105">
+        <v>1.7598341158863948</v>
+      </c>
+      <c r="J105">
+        <v>-2.1902027351134392</v>
+      </c>
+      <c r="K105">
+        <v>2.0838846526725989</v>
+      </c>
+      <c r="M105" s="14">
+        <f t="shared" si="14"/>
+        <v>0.28918750798290105</v>
+      </c>
+      <c r="N105" s="14">
+        <f t="shared" si="14"/>
+        <v>-0.74061368614327683</v>
+      </c>
+      <c r="O105" s="14">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="Q105">
+        <f t="shared" si="15"/>
+        <v>0.29595643853495757</v>
+      </c>
+      <c r="R105">
+        <f t="shared" si="15"/>
+        <v>-0.74552285429814225</v>
+      </c>
+      <c r="S105">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="U105" s="16">
+        <f>AL5*$U$3</f>
+        <v>-0.70902671084060331</v>
+      </c>
+      <c r="V105" s="16">
+        <f>AM5*$U$4</f>
+        <v>-0.6168576236726484</v>
+      </c>
+      <c r="X105" s="14">
+        <f>AL12*$AA$3</f>
+        <v>-0.77567572077572222</v>
+      </c>
+      <c r="Y105" s="14">
+        <f>AM12*$AA$4</f>
+        <v>0.62761794935667969</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U106" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>180</v>
+      </c>
+      <c r="E107" t="s">
+        <v>185</v>
+      </c>
+      <c r="I107" t="s">
+        <v>189</v>
+      </c>
+      <c r="U107" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A108" cm="1">
+        <f t="array" ref="A108:C110">MMULT(_xlfn.ANCHORARRAY(I93),_xlfn.ANCHORARRAY(A93))</f>
+        <v>1.5131089475069888</v>
+      </c>
+      <c r="B108">
+        <v>-1.833275331420656</v>
+      </c>
+      <c r="C108">
+        <v>0.57407817802503169</v>
+      </c>
+      <c r="E108" cm="1">
+        <f t="array" ref="E108:G110">MMULT(_xlfn.ANCHORARRAY(I93),_xlfn.ANCHORARRAY(E93))</f>
+        <v>1.9519902918715164</v>
+      </c>
+      <c r="F108">
+        <v>-2.1641235679765813</v>
+      </c>
+      <c r="G108">
+        <v>1.7598341158863948</v>
+      </c>
+      <c r="I108" cm="1">
+        <f t="array" ref="I108:K110">MMULT(_xlfn.ANCHORARRAY(I93),_xlfn.ANCHORARRAY(I93))</f>
+        <v>2.0190263085175686</v>
+      </c>
+      <c r="J108">
+        <v>-2.1964614667149984</v>
+      </c>
+      <c r="K108">
+        <v>1.9308535303573302</v>
+      </c>
+      <c r="U108" s="14">
+        <f>$AC$152*M93+$AC$153*P93+$AC$154*S93</f>
+        <v>0.85692185000260301</v>
+      </c>
+      <c r="V108" s="14">
+        <f t="shared" ref="V108:V110" si="16">$AC$152*N93+$AC$153*Q93+$AC$154*T93</f>
+        <v>0.51437212436558544</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>-1.3814094925825509</v>
+      </c>
+      <c r="B109">
+        <v>1.9840562466545315</v>
+      </c>
+      <c r="C109">
+        <v>-1.0375141823763196</v>
+      </c>
+      <c r="E109">
+        <v>-2.0868156213983542</v>
+      </c>
+      <c r="F109">
+        <v>2.5069547140727932</v>
+      </c>
+      <c r="G109">
+        <v>-2.1902027351134392</v>
+      </c>
+      <c r="I109">
+        <v>-2.1964614667149993</v>
+      </c>
+      <c r="J109">
+        <v>2.5617590421281</v>
+      </c>
+      <c r="K109">
+        <v>-2.3510313539583199</v>
+      </c>
+      <c r="U109" s="14">
+        <f t="shared" ref="U109:U110" si="17">$AC$152*M94+$AC$153*P94+$AC$154*S94</f>
+        <v>-0.99796466927887573</v>
+      </c>
+      <c r="V109" s="14">
+        <f t="shared" si="16"/>
+        <v>6.0117780285517952E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1.0621745962568658</v>
+      </c>
+      <c r="B110">
+        <v>-1.7381928490272949</v>
+      </c>
+      <c r="C110">
+        <v>1.149517486905387</v>
+      </c>
+      <c r="E110">
+        <v>1.8133534453388238</v>
+      </c>
+      <c r="F110">
+        <v>-2.2915701630314245</v>
+      </c>
+      <c r="G110">
+        <v>2.0838846526725989</v>
+      </c>
+      <c r="I110">
+        <v>1.9308535303573304</v>
+      </c>
+      <c r="J110">
+        <v>-2.3510313539583199</v>
+      </c>
+      <c r="K110">
+        <v>2.2107634602498205</v>
+      </c>
+      <c r="U110" s="14">
+        <f t="shared" si="17"/>
+        <v>0.70904534338822844</v>
+      </c>
+      <c r="V110" s="14">
+        <f t="shared" si="16"/>
+        <v>-0.61683423249866121</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3))</f>
+        <v>4.6998461442465498</v>
+      </c>
+      <c r="E113">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E98),_xlfn.MUNIT(3))</f>
+        <v>4.6780060570600819</v>
+      </c>
+      <c r="I113">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I98),_xlfn.MUNIT(3))</f>
+        <v>4.646682681066908</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A103),_xlfn.MUNIT(3))</f>
+        <v>4.6780060570600819</v>
+      </c>
+      <c r="E118">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3))</f>
+        <v>6.3305932194185939</v>
+      </c>
+      <c r="I118">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I103),_xlfn.MUNIT(3))</f>
+        <v>6.5428296586169088</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A108),_xlfn.MUNIT(3))</f>
+        <v>4.646682681066908</v>
+      </c>
+      <c r="E123">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E108),_xlfn.MUNIT(3))</f>
+        <v>6.5428296586169088</v>
+      </c>
+      <c r="I123">
+        <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3))</f>
+        <v>6.7915488108954891</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <f>A113/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3))))</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="E126">
+        <f>E113/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3))))</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="I126">
+        <f>I113/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3))))</f>
+        <v>0.8224637814474921</v>
+      </c>
+    </row>
+    <row r="131" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <f>A118/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3))))</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="E131">
+        <f>E118/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3))))</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="I131">
+        <f>I118/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3))))</f>
+        <v>0.99783560478438982</v>
+      </c>
+    </row>
+    <row r="136" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <f>A123/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3))))</f>
+        <v>0.8224637814474921</v>
+      </c>
+      <c r="E136">
+        <f>E123/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E103),_xlfn.MUNIT(3))))</f>
+        <v>0.99783560478438982</v>
+      </c>
+      <c r="I136">
+        <f>I123/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I108),_xlfn.MUNIT(3))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC139" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT139" t="s">
+        <v>112</v>
+      </c>
+      <c r="CD139" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="140" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <f>A113</f>
+        <v>4.6998461442465498</v>
+      </c>
+      <c r="B140">
+        <f>E113</f>
+        <v>4.6780060570600819</v>
+      </c>
+      <c r="C140">
+        <f>I113</f>
+        <v>4.646682681066908</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140" cm="1">
+        <f t="array" ref="G140:G142">MMULT($A$140:$C$142,F140:F142)</f>
+        <v>14.024534882373539</v>
+      </c>
+      <c r="H140">
+        <f>G140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.48736897513065353</v>
+      </c>
+      <c r="I140" cm="1">
+        <f t="array" ref="I140:I142">MMULT($A$140:$C$142,H140:H142)</f>
+        <v>8.047367450037564</v>
+      </c>
+      <c r="J140">
+        <f t="shared" ref="J140" si="18">I140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.27965542240933233</v>
+      </c>
+      <c r="K140" cm="1">
+        <f t="array" ref="K140:K142">MMULT($A$140:$C$142,J140:J142)</f>
+        <v>4.6726852112206263</v>
+      </c>
+      <c r="L140">
+        <f t="shared" ref="L140" si="19">K140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.16238127122226101</v>
+      </c>
+      <c r="M140" cm="1">
+        <f t="array" ref="M140:M142">MMULT($A$140:$C$142,L140:L142)</f>
+        <v>2.715312989412932</v>
+      </c>
+      <c r="N140" cm="1">
+        <f t="array" ref="N140:N142">MMULT($A$140:$C$142,M140:M142)</f>
+        <v>45.407360153100647</v>
+      </c>
+      <c r="O140">
+        <f t="shared" ref="O140" si="20">N140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>1.5779588247891891</v>
+      </c>
+      <c r="P140" cm="1">
+        <f t="array" ref="P140:P142">MMULT($A$140:$C$142,O140:O142)</f>
+        <v>26.387818919345605</v>
+      </c>
+      <c r="Q140">
+        <f t="shared" ref="Q140" si="21">P140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.91700754217655622</v>
+      </c>
+      <c r="R140" cm="1">
+        <f t="array" ref="R140:R142">MMULT($A$140:$C$142,Q140:Q142)</f>
+        <v>15.334895929340741</v>
+      </c>
+      <c r="S140">
+        <f t="shared" ref="S140" si="22">R140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.53290555269759898</v>
+      </c>
+      <c r="T140" cm="1">
+        <f t="array" ref="T140:T142">MMULT($A$140:$C$142,S140:S142)</f>
+        <v>8.9116511418899975</v>
+      </c>
+      <c r="U140" cm="1">
+        <f t="array" ref="U140:U142">MMULT($A$140:$C$142,T140:T142)</f>
+        <v>149.02739472143</v>
+      </c>
+      <c r="V140">
+        <f t="shared" ref="V140" si="23">U140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>5.1788761082593879</v>
+      </c>
+      <c r="W140" cm="1">
+        <f t="array" ref="W140:W142">MMULT($A$140:$C$142,V140:V142)</f>
+        <v>86.60509727763332</v>
+      </c>
+      <c r="X140">
+        <f t="shared" ref="X140" si="24">W140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>3.0096283303013349</v>
+      </c>
+      <c r="Y140" cm="1">
+        <f t="array" ref="Y140:Y142">MMULT($A$140:$C$142,X140:X142)</f>
+        <v>50.329289380114972</v>
+      </c>
+      <c r="Z140">
+        <f t="shared" ref="Z140" si="25">Y140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>1.7490016168072302</v>
+      </c>
+      <c r="AA140">
+        <f>X140/SUM(X140:X142)</f>
+        <v>0.2794201365991264</v>
+      </c>
+      <c r="AC140">
+        <f>Z140/SUM($Z$140:$Z$142)</f>
+        <v>0.27942013659904996</v>
+      </c>
+      <c r="AD140">
+        <f>AC140</f>
+        <v>0.27942013659904996</v>
+      </c>
+      <c r="AE140">
+        <v>0</v>
+      </c>
+      <c r="AF140">
+        <v>0</v>
+      </c>
+      <c r="AH140" cm="1">
+        <f t="array" ref="AH140:AJ142">AC140*A93:C95</f>
+        <v>0.27942013659905002</v>
+      </c>
+      <c r="AI140">
+        <v>-0.22748634152251729</v>
+      </c>
+      <c r="AJ140">
+        <v>-7.7701721009391531E-2</v>
+      </c>
+      <c r="AL140" cm="1">
+        <f t="array" ref="AL140:AN142">AC141*E93:G95</f>
+        <v>0.35558086797551886</v>
+      </c>
+      <c r="AM140">
+        <v>-0.29538021007806753</v>
+      </c>
+      <c r="AN140">
+        <v>0.16271041285821186</v>
+      </c>
+      <c r="AP140" cm="1">
+        <f t="array" ref="AP140:AR142">AC142*I93:K95</f>
+        <v>0.36499899542543113</v>
+      </c>
+      <c r="AQ140">
+        <v>-0.30209283478617127</v>
+      </c>
+      <c r="AR140">
+        <v>0.21094774668613725</v>
+      </c>
+      <c r="AT140">
+        <f>AH140+AL140+AP140</f>
+        <v>1</v>
+      </c>
+      <c r="AU140">
+        <f t="shared" ref="AU140:AU142" si="26">AI140+AM140+AQ140</f>
+        <v>-0.82495938638675614</v>
+      </c>
+      <c r="AV140">
+        <f t="shared" ref="AV140:AV142" si="27">AJ140+AN140+AR140</f>
+        <v>0.29595643853495757</v>
+      </c>
+      <c r="AY140">
+        <v>1</v>
+      </c>
+      <c r="AZ140" cm="1">
+        <f t="array" ref="AZ140:AZ142">MMULT($AT$140:$AV$142,AY140:AY142)</f>
+        <v>0.47099705214820142</v>
+      </c>
+      <c r="BA140">
+        <f>AZ140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>0.51078831173026362</v>
+      </c>
+      <c r="BB140" cm="1">
+        <f t="array" ref="BB140:BB142">MMULT($AT$140:$AV$142,BA140:BA142)</f>
+        <v>1.1978398093026457</v>
+      </c>
+      <c r="BC140">
+        <f t="shared" ref="BC140" si="28">BB140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>1.2990369496505474</v>
+      </c>
+      <c r="BD140" cm="1">
+        <f t="array" ref="BD140:BD142">MMULT($AT$140:$AV$142,BC140:BC142)</f>
+        <v>3.0158281988966844</v>
+      </c>
+      <c r="BE140">
+        <f t="shared" ref="BE140" si="29">BD140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>3.2706145126748045</v>
+      </c>
+      <c r="BF140" cm="1">
+        <f t="array" ref="BF140:BF142">MMULT($AT$140:$AV$142,BE140:BE142)</f>
+        <v>7.4747387202002393</v>
+      </c>
+      <c r="BG140">
+        <f t="shared" ref="BG140" si="30">BF140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>8.1062273194749377</v>
+      </c>
+      <c r="BJ140">
+        <f>BG140/SUM(BG$140:BG$142)</f>
+        <v>1.3507123343135214</v>
+      </c>
+    </row>
+    <row r="141" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <f>A118</f>
+        <v>4.6780060570600819</v>
+      </c>
+      <c r="B141">
+        <f>E118</f>
+        <v>6.3305932194185939</v>
+      </c>
+      <c r="C141">
+        <f>I118</f>
+        <v>6.5428296586169088</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>17.551428935095586</v>
+      </c>
+      <c r="H141">
+        <f t="shared" ref="H141:L142" si="31">G141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.60993266471367891</v>
+      </c>
+      <c r="I141">
+        <v>10.229522033857513</v>
+      </c>
+      <c r="J141">
+        <f t="shared" si="31"/>
+        <v>0.35548784409125522</v>
+      </c>
+      <c r="K141">
+        <v>5.9458741523964278</v>
+      </c>
+      <c r="L141">
+        <f t="shared" si="31"/>
+        <v>0.20662607467655678</v>
+      </c>
+      <c r="M141">
+        <v>3.4554014613298891</v>
+      </c>
+      <c r="N141">
+        <v>57.783893731253237</v>
+      </c>
+      <c r="O141">
+        <f t="shared" ref="O141" si="32">N141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>2.0080578288734863</v>
+      </c>
+      <c r="P141">
+        <v>33.580269040208748</v>
+      </c>
+      <c r="Q141">
+        <f t="shared" ref="Q141" si="33">P141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>1.1669535884079416</v>
+      </c>
+      <c r="R141">
+        <v>19.514683744217756</v>
+      </c>
+      <c r="S141">
+        <f t="shared" ref="S141" si="34">R141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.67815806343579765</v>
+      </c>
+      <c r="T141">
+        <v>11.340673891351836</v>
+      </c>
+      <c r="U141">
+        <v>189.64735688647738</v>
+      </c>
+      <c r="V141">
+        <f t="shared" ref="V141" si="35">U141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>6.5904672587870552</v>
+      </c>
+      <c r="W141">
+        <v>110.21079595728307</v>
+      </c>
+      <c r="X141">
+        <f t="shared" ref="X141" si="36">W141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>3.8299539431816134</v>
+      </c>
+      <c r="Y141">
+        <v>64.047396942089932</v>
+      </c>
+      <c r="Z141">
+        <f t="shared" ref="Z141" si="37">Y141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>2.2257218844871729</v>
+      </c>
+      <c r="AC141">
+        <f>Z141/SUM($Z$140:$Z$142)</f>
+        <v>0.35558086797551891</v>
+      </c>
+      <c r="AD141">
+        <v>0</v>
+      </c>
+      <c r="AE141">
+        <f>AC141</f>
+        <v>0.35558086797551891</v>
+      </c>
+      <c r="AF141">
+        <v>0</v>
+      </c>
+      <c r="AH141">
+        <v>-0.22748634152251729</v>
+      </c>
+      <c r="AI141">
+        <v>0.27942013659905002</v>
+      </c>
+      <c r="AJ141">
+        <v>-9.2577921818565403E-2</v>
+      </c>
+      <c r="AL141">
+        <v>-0.29538021007806753</v>
+      </c>
+      <c r="AM141">
+        <v>0.35558086797551886</v>
+      </c>
+      <c r="AN141">
+        <v>-0.31117875179393156</v>
+      </c>
+      <c r="AP141">
+        <v>-0.30209283478617133</v>
+      </c>
+      <c r="AQ141">
+        <v>0.36499899542543102</v>
+      </c>
+      <c r="AR141">
+        <v>-0.34176618068564535</v>
+      </c>
+      <c r="AT141">
+        <f t="shared" ref="AT141:AT142" si="38">AH141+AL141+AP141</f>
+        <v>-0.82495938638675614</v>
+      </c>
+      <c r="AU141">
+        <f t="shared" si="26"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="AV141">
+        <f t="shared" si="27"/>
+        <v>-0.74552285429814225</v>
+      </c>
+      <c r="AY141">
+        <v>1</v>
+      </c>
+      <c r="AZ141">
+        <v>-0.5704822406848985</v>
+      </c>
+      <c r="BA141">
+        <f t="shared" ref="BA141" si="39">AZ141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>-0.61867831075054847</v>
+      </c>
+      <c r="BB141">
+        <v>-1.4850872662922221</v>
+      </c>
+      <c r="BC141">
+        <f t="shared" ref="BC141" si="40">BB141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>-1.6105519430784687</v>
+      </c>
+      <c r="BD141">
+        <v>-3.6599690693111007</v>
+      </c>
+      <c r="BE141">
+        <f t="shared" ref="BE141" si="41">BD141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>-3.9691743576139498</v>
+      </c>
+      <c r="BF141">
+        <v>-9.0092814972132356</v>
+      </c>
+      <c r="BG141">
+        <f t="shared" ref="BG141" si="42">BF141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>-9.7704129248271006</v>
+      </c>
+      <c r="BJ141">
+        <f>BG141/SUM(BG$140:BG$142)</f>
+        <v>-1.6280097669102895</v>
+      </c>
+    </row>
+    <row r="142" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <f>A123</f>
+        <v>4.646682681066908</v>
+      </c>
+      <c r="B142">
+        <f>E123</f>
+        <v>6.5428296586169088</v>
+      </c>
+      <c r="C142">
+        <f>I123</f>
+        <v>6.7915488108954891</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>17.981061150579304</v>
+      </c>
+      <c r="H142">
+        <f t="shared" si="31"/>
+        <v>0.6248628862361465</v>
+      </c>
+      <c r="I142">
+        <v>10.499121296466662</v>
+      </c>
+      <c r="J142">
+        <f t="shared" si="31"/>
+        <v>0.36485673349941239</v>
+      </c>
+      <c r="K142">
+        <v>6.1033087321190891</v>
+      </c>
+      <c r="L142">
+        <f t="shared" si="31"/>
+        <v>0.21209711028758396</v>
+      </c>
+      <c r="M142">
+        <v>3.5469213275234863</v>
+      </c>
+      <c r="N142">
+        <v>59.314390329480474</v>
+      </c>
+      <c r="O142">
+        <f t="shared" ref="O142" si="43">N142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>2.0612443740798057</v>
+      </c>
+      <c r="P142">
+        <v>34.469696039302661</v>
+      </c>
+      <c r="Q142">
+        <f t="shared" ref="Q142" si="44">P142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>1.1978622159408763</v>
+      </c>
+      <c r="R142">
+        <v>20.031561321394342</v>
+      </c>
+      <c r="S142">
+        <f t="shared" ref="S142" si="45">R142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>0.69612016322515868</v>
+      </c>
+      <c r="T142">
+        <v>11.641049759834466</v>
+      </c>
+      <c r="U142">
+        <v>194.67047015974859</v>
+      </c>
+      <c r="V142">
+        <f t="shared" ref="V142" si="46">U142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>6.7650263146482388</v>
+      </c>
+      <c r="W142">
+        <v>113.12990498750165</v>
+      </c>
+      <c r="X142">
+        <f t="shared" ref="X142" si="47">W142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>3.9313963930228795</v>
+      </c>
+      <c r="Y142">
+        <v>65.74379458763832</v>
+      </c>
+      <c r="Z142">
+        <f t="shared" ref="Z142" si="48">Y142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <v>2.2846736849468146</v>
+      </c>
+      <c r="AC142">
+        <f>Z142/SUM($Z$140:$Z$142)</f>
+        <v>0.36499899542543107</v>
+      </c>
+      <c r="AD142">
+        <v>0</v>
+      </c>
+      <c r="AE142">
+        <v>0</v>
+      </c>
+      <c r="AF142">
+        <f>AC142</f>
+        <v>0.36499899542543107</v>
+      </c>
+      <c r="AH142">
+        <v>-7.7701721009391531E-2</v>
+      </c>
+      <c r="AI142">
+        <v>-9.2577921818565403E-2</v>
+      </c>
+      <c r="AJ142">
+        <v>0.27942013659904996</v>
+      </c>
+      <c r="AL142">
+        <v>0.16271041285821186</v>
+      </c>
+      <c r="AM142">
+        <v>-0.31117875179393156</v>
+      </c>
+      <c r="AN142">
+        <v>0.35558086797551886</v>
+      </c>
+      <c r="AP142">
+        <v>0.21094774668613725</v>
+      </c>
+      <c r="AQ142">
+        <v>-0.34176618068564535</v>
+      </c>
+      <c r="AR142">
+        <v>0.36499899542543113</v>
+      </c>
+      <c r="AT142">
+        <f t="shared" si="38"/>
+        <v>0.29595643853495757</v>
+      </c>
+      <c r="AU142">
+        <f t="shared" si="26"/>
+        <v>-0.74552285429814225</v>
+      </c>
+      <c r="AV142">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="AY142">
+        <v>1</v>
+      </c>
+      <c r="AZ142">
+        <v>0.55043358423681532</v>
+      </c>
+      <c r="BA142">
+        <f>AZ142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>0.59693588299464351</v>
+      </c>
+      <c r="BB142">
+        <v>1.209345792702718</v>
+      </c>
+      <c r="BC142">
+        <f t="shared" ref="BC142" si="49">BB142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>1.3115149934279213</v>
+      </c>
+      <c r="BD142">
+        <v>2.8966766241710911</v>
+      </c>
+      <c r="BE142">
+        <f t="shared" ref="BE142" si="50">BD142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>3.1413966515087903</v>
+      </c>
+      <c r="BF142">
+        <v>7.0684662707961188</v>
+      </c>
+      <c r="BG142">
+        <f t="shared" ref="BG142" si="51">BF142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <v>7.6656317412496344</v>
+      </c>
+      <c r="BJ142">
+        <f>BG142/SUM(BG$140:BG$142)</f>
+        <v>1.2772974325967681</v>
+      </c>
+    </row>
+    <row r="143" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="G143">
+        <f>G140*G140+G141*G141+G142*G142</f>
+        <v>828.05879643149513</v>
+      </c>
+      <c r="AZ143">
+        <f>AZ140*AZ140+AZ141*AZ141+AZ142*AZ142</f>
+        <v>0.85026534072494531</v>
+      </c>
+    </row>
+    <row r="144" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="G144">
+        <f>SQRT(G143)</f>
+        <v>28.776010780361741</v>
+      </c>
+      <c r="H144">
+        <f>H140/SUM(H140:H142)</f>
+        <v>0.28299791788178902</v>
+      </c>
+      <c r="J144">
+        <f>J140/SUM(J140:J142)</f>
+        <v>0.27965542240933233</v>
+      </c>
+      <c r="L144">
+        <f>L140/SUM(L140:L142)</f>
+        <v>0.27943559801264667</v>
+      </c>
+      <c r="N144">
+        <f>N140/SUM(N140:N142)</f>
+        <v>0.27942020335829693</v>
+      </c>
+      <c r="P144">
+        <f>P140/SUM(P140:P142)</f>
+        <v>0.2794201409857836</v>
+      </c>
+      <c r="R144">
+        <f>R140/SUM(R140:R142)</f>
+        <v>0.2794201368872965</v>
+      </c>
+      <c r="T144">
+        <f>T140/SUM(T140:T142)</f>
+        <v>0.27942013661798559</v>
+      </c>
+      <c r="V144">
+        <f>V140/SUM(V140:V142)</f>
+        <v>0.2794201366002893</v>
+      </c>
+      <c r="X144">
+        <f>X140/SUM(X140:X142)</f>
+        <v>0.2794201365991264</v>
+      </c>
+      <c r="Z144">
+        <f>Z140/SUM(Z140:Z142)</f>
+        <v>0.27942013659904996</v>
+      </c>
+      <c r="AZ144">
+        <f>SQRT(AZ143)</f>
+        <v>0.92209833571314148</v>
+      </c>
+      <c r="BA144">
+        <f>BA140/SUM(BA140:BA142)</f>
+        <v>1.0444588707693632</v>
+      </c>
+      <c r="BC144">
+        <f>BC140/SUM(BC140:BC142)</f>
+        <v>1.2990369496505474</v>
+      </c>
+      <c r="BE144">
+        <f>BE140/SUM(BE140:BE142)</f>
+        <v>1.3388591918539032</v>
+      </c>
+      <c r="BG144">
+        <f>BG140/SUM(BG140:BG142)</f>
+        <v>1.3507123343135214</v>
+      </c>
+      <c r="BJ144">
+        <f>SUMPRODUCT(BJ140:BJ142,MMULT($AT$140:$AV$142,BJ140:BJ142))</f>
+        <v>13.856218420732336</v>
+      </c>
+    </row>
+    <row r="145" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>116</v>
+      </c>
+      <c r="AT145" cm="1">
+        <f t="array" ref="AT145:AV147">AT140:AV142 - BJ144 * MMULT(BJ140:BJ142, TRANSPOSE(BJ140:BJ142))</f>
+        <v>-24.279614804268633</v>
+      </c>
+      <c r="AU145">
+        <v>29.644489036911985</v>
+      </c>
+      <c r="AV145">
+        <v>-23.609642308320534</v>
+      </c>
+      <c r="AY145">
+        <v>1</v>
+      </c>
+      <c r="AZ145" cm="1">
+        <f t="array" ref="AZ145:AZ147">MMULT($AT$145:$AV$147,AY145:AY147)</f>
+        <v>-18.244768075677182</v>
+      </c>
+      <c r="BA145">
+        <f>AZ145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>-0.5475227901041696</v>
+      </c>
+      <c r="BB145" cm="1">
+        <f t="array" ref="BB145:BB147">MMULT($AT$145:$AV$147,BA145:BA147)</f>
+        <v>45.004167137490029</v>
+      </c>
+      <c r="BC145">
+        <f t="shared" ref="BC145" si="52">BB145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>1.3505683961136534</v>
+      </c>
+      <c r="BD145" cm="1">
+        <f t="array" ref="BD145:BD147">MMULT($AT$145:$AV$147,BC145:BC147)</f>
+        <v>-111.21054372594716</v>
+      </c>
+      <c r="BE145">
+        <f t="shared" ref="BE145" si="53">BD145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>-3.337411960364002</v>
+      </c>
+      <c r="BF145" cm="1">
+        <f t="array" ref="BF145:BF147">MMULT($AT$145:$AV$147,BE145:BE147)</f>
+        <v>274.8073218656919</v>
+      </c>
+      <c r="BG145">
+        <f t="shared" ref="BG145" si="54">BF145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>8.2469270634109453</v>
+      </c>
+      <c r="BJ145">
+        <f>BG145/SUM(BG$145:BG$147)</f>
+        <v>1.3506116231039265</v>
+      </c>
+    </row>
+    <row r="146" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <f>A126</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="B146">
+        <f>E126</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="C146">
+        <f>I126</f>
+        <v>0.8224637814474921</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146" cm="1">
+        <f t="array" ref="G146:G148">MMULT($A$146:$C$148,F146:F148)</f>
+        <v>2.6800874442532763</v>
+      </c>
+      <c r="H146">
+        <f>G146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.55533951862419872</v>
+      </c>
+      <c r="I146" cm="1">
+        <f t="array" ref="I146:I148">MMULT($A$146:$C$148,H146:H148)</f>
+        <v>1.5434186437477948</v>
+      </c>
+      <c r="J146">
+        <f t="shared" ref="J146" si="55">I146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.31981097053097252</v>
+      </c>
+      <c r="K146" cm="1">
+        <f t="array" ref="K146:K148">MMULT($A$146:$C$148,J146:J148)</f>
+        <v>0.89127067879257527</v>
+      </c>
+      <c r="L146">
+        <f t="shared" ref="L146" si="56">K146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.18467973154601167</v>
+      </c>
+      <c r="M146" cm="1">
+        <f t="array" ref="M146:M148">MMULT($A$146:$C$148,L146:L148)</f>
+        <v>0.51478564613098365</v>
+      </c>
+      <c r="N146">
+        <f t="shared" ref="N146" si="57">M146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.10666846469133749</v>
+      </c>
+      <c r="O146" cm="1">
+        <f t="array" ref="O146:O148">MMULT($A$146:$C$148,N146:N148)</f>
+        <v>0.29733783140494713</v>
+      </c>
+      <c r="P146">
+        <f t="shared" ref="P146" si="58">O146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>6.1611216647146763E-2</v>
+      </c>
+      <c r="Q146" cm="1">
+        <f t="array" ref="Q146:Q148">MMULT($A$146:$C$148,P146:P148)</f>
+        <v>0.17174117845826059</v>
+      </c>
+      <c r="R146">
+        <f t="shared" ref="R146" si="59">Q146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>3.5586399830896655E-2</v>
+      </c>
+      <c r="S146" cm="1">
+        <f t="array" ref="S146:S148">MMULT($A$146:$C$148,R146:R148)</f>
+        <v>9.9197047927088791E-2</v>
+      </c>
+      <c r="T146">
+        <f t="shared" ref="T146" si="60">S146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>2.0554568457418237E-2</v>
+      </c>
+      <c r="U146" cm="1">
+        <f t="array" ref="U146:U148">MMULT($A$146:$C$148,T146:T148)</f>
+        <v>5.7295835950954645E-2</v>
+      </c>
+      <c r="V146">
+        <f t="shared" ref="V146" si="61">U146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>1.1872240222758661E-2</v>
+      </c>
+      <c r="W146" cm="1">
+        <f t="array" ref="W146:W148">MMULT($A$146:$C$148,V146:V148)</f>
+        <v>3.3093855993569496E-2</v>
+      </c>
+      <c r="X146">
+        <f t="shared" ref="X146" si="62">W146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>6.8573606045186303E-3</v>
+      </c>
+      <c r="Y146" cm="1">
+        <f t="array" ref="Y146:Y148">MMULT($A$146:$C$148,X146:X148)</f>
+        <v>1.9114884814763054E-2</v>
+      </c>
+      <c r="Z146">
+        <f t="shared" ref="Z146:Z148" si="63">Y146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>3.9607852924161335E-3</v>
+      </c>
+      <c r="AA146">
+        <f>X146/SUM(X146:X148)</f>
+        <v>0.3197339918327633</v>
+      </c>
+      <c r="AC146">
+        <f>Z146/SUM($Z$146:$Z$148)</f>
+        <v>0.31973399183170131</v>
+      </c>
+      <c r="AD146">
+        <f>AC146</f>
+        <v>0.31973399183170131</v>
+      </c>
+      <c r="AE146">
+        <v>0</v>
+      </c>
+      <c r="AF146">
+        <v>0</v>
+      </c>
+      <c r="AT146">
+        <v>29.644489036911985</v>
+      </c>
+      <c r="AU146">
+        <v>-35.724740246568054</v>
+      </c>
+      <c r="AV146">
+        <v>28.067827890365692</v>
+      </c>
+      <c r="AY146">
+        <v>1</v>
+      </c>
+      <c r="AZ146">
+        <v>21.987576680709623</v>
+      </c>
+      <c r="BA146">
+        <f>AZ146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>0.65984392248322254</v>
+      </c>
+      <c r="BB146">
+        <v>-54.247807541274952</v>
+      </c>
+      <c r="BC146">
+        <f t="shared" ref="BC146" si="64">BB146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>-1.6279686767643629</v>
+      </c>
+      <c r="BD146">
+        <v>134.04951934355591</v>
+      </c>
+      <c r="BE146">
+        <f t="shared" ref="BE146" si="65">BD146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>4.0228062389542005</v>
+      </c>
+      <c r="BF146">
+        <v>-331.24374548012474</v>
+      </c>
+      <c r="BG146">
+        <f t="shared" ref="BG146" si="66">BF146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>-9.9405757846610356</v>
+      </c>
+      <c r="BJ146">
+        <f t="shared" ref="BJ146:BJ147" si="67">BG146/SUM(BG$145:BG$147)</f>
+        <v>-1.627983016204301</v>
+      </c>
+    </row>
+    <row r="147" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <f>A131</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="B147">
+        <f>E131</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="C147">
+        <f>I131</f>
+        <v>0.99783560478438982</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>2.8554592675901738</v>
+      </c>
+      <c r="H147">
+        <f>G147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.59167822248290647</v>
+      </c>
+      <c r="I147">
+        <v>1.6510784394907587</v>
+      </c>
+      <c r="J147">
+        <f t="shared" ref="J147" si="68">I147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.34211910054041522</v>
+      </c>
+      <c r="K147">
+        <v>0.95373476848455829</v>
+      </c>
+      <c r="L147">
+        <f t="shared" ref="L147" si="69">K147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.1976228829253539</v>
+      </c>
+      <c r="M147">
+        <v>0.55087700032616083</v>
+      </c>
+      <c r="N147">
+        <f t="shared" ref="N147" si="70">M147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.11414693533162271</v>
+      </c>
+      <c r="O147">
+        <v>0.318184602702002</v>
+      </c>
+      <c r="P147">
+        <f t="shared" ref="P147" si="71">O147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>6.5930865232419256E-2</v>
+      </c>
+      <c r="Q147">
+        <v>0.18378221783365095</v>
+      </c>
+      <c r="R147">
+        <f t="shared" ref="R147" si="72">Q147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>3.8081417306838526E-2</v>
+      </c>
+      <c r="S147">
+        <v>0.10615190732987274</v>
+      </c>
+      <c r="T147">
+        <f t="shared" ref="T147" si="73">S147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>2.1995681239436862E-2</v>
+      </c>
+      <c r="U147">
+        <v>6.1312936223166664E-2</v>
+      </c>
+      <c r="V147">
+        <f t="shared" ref="V147" si="74">U147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>1.2704621470698473E-2</v>
+      </c>
+      <c r="W147">
+        <v>3.5414117768907474E-2</v>
+      </c>
+      <c r="X147">
+        <f t="shared" ref="X147" si="75">W147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>7.3381408343433071E-3</v>
+      </c>
+      <c r="Y147">
+        <v>2.0455059153692355E-2</v>
+      </c>
+      <c r="Z147">
+        <f t="shared" si="63"/>
+        <v>4.2384821167676476E-3</v>
+      </c>
+      <c r="AC147">
+        <f>Z147/SUM($Z$146:$Z$148)</f>
+        <v>0.34215103986985285</v>
+      </c>
+      <c r="AD147">
+        <v>0</v>
+      </c>
+      <c r="AE147">
+        <f>AC147</f>
+        <v>0.34215103986985285</v>
+      </c>
+      <c r="AF147">
+        <v>0</v>
+      </c>
+      <c r="AT147">
+        <v>-23.609642308320534</v>
+      </c>
+      <c r="AU147">
+        <v>28.067827890365692</v>
+      </c>
+      <c r="AV147">
+        <v>-21.606264212109792</v>
+      </c>
+      <c r="AY147">
+        <v>1</v>
+      </c>
+      <c r="AZ147">
+        <v>-17.148078630064635</v>
+      </c>
+      <c r="BA147">
+        <f>AZ147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>-0.51461130212860706</v>
+      </c>
+      <c r="BB147">
+        <v>42.56603064110454</v>
+      </c>
+      <c r="BC147">
+        <f t="shared" ref="BC147" si="76">BB147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>1.2774002806507092</v>
+      </c>
+      <c r="BD147">
+        <v>-105.17982934385645</v>
+      </c>
+      <c r="BE147">
+        <f t="shared" ref="BE147" si="77">BD147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>-3.1564311141779871</v>
+      </c>
+      <c r="BF147">
+        <v>259.90522039121441</v>
+      </c>
+      <c r="BG147">
+        <f t="shared" ref="BG147" si="78">BF147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <v>7.7997172033635183</v>
+      </c>
+      <c r="BJ147">
+        <f t="shared" si="67"/>
+        <v>1.2773713931003745</v>
+      </c>
+    </row>
+    <row r="148" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <f>A136</f>
+        <v>0.8224637814474921</v>
+      </c>
+      <c r="B148">
+        <f>E136</f>
+        <v>0.99783560478438982</v>
+      </c>
+      <c r="C148">
+        <f>I136</f>
+        <v>1</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>2.8202993862318819</v>
+      </c>
+      <c r="H148">
+        <f>G148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.58439276184233468</v>
+      </c>
+      <c r="I148">
+        <v>1.6315369992862068</v>
+      </c>
+      <c r="J148">
+        <f t="shared" ref="J148" si="79">I148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.33806992892861243</v>
+      </c>
+      <c r="K148">
+        <v>0.94248148869594528</v>
+      </c>
+      <c r="L148">
+        <f t="shared" ref="L148" si="80">K148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.19529109670167979</v>
+      </c>
+      <c r="M148">
+        <v>0.54437863596877545</v>
+      </c>
+      <c r="N148">
+        <f t="shared" ref="N148" si="81">M148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>0.11280041264938219</v>
+      </c>
+      <c r="O148">
+        <v>0.31443123773153231</v>
+      </c>
+      <c r="P148">
+        <f t="shared" ref="P148" si="82">O148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>6.5153132438516947E-2</v>
+      </c>
+      <c r="Q148">
+        <v>0.18161429144485913</v>
+      </c>
+      <c r="R148">
+        <f t="shared" ref="R148" si="83">Q148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>3.7632202412844727E-2</v>
+      </c>
+      <c r="S148">
+        <v>0.10489972145528234</v>
+      </c>
+      <c r="T148">
+        <f t="shared" ref="T148" si="84">S148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>2.1736216458795421E-2</v>
+      </c>
+      <c r="U148">
+        <v>6.0589678450503101E-2</v>
+      </c>
+      <c r="V148">
+        <f t="shared" ref="V148" si="85">U148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>1.2554755605622529E-2</v>
+      </c>
+      <c r="W148">
+        <v>3.4996366842256793E-2</v>
+      </c>
+      <c r="X148">
+        <f t="shared" ref="X148" si="86">W148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <v>7.2515788831620312E-3</v>
+      </c>
+      <c r="Y148">
+        <v>2.0213767814133466E-2</v>
+      </c>
+      <c r="Z148">
+        <f t="shared" si="63"/>
+        <v>4.1884842644042313E-3</v>
+      </c>
+      <c r="AC148">
+        <f>Z148/SUM($Z$146:$Z$148)</f>
+        <v>0.33811496829844595</v>
+      </c>
+      <c r="AD148">
+        <v>0</v>
+      </c>
+      <c r="AE148">
+        <v>0</v>
+      </c>
+      <c r="AF148">
+        <f>AC148</f>
+        <v>0.33811496829844595</v>
+      </c>
+      <c r="AZ148">
+        <f>AZ145*AZ145+AZ146*AZ146+AZ147*AZ147</f>
+        <v>1110.3816911282142</v>
+      </c>
+    </row>
+    <row r="149" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="G149">
+        <f>G146*G146+G147*G147+G148*G148</f>
+        <v>23.290604965690598</v>
+      </c>
+      <c r="AZ149">
+        <f>SQRT(AZ148)</f>
+        <v>33.322390237319624</v>
+      </c>
+      <c r="BA149">
+        <f>BA145/SUM(BA145:BA147)</f>
+        <v>1.3610145891584429</v>
+      </c>
+      <c r="BC149">
+        <f>BC145/SUM(BC145:BC147)</f>
+        <v>1.3505683961136536</v>
+      </c>
+      <c r="BE149">
+        <f>BE145/SUM(BE145:BE147)</f>
+        <v>1.3506119829128844</v>
+      </c>
+      <c r="BG149">
+        <f>BG145/SUM(BG145:BG147)</f>
+        <v>1.3506116231039265</v>
+      </c>
+      <c r="BJ149" cm="1">
+        <f t="array" ref="BJ149">MMULT(MMULT(TRANSPOSE(BJ145:BJ147),$AT$140:$AV$142),BJ145:BJ147)</f>
+        <v>13.855829650878038</v>
+      </c>
+    </row>
+    <row r="150" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="G150">
+        <f>SQRT(G149)</f>
+        <v>4.8260340825247594</v>
+      </c>
+      <c r="H150">
+        <f>H146/SUM(H146:H148)</f>
+        <v>0.32074399322297265</v>
+      </c>
+      <c r="J150">
+        <f>J146/SUM(J146:J148)</f>
+        <v>0.31981097053097246</v>
+      </c>
+      <c r="L150">
+        <f>L146/SUM(L146:L148)</f>
+        <v>0.31973985861262633</v>
+      </c>
+      <c r="N150">
+        <f>N146/SUM(N146:N148)</f>
+        <v>0.31973443895508913</v>
+      </c>
+      <c r="P150">
+        <f>P146/SUM(P146:P148)</f>
+        <v>0.31973402590811012</v>
+      </c>
+      <c r="R150">
+        <f>R146/SUM(R146:R148)</f>
+        <v>0.31973399442867606</v>
+      </c>
+      <c r="T150">
+        <f>T146/SUM(T146:T148)</f>
+        <v>0.31973399202954284</v>
+      </c>
+      <c r="V150">
+        <f>V146/SUM(V146:V148)</f>
+        <v>0.31973399184669837</v>
+      </c>
+      <c r="X150">
+        <f>X146/SUM(X146:X148)</f>
+        <v>0.3197339918327633</v>
+      </c>
+      <c r="Z150">
+        <f>Z146/SUM(Z146:Z148)</f>
+        <v>0.31973399183170131</v>
+      </c>
+    </row>
+    <row r="151" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC151" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="152" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <f>A61</f>
+        <v>4.6998461442465507</v>
+      </c>
+      <c r="B152">
+        <f>E61</f>
+        <v>5.0008761472810752</v>
+      </c>
+      <c r="C152">
+        <f>I61</f>
+        <v>5.1017685503914061</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152" cm="1">
+        <f t="array" ref="G152:G154">MMULT($A$152:$C$154,F152:F154)</f>
+        <v>14.802490841919031</v>
+      </c>
+      <c r="H152">
+        <f>G152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.49961318616579287</v>
+      </c>
+      <c r="I152" cm="1">
+        <f t="array" ref="I152:I154">MMULT($A$152:$C$154,H152:H154)</f>
+        <v>8.5364959841015722</v>
+      </c>
+      <c r="J152">
+        <f>I152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.28812353291451615</v>
+      </c>
+      <c r="K152" cm="1">
+        <f t="array" ref="K152:K154">MMULT($A$152:$C$154,J152:J154)</f>
+        <v>4.9506211888317004</v>
+      </c>
+      <c r="L152">
+        <f>K152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.1670932042496325</v>
+      </c>
+      <c r="M152" cm="1">
+        <f t="array" ref="M152:M154">MMULT($A$152:$C$154,L152:L154)</f>
+        <v>2.8716226760032302</v>
+      </c>
+      <c r="N152">
+        <f>M152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>9.6922914524696036E-2</v>
+      </c>
+      <c r="O152" cm="1">
+        <f t="array" ref="O152:O154">MMULT($A$152:$C$154,N152:N154)</f>
+        <v>1.6657054041678983</v>
+      </c>
+      <c r="P152">
+        <f>O152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>5.6220834255352514E-2</v>
+      </c>
+      <c r="Q152" cm="1">
+        <f t="array" ref="Q152:Q154">MMULT($A$152:$C$154,P152:P154)</f>
+        <v>0.96620466078466793</v>
+      </c>
+      <c r="R152">
+        <f>Q152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>3.2611308070924966E-2</v>
+      </c>
+      <c r="S152" cm="1">
+        <f t="array" ref="S152:S154">MMULT($A$152:$C$154,R152:R154)</f>
+        <v>0.56045411924309341</v>
+      </c>
+      <c r="T152">
+        <f>S152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>1.8916429079748304E-2</v>
+      </c>
+      <c r="U152" cm="1">
+        <f t="array" ref="U152:U154">MMULT($A$152:$C$154,T152:T154)</f>
+        <v>0.32509553372089289</v>
+      </c>
+      <c r="V152">
+        <f>U152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>1.0972613808387092E-2</v>
+      </c>
+      <c r="W152" cm="1">
+        <f t="array" ref="W152:W154">MMULT($A$152:$C$154,V152:V154)</f>
+        <v>0.18857405524875154</v>
+      </c>
+      <c r="X152">
+        <f>W152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>6.3647453376041987E-3</v>
+      </c>
+      <c r="Y152" cm="1">
+        <f t="array" ref="Y152:Y154">MMULT($A$152:$C$154,X152:X154)</f>
+        <v>0.10938376761430459</v>
+      </c>
+      <c r="Z152">
+        <f>Y152/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>3.6919173425758712E-3</v>
+      </c>
+      <c r="AA152">
+        <f>X152/SUM(X152:X154)</f>
+        <v>0.2880644803920136</v>
+      </c>
+      <c r="AC152">
+        <f>Z152/SUM($Z$152:$Z$154)</f>
+        <v>0.28806448039200921</v>
+      </c>
+      <c r="AD152">
+        <f>AC152</f>
+        <v>0.28806448039200921</v>
+      </c>
+      <c r="AE152">
+        <v>0</v>
+      </c>
+      <c r="AF152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <f>A66</f>
+        <v>5.0008761472810752</v>
+      </c>
+      <c r="B153">
+        <f>E66</f>
+        <v>6.3305932194185948</v>
+      </c>
+      <c r="C153">
+        <f>I66</f>
+        <v>6.5334194267584671</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>17.864888793458135</v>
+      </c>
+      <c r="H153">
+        <f>G153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.60297514154314169</v>
+      </c>
+      <c r="I153">
+        <v>10.379079848418346</v>
+      </c>
+      <c r="J153">
+        <f>I153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.35031436316465236</v>
+      </c>
+      <c r="K153">
+        <v>6.0208047090736745</v>
+      </c>
+      <c r="L153">
+        <f>K153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.20321400338001047</v>
+      </c>
+      <c r="M153">
+        <v>3.4924191902466948</v>
+      </c>
+      <c r="N153">
+        <f>M153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.11787601814449099</v>
+      </c>
+      <c r="O153">
+        <v>2.0258035847967659</v>
+      </c>
+      <c r="P153">
+        <f>O153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>6.8374856255961292E-2</v>
+      </c>
+      <c r="Q153">
+        <v>1.1750822712165907</v>
+      </c>
+      <c r="R153">
+        <f>Q153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>3.9661338338199972E-2</v>
+      </c>
+      <c r="S153">
+        <v>0.681615113622145</v>
+      </c>
+      <c r="T153">
+        <f>S153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>2.3005850994424249E-2</v>
+      </c>
+      <c r="U153">
+        <v>0.39537585959396954</v>
+      </c>
+      <c r="V153">
+        <f>U153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>1.3344713065816249E-2</v>
+      </c>
+      <c r="W153">
+        <v>0.22934067514796652</v>
+      </c>
+      <c r="X153">
+        <f>W153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>7.7406989574759283E-3</v>
+      </c>
+      <c r="Y153">
+        <v>0.13303074530481829</v>
+      </c>
+      <c r="Z153">
+        <f>Y153/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>4.4900493592289099E-3</v>
+      </c>
+      <c r="AC153">
+        <f>Z153/SUM($Z$152:$Z$154)</f>
+        <v>0.35033929949751286</v>
+      </c>
+      <c r="AD153">
+        <v>0</v>
+      </c>
+      <c r="AE153">
+        <f>AC153</f>
+        <v>0.35033929949751286</v>
+      </c>
+      <c r="AF153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <f>A71</f>
+        <v>5.1017685503914061</v>
+      </c>
+      <c r="B154">
+        <f>E71</f>
+        <v>6.5334194267584671</v>
+      </c>
+      <c r="C154">
+        <f>I71</f>
+        <v>6.7915488108954891</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>18.426736788045361</v>
+      </c>
+      <c r="H154">
+        <f>G154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.62193861665786043</v>
+      </c>
+      <c r="I154">
+        <v>10.712326816564564</v>
+      </c>
+      <c r="J154">
+        <f>I154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.3615621039208316</v>
+      </c>
+      <c r="K154">
+        <v>6.2142569215717973</v>
+      </c>
+      <c r="L154">
+        <f>K154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.20974339612135257</v>
+      </c>
+      <c r="M154">
+        <v>3.6046356844183771</v>
+      </c>
+      <c r="N154">
+        <f>M154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>0.12166354558106943</v>
+      </c>
+      <c r="O154">
+        <v>2.0908956523489608</v>
+      </c>
+      <c r="P154">
+        <f>O154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>7.0571841588441653E-2</v>
+      </c>
+      <c r="Q154">
+        <v>1.2128394050679261</v>
+      </c>
+      <c r="R154">
+        <f>Q154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>4.093571588353398E-2</v>
+      </c>
+      <c r="S154">
+        <v>0.70351641682537724</v>
+      </c>
+      <c r="T154">
+        <f>S154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>2.3745063062947398E-2</v>
+      </c>
+      <c r="U154">
+        <v>0.40807987159065012</v>
+      </c>
+      <c r="V154">
+        <f>U154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>1.3773498462715519E-2</v>
+      </c>
+      <c r="W154">
+        <v>0.23670973073826759</v>
+      </c>
+      <c r="X154">
+        <f>W154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>7.9894190804485465E-3</v>
+      </c>
+      <c r="Y154">
+        <v>0.13730522019566774</v>
+      </c>
+      <c r="Z154">
+        <f>Y154/SQRT(SUMSQ($G$152:$G$154))</f>
+        <v>4.6343212957705108E-3</v>
+      </c>
+      <c r="AC154">
+        <f>Z154/SUM($Z$152:$Z$154)</f>
+        <v>0.36159622011047787</v>
+      </c>
+      <c r="AD154">
+        <v>0</v>
+      </c>
+      <c r="AE154">
+        <v>0</v>
+      </c>
+      <c r="AF154">
+        <f>AC154</f>
+        <v>0.36159622011047787</v>
+      </c>
+    </row>
+    <row r="155" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="G155">
+        <f>G152*G152+G153*G153+G154*G154</f>
+        <v>877.81261538362708</v>
+      </c>
+    </row>
+    <row r="156" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="G156">
+        <f>SQRT(G155)</f>
+        <v>29.627902649084479</v>
+      </c>
+      <c r="H156">
+        <f>H152/SUM(H152:H154)</f>
+        <v>0.28971028130223786</v>
+      </c>
+      <c r="J156">
+        <f>J152/SUM(J152:J154)</f>
+        <v>0.28812353291451609</v>
+      </c>
+      <c r="L156">
+        <f>L152/SUM(L152:L154)</f>
+        <v>0.28806659827452286</v>
+      </c>
+      <c r="N156">
+        <f>N152/SUM(N152:N154)</f>
+        <v>0.28806455634736788</v>
+      </c>
+      <c r="P156">
+        <f>P152/SUM(P152:P154)</f>
+        <v>0.28806448311605698</v>
+      </c>
+      <c r="R156">
+        <f>R152/SUM(R152:R154)</f>
+        <v>0.28806448048970379</v>
+      </c>
+      <c r="T156">
+        <f>T152/SUM(T152:T154)</f>
+        <v>0.28806448039551286</v>
+      </c>
+      <c r="V156">
+        <f>V152/SUM(V152:V154)</f>
+        <v>0.28806448039213473</v>
+      </c>
+      <c r="X156">
+        <f>X152/SUM(X152:X154)</f>
+        <v>0.2880644803920136</v>
+      </c>
+      <c r="Z156">
+        <f>Z152/SUM(Z152:Z154)</f>
+        <v>0.28806448039200921</v>
+      </c>
+    </row>
+    <row r="157" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="158" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <f>A73</f>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="B158">
+        <f>E73</f>
+        <v>0.91681576858937075</v>
+      </c>
+      <c r="C158">
+        <f>I73</f>
+        <v>0.90301407305509662</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158" cm="1">
+        <f t="array" ref="G158:G160">MMULT($A$158:$C$160,F158:F160)</f>
+        <v>2.8198298416444674</v>
+      </c>
+      <c r="H158">
+        <f>G158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.56572387095022025</v>
+      </c>
+      <c r="I158" cm="1">
+        <f t="array" ref="I158:I160">MMULT($A$158:$C$160,H158:H160)</f>
+        <v>1.6268400743660727</v>
+      </c>
+      <c r="J158">
+        <f>I158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.32638219891686582</v>
+      </c>
+      <c r="K158" cm="1">
+        <f t="array" ref="K158:K160">MMULT($A$158:$C$160,J158:J160)</f>
+        <v>0.93932791073583277</v>
+      </c>
+      <c r="L158">
+        <f>K158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.18845116606155088</v>
+      </c>
+      <c r="M158" cm="1">
+        <f t="array" ref="M158:M160">MMULT($A$158:$C$160,L158:L160)</f>
+        <v>0.54238049816872891</v>
+      </c>
+      <c r="N158">
+        <f>M158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.10881422361747214</v>
+      </c>
+      <c r="O158" cm="1">
+        <f t="array" ref="O158:O160">MMULT($A$158:$C$160,N158:N160)</f>
+        <v>0.31317818449536355</v>
+      </c>
+      <c r="P158">
+        <f>O158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>6.2830874478069912E-2</v>
+      </c>
+      <c r="Q158" cm="1">
+        <f t="array" ref="Q158:Q160">MMULT($A$158:$C$160,P158:P160)</f>
+        <v>0.18083353135150149</v>
+      </c>
+      <c r="R158">
+        <f>Q158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>3.627943922109466E-2</v>
+      </c>
+      <c r="S158" cm="1">
+        <f t="array" ref="S158:S160">MMULT($A$158:$C$160,R158:R160)</f>
+        <v>0.10441584936873764</v>
+      </c>
+      <c r="T158">
+        <f>S158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>2.0948263480674648E-2</v>
+      </c>
+      <c r="U158" cm="1">
+        <f t="array" ref="U158:U160">MMULT($A$158:$C$160,T158:T160)</f>
+        <v>6.0291194442583136E-2</v>
+      </c>
+      <c r="V158">
+        <f>U158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>1.2095824861680074E-2</v>
+      </c>
+      <c r="W158" cm="1">
+        <f t="array" ref="W158:W160">MMULT($A$158:$C$160,V158:V160)</f>
+        <v>3.4812991986408776E-2</v>
+      </c>
+      <c r="X158">
+        <f>W158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>6.9843010720195492E-3</v>
+      </c>
+      <c r="Y158" cm="1">
+        <f t="array" ref="Y158:Y160">MMULT($A$158:$C$160,X158:X160)</f>
+        <v>2.0101516021549849E-2</v>
+      </c>
+      <c r="Z158">
+        <f>Y158/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>4.0328346369464564E-3</v>
+      </c>
+      <c r="AA158">
+        <f>X158/SUM(X158:X160)</f>
+        <v>0.32637048307042116</v>
+      </c>
+      <c r="AC158">
+        <f>Z158/SUM($Z$158:$Z$160)</f>
+        <v>0.32637048307041888</v>
+      </c>
+      <c r="AD158">
+        <f>AC158</f>
+        <v>0.32637048307041888</v>
+      </c>
+      <c r="AE158">
+        <v>0</v>
+      </c>
+      <c r="AF158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <f>A78</f>
+        <v>0.91681576858937075</v>
+      </c>
+      <c r="B159">
+        <f>E78</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="C159">
+        <f>I78</f>
+        <v>0.99640046664270443</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>2.913216235232075</v>
+      </c>
+      <c r="H159">
+        <f>G159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.58445936743097671</v>
+      </c>
+      <c r="I159">
+        <v>1.6827205431456838</v>
+      </c>
+      <c r="J159">
+        <f>I159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.33759312896719768</v>
+      </c>
+      <c r="K159">
+        <v>0.97164061562083359</v>
+      </c>
+      <c r="L159">
+        <f>K159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.19493385101595725</v>
+      </c>
+      <c r="M159">
+        <v>0.56103942245631278</v>
+      </c>
+      <c r="N159">
+        <f>M159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.11255764058534957</v>
+      </c>
+      <c r="O159">
+        <v>0.32395213885289953</v>
+      </c>
+      <c r="P159">
+        <f>O159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>6.4992381911806313E-2</v>
+      </c>
+      <c r="Q159">
+        <v>0.18705456625098638</v>
+      </c>
+      <c r="R159">
+        <f>Q159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>3.7527524439811465E-2</v>
+      </c>
+      <c r="S159">
+        <v>0.10800796329205062</v>
+      </c>
+      <c r="T159">
+        <f>S159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>2.166892561552378E-2</v>
+      </c>
+      <c r="U159">
+        <v>6.2365332041023236E-2</v>
+      </c>
+      <c r="V159">
+        <f>U159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>1.2511945413971496E-2</v>
+      </c>
+      <c r="W159">
+        <v>3.601062849471344E-2</v>
+      </c>
+      <c r="X159">
+        <f>W159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>7.2245749890706206E-3</v>
+      </c>
+      <c r="Y159">
+        <v>2.079304835146522E-2</v>
+      </c>
+      <c r="Z159">
+        <f>Y159/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>4.1715722092599689E-3</v>
+      </c>
+      <c r="AC159">
+        <f>Z159/SUM($Z$158:$Z$160)</f>
+        <v>0.33759828003515202</v>
+      </c>
+      <c r="AD159">
+        <v>0</v>
+      </c>
+      <c r="AE159">
+        <f>AC159</f>
+        <v>0.33759828003515202</v>
+      </c>
+      <c r="AF159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <f>A83</f>
+        <v>0.90301407305509662</v>
+      </c>
+      <c r="B160">
+        <f>E83</f>
+        <v>0.99640046664270443</v>
+      </c>
+      <c r="C160">
+        <f>I83</f>
+        <v>1</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>2.8994145396978013</v>
+      </c>
+      <c r="H160">
+        <f>G160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.58169042424581907</v>
+      </c>
+      <c r="I160">
+        <v>1.6749026276189984</v>
+      </c>
+      <c r="J160">
+        <f>I160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.3360246721159364</v>
+      </c>
+      <c r="K160">
+        <v>0.96713034217082061</v>
+      </c>
+      <c r="L160">
+        <f>K160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.19402898458837972</v>
+      </c>
+      <c r="M160">
+        <v>0.55843521974236232</v>
+      </c>
+      <c r="N160">
+        <f>M160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>0.1120351765634723</v>
+      </c>
+      <c r="O160">
+        <v>0.32244843744205803</v>
+      </c>
+      <c r="P160">
+        <f>O160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>6.4690704211141065E-2</v>
+      </c>
+      <c r="Q160">
+        <v>0.18618630775234118</v>
+      </c>
+      <c r="R160">
+        <f>Q160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>3.7353331461361196E-2</v>
+      </c>
+      <c r="S160">
+        <v>0.10750661850433035</v>
+      </c>
+      <c r="T160">
+        <f>S160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>2.1568344115959103E-2</v>
+      </c>
+      <c r="U160">
+        <v>6.2075848440028406E-2</v>
+      </c>
+      <c r="V160">
+        <f>U160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>1.2453868227570809E-2</v>
+      </c>
+      <c r="W160">
+        <v>3.5843476551966881E-2</v>
+      </c>
+      <c r="X160">
+        <f>W160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>7.1910403967732767E-3</v>
+      </c>
+      <c r="Y160">
+        <v>2.0696532445665904E-2</v>
+      </c>
+      <c r="Z160">
+        <f>Y160/SQRT(SUMSQ($G$158:$G$160))</f>
+        <v>4.1522088593759863E-3</v>
+      </c>
+      <c r="AC160">
+        <f>Z160/SUM($Z$158:$Z$160)</f>
+        <v>0.3360312368944291</v>
+      </c>
+      <c r="AD160">
+        <v>0</v>
+      </c>
+      <c r="AE160">
+        <v>0</v>
+      </c>
+      <c r="AF160">
+        <f>AC160</f>
+        <v>0.3360312368944291</v>
+      </c>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G161">
+        <f>G158*G158+G159*G159+G160*G160</f>
+        <v>24.844873842059421</v>
+      </c>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G162">
+        <f>SQRT(G161)</f>
+        <v>4.9844632451307556</v>
+      </c>
+      <c r="H162">
+        <f>H158/SUM(H158:H160)</f>
+        <v>0.32665423763768908</v>
+      </c>
+      <c r="J162">
+        <f>J158/SUM(J158:J160)</f>
+        <v>0.32638219891686587</v>
+      </c>
+      <c r="L162">
+        <f>L158/SUM(L158:L160)</f>
+        <v>0.32637096696279178</v>
+      </c>
+      <c r="N162">
+        <f>N158/SUM(N158:N160)</f>
+        <v>0.32637050305649329</v>
+      </c>
+      <c r="P162">
+        <f>P158/SUM(P158:P160)</f>
+        <v>0.32637048389589829</v>
+      </c>
+      <c r="R162">
+        <f>R158/SUM(R158:R160)</f>
+        <v>0.32637048310451328</v>
+      </c>
+      <c r="T162">
+        <f>T158/SUM(T158:T160)</f>
+        <v>0.32637048307182698</v>
+      </c>
+      <c r="V162">
+        <f>V158/SUM(V158:V160)</f>
+        <v>0.32637048307047689</v>
+      </c>
+      <c r="X162">
+        <f>X158/SUM(X158:X160)</f>
+        <v>0.32637048307042116</v>
+      </c>
+      <c r="Z162">
+        <f>Z158/SUM(Z158:Z160)</f>
+        <v>0.32637048307041888</v>
+      </c>
+    </row>
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>194</v>
+      </c>
+      <c r="B165" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>196</v>
+      </c>
+      <c r="B166">
+        <v>17.1859</v>
+      </c>
+      <c r="D166" cm="1">
+        <f t="array" ref="D166:D168">B166*AC152:AC154</f>
+        <v>4.950647353569031</v>
+      </c>
+      <c r="F166" cm="1">
+        <f t="array" ref="F166:F168">B166*AC140:AC142</f>
+        <v>4.8020865255776126</v>
+      </c>
+    </row>
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>197</v>
+      </c>
+      <c r="B167">
+        <v>295.73480000000001</v>
+      </c>
+      <c r="D167">
+        <v>6.020896167234306</v>
+      </c>
+      <c r="F167">
+        <v>6.1109772389404702</v>
+      </c>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>198</v>
+      </c>
+      <c r="B168">
+        <v>0.38030000000000003</v>
+      </c>
+      <c r="D168">
+        <v>6.2143564791966615</v>
+      </c>
+      <c r="F168">
+        <v>6.2728362354819156</v>
+      </c>
+    </row>
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>199</v>
+      </c>
+      <c r="B169">
+        <v>1.2999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>200</v>
+      </c>
+      <c r="B170" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>202</v>
+      </c>
+      <c r="B171">
+        <v>27.883299999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3384,7 +11450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3902,6 +11968,9 @@
       <c r="A38" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
@@ -4906,7 +12975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6685,9 +14754,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AE23"/>
+  <dimension ref="A1:AE47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
@@ -7969,6 +16038,780 @@
         <v>1</v>
       </c>
     </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$40:$E$43, '4. STATIS Intra-struktur'!$B$40:$E$43)</f>
+        <v>128.0577808279188</v>
+      </c>
+      <c r="C27">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$40:$E$43))</f>
+        <v>11.316261786823368</v>
+      </c>
+      <c r="D27">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$40:$E$43))</f>
+        <v>11.316261786823368</v>
+      </c>
+      <c r="E27">
+        <f>C27*D27</f>
+        <v>128.0577808279188</v>
+      </c>
+      <c r="F27" s="2">
+        <f>B27/E27</f>
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <f>F27</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="2">
+        <f>F28</f>
+        <v>0.89853521856455254</v>
+      </c>
+      <c r="J27" s="2">
+        <f>F29</f>
+        <v>0.88524677360514281</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$40:$E$43, '4. STATIS Intra-struktur'!$B$46:$E$49)</f>
+        <v>99.391202772007063</v>
+      </c>
+      <c r="C28">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$40:$E$43))</f>
+        <v>11.316261786823368</v>
+      </c>
+      <c r="D28">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$46:$E$49))</f>
+        <v>9.7748444775049972</v>
+      </c>
+      <c r="E28">
+        <f>C28*D28</f>
+        <v>110.61469903293123</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" ref="F28" si="34">B28/E28</f>
+        <v>0.89853521856455254</v>
+      </c>
+      <c r="H28" s="2">
+        <f>F30</f>
+        <v>0.89853521856455254</v>
+      </c>
+      <c r="I28" s="2">
+        <f>F31</f>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <f>F32</f>
+        <v>0.99412581136965816</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$40:$E$43, '4. STATIS Intra-struktur'!$B$52:$E$55)</f>
+        <v>107.52627206827904</v>
+      </c>
+      <c r="C29">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$40:$E$43))</f>
+        <v>11.316261786823368</v>
+      </c>
+      <c r="D29">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$52:$E$55))</f>
+        <v>10.733645574619008</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ref="E29:E35" si="35">C29*D29</f>
+        <v>121.46474324936683</v>
+      </c>
+      <c r="F29" s="2">
+        <f>B29/E29</f>
+        <v>0.88524677360514281</v>
+      </c>
+      <c r="H29" s="2">
+        <f>F33</f>
+        <v>0.88524677360514281</v>
+      </c>
+      <c r="I29" s="2">
+        <f>F34</f>
+        <v>0.99412581136965816</v>
+      </c>
+      <c r="J29" s="2">
+        <f>F35</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$46:$E$49, '4. STATIS Intra-struktur'!$B$40:$E$43)</f>
+        <v>99.391202772007063</v>
+      </c>
+      <c r="C30">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$46:$E$49))</f>
+        <v>9.7748444775049972</v>
+      </c>
+      <c r="D30">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$40:$E$43))</f>
+        <v>11.316261786823368</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="35"/>
+        <v>110.61469903293123</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" ref="F30:F35" si="36">B30/E30</f>
+        <v>0.89853521856455254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$46:$E$49, '4. STATIS Intra-struktur'!$B$46:$E$49)</f>
+        <v>95.547584559409941</v>
+      </c>
+      <c r="C31">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$46:$E$49))</f>
+        <v>9.7748444775049972</v>
+      </c>
+      <c r="D31">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$46:$E$49))</f>
+        <v>9.7748444775049972</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="35"/>
+        <v>95.547584559409941</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$46:$E$49, '4. STATIS Intra-struktur'!$B$52:$E$55)</f>
+        <v>104.30339796474451</v>
+      </c>
+      <c r="C32">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$46:$E$49))</f>
+        <v>9.7748444775049972</v>
+      </c>
+      <c r="D32">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$52:$E$55))</f>
+        <v>10.733645574619008</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="35"/>
+        <v>104.91971616856056</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="36"/>
+        <v>0.99412581136965816</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$52:$E$55, '4. STATIS Intra-struktur'!$B$40:$E$43)</f>
+        <v>107.52627206827904</v>
+      </c>
+      <c r="C33">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$52:$E$55))</f>
+        <v>10.733645574619008</v>
+      </c>
+      <c r="D33">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$40:$E$43))</f>
+        <v>11.316261786823368</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="35"/>
+        <v>121.46474324936683</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="36"/>
+        <v>0.88524677360514281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$52:$E$55, '4. STATIS Intra-struktur'!$B$46:$E$49)</f>
+        <v>104.30339796474451</v>
+      </c>
+      <c r="C34">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$52:$E$55))</f>
+        <v>10.733645574619008</v>
+      </c>
+      <c r="D34">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$46:$E$49))</f>
+        <v>9.7748444775049972</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="35"/>
+        <v>104.91971616856056</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="36"/>
+        <v>0.99412581136965816</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$52:$E$55, '4. STATIS Intra-struktur'!$B$52:$E$55)</f>
+        <v>115.21114732153822</v>
+      </c>
+      <c r="C35">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$52:$E$55))</f>
+        <v>10.733645574619008</v>
+      </c>
+      <c r="D35">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$52:$E$55))</f>
+        <v>10.733645574619008</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="35"/>
+        <v>115.21114732153821</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M37">
+        <f t="shared" ref="M37:U37" si="37">SQRT(M38)</f>
+        <v>4.8260340825247594</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="37"/>
+        <v>0.55533951862419872</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="37"/>
+        <v>0.20720947736797704</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="37"/>
+        <v>4.2935767511110189E-2</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="37"/>
+        <v>8.896697946370111E-3</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="37"/>
+        <v>1.8434801317681053E-3</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="37"/>
+        <v>3.8198655464191856E-4</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="37"/>
+        <v>7.9151234348946148E-5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M38">
+        <f t="shared" ref="M38:U38" si="38">SUMSQ(_xlfn.ANCHORARRAY(M39))</f>
+        <v>23.290604965690598</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="38"/>
+        <v>0.30840198094575677</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="38"/>
+        <v>1</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="38"/>
+        <v>4.2935767511110189E-2</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="38"/>
+        <v>1.8434801317681051E-3</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="38"/>
+        <v>7.9151234348946148E-5</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="38"/>
+        <v>3.3984189962237508E-6</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="38"/>
+        <v>1.4591372792720343E-7</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="38"/>
+        <v>6.2649178989617929E-9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$59:$D$61, '4. STATIS Intra-struktur'!$B$59:$D$61)</f>
+        <v>4.6998461442465498</v>
+      </c>
+      <c r="C39">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$59:$D$61))</f>
+        <v>2.1679128543939559</v>
+      </c>
+      <c r="D39">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$59:$D$61))</f>
+        <v>2.1679128543939559</v>
+      </c>
+      <c r="E39">
+        <f>C39*D39</f>
+        <v>4.6998461442465489</v>
+      </c>
+      <c r="F39" s="2">
+        <f>B39/E39</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="H39" s="2">
+        <f>F39</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="I39" s="2">
+        <f>F40</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="J39" s="2">
+        <f>F41</f>
+        <v>0.8224637814474921</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" cm="1">
+        <f t="array" ref="M39:M41">MMULT(H39:J41,L39:L41)</f>
+        <v>2.6800874442532763</v>
+      </c>
+      <c r="N39">
+        <f t="shared" ref="N39:O41" si="39">M39/M$37</f>
+        <v>0.55533951862419872</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="39"/>
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <f t="shared" ref="P39:U41" si="40">O39/$M$37</f>
+        <v>0.20720947736797704</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="40"/>
+        <v>4.2935767511110189E-2</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="40"/>
+        <v>8.896697946370111E-3</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="40"/>
+        <v>1.8434801317681053E-3</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="40"/>
+        <v>3.8198655464191856E-4</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="40"/>
+        <v>7.9151234348946148E-5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$59:$D$61, '4. STATIS Intra-struktur'!$B$64:$D$66)</f>
+        <v>4.6780060570600819</v>
+      </c>
+      <c r="C40">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$59:$D$61))</f>
+        <v>2.1679128543939559</v>
+      </c>
+      <c r="D40">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$64:$D$66))</f>
+        <v>2.5160670140953307</v>
+      </c>
+      <c r="E40">
+        <f t="shared" ref="E40:E47" si="41">C40*D40</f>
+        <v>5.4546140223738862</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" ref="F40" si="42">B40/E40</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="H40" s="2">
+        <f>F42</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="I40" s="2">
+        <f>F43</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="J40" s="2">
+        <f>F44</f>
+        <v>0.99783560478438982</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>2.8554592675901738</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="39"/>
+        <v>0.59167822248290647</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="39"/>
+        <v>1.0654351124672947</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="40"/>
+        <v>0.22076825282383999</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="40"/>
+        <v>4.5745274287069308E-2</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="40"/>
+        <v>9.4788543770783894E-3</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="40"/>
+        <v>1.9641084615215749E-3</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="40"/>
+        <v>4.0698188780590697E-4</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="40"/>
+        <v>8.4330504270494652E-5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$59:$D$61, '4. STATIS Intra-struktur'!$B$69:$D$71)</f>
+        <v>4.646682681066908</v>
+      </c>
+      <c r="C41">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$59:$D$61))</f>
+        <v>2.1679128543939559</v>
+      </c>
+      <c r="D41">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$69:$D$71))</f>
+        <v>2.606060016748557</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="41"/>
+        <v>5.649711009631325</v>
+      </c>
+      <c r="F41" s="2">
+        <f>B41/E41</f>
+        <v>0.8224637814474921</v>
+      </c>
+      <c r="H41" s="2">
+        <f>F45</f>
+        <v>0.8224637814474921</v>
+      </c>
+      <c r="I41" s="2">
+        <f>F46</f>
+        <v>0.99783560478438982</v>
+      </c>
+      <c r="J41" s="2">
+        <f>F47</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>2.8202993862318819</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="39"/>
+        <v>0.58439276184233468</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="39"/>
+        <v>1.0523161818019229</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="40"/>
+        <v>0.21804988605704156</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="40"/>
+        <v>4.5182002930026527E-2</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="40"/>
+        <v>9.3621392135692042E-3</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="40"/>
+        <v>1.9399239734899185E-3</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="40"/>
+        <v>4.0197063268045536E-4</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="40"/>
+        <v>8.3292124714992228E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$64:$D$66, '4. STATIS Intra-struktur'!$B$59:$D$61)</f>
+        <v>4.6780060570600819</v>
+      </c>
+      <c r="C42">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$64:$D$66))</f>
+        <v>2.5160670140953307</v>
+      </c>
+      <c r="D42">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$59:$D$61))</f>
+        <v>2.1679128543939559</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="41"/>
+        <v>5.4546140223738862</v>
+      </c>
+      <c r="F42" s="2">
+        <f t="shared" ref="F42:F47" si="43">B42/E42</f>
+        <v>0.85762366280578384</v>
+      </c>
+      <c r="M42">
+        <f>SUM(M39:M41)</f>
+        <v>8.3558460980753324</v>
+      </c>
+      <c r="N42">
+        <f>SUM(N39:N41)</f>
+        <v>1.7314105029494398</v>
+      </c>
+      <c r="O42">
+        <f>SUM(O39:O41)</f>
+        <v>3.117751294269218</v>
+      </c>
+      <c r="P42">
+        <f>SUM(P39:P41)</f>
+        <v>0.64602761624885863</v>
+      </c>
+      <c r="Q42">
+        <f>SUM(Q39:Q41)</f>
+        <v>0.13386304472820604</v>
+      </c>
+      <c r="R42">
+        <f t="shared" ref="R42:U42" si="44">SUM(R39:R41)</f>
+        <v>2.7737691537017703E-2</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="44"/>
+        <v>5.7475125667795987E-3</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="44"/>
+        <v>1.1909390751282808E-3</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="44"/>
+        <v>2.4677386333443301E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$64:$D$66, '4. STATIS Intra-struktur'!$B$64:$D$66)</f>
+        <v>6.3305932194185939</v>
+      </c>
+      <c r="C43">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$64:$D$66))</f>
+        <v>2.5160670140953307</v>
+      </c>
+      <c r="D43">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$64:$D$66))</f>
+        <v>2.5160670140953307</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="41"/>
+        <v>6.330593219418593</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="43"/>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$64:$D$66, '4. STATIS Intra-struktur'!$B$69:$D$71)</f>
+        <v>6.5428296586169088</v>
+      </c>
+      <c r="C44">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$64:$D$66))</f>
+        <v>2.5160670140953307</v>
+      </c>
+      <c r="D44">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$69:$D$71))</f>
+        <v>2.606060016748557</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="41"/>
+        <v>6.5570216448937693</v>
+      </c>
+      <c r="F44" s="2">
+        <f t="shared" si="43"/>
+        <v>0.99783560478438982</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$69:$D$71, '4. STATIS Intra-struktur'!$B$59:$D$61)</f>
+        <v>4.646682681066908</v>
+      </c>
+      <c r="C45">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$69:$D$71))</f>
+        <v>2.606060016748557</v>
+      </c>
+      <c r="D45">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$59:$D$61))</f>
+        <v>2.1679128543939559</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="41"/>
+        <v>5.649711009631325</v>
+      </c>
+      <c r="F45" s="2">
+        <f t="shared" si="43"/>
+        <v>0.8224637814474921</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$69:$D$71, '4. STATIS Intra-struktur'!$B$64:$D$66)</f>
+        <v>6.5428296586169088</v>
+      </c>
+      <c r="C46">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$69:$D$71))</f>
+        <v>2.606060016748557</v>
+      </c>
+      <c r="D46">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$64:$D$66))</f>
+        <v>2.5160670140953307</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="41"/>
+        <v>6.5570216448937693</v>
+      </c>
+      <c r="F46" s="2">
+        <f t="shared" si="43"/>
+        <v>0.99783560478438982</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <f>SUMPRODUCT('4. STATIS Intra-struktur'!$B$69:$D$71, '4. STATIS Intra-struktur'!$B$69:$D$71)</f>
+        <v>6.7915488108954882</v>
+      </c>
+      <c r="C47">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$69:$D$71))</f>
+        <v>2.606060016748557</v>
+      </c>
+      <c r="D47">
+        <f>SQRT(SUMSQ('4. STATIS Intra-struktur'!$B$69:$D$71))</f>
+        <v>2.606060016748557</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="41"/>
+        <v>6.7915488108954891</v>
+      </c>
+      <c r="F47" s="2">
+        <f t="shared" si="43"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Olahan Data Sampel.xlsx
+++ b/data/Olahan Data Sampel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F46061-333D-45A3-AB5C-040F5F482227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0D4AA7-027B-4C7B-A342-054A932546A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="1665" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Original" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="221">
   <si>
     <t>Data Tahun 2020</t>
   </si>
@@ -404,21 +404,12 @@
     <t>rvw</t>
   </si>
   <si>
-    <t>trv atau hv</t>
-  </si>
-  <si>
     <t>trw atau hw</t>
   </si>
   <si>
     <t>rvv</t>
   </si>
   <si>
-    <t>hw</t>
-  </si>
-  <si>
-    <t>hv</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
@@ -669,13 +660,76 @@
   </si>
   <si>
     <t>λ₁ / λ₂ (Rasio Kegentingan)</t>
+  </si>
+  <si>
+    <t>trs atau Hs</t>
+  </si>
+  <si>
+    <t>Hs</t>
+  </si>
+  <si>
+    <t>RVs</t>
+  </si>
+  <si>
+    <t>Hw</t>
+  </si>
+  <si>
+    <t>RVw</t>
+  </si>
+  <si>
+    <t>Tahun (k)</t>
+  </si>
+  <si>
+    <t>Global (u₁)</t>
+  </si>
+  <si>
+    <t>JAWA BARAT (u₁)</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>Beta k gabungan</t>
+  </si>
+  <si>
+    <t>Beta k provinsi</t>
+  </si>
+  <si>
+    <t>lambda1</t>
+  </si>
+  <si>
+    <t>trace</t>
+  </si>
+  <si>
+    <t>determinan</t>
+  </si>
+  <si>
+    <t>u11^2 + u12^2 = 1</t>
+  </si>
+  <si>
+    <t>u11 =</t>
+  </si>
+  <si>
+    <t>u12^2 =</t>
+  </si>
+  <si>
+    <t>u12 =</t>
+  </si>
+  <si>
+    <t>* u12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -704,6 +758,13 @@
       <color rgb="FFA9B1D6"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -853,10 +914,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -876,9 +938,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{23909689-85FE-4729-945D-2D3F71B037DB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2800,7 +2865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE09AFDF-31FA-40C7-B91C-9F3ECBF96D71}">
-  <dimension ref="A1:CD171"/>
+  <dimension ref="A1:CD232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -2867,22 +2932,22 @@
         <v>0</v>
       </c>
       <c r="S1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="U1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Y1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AK1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AS1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="BE1" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="BF1" s="7"/>
       <c r="BG1" s="7"/>
@@ -2940,70 +3005,70 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
+        <v>130</v>
+      </c>
+      <c r="T2" t="s">
+        <v>131</v>
+      </c>
+      <c r="U2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V2" t="s">
         <v>133</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>134</v>
       </c>
-      <c r="U2" t="s">
-        <v>135</v>
-      </c>
-      <c r="V2" t="s">
-        <v>136</v>
-      </c>
-      <c r="W2" t="s">
-        <v>137</v>
-      </c>
       <c r="Y2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB2" t="s">
         <v>133</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
         <v>134</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>137</v>
       </c>
       <c r="AJ2" s="6" t="s">
         <v>112</v>
       </c>
       <c r="AK2" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AN2" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AQ2" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AR2" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AS2" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AT2" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="BE2" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="BP2" s="10"/>
     </row>
@@ -3051,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="T3">
         <v>2.3008000000000002</v>
@@ -3066,7 +3131,7 @@
         <v>76.69</v>
       </c>
       <c r="Y3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Z3">
         <v>2.2692000000000001</v>
@@ -3195,7 +3260,7 @@
         <v>1.2248157766231845E-4</v>
       </c>
       <c r="S4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="T4">
         <v>0.69920000000000004</v>
@@ -3210,7 +3275,7 @@
         <v>100</v>
       </c>
       <c r="Y4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Z4">
         <v>0.70579999999999998</v>
@@ -3294,7 +3359,7 @@
     </row>
     <row r="5" spans="1:68" x14ac:dyDescent="0.25">
       <c r="M5" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N5" s="7">
         <f>1/SQRT(N1)</f>
@@ -3310,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3325,7 +3390,7 @@
         <v>100</v>
       </c>
       <c r="Y5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Z5">
         <v>2.5000000000000001E-2</v>
@@ -3424,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3439,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="Z6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AA6">
         <f>1/AA3</f>
@@ -3522,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="U7">
         <f>1/U3</f>
@@ -3578,7 +3643,7 @@
         <v>1.1958861516383639</v>
       </c>
       <c r="AK8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="BE8" s="9" t="s">
         <v>89</v>
@@ -3605,7 +3670,7 @@
         <v>272.06909999999993</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N9">
         <f>SQRT(N1)</f>
@@ -3627,34 +3692,34 @@
         <v>112</v>
       </c>
       <c r="AK9" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AL9" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AM9" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AN9" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AO9" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AQ9" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AR9" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AS9" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AT9" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="BE9" s="9" cm="1">
         <f t="array" ref="BE9:BH12">MMULT(BE3:BG6,TRANSPOSE(BE3:BG6))</f>
@@ -3698,7 +3763,7 @@
     </row>
     <row r="10" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N10">
         <f t="shared" ref="N10:Q10" si="1">SQRT(N2)</f>
@@ -3783,10 +3848,10 @@
     </row>
     <row r="11" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I11" t="s">
         <v>46</v>
@@ -3808,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AE11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AJ11" s="9"/>
       <c r="AK11" t="s">
@@ -4168,7 +4233,7 @@
         <v>0.10355428696626937</v>
       </c>
       <c r="N15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AA15">
         <f t="shared" si="4"/>
@@ -4195,16 +4260,16 @@
     </row>
     <row r="16" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N16" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AK16" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="BE16" s="9" cm="1">
         <f t="array" ref="BE16:BH19">MMULT(_xlfn.ANCHORARRAY(BE9),$N1:$Q4)</f>
@@ -4257,25 +4322,25 @@
         <v>91</v>
       </c>
       <c r="N17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AA17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AF17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AN17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="BE17" s="9">
         <v>-0.73466190132174647</v>
@@ -4827,13 +4892,13 @@
         <v>81</v>
       </c>
       <c r="N22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AK22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="BE22" s="9" cm="1">
         <f t="array" ref="BE22:BH25">MMULT(_xlfn.ANCHORARRAY(BE16),_xlfn.ANCHORARRAY(BE9))</f>
@@ -4886,13 +4951,13 @@
         <v>88</v>
       </c>
       <c r="N23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q23" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="T23" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AA23" cm="1">
         <f t="array" ref="AA23:AB25">MMULT(MMULT(MMULT(_xlfn.ANCHORARRAY(AE12),N1:Q4),_xlfn.ANCHORARRAY(AK24)),U7:V8)</f>
@@ -4902,10 +4967,10 @@
         <v>0.25971799756759339</v>
       </c>
       <c r="AK23" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AN23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BE23" s="9">
         <v>-5.4872511926510894</v>
@@ -5362,7 +5427,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="BE28" s="9">
         <v>-8.9228899764929253</v>
@@ -5413,7 +5478,7 @@
       </c>
       <c r="AA29" s="5"/>
       <c r="AN29" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BE29" s="9">
         <v>-1.106824511079775</v>
@@ -5492,6 +5557,19 @@
       <c r="L30">
         <v>6.6247182254647967</v>
       </c>
+      <c r="N30" cm="1">
+        <f t="array" ref="N30:Q33">MMULT(_xlfn.ANCHORARRAY(I18),$N$9:$Q$12)</f>
+        <v>3.1114668465347499</v>
+      </c>
+      <c r="O30">
+        <v>-2.187696916723108</v>
+      </c>
+      <c r="P30">
+        <v>-0.3014368351054697</v>
+      </c>
+      <c r="Q30">
+        <v>4.0506901237685869E-2</v>
+      </c>
       <c r="AN30" s="14">
         <f t="shared" ref="AN30:AO33" si="13">$AC$140*N24+$AC$141*Q24+$AC$142*T24</f>
         <v>2.1847888031448481</v>
@@ -5574,6 +5652,18 @@
       <c r="L31">
         <v>-2.5497786518746666</v>
       </c>
+      <c r="N31">
+        <v>-1.6717660934952594</v>
+      </c>
+      <c r="O31">
+        <v>1.3608178452264945</v>
+      </c>
+      <c r="P31">
+        <v>-0.13139082773916053</v>
+      </c>
+      <c r="Q31">
+        <v>-1.4331622585731755E-2</v>
+      </c>
       <c r="AN31" s="14">
         <f t="shared" si="13"/>
         <v>-1.2878503514697393</v>
@@ -5630,6 +5720,18 @@
       <c r="L32">
         <v>-3.301013025799306</v>
       </c>
+      <c r="N32">
+        <v>-0.36426994741579749</v>
+      </c>
+      <c r="O32">
+        <v>-0.20777998586306756</v>
+      </c>
+      <c r="P32">
+        <v>0.76935667678406139</v>
+      </c>
+      <c r="Q32">
+        <v>-2.3340871915296262E-2</v>
+      </c>
       <c r="AN32" s="14">
         <f t="shared" si="13"/>
         <v>2.9434336038411016E-2</v>
@@ -5714,6 +5816,18 @@
       </c>
       <c r="L33">
         <v>5.1554809526040906</v>
+      </c>
+      <c r="N33">
+        <v>1.9856546623306577</v>
+      </c>
+      <c r="O33">
+        <v>-0.91935174251065921</v>
+      </c>
+      <c r="P33">
+        <v>-0.94681417757614472</v>
+      </c>
+      <c r="Q33">
+        <v>4.5090140895720013E-2</v>
       </c>
       <c r="AN33" s="14">
         <f t="shared" si="13"/>
@@ -5847,6 +5961,19 @@
       <c r="L35">
         <v>7.8637164945963098</v>
       </c>
+      <c r="N35" cm="1">
+        <f t="array" ref="N35:Q38">MMULT(_xlfn.ANCHORARRAY(N30),_xlfn.ANCHORARRAY(I18))</f>
+        <v>24.937250501640968</v>
+      </c>
+      <c r="O35">
+        <v>-13.74568156740583</v>
+      </c>
+      <c r="P35">
+        <v>-2.0509276693175909</v>
+      </c>
+      <c r="Q35">
+        <v>15.022073824723901</v>
+      </c>
       <c r="BE35" s="9">
         <v>2.3966004518425543</v>
       </c>
@@ -5921,6 +6048,18 @@
       <c r="L36">
         <v>-4.2044392515892737</v>
       </c>
+      <c r="N36">
+        <v>-13.745681567405832</v>
+      </c>
+      <c r="O36">
+        <v>7.8170238253286337</v>
+      </c>
+      <c r="P36">
+        <v>0.52928840522171483</v>
+      </c>
+      <c r="Q36">
+        <v>-7.6623439940530318</v>
+      </c>
       <c r="BE36" s="9" t="s">
         <v>100</v>
       </c>
@@ -5963,6 +6102,18 @@
       <c r="L37">
         <v>-0.97222832631927592</v>
       </c>
+      <c r="N37">
+        <v>-2.0509276693175913</v>
+      </c>
+      <c r="O37">
+        <v>0.52928840522171494</v>
+      </c>
+      <c r="P37">
+        <v>1.6731032886820585</v>
+      </c>
+      <c r="Q37">
+        <v>-2.7818860672601695</v>
+      </c>
       <c r="BE37" s="9" t="s">
         <v>101</v>
       </c>
@@ -6010,6 +6161,18 @@
       </c>
       <c r="L38">
         <v>4.8526701571483075</v>
+      </c>
+      <c r="N38">
+        <v>15.022073824723902</v>
+      </c>
+      <c r="O38">
+        <v>-7.6623439940530309</v>
+      </c>
+      <c r="P38">
+        <v>-2.7818860672601695</v>
+      </c>
+      <c r="Q38">
+        <v>10.638802220954711</v>
       </c>
       <c r="BE38" s="9" cm="1">
         <f t="array" ref="BE38:BH41">MMULT(_xlfn.ANCHORARRAY(BE22),$N$1:$Q$4)</f>
@@ -6138,6 +6301,19 @@
       <c r="L40">
         <v>8.4767927539891801</v>
       </c>
+      <c r="N40" cm="1">
+        <f t="array" ref="N40:Q43">MMULT(_xlfn.ANCHORARRAY(N35),N9:Q12)</f>
+        <v>13.528780562678946</v>
+      </c>
+      <c r="O40">
+        <v>-9.7586109797737812</v>
+      </c>
+      <c r="P40">
+        <v>-0.9207323601229398</v>
+      </c>
+      <c r="Q40">
+        <v>0.16625138724216693</v>
+      </c>
       <c r="BE40" s="9">
         <v>-0.85796208915392924</v>
       </c>
@@ -6212,6 +6388,18 @@
       <c r="L41">
         <v>-4.4468639114985038</v>
       </c>
+      <c r="N41">
+        <v>-7.4572098314390054</v>
+      </c>
+      <c r="O41">
+        <v>5.5496189226360713</v>
+      </c>
+      <c r="P41">
+        <v>0.2376158700358495</v>
+      </c>
+      <c r="Q41">
+        <v>-8.4800230207989671E-2</v>
+      </c>
       <c r="BE41" s="9">
         <v>0.66516991200872899</v>
       </c>
@@ -6286,6 +6474,18 @@
       <c r="L42">
         <v>-1.2617816797663772</v>
       </c>
+      <c r="N42">
+        <v>-1.1126547566380036</v>
+      </c>
+      <c r="O42">
+        <v>0.37576308001425462</v>
+      </c>
+      <c r="P42">
+        <v>0.75111392896183948</v>
+      </c>
+      <c r="Q42">
+        <v>-3.0787521298854998E-2</v>
+      </c>
       <c r="BE42" s="9" t="s">
         <v>104</v>
       </c>
@@ -6333,6 +6533,18 @@
       </c>
       <c r="L43">
         <v>5.6865222721580517</v>
+      </c>
+      <c r="N43">
+        <v>8.149669120807026</v>
+      </c>
+      <c r="O43">
+        <v>-5.4398055028770305</v>
+      </c>
+      <c r="P43">
+        <v>-1.2488848644544492</v>
+      </c>
+      <c r="Q43">
+        <v>0.11774110874876328</v>
       </c>
       <c r="BE43" s="9" cm="1">
         <f t="array" ref="BE43:BH46">MMULT(_xlfn.ANCHORARRAY(BE27),$N$1:$Q$4)</f>
@@ -7184,7 +7396,7 @@
     </row>
     <row r="60" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BE60" s="9"/>
       <c r="BP60" s="10"/>
@@ -7514,7 +7726,7 @@
         <v>0.10355428696626937</v>
       </c>
       <c r="M90" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="V90">
         <f>V88/V89</f>
@@ -7523,33 +7735,33 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M91" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N91" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E92" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I92" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M92" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P92" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S92" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
@@ -7705,36 +7917,36 @@
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M96" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N96" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E97" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I97" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M97" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P97" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S97" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="V97" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.25">
@@ -7898,30 +8110,30 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="X101" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E102" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I102" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M102" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q102" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="U102" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="X102" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.25">
@@ -8136,21 +8348,21 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="U106" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E107" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I107" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="U107" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.25">
@@ -8269,7 +8481,7 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -8316,7 +8528,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -8363,7 +8575,7 @@
     </row>
     <row r="139" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="AC139" t="s">
         <v>110</v>
@@ -8372,7 +8584,7 @@
         <v>112</v>
       </c>
       <c r="CD139" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140" spans="1:82" x14ac:dyDescent="0.25">
@@ -9001,7 +9213,7 @@
     </row>
     <row r="145" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="AT145" cm="1">
         <f t="array" ref="AT145:AV147">AT140:AV142 - BJ144 * MMULT(BJ140:BJ142, TRANSPOSE(BJ140:BJ142))</f>
@@ -9540,7 +9752,7 @@
     </row>
     <row r="151" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="AC151" t="s">
         <v>111</v>
@@ -9917,7 +10129,7 @@
     </row>
     <row r="157" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
     </row>
     <row r="158" spans="1:62" x14ac:dyDescent="0.25">
@@ -10291,15 +10503,15 @@
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B165" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B166">
         <v>17.1859</v>
@@ -10315,7 +10527,7 @@
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B167">
         <v>295.73480000000001</v>
@@ -10329,7 +10541,7 @@
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B168">
         <v>0.38030000000000003</v>
@@ -10343,7 +10555,7 @@
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B169">
         <v>1.2999999999999999E-3</v>
@@ -10351,18 +10563,735 @@
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B170" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B171">
         <v>27.883299999999998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A173" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B173" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C173" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D173" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E173" s="18" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="174" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A174" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B174" s="17">
+        <v>0.49659999999999999</v>
+      </c>
+      <c r="C174" s="17">
+        <v>0.64039999999999997</v>
+      </c>
+      <c r="D174">
+        <f>B174*$B$166</f>
+        <v>8.5345179400000006</v>
+      </c>
+      <c r="E174">
+        <f t="shared" ref="E174:E176" si="87">C174*$B$166</f>
+        <v>11.00585036</v>
+      </c>
+    </row>
+    <row r="175" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B175" s="17">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="C175" s="17">
+        <v>0.57020000000000004</v>
+      </c>
+      <c r="D175">
+        <f t="shared" ref="D175:D176" si="88">B175*$B$166</f>
+        <v>10.3802836</v>
+      </c>
+      <c r="E175">
+        <f t="shared" si="87"/>
+        <v>9.799400180000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B176" s="17">
+        <v>0.62339999999999995</v>
+      </c>
+      <c r="C176" s="17">
+        <v>0.51449999999999996</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="88"/>
+        <v>10.713690059999999</v>
+      </c>
+      <c r="E176">
+        <f t="shared" si="87"/>
+        <v>8.8421455499999997</v>
+      </c>
+    </row>
+    <row r="182" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B182">
+        <v>1.2</v>
+      </c>
+      <c r="C182">
+        <v>-0.8</v>
+      </c>
+      <c r="D182">
+        <v>0.5</v>
+      </c>
+      <c r="E182">
+        <v>600000</v>
+      </c>
+      <c r="G182">
+        <f>E182/SUM(E182:E183)</f>
+        <v>0.6</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <f>SQRT(G182)</f>
+        <v>0.7745966692414834</v>
+      </c>
+      <c r="K182">
+        <f t="shared" ref="K182:K183" si="89">SQRT(H182)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B183">
+        <v>-1</v>
+      </c>
+      <c r="C183">
+        <v>0.5</v>
+      </c>
+      <c r="D183">
+        <v>-0.4</v>
+      </c>
+      <c r="E183">
+        <v>400000</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <f>E183/SUM(E182:E183)</f>
+        <v>0.4</v>
+      </c>
+      <c r="J183">
+        <f t="shared" ref="J183" si="90">SQRT(G183)</f>
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <f t="shared" si="89"/>
+        <v>0.63245553203367588</v>
+      </c>
+    </row>
+    <row r="185" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B185">
+        <v>1.4</v>
+      </c>
+      <c r="C185">
+        <v>-0.9</v>
+      </c>
+      <c r="D185">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="186" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B186">
+        <v>-0.8</v>
+      </c>
+      <c r="C186">
+        <v>0.4</v>
+      </c>
+      <c r="D186">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="188" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B188" cm="1">
+        <f t="array" ref="B188:C189">MMULT(MMULT(MMULT(J182:K183,B182:D183),TRANSPOSE(B182:D183)),J182:K183)</f>
+        <v>1.3980000000000001</v>
+      </c>
+      <c r="C188">
+        <v>-0.88181630740194428</v>
+      </c>
+      <c r="E188">
+        <f>B188^2</f>
+        <v>1.9544040000000005</v>
+      </c>
+      <c r="F188">
+        <f t="shared" ref="F188:F189" si="91">C188^2</f>
+        <v>0.77760000000000029</v>
+      </c>
+      <c r="H188">
+        <f>SUMPRODUCT(E188:F189)</f>
+        <v>3.8277000000000005</v>
+      </c>
+      <c r="J188">
+        <v>3.8277000000000005</v>
+      </c>
+      <c r="K188">
+        <v>4.2604680000000013</v>
+      </c>
+    </row>
+    <row r="189" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B189">
+        <v>-0.88181630740194406</v>
+      </c>
+      <c r="C189">
+        <v>0.56400000000000006</v>
+      </c>
+      <c r="E189">
+        <f t="shared" ref="E189" si="92">B189^2</f>
+        <v>0.77759999999999985</v>
+      </c>
+      <c r="F189">
+        <f t="shared" si="91"/>
+        <v>0.31809600000000005</v>
+      </c>
+      <c r="J189">
+        <v>4.2604680000000013</v>
+      </c>
+      <c r="K189">
+        <v>4.9763080000000004</v>
+      </c>
+    </row>
+    <row r="190" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K190" t="s">
+        <v>214</v>
+      </c>
+      <c r="L190">
+        <f>SUMPRODUCT(J188:K189,_xlfn.MUNIT(2))</f>
+        <v>8.8040080000000014</v>
+      </c>
+      <c r="N190" t="s">
+        <v>213</v>
+      </c>
+      <c r="O190">
+        <f>(L190+SQRT(L190^2-4*L191))/2</f>
+        <v>8.7010053565292136</v>
+      </c>
+    </row>
+    <row r="191" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B191" cm="1">
+        <f t="array" ref="B191:C192">MMULT(MMULT(MMULT(J182:K183,B185:D186),TRANSPOSE(B185:D186)),J182:K183)</f>
+        <v>1.8780000000000001</v>
+      </c>
+      <c r="C191">
+        <v>-0.81323059460401514</v>
+      </c>
+      <c r="E191">
+        <f t="shared" ref="E191:E192" si="93">B191^2</f>
+        <v>3.5268840000000004</v>
+      </c>
+      <c r="F191">
+        <f t="shared" ref="F191:F192" si="94">C191^2</f>
+        <v>0.66134400000000004</v>
+      </c>
+      <c r="H191">
+        <f>SUMPRODUCT(E191:F192)</f>
+        <v>4.9763080000000004</v>
+      </c>
+      <c r="K191" t="s">
+        <v>215</v>
+      </c>
+      <c r="L191">
+        <f>J188*K189-J189*K188</f>
+        <v>0.89622655257599249</v>
+      </c>
+    </row>
+    <row r="192" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B192">
+        <v>-0.81323059460401526</v>
+      </c>
+      <c r="C192">
+        <v>0.35600000000000009</v>
+      </c>
+      <c r="E192">
+        <f t="shared" si="93"/>
+        <v>0.66134400000000015</v>
+      </c>
+      <c r="F192">
+        <f t="shared" si="94"/>
+        <v>0.12673600000000007</v>
+      </c>
+    </row>
+    <row r="193" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J193">
+        <f>J188-O190</f>
+        <v>-4.8733053565292135</v>
+      </c>
+      <c r="K193">
+        <f>K188</f>
+        <v>4.2604680000000013</v>
+      </c>
+    </row>
+    <row r="194" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B194">
+        <f>B188*B191</f>
+        <v>2.6254440000000003</v>
+      </c>
+      <c r="C194">
+        <f t="shared" ref="C194:C195" si="95">C188*C191</f>
+        <v>0.71712000000000009</v>
+      </c>
+      <c r="H194">
+        <f>SUMPRODUCT(B194:C195)</f>
+        <v>4.2604680000000013</v>
+      </c>
+      <c r="J194">
+        <f>J189</f>
+        <v>4.2604680000000013</v>
+      </c>
+      <c r="K194">
+        <f>K189-O190</f>
+        <v>-3.7246973565292132</v>
+      </c>
+    </row>
+    <row r="195" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B195">
+        <f t="shared" ref="B195:C195" si="96">B189*B192</f>
+        <v>0.71712000000000009</v>
+      </c>
+      <c r="C195">
+        <f t="shared" si="95"/>
+        <v>0.20078400000000007</v>
+      </c>
+    </row>
+    <row r="196" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J196" t="str">
+        <f>J193&amp;" * u11 + "&amp;J194&amp;" * u12"</f>
+        <v>-4.87330535652921 * u11 + 4.260468 * u12</v>
+      </c>
+    </row>
+    <row r="197" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J197" t="s">
+        <v>217</v>
+      </c>
+      <c r="K197">
+        <f>-(J194)/J193</f>
+        <v>0.87424605853845416</v>
+      </c>
+      <c r="L197" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="198" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J198" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="199" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J199" t="str">
+        <f>K197&amp;"^2 u12^2 + u12^2 = 1"</f>
+        <v>0.874246058538454^2 u12^2 + u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="200" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J200" t="str">
+        <f>"("&amp;K197&amp;"^2 + 1) u12^2 = 1"</f>
+        <v>(0.874246058538454^2 + 1) u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="201" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J201" t="str">
+        <f>"("&amp;K197^2&amp;" + 1) u12^2 = 1"</f>
+        <v>(0.764306170870022 + 1) u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="202" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J202" t="str">
+        <f>K197^2 + 1&amp;" u12^2 = 1"</f>
+        <v>1.76430617087002 u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="203" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J203" t="s">
+        <v>218</v>
+      </c>
+      <c r="K203">
+        <f>1 /( K197^2 + 1)</f>
+        <v>0.56679504754374677</v>
+      </c>
+    </row>
+    <row r="204" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J204" t="s">
+        <v>219</v>
+      </c>
+      <c r="K204">
+        <f>SQRT(K203)</f>
+        <v>0.75285791989175932</v>
+      </c>
+    </row>
+    <row r="205" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J205" t="s">
+        <v>217</v>
+      </c>
+      <c r="K205">
+        <f>K197*K204</f>
+        <v>0.65818306910482982</v>
+      </c>
+      <c r="M205">
+        <f>K205*O190</f>
+        <v>5.7268544098579621</v>
+      </c>
+    </row>
+    <row r="206" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M206">
+        <f>K204*O190</f>
+        <v>6.5506207936836391</v>
+      </c>
+    </row>
+    <row r="208" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B208">
+        <v>1.2</v>
+      </c>
+      <c r="C208">
+        <v>-0.8</v>
+      </c>
+      <c r="D208">
+        <v>0.5</v>
+      </c>
+      <c r="E208">
+        <v>600000</v>
+      </c>
+      <c r="G208">
+        <f>E208/SUM(E208:E209)</f>
+        <v>0.6</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <f>SQRT(G208)</f>
+        <v>0.7745966692414834</v>
+      </c>
+      <c r="K208">
+        <f t="shared" ref="K208:K209" si="97">SQRT(H208)</f>
+        <v>0</v>
+      </c>
+      <c r="O208" cm="1">
+        <f t="array" ref="O208:P209">MMULT(MMULT(J208:K209,B208:D209),TRANSPOSE(MMULT(J208:K209,B208:D209)))</f>
+        <v>1.3980000000000001</v>
+      </c>
+      <c r="P208">
+        <v>-0.88181630740194417</v>
+      </c>
+    </row>
+    <row r="209" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B209">
+        <v>-1</v>
+      </c>
+      <c r="C209">
+        <v>0.5</v>
+      </c>
+      <c r="D209">
+        <v>-0.4</v>
+      </c>
+      <c r="E209">
+        <v>400000</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <f>E209/SUM(E208:E209)</f>
+        <v>0.4</v>
+      </c>
+      <c r="J209">
+        <f t="shared" ref="J209" si="98">SQRT(G209)</f>
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <f t="shared" si="97"/>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="O209">
+        <v>-0.88181630740194417</v>
+      </c>
+      <c r="P209">
+        <v>0.56400000000000006</v>
+      </c>
+    </row>
+    <row r="211" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B211">
+        <v>1.4</v>
+      </c>
+      <c r="C211">
+        <v>-0.9</v>
+      </c>
+      <c r="D211">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="212" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B212">
+        <v>-0.8</v>
+      </c>
+      <c r="C212">
+        <v>0.4</v>
+      </c>
+      <c r="D212">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="214" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B214" cm="1">
+        <f t="array" ref="B214:C215">MMULT(MMULT(MMULT(J208:K209,B208:D209),TRANSPOSE(B208:D209)),J208:K209)</f>
+        <v>1.3980000000000001</v>
+      </c>
+      <c r="C214">
+        <v>-0.88181630740194428</v>
+      </c>
+      <c r="E214">
+        <f>B214^2</f>
+        <v>1.9544040000000005</v>
+      </c>
+      <c r="F214">
+        <f t="shared" ref="F214:F215" si="99">C214^2</f>
+        <v>0.77760000000000029</v>
+      </c>
+      <c r="H214">
+        <f>SUMPRODUCT(E214:F215)</f>
+        <v>3.8277000000000005</v>
+      </c>
+      <c r="J214">
+        <v>3.8277000000000005</v>
+      </c>
+      <c r="K214">
+        <v>4.2604680000000013</v>
+      </c>
+    </row>
+    <row r="215" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B215">
+        <v>-0.88181630740194406</v>
+      </c>
+      <c r="C215">
+        <v>0.56400000000000006</v>
+      </c>
+      <c r="E215">
+        <f t="shared" ref="E215" si="100">B215^2</f>
+        <v>0.77759999999999985</v>
+      </c>
+      <c r="F215">
+        <f t="shared" si="99"/>
+        <v>0.31809600000000005</v>
+      </c>
+      <c r="J215">
+        <v>4.2604680000000013</v>
+      </c>
+      <c r="K215">
+        <v>4.9763080000000004</v>
+      </c>
+    </row>
+    <row r="216" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K216" t="s">
+        <v>214</v>
+      </c>
+      <c r="L216">
+        <f>SUMPRODUCT(J214:K215,_xlfn.MUNIT(2))</f>
+        <v>8.8040080000000014</v>
+      </c>
+      <c r="N216" t="s">
+        <v>213</v>
+      </c>
+      <c r="O216">
+        <f>(L216+SQRT(L216^2-4*L217))/2</f>
+        <v>8.7010053565292136</v>
+      </c>
+    </row>
+    <row r="217" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B217" cm="1">
+        <f t="array" ref="B217:C218">MMULT(MMULT(MMULT(J208:K209,B211:D212),TRANSPOSE(B211:D212)),J208:K209)</f>
+        <v>1.8780000000000001</v>
+      </c>
+      <c r="C217">
+        <v>-0.81323059460401514</v>
+      </c>
+      <c r="E217">
+        <f t="shared" ref="E217:E218" si="101">B217^2</f>
+        <v>3.5268840000000004</v>
+      </c>
+      <c r="F217">
+        <f t="shared" ref="F217:F218" si="102">C217^2</f>
+        <v>0.66134400000000004</v>
+      </c>
+      <c r="H217">
+        <f>SUMPRODUCT(E217:F218)</f>
+        <v>4.9763080000000004</v>
+      </c>
+      <c r="K217" t="s">
+        <v>215</v>
+      </c>
+      <c r="L217">
+        <f>J214*K215-J215*K214</f>
+        <v>0.89622655257599249</v>
+      </c>
+    </row>
+    <row r="218" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B218">
+        <v>-0.81323059460401526</v>
+      </c>
+      <c r="C218">
+        <v>0.35600000000000009</v>
+      </c>
+      <c r="E218">
+        <f t="shared" si="101"/>
+        <v>0.66134400000000015</v>
+      </c>
+      <c r="F218">
+        <f t="shared" si="102"/>
+        <v>0.12673600000000007</v>
+      </c>
+    </row>
+    <row r="219" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J219">
+        <f>J214-O216</f>
+        <v>-4.8733053565292135</v>
+      </c>
+      <c r="K219">
+        <f>K214</f>
+        <v>4.2604680000000013</v>
+      </c>
+    </row>
+    <row r="220" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B220">
+        <f>B214*B217</f>
+        <v>2.6254440000000003</v>
+      </c>
+      <c r="C220">
+        <f t="shared" ref="C220:C221" si="103">C214*C217</f>
+        <v>0.71712000000000009</v>
+      </c>
+      <c r="H220">
+        <f>SUMPRODUCT(B220:C221)</f>
+        <v>4.2604680000000013</v>
+      </c>
+      <c r="J220">
+        <f>J215</f>
+        <v>4.2604680000000013</v>
+      </c>
+      <c r="K220">
+        <f>K215-O216</f>
+        <v>-3.7246973565292132</v>
+      </c>
+    </row>
+    <row r="221" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B221">
+        <f t="shared" ref="B221:C221" si="104">B215*B218</f>
+        <v>0.71712000000000009</v>
+      </c>
+      <c r="C221">
+        <f t="shared" si="103"/>
+        <v>0.20078400000000007</v>
+      </c>
+    </row>
+    <row r="222" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J222" t="str">
+        <f>J219&amp;" * u11 + "&amp;J220&amp;" * u12"</f>
+        <v>-4.87330535652921 * u11 + 4.260468 * u12</v>
+      </c>
+    </row>
+    <row r="223" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J223" t="s">
+        <v>217</v>
+      </c>
+      <c r="K223">
+        <f>-(J220)/J219</f>
+        <v>0.87424605853845416</v>
+      </c>
+      <c r="L223" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="224" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J224" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="225" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J225" t="str">
+        <f>K223&amp;"^2 u12^2 + u12^2 = 1"</f>
+        <v>0.874246058538454^2 u12^2 + u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="226" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J226" t="str">
+        <f>"("&amp;K223&amp;"^2 + 1) u12^2 = 1"</f>
+        <v>(0.874246058538454^2 + 1) u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="227" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J227" t="str">
+        <f>"("&amp;K223^2&amp;" + 1) u12^2 = 1"</f>
+        <v>(0.764306170870022 + 1) u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="228" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J228" t="str">
+        <f>K223^2 + 1&amp;" u12^2 = 1"</f>
+        <v>1.76430617087002 u12^2 = 1</v>
+      </c>
+    </row>
+    <row r="229" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J229" t="s">
+        <v>218</v>
+      </c>
+      <c r="K229">
+        <f>1 /( K223^2 + 1)</f>
+        <v>0.56679504754374677</v>
+      </c>
+    </row>
+    <row r="230" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J230" t="s">
+        <v>219</v>
+      </c>
+      <c r="K230">
+        <f>SQRT(K229)</f>
+        <v>0.75285791989175932</v>
+      </c>
+    </row>
+    <row r="231" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J231" t="s">
+        <v>217</v>
+      </c>
+      <c r="K231">
+        <f>K223*K230</f>
+        <v>0.65818306910482982</v>
+      </c>
+      <c r="M231">
+        <f>K231*O216</f>
+        <v>5.7268544098579621</v>
+      </c>
+    </row>
+    <row r="232" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="M232">
+        <f>K230*O216</f>
+        <v>6.5506207936836391</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olahan Data Sampel.xlsx
+++ b/data/Olahan Data Sampel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0D4AA7-027B-4C7B-A342-054A932546A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC91A2A-6222-49A2-B4A4-97F936F864BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1665" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Original" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -767,7 +767,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -795,6 +795,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -939,7 +945,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5426,6 +5432,14 @@
       <c r="A28" t="s">
         <v>82</v>
       </c>
+      <c r="AK28" s="18" cm="1">
+        <f t="array" ref="AK28">AK24/MAX(ABS($AK$24:$AL$27))</f>
+        <v>-1</v>
+      </c>
+      <c r="AL28" s="18" cm="1">
+        <f t="array" ref="AL28">AL24/MAX(ABS($AK$24:$AL$27))</f>
+        <v>-0.16502898898387439</v>
+      </c>
       <c r="AN28" t="s">
         <v>188</v>
       </c>
@@ -5477,6 +5491,14 @@
         <v>85</v>
       </c>
       <c r="AA29" s="5"/>
+      <c r="AK29" s="18" cm="1">
+        <f t="array" ref="AK29">AK25/MAX(ABS($AK$24:$AL$27))</f>
+        <v>0.56296106583677197</v>
+      </c>
+      <c r="AL29" s="18" cm="1">
+        <f t="array" ref="AL29">AL25/MAX(ABS($AK$24:$AL$27))</f>
+        <v>-0.19907275788899079</v>
+      </c>
       <c r="AN29" t="s">
         <v>125</v>
       </c>
@@ -5570,6 +5592,14 @@
       <c r="Q30">
         <v>4.0506901237685869E-2</v>
       </c>
+      <c r="AK30" s="18" cm="1">
+        <f t="array" ref="AK30">AK26/MAX(ABS($AK$24:$AL$27))</f>
+        <v>5.2822795073073296E-2</v>
+      </c>
+      <c r="AL30" s="18" cm="1">
+        <f t="array" ref="AL30">AL26/MAX(ABS($AK$24:$AL$27))</f>
+        <v>0.73923714763566162</v>
+      </c>
       <c r="AN30" s="14">
         <f t="shared" ref="AN30:AO33" si="13">$AC$140*N24+$AC$141*Q24+$AC$142*T24</f>
         <v>2.1847888031448481</v>
@@ -5664,6 +5694,14 @@
       <c r="Q31">
         <v>-1.4331622585731755E-2</v>
       </c>
+      <c r="AK31" s="18" cm="1">
+        <f t="array" ref="AK31">AK27/MAX(ABS($AK$24:$AL$27))</f>
+        <v>-0.54354593508153848</v>
+      </c>
+      <c r="AL31" s="18" cm="1">
+        <f t="array" ref="AL31">AL27/MAX(ABS($AK$24:$AL$27))</f>
+        <v>-0.65720629029983291</v>
+      </c>
       <c r="AN31" s="14">
         <f t="shared" si="13"/>
         <v>-1.2878503514697393</v>
@@ -5883,6 +5921,14 @@
       </c>
       <c r="I34" t="s">
         <v>92</v>
+      </c>
+      <c r="AN34" s="18" cm="1">
+        <f t="array" ref="AN34">AN30/MAX(ABS($AN$30:$AO$33))</f>
+        <v>1</v>
+      </c>
+      <c r="AO34" s="18" cm="1">
+        <f t="array" ref="AO34">AO30/MAX(ABS($AN$30:$AO$33))</f>
+        <v>0.20749227938520265</v>
       </c>
       <c r="BE34" s="9">
         <v>-1.6988050928849565</v>
@@ -5974,6 +6020,14 @@
       <c r="Q35">
         <v>15.022073824723901</v>
       </c>
+      <c r="AN35" s="18" cm="1">
+        <f t="array" ref="AN35">AN31/MAX(ABS($AN$30:$AO$33))</f>
+        <v>-0.58946217117918687</v>
+      </c>
+      <c r="AO35" s="18" cm="1">
+        <f t="array" ref="AO35">AO31/MAX(ABS($AN$30:$AO$33))</f>
+        <v>0.16978108618992893</v>
+      </c>
       <c r="BE35" s="9">
         <v>2.3966004518425543</v>
       </c>
@@ -6060,6 +6114,14 @@
       <c r="Q36">
         <v>-7.6623439940530318</v>
       </c>
+      <c r="AN36" s="18" cm="1">
+        <f t="array" ref="AN36">AN32/MAX(ABS($AN$30:$AO$33))</f>
+        <v>1.3472394217712203E-2</v>
+      </c>
+      <c r="AO36" s="18" cm="1">
+        <f t="array" ref="AO36">AO32/MAX(ABS($AN$30:$AO$33))</f>
+        <v>-0.72801739995919501</v>
+      </c>
       <c r="BE36" s="9" t="s">
         <v>100</v>
       </c>
@@ -6113,6 +6175,14 @@
       </c>
       <c r="Q37">
         <v>-2.7818860672601695</v>
+      </c>
+      <c r="AN37" s="18" cm="1">
+        <f t="array" ref="AN37">AN33/MAX(ABS($AN$30:$AO$33))</f>
+        <v>0.50821022750936773</v>
+      </c>
+      <c r="AO37" s="18" cm="1">
+        <f t="array" ref="AO37">AO33/MAX(ABS($AN$30:$AO$33))</f>
+        <v>0.69297766096555924</v>
       </c>
       <c r="BE37" s="9" t="s">
         <v>101</v>
@@ -8350,6 +8420,14 @@
       <c r="U106" t="s">
         <v>189</v>
       </c>
+      <c r="X106" s="18" cm="1">
+        <f t="array" ref="X106">(MAX(ABS($AN$30:$AO$33))/MAX(ABS($X$103:$Y$105)))*0.8*X103</f>
+        <v>-1.4546018640702789</v>
+      </c>
+      <c r="Y106" s="18" cm="1">
+        <f t="array" ref="Y106">(MAX(ABS($AN$30:$AO$33))/MAX(ABS($X$103:$Y$105)))*0.8*Y103</f>
+        <v>-0.98228900548454134</v>
+      </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -8363,6 +8441,14 @@
       </c>
       <c r="U107" t="s">
         <v>128</v>
+      </c>
+      <c r="X107" s="18" cm="1">
+        <f t="array" ref="X107">(MAX(ABS($AN$30:$AO$33))/MAX(ABS($X$103:$Y$105)))*0.8*X104</f>
+        <v>1.7478310425158787</v>
+      </c>
+      <c r="Y107" s="18" cm="1">
+        <f t="array" ref="Y107">(MAX(ABS($AN$30:$AO$33))/MAX(ABS($X$103:$Y$105)))*0.8*Y104</f>
+        <v>4.6178594918020233E-2</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.25">
@@ -8404,6 +8490,14 @@
         <f t="shared" ref="V108:V110" si="16">$AC$152*N93+$AC$153*Q93+$AC$154*T93</f>
         <v>0.51437212436558544</v>
       </c>
+      <c r="X108" s="18" cm="1">
+        <f t="array" ref="X108">(MAX(ABS($AN$30:$AO$33))/MAX(ABS($X$103:$Y$105)))*0.8*X105</f>
+        <v>-1.3658922201356467</v>
+      </c>
+      <c r="Y108" s="18" cm="1">
+        <f t="array" ref="Y108">(MAX(ABS($AN$30:$AO$33))/MAX(ABS($X$103:$Y$105)))*0.8*Y105</f>
+        <v>1.1051763659515697</v>
+      </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109">
@@ -8479,12 +8573,30 @@
         <v>-0.61683423249866121</v>
       </c>
     </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U111" s="18" cm="1">
+        <f t="array" ref="U111">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U108</f>
+        <v>1.5452684095797597</v>
+      </c>
+      <c r="V111" s="18" cm="1">
+        <f t="array" ref="V111">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*V108</f>
+        <v>0.92755598955512242</v>
+      </c>
+    </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="U112" s="18" cm="1">
+        <f t="array" ref="U112">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U109</f>
+        <v>-1.7996078374109317</v>
+      </c>
+      <c r="V112" s="18" cm="1">
+        <f t="array" ref="V112">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*V109</f>
+        <v>0.10840907689421803</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3))</f>
         <v>4.6998461442465498</v>
@@ -8497,8 +8609,16 @@
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I98),_xlfn.MUNIT(3))</f>
         <v>4.646682681066908</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="U113" s="18" cm="1">
+        <f t="array" ref="U113">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U110</f>
+        <v>1.2786059429971754</v>
+      </c>
+      <c r="V113" s="18" cm="1">
+        <f t="array" ref="V113">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*V110</f>
+        <v>-1.112323665716614</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A103),_xlfn.MUNIT(3))</f>
         <v>4.6780060570600819</v>
@@ -8512,7 +8632,7 @@
         <v>6.5428296586169088</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A108),_xlfn.MUNIT(3))</f>
         <v>4.646682681066908</v>
@@ -8526,12 +8646,12 @@
         <v>6.7915488108954891</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126">
         <f>A113/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A98),_xlfn.MUNIT(3))))</f>
         <v>1.0000000000000002</v>
@@ -10587,10 +10707,10 @@
       <c r="C173" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D173" s="18" t="s">
+      <c r="D173" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="E173" s="18" t="s">
+      <c r="E173" s="17" t="s">
         <v>212</v>
       </c>
     </row>
@@ -10874,7 +10994,7 @@
     </row>
     <row r="195" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B195">
-        <f t="shared" ref="B195:C195" si="96">B189*B192</f>
+        <f t="shared" ref="B195" si="96">B189*B192</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="C195">
@@ -11202,7 +11322,7 @@
     </row>
     <row r="221" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B221">
-        <f t="shared" ref="B221:C221" si="104">B215*B218</f>
+        <f t="shared" ref="B221" si="104">B215*B218</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="C221">

--- a/data/Olahan Data Sampel.xlsx
+++ b/data/Olahan Data Sampel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC91A2A-6222-49A2-B4A4-97F936F864BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D60502B-0101-44EF-9EDC-A34F18D183F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="1650" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Data Original" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3675,6 +3675,18 @@
       <c r="D9">
         <v>272.06909999999993</v>
       </c>
+      <c r="F9">
+        <v>2.18747858637346</v>
+      </c>
+      <c r="G9">
+        <v>2.1601500796804798</v>
+      </c>
+      <c r="H9">
+        <v>7.6625078348824705E-4</v>
+      </c>
+      <c r="I9">
+        <v>4.3483949168374298</v>
+      </c>
       <c r="M9" s="6" t="s">
         <v>162</v>
       </c>
@@ -3771,20 +3783,36 @@
       <c r="A10" t="s">
         <v>151</v>
       </c>
+      <c r="F10">
+        <f>A12^2</f>
+        <v>2.1874785863734552</v>
+      </c>
+      <c r="G10">
+        <f t="shared" ref="G10:H10" si="1">B12^2</f>
+        <v>2.1601500796804847</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>7.6625078348824705E-4</v>
+      </c>
+      <c r="I10">
+        <f>SUM(F10:H10)</f>
+        <v>4.3483949168374281</v>
+      </c>
       <c r="N10">
-        <f t="shared" ref="N10:Q10" si="1">SQRT(N2)</f>
+        <f t="shared" ref="N10:Q10" si="2">SQRT(N2)</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.70994013151837376</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ10" s="9"/>
@@ -3863,19 +3891,19 @@
         <v>46</v>
       </c>
       <c r="N11">
-        <f t="shared" ref="N11:Q11" si="2">SQRT(N3)</f>
+        <f t="shared" ref="N11:Q11" si="3">SQRT(N3)</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.44893458404083886</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA11" t="s">
@@ -3953,7 +3981,7 @@
         <v>-1.4790127066301544</v>
       </c>
       <c r="B12">
-        <v>1.4697449029272016</v>
+        <v>1.4697449029272001</v>
       </c>
       <c r="C12">
         <v>-2.7681235223310521E-2</v>
@@ -3977,31 +4005,31 @@
         <v>-1.1698614761101329</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:Q12" si="3">SQRT(N4)</f>
+        <f t="shared" ref="N12:Q12" si="4">SQRT(N4)</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1067139542913447E-2</v>
       </c>
       <c r="AA12">
-        <f t="shared" ref="AA12:AC15" si="4">$M1*A12+$M1*E12+$M1*I12</f>
+        <f t="shared" ref="AA12:AC15" si="5">$M1*A12+$M1*E12+$M1*I12</f>
         <v>-1.3225998392037082</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="4"/>
-        <v>1.2841918916027262</v>
+        <f t="shared" si="5"/>
+        <v>1.2841918916027257</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.64370935000393115</v>
       </c>
       <c r="AE12" cm="1">
@@ -4086,7 +4114,7 @@
         <v>0.39523545574314989</v>
       </c>
       <c r="B13">
-        <v>-0.84996221012035955</v>
+        <v>-0.84996221012036</v>
       </c>
       <c r="C13">
         <v>0.76402554578205428</v>
@@ -4110,19 +4138,19 @@
         <v>0.98117866422162847</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.66117354123641858</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.3070630477922212</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.3794842886867094</v>
       </c>
       <c r="AE13">
-        <v>1.2841918916027262</v>
+        <v>1.2841918916027257</v>
       </c>
       <c r="AF13">
         <v>-1.3070630477922212</v>
@@ -4182,15 +4210,15 @@
         <v>-0.74538955508466542</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.66208574495665029</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.2689926719492801E-2</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.73594142757906622</v>
       </c>
       <c r="AE14">
@@ -4242,15 +4270,15 @@
         <v>147</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-6.5944698935950009E-4</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8122947000204971E-4</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.6648889628866119E-4</v>
       </c>
       <c r="BE15" s="9" t="s">
@@ -4268,6 +4296,34 @@
       <c r="A16" t="s">
         <v>148</v>
       </c>
+      <c r="C16">
+        <f>A12*A13</f>
+        <v>-0.58455826115487874</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ref="D16:E16" si="6">B12*B13</f>
+        <v>-1.2492276260051369</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="6"/>
+        <v>-2.1149170849411248E-2</v>
+      </c>
+      <c r="F16">
+        <v>-0.58455826115487897</v>
+      </c>
+      <c r="G16">
+        <v>-1.2492276260051369</v>
+      </c>
+      <c r="H16">
+        <v>-2.1149170849411248E-2</v>
+      </c>
+      <c r="I16">
+        <f>SUM(F16:H16)</f>
+        <v>-1.854935058009427</v>
+      </c>
+      <c r="J16">
+        <v>-1.854935058009427</v>
+      </c>
       <c r="N16" t="s">
         <v>152</v>
       </c>
@@ -4388,16 +4444,16 @@
     <row r="18" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A18" s="15" cm="1">
         <f t="array" ref="A18:D21">MMULT(A12:C15,TRANSPOSE(A12:C15))</f>
-        <v>4.3483949168374334</v>
+        <v>4.3483949168374281</v>
       </c>
       <c r="B18" s="15">
-        <v>-1.8549350580094275</v>
+        <v>-1.8549350580094268</v>
       </c>
       <c r="C18" s="15">
-        <v>-1.7132067475354562</v>
+        <v>-1.713206747535456</v>
       </c>
       <c r="D18" s="15">
-        <v>3.0852147797134633</v>
+        <v>3.0852147797134624</v>
       </c>
       <c r="E18" s="15" cm="1">
         <f t="array" ref="E18:H21">MMULT(E12:G15,TRANSPOSE(E12:G15))</f>
@@ -4427,10 +4483,10 @@
       </c>
       <c r="N18" s="14" cm="1">
         <f t="array" ref="N18:O21">MMULT(MMULT(_xlfn.ANCHORARRAY(A18),N9:Q12),MMULT(AP3:AQ6,U7:V8))</f>
-        <v>-1.7840028133002299</v>
+        <v>-1.7840028133002281</v>
       </c>
       <c r="O18" s="14">
-        <v>-0.90268005148704777</v>
+        <v>-0.90268005148704722</v>
       </c>
       <c r="Q18" s="14" cm="1">
         <f t="array" ref="Q18:R21">MMULT(_xlfn.ANCHORARRAY(E18),MMULT(N9:Q12,MMULT(AP3:AQ6,U7:V8)))</f>
@@ -4451,32 +4507,32 @@
         <v>5.1983647840595868</v>
       </c>
       <c r="AB18" s="14">
-        <f t="shared" ref="AB18:AB21" si="5">$AC$152*B18+$AC$153*F18+$AC$154*J18</f>
-        <v>-2.6826662967097858</v>
+        <f t="shared" ref="AB18:AB21" si="7">$AC$152*B18+$AC$153*F18+$AC$154*J18</f>
+        <v>-2.6826662967097863</v>
       </c>
       <c r="AC18" s="14">
-        <f t="shared" ref="AC18:AC21" si="6">$AC$152*C18+$AC$153*G18+$AC$154*K18</f>
+        <f t="shared" ref="AC18:AC21" si="8">$AC$152*C18+$AC$153*G18+$AC$154*K18</f>
         <v>-0.88459957528567312</v>
       </c>
       <c r="AD18" s="14">
-        <f t="shared" ref="AD18:AD21" si="7">$AC$152*D18+$AC$153*H18+$AC$154*L18</f>
+        <f t="shared" ref="AD18:AD21" si="9">$AC$152*D18+$AC$153*H18+$AC$154*L18</f>
         <v>3.2993773055271287</v>
       </c>
       <c r="AF18">
         <f>$AC$140*A18+$AC$141*E18+$AC$142*I18</f>
-        <v>5.2082977427754162</v>
+        <v>5.2082977427754145</v>
       </c>
       <c r="AG18">
-        <f t="shared" ref="AG18:AG21" si="8">$AC$140*B18+$AC$141*F18+$AC$142*J18</f>
+        <f t="shared" ref="AG18:AG21" si="10">$AC$140*B18+$AC$141*F18+$AC$142*J18</f>
         <v>-2.6925882969022874</v>
       </c>
       <c r="AH18">
-        <f t="shared" ref="AH18:AH21" si="9">$AC$140*C18+$AC$141*G18+$AC$142*K18</f>
-        <v>-0.87429347550452297</v>
+        <f t="shared" ref="AH18:AH21" si="11">$AC$140*C18+$AC$141*G18+$AC$142*K18</f>
+        <v>-0.87429347550452285</v>
       </c>
       <c r="AI18">
-        <f t="shared" ref="AI18:AI21" si="10">$AC$140*D18+$AC$141*H18+$AC$142*L18</f>
-        <v>3.3014275496303838</v>
+        <f t="shared" ref="AI18:AI21" si="12">$AC$140*D18+$AC$141*H18+$AC$142*L18</f>
+        <v>3.3014275496303833</v>
       </c>
       <c r="AK18">
         <f>AP3*$U$3</f>
@@ -4533,16 +4589,16 @@
     </row>
     <row r="19" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
-        <v>-1.8549350580094275</v>
+        <v>-1.8549350580094268</v>
       </c>
       <c r="B19" s="15">
-        <v>1.4623818587167476</v>
+        <v>1.4623818587167481</v>
       </c>
       <c r="C19" s="15">
         <v>-0.94814668119777612</v>
       </c>
       <c r="D19" s="15">
-        <v>-0.21040376463410959</v>
+        <v>-0.21040376463410981</v>
       </c>
       <c r="E19" s="15">
         <v>-2.9515908962260076</v>
@@ -4569,10 +4625,10 @@
         <v>-1.2949708034456504</v>
       </c>
       <c r="N19" s="14">
-        <v>0.92965439420652174</v>
+        <v>0.92965439420652163</v>
       </c>
       <c r="O19" s="14">
-        <v>-0.63659573097812883</v>
+        <v>-0.63659573097812916</v>
       </c>
       <c r="Q19" s="14">
         <v>1.3894454889944623</v>
@@ -4587,35 +4643,35 @@
         <v>-0.27715679672362903</v>
       </c>
       <c r="AA19" s="14">
-        <f t="shared" ref="AA19:AA21" si="11">$AC$152*A19+$AC$153*E19+$AC$154*I19</f>
-        <v>-2.6826662967097858</v>
+        <f t="shared" ref="AA19:AA21" si="13">$AC$152*A19+$AC$153*E19+$AC$154*I19</f>
+        <v>-2.6826662967097863</v>
       </c>
       <c r="AB19" s="14">
-        <f t="shared" si="5"/>
-        <v>1.8043429593760623</v>
+        <f t="shared" si="7"/>
+        <v>1.8043429593760627</v>
       </c>
       <c r="AC19" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-0.59413967599270268</v>
       </c>
       <c r="AD19" s="14">
-        <f t="shared" si="7"/>
-        <v>-0.88653434456733526</v>
+        <f t="shared" si="9"/>
+        <v>-0.88653434456733549</v>
       </c>
       <c r="AF19">
-        <f t="shared" ref="AF19:AF21" si="12">$AC$140*A19+$AC$141*E19+$AC$142*I19</f>
+        <f t="shared" ref="AF19:AF21" si="14">$AC$140*A19+$AC$141*E19+$AC$142*I19</f>
         <v>-2.6925882969022874</v>
       </c>
       <c r="AG19">
-        <f t="shared" si="8"/>
-        <v>1.8085470514279762</v>
+        <f t="shared" si="10"/>
+        <v>1.8085470514279764</v>
       </c>
       <c r="AH19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-0.59015890937257376</v>
       </c>
       <c r="AI19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-0.89447325210375794</v>
       </c>
       <c r="AK19">
@@ -4673,7 +4729,7 @@
     </row>
     <row r="20" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
-        <v>-1.7132067475354562</v>
+        <v>-1.713206747535456</v>
       </c>
       <c r="B20" s="15">
         <v>-0.94814668119777612</v>
@@ -4709,7 +4765,7 @@
         <v>-2.1090248139359531</v>
       </c>
       <c r="N20" s="14">
-        <v>0.28098046843212232</v>
+        <v>0.28098046843212227</v>
       </c>
       <c r="O20" s="14">
         <v>2.9116248291487659</v>
@@ -4727,35 +4783,35 @@
         <v>1.0213533148868346</v>
       </c>
       <c r="AA20" s="14">
+        <f t="shared" si="13"/>
+        <v>-0.88459957528567312</v>
+      </c>
+      <c r="AB20" s="14">
+        <f t="shared" si="7"/>
+        <v>-0.59413967599270268</v>
+      </c>
+      <c r="AC20" s="14">
+        <f t="shared" si="8"/>
+        <v>2.7792174526316735</v>
+      </c>
+      <c r="AD20" s="14">
+        <f t="shared" si="9"/>
+        <v>-2.6035096998491403</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="14"/>
+        <v>-0.87429347550452285</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="10"/>
+        <v>-0.59015890937257376</v>
+      </c>
+      <c r="AH20">
         <f t="shared" si="11"/>
-        <v>-0.88459957528567312</v>
-      </c>
-      <c r="AB20" s="14">
-        <f t="shared" si="5"/>
-        <v>-0.59413967599270268</v>
-      </c>
-      <c r="AC20" s="14">
-        <f t="shared" si="6"/>
-        <v>2.779217452631674</v>
-      </c>
-      <c r="AD20" s="14">
-        <f t="shared" si="7"/>
-        <v>-2.6035096998491403</v>
-      </c>
-      <c r="AF20">
+        <v>2.7542017290879865</v>
+      </c>
+      <c r="AI20">
         <f t="shared" si="12"/>
-        <v>-0.87429347550452297</v>
-      </c>
-      <c r="AG20">
-        <f t="shared" si="8"/>
-        <v>-0.59015890937257376</v>
-      </c>
-      <c r="AH20">
-        <f t="shared" si="9"/>
-        <v>2.7542017290879865</v>
-      </c>
-      <c r="AI20">
-        <f t="shared" si="10"/>
         <v>-2.5866468791064463</v>
       </c>
       <c r="AK20">
@@ -4781,10 +4837,10 @@
     </row>
     <row r="21" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
-        <v>3.0852147797134633</v>
+        <v>3.0852147797134624</v>
       </c>
       <c r="B21" s="15">
-        <v>-0.21040376463410959</v>
+        <v>-0.21040376463410981</v>
       </c>
       <c r="C21" s="15">
         <v>-3.9818554150690564</v>
@@ -4817,7 +4873,7 @@
         <v>4.0742362306791646</v>
       </c>
       <c r="N21" s="14">
-        <v>-0.98793971041736861</v>
+        <v>-0.98793971041736839</v>
       </c>
       <c r="O21" s="14">
         <v>-2.3238208667897333</v>
@@ -4835,35 +4891,35 @@
         <v>-1.1658560759962251</v>
       </c>
       <c r="AA21" s="14">
+        <f t="shared" si="13"/>
+        <v>3.2993773055271287</v>
+      </c>
+      <c r="AB21" s="14">
+        <f t="shared" si="7"/>
+        <v>-0.88653434456733549</v>
+      </c>
+      <c r="AC21" s="14">
+        <f t="shared" si="8"/>
+        <v>-2.6035096998491403</v>
+      </c>
+      <c r="AD21" s="14">
+        <f t="shared" si="9"/>
+        <v>3.8391022585355756</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="14"/>
+        <v>3.3014275496303833</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="10"/>
+        <v>-0.89447325210375794</v>
+      </c>
+      <c r="AH21">
         <f t="shared" si="11"/>
-        <v>3.2993773055271287</v>
-      </c>
-      <c r="AB21" s="14">
-        <f t="shared" si="5"/>
-        <v>-0.88653434456733526</v>
-      </c>
-      <c r="AC21" s="14">
-        <f t="shared" si="6"/>
-        <v>-2.6035096998491403</v>
-      </c>
-      <c r="AD21" s="14">
-        <f t="shared" si="7"/>
-        <v>3.8391022585355761</v>
-      </c>
-      <c r="AF21">
+        <v>-2.5866468791064463</v>
+      </c>
+      <c r="AI21">
         <f t="shared" si="12"/>
-        <v>3.3014275496303838</v>
-      </c>
-      <c r="AG21">
-        <f t="shared" si="8"/>
-        <v>-0.89447325210375794</v>
-      </c>
-      <c r="AH21">
-        <f t="shared" si="9"/>
-        <v>-2.5866468791064463</v>
-      </c>
-      <c r="AI21">
-        <f t="shared" si="10"/>
         <v>3.833623864399482</v>
       </c>
       <c r="AK21">
@@ -5018,16 +5074,16 @@
     <row r="24" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A24" cm="1">
         <f t="array" ref="A24:D27">MMULT(_xlfn.ANCHORARRAY(A18),$N$1:$Q$4)</f>
-        <v>1.2798207543977949</v>
+        <v>1.2798207543977933</v>
       </c>
       <c r="B24">
-        <v>-0.93491507534455331</v>
+        <v>-0.93491507534455298</v>
       </c>
       <c r="C24">
-        <v>-0.34528356102688862</v>
+        <v>-0.34528356102688856</v>
       </c>
       <c r="D24">
-        <v>3.7788197364640726E-4</v>
+        <v>3.7788197364640715E-4</v>
       </c>
       <c r="E24" cm="1">
         <f t="array" ref="E24:H27">MMULT(_xlfn.ANCHORARRAY(E18),$N$1:$Q$4)</f>
@@ -5057,7 +5113,7 @@
       </c>
       <c r="N24" s="14" cm="1">
         <f t="array" ref="N24:O27">MMULT(A12:C15,MMULT(X103:Y105,AA6:AB7))</f>
-        <v>1.7937109530788702</v>
+        <v>1.7937109530788693</v>
       </c>
       <c r="O24" s="14">
         <v>1.0072726431596752</v>
@@ -5077,10 +5133,10 @@
         <v>0.169612023356145</v>
       </c>
       <c r="AA24">
-        <v>-1.1102050003853463</v>
+        <v>-1.1102050003853461</v>
       </c>
       <c r="AB24">
-        <v>0.19409637818033543</v>
+        <v>0.19409637818033545</v>
       </c>
       <c r="AK24" s="14" cm="1">
         <f t="array" ref="AK24:AL27">MMULT(N5:Q8,AK18:AL21)</f>
@@ -5135,16 +5191,16 @@
     </row>
     <row r="25" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>-0.54594498216071186</v>
+        <v>-0.54594498216071163</v>
       </c>
       <c r="B25">
-        <v>0.73706237839498923</v>
+        <v>0.73706237839498945</v>
       </c>
       <c r="C25">
         <v>-0.19109162564923815</v>
       </c>
       <c r="D25">
-        <v>-2.5770585038476864E-5</v>
+        <v>-2.5770585038476891E-5</v>
       </c>
       <c r="E25">
         <v>-0.86871302163810715</v>
@@ -5171,10 +5227,10 @@
         <v>-1.5861006703266336E-4</v>
       </c>
       <c r="N25" s="14">
-        <v>-1.1701888658435529</v>
+        <v>-1.1701888658435533</v>
       </c>
       <c r="O25" s="14">
-        <v>0.28181366262527546</v>
+        <v>0.28181366262527541</v>
       </c>
       <c r="Q25" s="14">
         <v>-1.3443097323112525</v>
@@ -5323,10 +5379,10 @@
     </row>
     <row r="27" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>0.90804123874835452</v>
+        <v>0.90804123874835418</v>
       </c>
       <c r="B27">
-        <v>-0.10604665139962893</v>
+        <v>-0.10604665139962904</v>
       </c>
       <c r="C27">
         <v>-0.80251214232436907</v>
@@ -5542,42 +5598,42 @@
     <row r="30" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A30" cm="1">
         <f t="array" ref="A30:D33">MMULT(_xlfn.ANCHORARRAY(A24),_xlfn.ANCHORARRAY(A18))</f>
-        <v>7.8920807860189752</v>
+        <v>7.8920807860189592</v>
       </c>
       <c r="B30">
-        <v>-3.413887276255267</v>
+        <v>-3.4138872762552634</v>
       </c>
       <c r="C30">
-        <v>-2.9910613694023636</v>
+        <v>-2.9910613694023609</v>
       </c>
       <c r="D30">
-        <v>5.5216975437871998</v>
+        <v>5.5216975437871936</v>
       </c>
       <c r="E30" cm="1">
         <f t="array" ref="E30:H33">MMULT(_xlfn.ANCHORARRAY(A24),_xlfn.ANCHORARRAY(E18))</f>
-        <v>9.7449886697646484</v>
+        <v>9.7449886697646395</v>
       </c>
       <c r="F30">
-        <v>-5.4070757961122897</v>
+        <v>-5.4070757961122844</v>
       </c>
       <c r="G30">
-        <v>-0.71244444595184864</v>
+        <v>-0.71244444595184808</v>
       </c>
       <c r="H30">
-        <v>5.6110396492239376</v>
+        <v>5.6110396492239323</v>
       </c>
       <c r="I30" cm="1">
         <f t="array" ref="I30:L33">MMULT(_xlfn.ANCHORARRAY(A24),_xlfn.ANCHORARRAY(I18))</f>
-        <v>10.454324198854978</v>
+        <v>10.454324198854968</v>
       </c>
       <c r="J30">
-        <v>-5.6352828246516955</v>
+        <v>-5.6352828246516911</v>
       </c>
       <c r="K30">
-        <v>-1.178233684741963</v>
+        <v>-1.1782336847419619</v>
       </c>
       <c r="L30">
-        <v>6.6247182254647967</v>
+        <v>6.6247182254647905</v>
       </c>
       <c r="N30" cm="1">
         <f t="array" ref="N30:Q33">MMULT(_xlfn.ANCHORARRAY(I18),$N$9:$Q$12)</f>
@@ -5601,11 +5657,11 @@
         <v>0.73923714763566162</v>
       </c>
       <c r="AN30" s="14">
-        <f t="shared" ref="AN30:AO33" si="13">$AC$140*N24+$AC$141*Q24+$AC$142*T24</f>
+        <f t="shared" ref="AN30:AO33" si="15">$AC$140*N24+$AC$141*Q24+$AC$142*T24</f>
         <v>2.1847888031448481</v>
       </c>
       <c r="AO30" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.45332680873979336</v>
       </c>
       <c r="BE30" s="9">
@@ -5647,40 +5703,40 @@
     </row>
     <row r="31" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>-3.413887276255267</v>
+        <v>-3.413887276255263</v>
       </c>
       <c r="B31">
-        <v>2.2717474509538089</v>
+        <v>2.2717474509538085</v>
       </c>
       <c r="C31">
-        <v>-0.69507228278609112</v>
+        <v>-0.6950722827860919</v>
       </c>
       <c r="D31">
-        <v>-1.0786478982066203</v>
+        <v>-1.0786478982066194</v>
       </c>
       <c r="E31">
-        <v>-5.0117256225504008</v>
+        <v>-5.011725622550399</v>
       </c>
       <c r="F31">
-        <v>3.1804046825027292</v>
+        <v>3.1804046825027288</v>
       </c>
       <c r="G31">
-        <v>-0.6334447541259578</v>
+        <v>-0.63344475412595802</v>
       </c>
       <c r="H31">
         <v>-2.0682497333207501</v>
       </c>
       <c r="I31">
-        <v>-5.2742114327761662</v>
+        <v>-5.2742114327761653</v>
       </c>
       <c r="J31">
-        <v>3.1511086638560286</v>
+        <v>3.1511086638560282</v>
       </c>
       <c r="K31">
-        <v>-0.17657032753071852</v>
+        <v>-0.17657032753071872</v>
       </c>
       <c r="L31">
-        <v>-2.5497786518746666</v>
+        <v>-2.5497786518746661</v>
       </c>
       <c r="N31">
         <v>-1.6717660934952594</v>
@@ -5703,11 +5759,11 @@
         <v>-0.65720629029983291</v>
       </c>
       <c r="AN31" s="14">
-        <f t="shared" si="13"/>
-        <v>-1.2878503514697393</v>
+        <f t="shared" si="15"/>
+        <v>-1.2878503514697395</v>
       </c>
       <c r="AO31" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.3709358160935271</v>
       </c>
       <c r="BE31" s="9" t="s">
@@ -5723,16 +5779,16 @@
     </row>
     <row r="32" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>-2.9910613694023636</v>
+        <v>-2.9910613694023609</v>
       </c>
       <c r="B32">
-        <v>-0.69507228278609123</v>
+        <v>-0.69507228278609179</v>
       </c>
       <c r="C32">
         <v>6.1094607248847677</v>
       </c>
       <c r="D32">
-        <v>-5.3697438180222203</v>
+        <v>-5.3697438180222195</v>
       </c>
       <c r="E32">
         <v>-1.7010686268312669</v>
@@ -5771,11 +5827,11 @@
         <v>-2.3340871915296262E-2</v>
       </c>
       <c r="AN32" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.9434336038411016E-2</v>
       </c>
       <c r="AO32" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-1.5905642639254738</v>
       </c>
       <c r="BE32" s="9" cm="1">
@@ -5820,40 +5876,40 @@
     </row>
     <row r="33" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5.5216975437871998</v>
+        <v>5.5216975437871945</v>
       </c>
       <c r="B33">
-        <v>-1.0786478982066208</v>
+        <v>-1.0786478982066194</v>
       </c>
       <c r="C33">
-        <v>-5.3697438180222212</v>
+        <v>-5.3697438180222195</v>
       </c>
       <c r="D33">
-        <v>6.0214891515023155</v>
+        <v>6.0214891515023137</v>
       </c>
       <c r="E33">
-        <v>5.5060323118878589</v>
+        <v>5.5060323118878571</v>
       </c>
       <c r="F33">
-        <v>-2.396633778321628</v>
+        <v>-2.3966337783216272</v>
       </c>
       <c r="G33">
-        <v>-2.0499463449125521</v>
+        <v>-2.0499463449125517</v>
       </c>
       <c r="H33">
         <v>4.5171643055982793</v>
       </c>
       <c r="I33">
-        <v>6.0754021358773729</v>
+        <v>6.075402135877372</v>
       </c>
       <c r="J33">
-        <v>-2.7672179106120818</v>
+        <v>-2.7672179106120809</v>
       </c>
       <c r="K33">
-        <v>-1.9550545988978589</v>
+        <v>-1.9550545988978587</v>
       </c>
       <c r="L33">
-        <v>5.1554809526040906</v>
+        <v>5.1554809526040897</v>
       </c>
       <c r="N33">
         <v>1.9856546623306577</v>
@@ -5868,11 +5924,11 @@
         <v>4.5090140895720013E-2</v>
       </c>
       <c r="AN33" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1.1103320147061626</v>
       </c>
       <c r="AO33" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1.5140098345070605</v>
       </c>
       <c r="BE33" s="9">
@@ -5970,16 +6026,16 @@
     <row r="35" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A35" cm="1">
         <f t="array" ref="A35:D38">MMULT(_xlfn.ANCHORARRAY(E24),_xlfn.ANCHORARRAY(A18))</f>
-        <v>9.7449886697646484</v>
+        <v>9.7449886697646395</v>
       </c>
       <c r="B35">
         <v>-5.0117256225504008</v>
       </c>
       <c r="C35">
-        <v>-1.7010686268312671</v>
+        <v>-1.7010686268312667</v>
       </c>
       <c r="D35">
-        <v>5.5060323118878589</v>
+        <v>5.5060323118878571</v>
       </c>
       <c r="E35" cm="1">
         <f t="array" ref="E35:H38">MMULT(_xlfn.ANCHORARRAY(E24),_xlfn.ANCHORARRAY(E18))</f>
@@ -6022,7 +6078,7 @@
       </c>
       <c r="AN35" s="18" cm="1">
         <f t="array" ref="AN35">AN31/MAX(ABS($AN$30:$AO$33))</f>
-        <v>-0.58946217117918687</v>
+        <v>-0.58946217117918698</v>
       </c>
       <c r="AO35" s="18" cm="1">
         <f t="array" ref="AO35">AO31/MAX(ABS($AN$30:$AO$33))</f>
@@ -6067,16 +6123,16 @@
     </row>
     <row r="36" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>-5.4070757961122888</v>
+        <v>-5.4070757961122844</v>
       </c>
       <c r="B36">
         <v>3.1804046825027292</v>
       </c>
       <c r="C36">
-        <v>-5.5899432676908459E-2</v>
+        <v>-5.5899432676908681E-2</v>
       </c>
       <c r="D36">
-        <v>-2.396633778321628</v>
+        <v>-2.3966337783216276</v>
       </c>
       <c r="E36">
         <v>-7.5194198870866575</v>
@@ -6129,16 +6185,16 @@
     </row>
     <row r="37" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>-0.71244444595184864</v>
+        <v>-0.71244444595184808</v>
       </c>
       <c r="B37">
-        <v>-0.6334447541259578</v>
+        <v>-0.63344475412595813</v>
       </c>
       <c r="C37">
         <v>2.6257697523275771</v>
       </c>
       <c r="D37">
-        <v>-2.0499463449125521</v>
+        <v>-2.0499463449125517</v>
       </c>
       <c r="E37">
         <v>6.3466291368932601E-2</v>
@@ -6197,16 +6253,16 @@
     </row>
     <row r="38" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5.6110396492239376</v>
+        <v>5.6110396492239323</v>
       </c>
       <c r="B38">
-        <v>-2.0682497333207506</v>
+        <v>-2.0682497333207501</v>
       </c>
       <c r="C38">
-        <v>-3.0245125135013708</v>
+        <v>-3.0245125135013704</v>
       </c>
       <c r="D38">
-        <v>4.5171643055982802</v>
+        <v>4.5171643055982793</v>
       </c>
       <c r="E38">
         <v>6.5689096569816332</v>
@@ -6334,13 +6390,13 @@
     <row r="40" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A40" cm="1">
         <f t="array" ref="A40:D43">MMULT(_xlfn.ANCHORARRAY(I24),_xlfn.ANCHORARRAY(A18))</f>
-        <v>10.454324198854978</v>
+        <v>10.45432419885497</v>
       </c>
       <c r="B40">
         <v>-5.2742114327761662</v>
       </c>
       <c r="C40">
-        <v>-2.0808637947344226</v>
+        <v>-2.0808637947344222</v>
       </c>
       <c r="D40">
         <v>6.0754021358773729</v>
@@ -6423,16 +6479,16 @@
     </row>
     <row r="41" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>-5.6352828246516964</v>
+        <v>-5.6352828246516911</v>
       </c>
       <c r="B41">
         <v>3.1511086638560286</v>
       </c>
       <c r="C41">
-        <v>0.35084888714161111</v>
+        <v>0.35084888714161089</v>
       </c>
       <c r="D41">
-        <v>-2.7672179106120818</v>
+        <v>-2.7672179106120809</v>
       </c>
       <c r="E41">
         <v>-7.6729804210794192</v>
@@ -6509,16 +6565,16 @@
     </row>
     <row r="42" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>-1.1782336847419628</v>
+        <v>-1.1782336847419619</v>
       </c>
       <c r="B42">
-        <v>-0.1765703275307185</v>
+        <v>-0.17657032753071875</v>
       </c>
       <c r="C42">
         <v>2.1633755697376986</v>
       </c>
       <c r="D42">
-        <v>-1.9550545988978587</v>
+        <v>-1.9550545988978583</v>
       </c>
       <c r="E42">
         <v>-0.767510328294851</v>
@@ -6569,16 +6625,16 @@
     </row>
     <row r="43" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>6.6247182254647967</v>
+        <v>6.6247182254647905</v>
       </c>
       <c r="B43">
-        <v>-2.5497786518746666</v>
+        <v>-2.5497786518746661</v>
       </c>
       <c r="C43">
-        <v>-3.3010130257993064</v>
+        <v>-3.301013025799306</v>
       </c>
       <c r="D43">
-        <v>5.1554809526040906</v>
+        <v>5.1554809526040897</v>
       </c>
       <c r="E43">
         <v>7.8637164945963098</v>
@@ -6747,42 +6803,42 @@
     <row r="46" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A46" cm="1">
         <f t="array" ref="A46:D49">MMULT(_xlfn.ANCHORARRAY(A30),$N$1:$Q$4)</f>
-        <v>2.322799326763346</v>
+        <v>2.3227993267633416</v>
       </c>
       <c r="B46">
-        <v>-1.7206503625647596</v>
+        <v>-1.7206503625647578</v>
       </c>
       <c r="C46">
-        <v>-0.6028252704251249</v>
+        <v>-0.60282527042512435</v>
       </c>
       <c r="D46">
-        <v>6.763062265372049E-4</v>
+        <v>6.7630622653720414E-4</v>
       </c>
       <c r="E46" cm="1">
         <f t="array" ref="E46:H49">MMULT(_xlfn.ANCHORARRAY(E30),$N$1:$Q$4)</f>
-        <v>2.8681476704528168</v>
+        <v>2.8681476704528146</v>
       </c>
       <c r="F46">
-        <v>-2.7252472551469453</v>
+        <v>-2.7252472551469427</v>
       </c>
       <c r="G46">
-        <v>-0.14358766429443562</v>
+        <v>-0.14358766429443551</v>
       </c>
       <c r="H46">
-        <v>6.8724898856276973E-4</v>
+        <v>6.8724898856276908E-4</v>
       </c>
       <c r="I46" cm="1">
         <f t="array" ref="I46:L49">MMULT(_xlfn.ANCHORARRAY(I30),$N$1:$Q$4)</f>
-        <v>3.0769194930042518</v>
+        <v>3.0769194930042487</v>
       </c>
       <c r="J46">
-        <v>-2.8402670184318284</v>
+        <v>-2.8402670184318262</v>
       </c>
       <c r="K46">
-        <v>-0.23746388051224848</v>
+        <v>-0.23746388051224826</v>
       </c>
       <c r="L46">
-        <v>8.1140593982324295E-4</v>
+        <v>8.1140593982324219E-4</v>
       </c>
       <c r="BE46" s="9">
         <v>0.55552825043387322</v>
@@ -6823,40 +6879,40 @@
     </row>
     <row r="47" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>-1.0047762157959013</v>
+        <v>-1.0047762157958999</v>
       </c>
       <c r="B47">
-        <v>1.1449947695481437</v>
+        <v>1.1449947695481435</v>
       </c>
       <c r="C47">
-        <v>-0.14008643925592709</v>
+        <v>-0.14008643925592723</v>
       </c>
       <c r="D47">
-        <v>-1.3211449631449074E-4</v>
+        <v>-1.3211449631449063E-4</v>
       </c>
       <c r="E47">
-        <v>-1.4750524250341466</v>
+        <v>-1.4750524250341459</v>
       </c>
       <c r="F47">
-        <v>1.6029716353299401</v>
+        <v>1.6029716353299399</v>
       </c>
       <c r="G47">
-        <v>-0.12766588780545651</v>
+        <v>-0.12766588780545657</v>
       </c>
       <c r="H47">
         <v>-2.5332249033679487E-4</v>
       </c>
       <c r="I47">
-        <v>-1.5523073188711991</v>
+        <v>-1.5523073188711989</v>
       </c>
       <c r="J47">
-        <v>1.5882060027747134</v>
+        <v>1.5882060027747131</v>
       </c>
       <c r="K47">
-        <v>-3.558638299154189E-2</v>
+        <v>-3.5586382991541932E-2</v>
       </c>
       <c r="L47">
-        <v>-3.1230091197130858E-4</v>
+        <v>-3.1230091197130853E-4</v>
       </c>
       <c r="BE47" s="9" t="s">
         <v>107</v>
@@ -6871,16 +6927,16 @@
     </row>
     <row r="48" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>-0.8803299818551753</v>
+        <v>-0.88032998185517453</v>
       </c>
       <c r="B48">
-        <v>-0.35032684989426</v>
+        <v>-0.35032684989426027</v>
       </c>
       <c r="C48">
         <v>1.2313145264439085</v>
       </c>
       <c r="D48">
-        <v>-6.5769469447384292E-4</v>
+        <v>-6.5769469447384281E-4</v>
       </c>
       <c r="E48">
         <v>-0.50065897300261319</v>
@@ -6948,40 +7004,40 @@
     </row>
     <row r="49" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>1.6251474972254412</v>
+        <v>1.6251474972254396</v>
       </c>
       <c r="B49">
-        <v>-0.5436547099952227</v>
+        <v>-0.54365470999522203</v>
       </c>
       <c r="C49">
-        <v>-1.0822303087213716</v>
+        <v>-1.0822303087213712</v>
       </c>
       <c r="D49">
-        <v>7.3752149115253888E-4</v>
+        <v>7.3752149115253866E-4</v>
       </c>
       <c r="E49">
-        <v>1.6205369019849765</v>
+        <v>1.620536901984976</v>
       </c>
       <c r="F49">
-        <v>-1.207939350630074</v>
+        <v>-1.2079393506300735</v>
       </c>
       <c r="G49">
-        <v>-0.41315082076561327</v>
+        <v>-0.41315082076561316</v>
       </c>
       <c r="H49">
         <v>5.5326941070958841E-4</v>
       </c>
       <c r="I49">
-        <v>1.7881139807935345</v>
+        <v>1.7881139807935342</v>
       </c>
       <c r="J49">
-        <v>-1.3947193084867251</v>
+        <v>-1.3947193084867247</v>
       </c>
       <c r="K49">
-        <v>-0.39402612374749446</v>
+        <v>-0.39402612374749441</v>
       </c>
       <c r="L49">
-        <v>6.3145144068298142E-4</v>
+        <v>6.3145144068298131E-4</v>
       </c>
       <c r="BE49" s="9">
         <v>-2.7757285874390365</v>
@@ -7070,16 +7126,16 @@
     <row r="51" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A51" cm="1">
         <f t="array" ref="A51:D54">MMULT(_xlfn.ANCHORARRAY(A35),$N$1:$Q$4)</f>
-        <v>2.8681476704528168</v>
+        <v>2.8681476704528146</v>
       </c>
       <c r="B51">
         <v>-2.5259848412381039</v>
       </c>
       <c r="C51">
-        <v>-0.34283721673893525</v>
+        <v>-0.34283721673893514</v>
       </c>
       <c r="D51">
-        <v>6.7438752421972756E-4</v>
+        <v>6.7438752421972734E-4</v>
       </c>
       <c r="E51" cm="1">
         <f t="array" ref="E51:H54">MMULT(_xlfn.ANCHORARRAY(E35),$N$1:$Q$4)</f>
@@ -7146,16 +7202,16 @@
     </row>
     <row r="52" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>-1.5914119938074607</v>
+        <v>-1.5914119938074593</v>
       </c>
       <c r="B52">
         <v>1.6029716353299401</v>
       </c>
       <c r="C52">
-        <v>-1.1266098036230342E-2</v>
+        <v>-1.1266098036230387E-2</v>
       </c>
       <c r="D52">
-        <v>-2.9354348624763618E-4</v>
+        <v>-2.9354348624763613E-4</v>
       </c>
       <c r="E52">
         <v>-2.2131176713646239</v>
@@ -7188,16 +7244,16 @@
     </row>
     <row r="53" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>-0.20968683979323627</v>
+        <v>-0.20968683979323613</v>
       </c>
       <c r="B53">
-        <v>-0.31926565163192466</v>
+        <v>-0.31926565163192483</v>
       </c>
       <c r="C53">
         <v>0.5292035720876086</v>
       </c>
       <c r="D53">
-        <v>-2.5108066244799261E-4</v>
+        <v>-2.5108066244799255E-4</v>
       </c>
       <c r="E53">
         <v>1.8679415842407541E-2</v>
@@ -7239,16 +7295,16 @@
     </row>
     <row r="54" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1.6514426895817722</v>
+        <v>1.6514426895817707</v>
       </c>
       <c r="B54">
-        <v>-1.0424288693610395</v>
+        <v>-1.0424288693610393</v>
       </c>
       <c r="C54">
-        <v>-0.60956708963144335</v>
+        <v>-0.60956708963144324</v>
       </c>
       <c r="D54">
-        <v>5.5326941070958852E-4</v>
+        <v>5.5326941070958841E-4</v>
       </c>
       <c r="E54">
         <v>1.9333632463363248</v>
@@ -7293,13 +7349,13 @@
     <row r="56" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A56" cm="1">
         <f t="array" ref="A56:D59">MMULT(_xlfn.ANCHORARRAY(A40),$N$1:$Q$4)</f>
-        <v>3.0769194930042518</v>
+        <v>3.0769194930042492</v>
       </c>
       <c r="B56">
         <v>-2.6582816243435152</v>
       </c>
       <c r="C56">
-        <v>-0.41938199349927341</v>
+        <v>-0.41938199349927335</v>
       </c>
       <c r="D56">
         <v>7.4412483853527982E-4</v>
@@ -7335,16 +7391,16 @@
     </row>
     <row r="57" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>-1.6585779474546976</v>
+        <v>-1.658577947454696</v>
       </c>
       <c r="B57">
         <v>1.5882060027747134</v>
       </c>
       <c r="C57">
-        <v>7.0710877895412499E-2</v>
+        <v>7.0710877895412458E-2</v>
       </c>
       <c r="D57">
-        <v>-3.3893321542719228E-4</v>
+        <v>-3.3893321542719217E-4</v>
       </c>
       <c r="E57">
         <v>-2.2583136487813391</v>
@@ -7375,16 +7431,16 @@
     </row>
     <row r="58" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>-0.34677805307528531</v>
+        <v>-0.34677805307528503</v>
       </c>
       <c r="B58">
-        <v>-8.8994091924783247E-2</v>
+        <v>-8.8994091924783372E-2</v>
       </c>
       <c r="C58">
         <v>0.43601160317175747</v>
       </c>
       <c r="D58">
-        <v>-2.3945817168898091E-4</v>
+        <v>-2.3945817168898086E-4</v>
       </c>
       <c r="E58">
         <v>-0.22589384500541632</v>
@@ -7426,16 +7482,16 @@
     </row>
     <row r="59" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>1.9497888391318225</v>
+        <v>1.9497888391318206</v>
       </c>
       <c r="B59">
-        <v>-1.285126662594579</v>
+        <v>-1.2851266625945788</v>
       </c>
       <c r="C59">
-        <v>-0.66529362797792757</v>
+        <v>-0.66529362797792746</v>
       </c>
       <c r="D59">
-        <v>6.3145144068298142E-4</v>
+        <v>6.3145144068298131E-4</v>
       </c>
       <c r="E59">
         <v>2.3144511409290853</v>
@@ -7474,15 +7530,15 @@
     <row r="61" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A61">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))</f>
-        <v>4.6998461442465507</v>
+        <v>4.6998461442465462</v>
       </c>
       <c r="E61">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E46),_xlfn.MUNIT(4))</f>
-        <v>5.0008761472810752</v>
+        <v>5.0008761472810725</v>
       </c>
       <c r="I61">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(I46),_xlfn.MUNIT(4))</f>
-        <v>5.1017685503914061</v>
+        <v>5.1017685503914025</v>
       </c>
       <c r="BE61" s="9"/>
       <c r="BP61" s="10"/>
@@ -7530,7 +7586,7 @@
     <row r="66" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A66">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A51),_xlfn.MUNIT(4))</f>
-        <v>5.0008761472810752</v>
+        <v>5.0008761472810725</v>
       </c>
       <c r="E66">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))</f>
@@ -7573,7 +7629,7 @@
     <row r="71" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A71">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(A56),_xlfn.MUNIT(4))</f>
-        <v>5.1017685503914061</v>
+        <v>5.1017685503914034</v>
       </c>
       <c r="E71">
         <f>SUMPRODUCT(_xlfn.ANCHORARRAY(E56),_xlfn.MUNIT(4))</f>
@@ -7596,11 +7652,11 @@
     <row r="73" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A73">
         <f>A61/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E73">
         <f>E61/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))))</f>
-        <v>0.91681576858937075</v>
+        <v>0.91681576858937086</v>
       </c>
       <c r="I73">
         <f>I61/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4))))</f>
@@ -7639,7 +7695,7 @@
     <row r="78" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A78">
         <f>A66/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
-        <v>0.91681576858937075</v>
+        <v>0.91681576858937086</v>
       </c>
       <c r="E78">
         <f>E66/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))))</f>
@@ -7653,7 +7709,7 @@
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>A71/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
-        <v>0.90301407305509662</v>
+        <v>0.90301407305509673</v>
       </c>
       <c r="E83">
         <f>E71/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(E51),_xlfn.MUNIT(4))))</f>
@@ -7764,7 +7820,7 @@
       </c>
       <c r="V89" cm="1">
         <f t="array" ref="V89">MAX(ABS(_xlfn.ANCHORARRAY(M93)))</f>
-        <v>0.99957362381448844</v>
+        <v>0.99957362381448789</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
@@ -7800,7 +7856,7 @@
       </c>
       <c r="V90">
         <f>V88/V89</f>
-        <v>2.9128668061864911</v>
+        <v>2.9128668061864924</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
@@ -7888,7 +7944,7 @@
       </c>
       <c r="V93">
         <f>M93*$V$90</f>
-        <v>2.4193791583338093</v>
+        <v>2.4193791583338102</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
@@ -7920,10 +7976,10 @@
         <v>-0.9363482775816786</v>
       </c>
       <c r="M94" s="14">
-        <v>-0.99957362381448844</v>
+        <v>-0.99957362381448789</v>
       </c>
       <c r="N94" s="14">
-        <v>2.8889343555920287E-2</v>
+        <v>2.888934355592062E-2</v>
       </c>
       <c r="P94" s="14">
         <v>-0.99669182814505353</v>
@@ -8238,27 +8294,27 @@
         <v>1.8133534453388238</v>
       </c>
       <c r="M103" s="14">
-        <f t="shared" ref="M103:O105" si="14">$AC$152*A93+$AC$153*E93+$AC$154*I93</f>
+        <f t="shared" ref="M103:O105" si="16">$AC$152*A93+$AC$153*E93+$AC$154*I93</f>
         <v>1</v>
       </c>
       <c r="N103" s="14">
-        <f t="shared" si="14"/>
-        <v>-0.82482658958326938</v>
+        <f t="shared" si="16"/>
+        <v>-0.82482658958326927</v>
       </c>
       <c r="O103" s="14">
-        <f t="shared" si="14"/>
-        <v>0.28918750798290105</v>
+        <f t="shared" si="16"/>
+        <v>0.2891875079829011</v>
       </c>
       <c r="Q103">
-        <f t="shared" ref="Q103:S105" si="15">$AC$140*A93+$AC$141*E93+$AC$142*I93</f>
+        <f t="shared" ref="Q103:S105" si="17">$AC$140*A93+$AC$141*E93+$AC$142*I93</f>
         <v>1</v>
       </c>
       <c r="R103">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>-0.82495938638675614</v>
       </c>
       <c r="S103">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.29595643853495757</v>
       </c>
       <c r="U103" s="16">
@@ -8307,27 +8363,27 @@
         <v>-2.2915701630314245</v>
       </c>
       <c r="M104" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.82482658958326938</v>
       </c>
       <c r="N104" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O104" s="14">
-        <f t="shared" si="14"/>
-        <v>-0.74061368614327683</v>
+        <f t="shared" si="16"/>
+        <v>-0.74061368614327694</v>
       </c>
       <c r="Q104">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>-0.82495938638675614</v>
       </c>
       <c r="R104">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="S104">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="U104" s="16">
@@ -8376,27 +8432,27 @@
         <v>2.0838846526725989</v>
       </c>
       <c r="M105" s="14">
-        <f t="shared" si="14"/>
-        <v>0.28918750798290105</v>
+        <f t="shared" si="16"/>
+        <v>0.2891875079829011</v>
       </c>
       <c r="N105" s="14">
-        <f t="shared" si="14"/>
-        <v>-0.74061368614327683</v>
+        <f t="shared" si="16"/>
+        <v>-0.74061368614327694</v>
       </c>
       <c r="O105" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="Q105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.29595643853495757</v>
       </c>
       <c r="R105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="S105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="U105" s="16">
@@ -8487,7 +8543,7 @@
         <v>0.85692185000260301</v>
       </c>
       <c r="V108" s="14">
-        <f t="shared" ref="V108:V110" si="16">$AC$152*N93+$AC$153*Q93+$AC$154*T93</f>
+        <f t="shared" ref="V108:V110" si="18">$AC$152*N93+$AC$153*Q93+$AC$154*T93</f>
         <v>0.51437212436558544</v>
       </c>
       <c r="X108" s="18" cm="1">
@@ -8528,12 +8584,12 @@
         <v>-2.3510313539583199</v>
       </c>
       <c r="U109" s="14">
-        <f t="shared" ref="U109:U110" si="17">$AC$152*M94+$AC$153*P94+$AC$154*S94</f>
-        <v>-0.99796466927887573</v>
+        <f t="shared" ref="U109:U110" si="19">$AC$152*M94+$AC$153*P94+$AC$154*S94</f>
+        <v>-0.9979646692788755</v>
       </c>
       <c r="V109" s="14">
-        <f t="shared" si="16"/>
-        <v>6.0117780285517952E-2</v>
+        <f t="shared" si="18"/>
+        <v>6.0117780285518056E-2</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.25">
@@ -8565,22 +8621,22 @@
         <v>2.2107634602498205</v>
       </c>
       <c r="U110" s="14">
-        <f t="shared" si="17"/>
-        <v>0.70904534338822844</v>
+        <f t="shared" si="19"/>
+        <v>0.70904534338822867</v>
       </c>
       <c r="V110" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-0.61683423249866121</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="U111" s="18" cm="1">
         <f t="array" ref="U111">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U108</f>
-        <v>1.5452684095797597</v>
+        <v>1.5452684095797602</v>
       </c>
       <c r="V111" s="18" cm="1">
         <f t="array" ref="V111">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*V108</f>
-        <v>0.92755598955512242</v>
+        <v>0.92755598955512264</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
@@ -8593,7 +8649,7 @@
       </c>
       <c r="V112" s="18" cm="1">
         <f t="array" ref="V112">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*V109</f>
-        <v>0.10840907689421803</v>
+        <v>0.10840907689421825</v>
       </c>
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.25">
@@ -8611,11 +8667,11 @@
       </c>
       <c r="U113" s="18" cm="1">
         <f t="array" ref="U113">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U110</f>
-        <v>1.2786059429971754</v>
+        <v>1.2786059429971761</v>
       </c>
       <c r="V113" s="18" cm="1">
         <f t="array" ref="V113">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*V110</f>
-        <v>-1.112323665716614</v>
+        <v>-1.1123236657166145</v>
       </c>
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.25">
@@ -8708,15 +8764,15 @@
       </c>
     </row>
     <row r="140" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A140">
+      <c r="A140" s="14">
         <f>A113</f>
         <v>4.6998461442465498</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="14">
         <f>E113</f>
         <v>4.6780060570600819</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="14">
         <f>I113</f>
         <v>4.646682681066908</v>
       </c>
@@ -8736,7 +8792,7 @@
         <v>8.047367450037564</v>
       </c>
       <c r="J140">
-        <f t="shared" ref="J140" si="18">I140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="J140" si="20">I140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.27965542240933233</v>
       </c>
       <c r="K140" cm="1">
@@ -8744,7 +8800,7 @@
         <v>4.6726852112206263</v>
       </c>
       <c r="L140">
-        <f t="shared" ref="L140" si="19">K140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="L140" si="21">K140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.16238127122226101</v>
       </c>
       <c r="M140" cm="1">
@@ -8756,7 +8812,7 @@
         <v>45.407360153100647</v>
       </c>
       <c r="O140">
-        <f t="shared" ref="O140" si="20">N140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="O140" si="22">N140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.5779588247891891</v>
       </c>
       <c r="P140" cm="1">
@@ -8764,7 +8820,7 @@
         <v>26.387818919345605</v>
       </c>
       <c r="Q140">
-        <f t="shared" ref="Q140" si="21">P140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Q140" si="23">P140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.91700754217655622</v>
       </c>
       <c r="R140" cm="1">
@@ -8772,7 +8828,7 @@
         <v>15.334895929340741</v>
       </c>
       <c r="S140">
-        <f t="shared" ref="S140" si="22">R140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="S140" si="24">R140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.53290555269759898</v>
       </c>
       <c r="T140" cm="1">
@@ -8784,7 +8840,7 @@
         <v>149.02739472143</v>
       </c>
       <c r="V140">
-        <f t="shared" ref="V140" si="23">U140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="V140" si="25">U140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>5.1788761082593879</v>
       </c>
       <c r="W140" cm="1">
@@ -8792,7 +8848,7 @@
         <v>86.60509727763332</v>
       </c>
       <c r="X140">
-        <f t="shared" ref="X140" si="24">W140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="X140" si="26">W140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>3.0096283303013349</v>
       </c>
       <c r="Y140" cm="1">
@@ -8800,7 +8856,7 @@
         <v>50.329289380114972</v>
       </c>
       <c r="Z140">
-        <f t="shared" ref="Z140" si="25">Y140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Z140" si="27">Y140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.7490016168072302</v>
       </c>
       <c r="AA140">
@@ -8856,11 +8912,11 @@
         <v>1</v>
       </c>
       <c r="AU140">
-        <f t="shared" ref="AU140:AU142" si="26">AI140+AM140+AQ140</f>
+        <f t="shared" ref="AU140:AU142" si="28">AI140+AM140+AQ140</f>
         <v>-0.82495938638675614</v>
       </c>
       <c r="AV140">
-        <f t="shared" ref="AV140:AV142" si="27">AJ140+AN140+AR140</f>
+        <f t="shared" ref="AV140:AV142" si="29">AJ140+AN140+AR140</f>
         <v>0.29595643853495757</v>
       </c>
       <c r="AY140">
@@ -8879,7 +8935,7 @@
         <v>1.1978398093026457</v>
       </c>
       <c r="BC140">
-        <f t="shared" ref="BC140" si="28">BB140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BC140" si="30">BB140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>1.2990369496505474</v>
       </c>
       <c r="BD140" cm="1">
@@ -8887,7 +8943,7 @@
         <v>3.0158281988966844</v>
       </c>
       <c r="BE140">
-        <f t="shared" ref="BE140" si="29">BD140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BE140" si="31">BD140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>3.2706145126748045</v>
       </c>
       <c r="BF140" cm="1">
@@ -8895,7 +8951,7 @@
         <v>7.4747387202002393</v>
       </c>
       <c r="BG140">
-        <f t="shared" ref="BG140" si="30">BF140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BG140" si="32">BF140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>8.1062273194749377</v>
       </c>
       <c r="BJ140">
@@ -8904,15 +8960,15 @@
       </c>
     </row>
     <row r="141" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A141">
+      <c r="A141" s="14">
         <f>A118</f>
         <v>4.6780060570600819</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="14">
         <f>E118</f>
         <v>6.3305932194185939</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="14">
         <f>I118</f>
         <v>6.5428296586169088</v>
       </c>
@@ -8923,21 +8979,21 @@
         <v>17.551428935095586</v>
       </c>
       <c r="H141">
-        <f t="shared" ref="H141:L142" si="31">G141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="H141:L142" si="33">G141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.60993266471367891</v>
       </c>
       <c r="I141">
         <v>10.229522033857513</v>
       </c>
       <c r="J141">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.35548784409125522</v>
       </c>
       <c r="K141">
         <v>5.9458741523964278</v>
       </c>
       <c r="L141">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.20662607467655678</v>
       </c>
       <c r="M141">
@@ -8947,21 +9003,21 @@
         <v>57.783893731253237</v>
       </c>
       <c r="O141">
-        <f t="shared" ref="O141" si="32">N141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="O141" si="34">N141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.0080578288734863</v>
       </c>
       <c r="P141">
         <v>33.580269040208748</v>
       </c>
       <c r="Q141">
-        <f t="shared" ref="Q141" si="33">P141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Q141" si="35">P141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.1669535884079416</v>
       </c>
       <c r="R141">
         <v>19.514683744217756</v>
       </c>
       <c r="S141">
-        <f t="shared" ref="S141" si="34">R141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="S141" si="36">R141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.67815806343579765</v>
       </c>
       <c r="T141">
@@ -8971,21 +9027,21 @@
         <v>189.64735688647738</v>
       </c>
       <c r="V141">
-        <f t="shared" ref="V141" si="35">U141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="V141" si="37">U141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>6.5904672587870552</v>
       </c>
       <c r="W141">
         <v>110.21079595728307</v>
       </c>
       <c r="X141">
-        <f t="shared" ref="X141" si="36">W141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="X141" si="38">W141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>3.8299539431816134</v>
       </c>
       <c r="Y141">
         <v>64.047396942089932</v>
       </c>
       <c r="Z141">
-        <f t="shared" ref="Z141" si="37">Y141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Z141" si="39">Y141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.2257218844871729</v>
       </c>
       <c r="AC141">
@@ -9030,15 +9086,15 @@
         <v>-0.34176618068564535</v>
       </c>
       <c r="AT141">
-        <f t="shared" ref="AT141:AT142" si="38">AH141+AL141+AP141</f>
+        <f t="shared" ref="AT141:AT142" si="40">AH141+AL141+AP141</f>
         <v>-0.82495938638675614</v>
       </c>
       <c r="AU141">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="AV141">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="AY141">
@@ -9048,28 +9104,28 @@
         <v>-0.5704822406848985</v>
       </c>
       <c r="BA141">
-        <f t="shared" ref="BA141" si="39">AZ141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BA141" si="41">AZ141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-0.61867831075054847</v>
       </c>
       <c r="BB141">
         <v>-1.4850872662922221</v>
       </c>
       <c r="BC141">
-        <f t="shared" ref="BC141" si="40">BB141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BC141" si="42">BB141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-1.6105519430784687</v>
       </c>
       <c r="BD141">
         <v>-3.6599690693111007</v>
       </c>
       <c r="BE141">
-        <f t="shared" ref="BE141" si="41">BD141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BE141" si="43">BD141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-3.9691743576139498</v>
       </c>
       <c r="BF141">
         <v>-9.0092814972132356</v>
       </c>
       <c r="BG141">
-        <f t="shared" ref="BG141" si="42">BF141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BG141" si="44">BF141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-9.7704129248271006</v>
       </c>
       <c r="BJ141">
@@ -9078,15 +9134,15 @@
       </c>
     </row>
     <row r="142" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A142">
+      <c r="A142" s="14">
         <f>A123</f>
         <v>4.646682681066908</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="14">
         <f>E123</f>
         <v>6.5428296586169088</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="14">
         <f>I123</f>
         <v>6.7915488108954891</v>
       </c>
@@ -9097,21 +9153,21 @@
         <v>17.981061150579304</v>
       </c>
       <c r="H142">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.6248628862361465</v>
       </c>
       <c r="I142">
         <v>10.499121296466662</v>
       </c>
       <c r="J142">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.36485673349941239</v>
       </c>
       <c r="K142">
         <v>6.1033087321190891</v>
       </c>
       <c r="L142">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.21209711028758396</v>
       </c>
       <c r="M142">
@@ -9121,21 +9177,21 @@
         <v>59.314390329480474</v>
       </c>
       <c r="O142">
-        <f t="shared" ref="O142" si="43">N142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="O142" si="45">N142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.0612443740798057</v>
       </c>
       <c r="P142">
         <v>34.469696039302661</v>
       </c>
       <c r="Q142">
-        <f t="shared" ref="Q142" si="44">P142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Q142" si="46">P142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.1978622159408763</v>
       </c>
       <c r="R142">
         <v>20.031561321394342</v>
       </c>
       <c r="S142">
-        <f t="shared" ref="S142" si="45">R142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="S142" si="47">R142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.69612016322515868</v>
       </c>
       <c r="T142">
@@ -9145,21 +9201,21 @@
         <v>194.67047015974859</v>
       </c>
       <c r="V142">
-        <f t="shared" ref="V142" si="46">U142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="V142" si="48">U142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>6.7650263146482388</v>
       </c>
       <c r="W142">
         <v>113.12990498750165</v>
       </c>
       <c r="X142">
-        <f t="shared" ref="X142" si="47">W142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="X142" si="49">W142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>3.9313963930228795</v>
       </c>
       <c r="Y142">
         <v>65.74379458763832</v>
       </c>
       <c r="Z142">
-        <f t="shared" ref="Z142" si="48">Y142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Z142" si="50">Y142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.2846736849468146</v>
       </c>
       <c r="AC142">
@@ -9204,15 +9260,15 @@
         <v>0.36499899542543113</v>
       </c>
       <c r="AT142">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.29595643853495757</v>
       </c>
       <c r="AU142">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="AV142">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AY142">
@@ -9229,21 +9285,21 @@
         <v>1.209345792702718</v>
       </c>
       <c r="BC142">
-        <f t="shared" ref="BC142" si="49">BB142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BC142" si="51">BB142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>1.3115149934279213</v>
       </c>
       <c r="BD142">
         <v>2.8966766241710911</v>
       </c>
       <c r="BE142">
-        <f t="shared" ref="BE142" si="50">BD142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BE142" si="52">BD142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>3.1413966515087903</v>
       </c>
       <c r="BF142">
         <v>7.0684662707961188</v>
       </c>
       <c r="BG142">
-        <f t="shared" ref="BG142" si="51">BF142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BG142" si="53">BF142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>7.6656317412496344</v>
       </c>
       <c r="BJ142">
@@ -9361,7 +9417,7 @@
         <v>45.004167137490029</v>
       </c>
       <c r="BC145">
-        <f t="shared" ref="BC145" si="52">BB145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BC145" si="54">BB145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>1.3505683961136534</v>
       </c>
       <c r="BD145" cm="1">
@@ -9369,7 +9425,7 @@
         <v>-111.21054372594716</v>
       </c>
       <c r="BE145">
-        <f t="shared" ref="BE145" si="53">BD145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BE145" si="55">BD145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-3.337411960364002</v>
       </c>
       <c r="BF145" cm="1">
@@ -9377,7 +9433,7 @@
         <v>274.8073218656919</v>
       </c>
       <c r="BG145">
-        <f t="shared" ref="BG145" si="54">BF145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BG145" si="56">BF145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>8.2469270634109453</v>
       </c>
       <c r="BJ145">
@@ -9386,15 +9442,15 @@
       </c>
     </row>
     <row r="146" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A146">
+      <c r="A146" s="14">
         <f>A126</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="14">
         <f>E126</f>
         <v>0.85762366280578384</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="14">
         <f>I126</f>
         <v>0.8224637814474921</v>
       </c>
@@ -9414,7 +9470,7 @@
         <v>1.5434186437477948</v>
       </c>
       <c r="J146">
-        <f t="shared" ref="J146" si="55">I146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="J146" si="57">I146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.31981097053097252</v>
       </c>
       <c r="K146" cm="1">
@@ -9422,7 +9478,7 @@
         <v>0.89127067879257527</v>
       </c>
       <c r="L146">
-        <f t="shared" ref="L146" si="56">K146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="L146" si="58">K146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.18467973154601167</v>
       </c>
       <c r="M146" cm="1">
@@ -9430,7 +9486,7 @@
         <v>0.51478564613098365</v>
       </c>
       <c r="N146">
-        <f t="shared" ref="N146" si="57">M146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="N146" si="59">M146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.10666846469133749</v>
       </c>
       <c r="O146" cm="1">
@@ -9438,7 +9494,7 @@
         <v>0.29733783140494713</v>
       </c>
       <c r="P146">
-        <f t="shared" ref="P146" si="58">O146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="P146" si="60">O146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.1611216647146763E-2</v>
       </c>
       <c r="Q146" cm="1">
@@ -9446,7 +9502,7 @@
         <v>0.17174117845826059</v>
       </c>
       <c r="R146">
-        <f t="shared" ref="R146" si="59">Q146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="R146" si="61">Q146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.5586399830896655E-2</v>
       </c>
       <c r="S146" cm="1">
@@ -9454,7 +9510,7 @@
         <v>9.9197047927088791E-2</v>
       </c>
       <c r="T146">
-        <f t="shared" ref="T146" si="60">S146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="T146" si="62">S146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>2.0554568457418237E-2</v>
       </c>
       <c r="U146" cm="1">
@@ -9462,7 +9518,7 @@
         <v>5.7295835950954645E-2</v>
       </c>
       <c r="V146">
-        <f t="shared" ref="V146" si="61">U146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="V146" si="63">U146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>1.1872240222758661E-2</v>
       </c>
       <c r="W146" cm="1">
@@ -9470,7 +9526,7 @@
         <v>3.3093855993569496E-2</v>
       </c>
       <c r="X146">
-        <f t="shared" ref="X146" si="62">W146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="X146" si="64">W146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.8573606045186303E-3</v>
       </c>
       <c r="Y146" cm="1">
@@ -9478,7 +9534,7 @@
         <v>1.9114884814763054E-2</v>
       </c>
       <c r="Z146">
-        <f t="shared" ref="Z146:Z148" si="63">Y146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="Z146:Z148" si="65">Y146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.9607852924161335E-3</v>
       </c>
       <c r="AA146">
@@ -9522,38 +9578,38 @@
         <v>-54.247807541274952</v>
       </c>
       <c r="BC146">
-        <f t="shared" ref="BC146" si="64">BB146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BC146" si="66">BB146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-1.6279686767643629</v>
       </c>
       <c r="BD146">
         <v>134.04951934355591</v>
       </c>
       <c r="BE146">
-        <f t="shared" ref="BE146" si="65">BD146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BE146" si="67">BD146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>4.0228062389542005</v>
       </c>
       <c r="BF146">
         <v>-331.24374548012474</v>
       </c>
       <c r="BG146">
-        <f t="shared" ref="BG146" si="66">BF146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BG146" si="68">BF146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-9.9405757846610356</v>
       </c>
       <c r="BJ146">
-        <f t="shared" ref="BJ146:BJ147" si="67">BG146/SUM(BG$145:BG$147)</f>
+        <f>BG146/SUM(BG$145:BG$147)</f>
         <v>-1.627983016204301</v>
       </c>
     </row>
     <row r="147" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A147">
+      <c r="A147" s="14">
         <f>A131</f>
         <v>0.85762366280578384</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="14">
         <f>E131</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="14">
         <f>I131</f>
         <v>0.99783560478438982</v>
       </c>
@@ -9571,63 +9627,63 @@
         <v>1.6510784394907587</v>
       </c>
       <c r="J147">
-        <f t="shared" ref="J147" si="68">I147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="J147" si="69">I147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.34211910054041522</v>
       </c>
       <c r="K147">
         <v>0.95373476848455829</v>
       </c>
       <c r="L147">
-        <f t="shared" ref="L147" si="69">K147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="L147" si="70">K147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.1976228829253539</v>
       </c>
       <c r="M147">
         <v>0.55087700032616083</v>
       </c>
       <c r="N147">
-        <f t="shared" ref="N147" si="70">M147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="N147" si="71">M147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.11414693533162271</v>
       </c>
       <c r="O147">
         <v>0.318184602702002</v>
       </c>
       <c r="P147">
-        <f t="shared" ref="P147" si="71">O147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="P147" si="72">O147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.5930865232419256E-2</v>
       </c>
       <c r="Q147">
         <v>0.18378221783365095</v>
       </c>
       <c r="R147">
-        <f t="shared" ref="R147" si="72">Q147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="R147" si="73">Q147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.8081417306838526E-2</v>
       </c>
       <c r="S147">
         <v>0.10615190732987274</v>
       </c>
       <c r="T147">
-        <f t="shared" ref="T147" si="73">S147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="T147" si="74">S147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>2.1995681239436862E-2</v>
       </c>
       <c r="U147">
         <v>6.1312936223166664E-2</v>
       </c>
       <c r="V147">
-        <f t="shared" ref="V147" si="74">U147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="V147" si="75">U147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>1.2704621470698473E-2</v>
       </c>
       <c r="W147">
         <v>3.5414117768907474E-2</v>
       </c>
       <c r="X147">
-        <f t="shared" ref="X147" si="75">W147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="X147" si="76">W147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>7.3381408343433071E-3</v>
       </c>
       <c r="Y147">
         <v>2.0455059153692355E-2</v>
       </c>
       <c r="Z147">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>4.2384821167676476E-3</v>
       </c>
       <c r="AC147">
@@ -9667,38 +9723,38 @@
         <v>42.56603064110454</v>
       </c>
       <c r="BC147">
-        <f t="shared" ref="BC147" si="76">BB147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BC147" si="77">BB147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>1.2774002806507092</v>
       </c>
       <c r="BD147">
         <v>-105.17982934385645</v>
       </c>
       <c r="BE147">
-        <f t="shared" ref="BE147" si="77">BD147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BE147" si="78">BD147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-3.1564311141779871</v>
       </c>
       <c r="BF147">
         <v>259.90522039121441</v>
       </c>
       <c r="BG147">
-        <f t="shared" ref="BG147" si="78">BF147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BG147" si="79">BF147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>7.7997172033635183</v>
       </c>
       <c r="BJ147">
-        <f t="shared" si="67"/>
+        <f>BG147/SUM(BG$145:BG$147)</f>
         <v>1.2773713931003745</v>
       </c>
     </row>
     <row r="148" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A148">
+      <c r="A148" s="14">
         <f>A136</f>
         <v>0.8224637814474921</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="14">
         <f>E136</f>
         <v>0.99783560478438982</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="14">
         <f>I136</f>
         <v>1</v>
       </c>
@@ -9716,63 +9772,63 @@
         <v>1.6315369992862068</v>
       </c>
       <c r="J148">
-        <f t="shared" ref="J148" si="79">I148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="J148" si="80">I148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.33806992892861243</v>
       </c>
       <c r="K148">
         <v>0.94248148869594528</v>
       </c>
       <c r="L148">
-        <f t="shared" ref="L148" si="80">K148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="L148" si="81">K148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.19529109670167979</v>
       </c>
       <c r="M148">
         <v>0.54437863596877545</v>
       </c>
       <c r="N148">
-        <f t="shared" ref="N148" si="81">M148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="N148" si="82">M148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.11280041264938219</v>
       </c>
       <c r="O148">
         <v>0.31443123773153231</v>
       </c>
       <c r="P148">
-        <f t="shared" ref="P148" si="82">O148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="P148" si="83">O148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.5153132438516947E-2</v>
       </c>
       <c r="Q148">
         <v>0.18161429144485913</v>
       </c>
       <c r="R148">
-        <f t="shared" ref="R148" si="83">Q148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="R148" si="84">Q148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.7632202412844727E-2</v>
       </c>
       <c r="S148">
         <v>0.10489972145528234</v>
       </c>
       <c r="T148">
-        <f t="shared" ref="T148" si="84">S148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="T148" si="85">S148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>2.1736216458795421E-2</v>
       </c>
       <c r="U148">
         <v>6.0589678450503101E-2</v>
       </c>
       <c r="V148">
-        <f t="shared" ref="V148" si="85">U148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="V148" si="86">U148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>1.2554755605622529E-2</v>
       </c>
       <c r="W148">
         <v>3.4996366842256793E-2</v>
       </c>
       <c r="X148">
-        <f t="shared" ref="X148" si="86">W148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="X148" si="87">W148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>7.2515788831620312E-3</v>
       </c>
       <c r="Y148">
         <v>2.0213767814133466E-2</v>
       </c>
       <c r="Z148">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>4.1884842644042313E-3</v>
       </c>
       <c r="AC148">
@@ -9879,112 +9935,112 @@
       </c>
     </row>
     <row r="152" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A152">
+      <c r="A152" s="14">
         <f>A61</f>
-        <v>4.6998461442465507</v>
-      </c>
-      <c r="B152">
+        <v>4.6998461442465462</v>
+      </c>
+      <c r="B152" s="14">
         <f>E61</f>
-        <v>5.0008761472810752</v>
-      </c>
-      <c r="C152">
+        <v>5.0008761472810725</v>
+      </c>
+      <c r="C152" s="14">
         <f>I61</f>
-        <v>5.1017685503914061</v>
+        <v>5.1017685503914025</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152" cm="1">
         <f t="array" ref="G152:G154">MMULT($A$152:$C$154,F152:F154)</f>
-        <v>14.802490841919031</v>
+        <v>14.80249084191902</v>
       </c>
       <c r="H152">
         <f>G152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.49961318616579287</v>
+        <v>0.49961318616579259</v>
       </c>
       <c r="I152" cm="1">
         <f t="array" ref="I152:I154">MMULT($A$152:$C$154,H152:H154)</f>
-        <v>8.5364959841015722</v>
+        <v>8.5364959841015668</v>
       </c>
       <c r="J152">
         <f>I152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.28812353291451615</v>
+        <v>0.28812353291451603</v>
       </c>
       <c r="K152" cm="1">
         <f t="array" ref="K152:K154">MMULT($A$152:$C$154,J152:J154)</f>
-        <v>4.9506211888317004</v>
+        <v>4.9506211888316969</v>
       </c>
       <c r="L152">
         <f>K152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.1670932042496325</v>
+        <v>0.16709320424963242</v>
       </c>
       <c r="M152" cm="1">
         <f t="array" ref="M152:M154">MMULT($A$152:$C$154,L152:L154)</f>
-        <v>2.8716226760032302</v>
+        <v>2.871622676003228</v>
       </c>
       <c r="N152">
         <f>M152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>9.6922914524696036E-2</v>
+        <v>9.692291452469598E-2</v>
       </c>
       <c r="O152" cm="1">
         <f t="array" ref="O152:O154">MMULT($A$152:$C$154,N152:N154)</f>
-        <v>1.6657054041678983</v>
+        <v>1.6657054041678969</v>
       </c>
       <c r="P152">
         <f>O152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>5.6220834255352514E-2</v>
+        <v>5.6220834255352486E-2</v>
       </c>
       <c r="Q152" cm="1">
         <f t="array" ref="Q152:Q154">MMULT($A$152:$C$154,P152:P154)</f>
-        <v>0.96620466078466793</v>
+        <v>0.96620466078466705</v>
       </c>
       <c r="R152">
         <f>Q152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>3.2611308070924966E-2</v>
+        <v>3.2611308070924945E-2</v>
       </c>
       <c r="S152" cm="1">
         <f t="array" ref="S152:S154">MMULT($A$152:$C$154,R152:R154)</f>
-        <v>0.56045411924309341</v>
+        <v>0.56045411924309296</v>
       </c>
       <c r="T152">
         <f>S152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>1.8916429079748304E-2</v>
+        <v>1.8916429079748293E-2</v>
       </c>
       <c r="U152" cm="1">
         <f t="array" ref="U152:U154">MMULT($A$152:$C$154,T152:T154)</f>
-        <v>0.32509553372089289</v>
+        <v>0.32509553372089262</v>
       </c>
       <c r="V152">
         <f>U152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>1.0972613808387092E-2</v>
+        <v>1.0972613808387086E-2</v>
       </c>
       <c r="W152" cm="1">
         <f t="array" ref="W152:W154">MMULT($A$152:$C$154,V152:V154)</f>
-        <v>0.18857405524875154</v>
+        <v>0.18857405524875137</v>
       </c>
       <c r="X152">
         <f>W152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>6.3647453376041987E-3</v>
+        <v>6.3647453376041952E-3</v>
       </c>
       <c r="Y152" cm="1">
         <f t="array" ref="Y152:Y154">MMULT($A$152:$C$154,X152:X154)</f>
-        <v>0.10938376761430459</v>
+        <v>0.10938376761430449</v>
       </c>
       <c r="Z152">
         <f>Y152/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>3.6919173425758712E-3</v>
+        <v>3.691917342575869E-3</v>
       </c>
       <c r="AA152">
         <f>X152/SUM(X152:X154)</f>
-        <v>0.2880644803920136</v>
+        <v>0.28806448039201349</v>
       </c>
       <c r="AC152">
         <f>Z152/SUM($Z$152:$Z$154)</f>
-        <v>0.28806448039200921</v>
+        <v>0.28806448039200916</v>
       </c>
       <c r="AD152">
         <f>AC152</f>
-        <v>0.28806448039200921</v>
+        <v>0.28806448039200916</v>
       </c>
       <c r="AE152">
         <v>0</v>
@@ -9994,15 +10050,15 @@
       </c>
     </row>
     <row r="153" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A153">
+      <c r="A153" s="14">
         <f>A66</f>
-        <v>5.0008761472810752</v>
-      </c>
-      <c r="B153">
+        <v>5.0008761472810725</v>
+      </c>
+      <c r="B153" s="14">
         <f>E66</f>
         <v>6.3305932194185948</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="14">
         <f>I66</f>
         <v>6.5334194267584671</v>
       </c>
@@ -10014,96 +10070,96 @@
       </c>
       <c r="H153">
         <f>G153/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.60297514154314169</v>
+        <v>0.6029751415431418</v>
       </c>
       <c r="I153">
-        <v>10.379079848418346</v>
+        <v>10.379079848418344</v>
       </c>
       <c r="J153">
         <f>I153/SQRT(SUMSQ($G$152:$G$154))</f>
         <v>0.35031436316465236</v>
       </c>
       <c r="K153">
-        <v>6.0208047090736745</v>
+        <v>6.0208047090736727</v>
       </c>
       <c r="L153">
         <f>K153/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.20321400338001047</v>
+        <v>0.20321400338001044</v>
       </c>
       <c r="M153">
-        <v>3.4924191902466948</v>
+        <v>3.4924191902466939</v>
       </c>
       <c r="N153">
         <f>M153/SQRT(SUMSQ($G$152:$G$154))</f>
         <v>0.11787601814449099</v>
       </c>
       <c r="O153">
-        <v>2.0258035847967659</v>
+        <v>2.0258035847967655</v>
       </c>
       <c r="P153">
         <f>O153/SQRT(SUMSQ($G$152:$G$154))</f>
         <v>6.8374856255961292E-2</v>
       </c>
       <c r="Q153">
-        <v>1.1750822712165907</v>
+        <v>1.1750822712165903</v>
       </c>
       <c r="R153">
         <f>Q153/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>3.9661338338199972E-2</v>
+        <v>3.9661338338199965E-2</v>
       </c>
       <c r="S153">
-        <v>0.681615113622145</v>
+        <v>0.68161511362214489</v>
       </c>
       <c r="T153">
         <f>S153/SQRT(SUMSQ($G$152:$G$154))</f>
         <v>2.3005850994424249E-2</v>
       </c>
       <c r="U153">
-        <v>0.39537585959396954</v>
+        <v>0.39537585959396943</v>
       </c>
       <c r="V153">
         <f>U153/SQRT(SUMSQ($G$152:$G$154))</f>
         <v>1.3344713065816249E-2</v>
       </c>
       <c r="W153">
-        <v>0.22934067514796652</v>
+        <v>0.22934067514796644</v>
       </c>
       <c r="X153">
         <f>W153/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>7.7406989574759283E-3</v>
+        <v>7.7406989574759274E-3</v>
       </c>
       <c r="Y153">
-        <v>0.13303074530481829</v>
+        <v>0.13303074530481823</v>
       </c>
       <c r="Z153">
         <f>Y153/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>4.4900493592289099E-3</v>
+        <v>4.4900493592289091E-3</v>
       </c>
       <c r="AC153">
         <f>Z153/SUM($Z$152:$Z$154)</f>
-        <v>0.35033929949751286</v>
+        <v>0.35033929949751291</v>
       </c>
       <c r="AD153">
         <v>0</v>
       </c>
       <c r="AE153">
         <f>AC153</f>
-        <v>0.35033929949751286</v>
+        <v>0.35033929949751291</v>
       </c>
       <c r="AF153">
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A154">
+      <c r="A154" s="14">
         <f>A71</f>
-        <v>5.1017685503914061</v>
-      </c>
-      <c r="B154">
+        <v>5.1017685503914034</v>
+      </c>
+      <c r="B154" s="14">
         <f>E71</f>
         <v>6.5334194267584671</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="14">
         <f>I71</f>
         <v>6.7915488108954891</v>
       </c>
@@ -10115,31 +10171,31 @@
       </c>
       <c r="H154">
         <f>G154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.62193861665786043</v>
+        <v>0.62193861665786065</v>
       </c>
       <c r="I154">
         <v>10.712326816564564</v>
       </c>
       <c r="J154">
         <f>I154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.3615621039208316</v>
+        <v>0.36156210392083171</v>
       </c>
       <c r="K154">
-        <v>6.2142569215717973</v>
+        <v>6.2142569215717964</v>
       </c>
       <c r="L154">
         <f>K154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.20974339612135257</v>
+        <v>0.20974339612135259</v>
       </c>
       <c r="M154">
-        <v>3.6046356844183771</v>
+        <v>3.6046356844183767</v>
       </c>
       <c r="N154">
         <f>M154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>0.12166354558106943</v>
+        <v>0.12166354558106944</v>
       </c>
       <c r="O154">
-        <v>2.0908956523489608</v>
+        <v>2.0908956523489604</v>
       </c>
       <c r="P154">
         <f>O154/SQRT(SUMSQ($G$152:$G$154))</f>
@@ -10150,31 +10206,31 @@
       </c>
       <c r="R154">
         <f>Q154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>4.093571588353398E-2</v>
+        <v>4.0935715883533993E-2</v>
       </c>
       <c r="S154">
-        <v>0.70351641682537724</v>
+        <v>0.70351641682537713</v>
       </c>
       <c r="T154">
         <f>S154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>2.3745063062947398E-2</v>
+        <v>2.3745063062947401E-2</v>
       </c>
       <c r="U154">
-        <v>0.40807987159065012</v>
+        <v>0.40807987159065007</v>
       </c>
       <c r="V154">
         <f>U154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>1.3773498462715519E-2</v>
+        <v>1.3773498462715521E-2</v>
       </c>
       <c r="W154">
-        <v>0.23670973073826759</v>
+        <v>0.23670973073826757</v>
       </c>
       <c r="X154">
         <f>W154/SQRT(SUMSQ($G$152:$G$154))</f>
-        <v>7.9894190804485465E-3</v>
+        <v>7.9894190804485482E-3</v>
       </c>
       <c r="Y154">
-        <v>0.13730522019566774</v>
+        <v>0.13730522019566771</v>
       </c>
       <c r="Z154">
         <f>Y154/SQRT(SUMSQ($G$152:$G$154))</f>
@@ -10182,7 +10238,7 @@
       </c>
       <c r="AC154">
         <f>Z154/SUM($Z$152:$Z$154)</f>
-        <v>0.36159622011047787</v>
+        <v>0.36159622011047793</v>
       </c>
       <c r="AD154">
         <v>0</v>
@@ -10192,59 +10248,59 @@
       </c>
       <c r="AF154">
         <f>AC154</f>
-        <v>0.36159622011047787</v>
+        <v>0.36159622011047793</v>
       </c>
     </row>
     <row r="155" spans="1:62" x14ac:dyDescent="0.25">
       <c r="G155">
         <f>G152*G152+G153*G153+G154*G154</f>
-        <v>877.81261538362708</v>
+        <v>877.81261538362673</v>
       </c>
     </row>
     <row r="156" spans="1:62" x14ac:dyDescent="0.25">
       <c r="G156">
         <f>SQRT(G155)</f>
-        <v>29.627902649084479</v>
+        <v>29.627902649084472</v>
       </c>
       <c r="H156">
         <f>H152/SUM(H152:H154)</f>
-        <v>0.28971028130223786</v>
+        <v>0.28971028130223769</v>
       </c>
       <c r="J156">
         <f>J152/SUM(J152:J154)</f>
-        <v>0.28812353291451609</v>
+        <v>0.28812353291451603</v>
       </c>
       <c r="L156">
         <f>L152/SUM(L152:L154)</f>
-        <v>0.28806659827452286</v>
+        <v>0.2880665982745228</v>
       </c>
       <c r="N156">
         <f>N152/SUM(N152:N154)</f>
-        <v>0.28806455634736788</v>
+        <v>0.28806455634736772</v>
       </c>
       <c r="P156">
         <f>P152/SUM(P152:P154)</f>
-        <v>0.28806448311605698</v>
+        <v>0.28806448311605687</v>
       </c>
       <c r="R156">
         <f>R152/SUM(R152:R154)</f>
-        <v>0.28806448048970379</v>
+        <v>0.28806448048970368</v>
       </c>
       <c r="T156">
         <f>T152/SUM(T152:T154)</f>
-        <v>0.28806448039551286</v>
+        <v>0.28806448039551269</v>
       </c>
       <c r="V156">
         <f>V152/SUM(V152:V154)</f>
-        <v>0.28806448039213473</v>
+        <v>0.28806448039213461</v>
       </c>
       <c r="X156">
         <f>X152/SUM(X152:X154)</f>
-        <v>0.2880644803920136</v>
+        <v>0.28806448039201349</v>
       </c>
       <c r="Z156">
         <f>Z152/SUM(Z152:Z154)</f>
-        <v>0.28806448039200921</v>
+        <v>0.28806448039200916</v>
       </c>
     </row>
     <row r="157" spans="1:62" x14ac:dyDescent="0.25">
@@ -10253,15 +10309,15 @@
       </c>
     </row>
     <row r="158" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A158">
+      <c r="A158" s="14">
         <f>A73</f>
-        <v>0.99999999999999978</v>
-      </c>
-      <c r="B158">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="B158" s="14">
         <f>E73</f>
-        <v>0.91681576858937075</v>
-      </c>
-      <c r="C158">
+        <v>0.91681576858937086</v>
+      </c>
+      <c r="C158" s="14">
         <f>I73</f>
         <v>0.90301407305509662</v>
       </c>
@@ -10278,75 +10334,75 @@
       </c>
       <c r="I158" cm="1">
         <f t="array" ref="I158:I160">MMULT($A$158:$C$160,H158:H160)</f>
-        <v>1.6268400743660727</v>
+        <v>1.6268400743660729</v>
       </c>
       <c r="J158">
         <f>I158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>0.32638219891686582</v>
+        <v>0.32638219891686587</v>
       </c>
       <c r="K158" cm="1">
         <f t="array" ref="K158:K160">MMULT($A$158:$C$160,J158:J160)</f>
-        <v>0.93932791073583277</v>
+        <v>0.93932791073583299</v>
       </c>
       <c r="L158">
         <f>K158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>0.18845116606155088</v>
+        <v>0.18845116606155091</v>
       </c>
       <c r="M158" cm="1">
         <f t="array" ref="M158:M160">MMULT($A$158:$C$160,L158:L160)</f>
-        <v>0.54238049816872891</v>
+        <v>0.54238049816872913</v>
       </c>
       <c r="N158">
         <f>M158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>0.10881422361747214</v>
+        <v>0.10881422361747219</v>
       </c>
       <c r="O158" cm="1">
         <f t="array" ref="O158:O160">MMULT($A$158:$C$160,N158:N160)</f>
-        <v>0.31317818449536355</v>
+        <v>0.31317818449536372</v>
       </c>
       <c r="P158">
         <f>O158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>6.2830874478069912E-2</v>
+        <v>6.2830874478069954E-2</v>
       </c>
       <c r="Q158" cm="1">
         <f t="array" ref="Q158:Q160">MMULT($A$158:$C$160,P158:P160)</f>
-        <v>0.18083353135150149</v>
+        <v>0.18083353135150163</v>
       </c>
       <c r="R158">
         <f>Q158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>3.627943922109466E-2</v>
+        <v>3.6279439221094688E-2</v>
       </c>
       <c r="S158" cm="1">
         <f t="array" ref="S158:S160">MMULT($A$158:$C$160,R158:R160)</f>
-        <v>0.10441584936873764</v>
+        <v>0.10441584936873774</v>
       </c>
       <c r="T158">
         <f>S158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>2.0948263480674648E-2</v>
+        <v>2.0948263480674665E-2</v>
       </c>
       <c r="U158" cm="1">
         <f t="array" ref="U158:U160">MMULT($A$158:$C$160,T158:T160)</f>
-        <v>6.0291194442583136E-2</v>
+        <v>6.0291194442583192E-2</v>
       </c>
       <c r="V158">
         <f>U158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>1.2095824861680074E-2</v>
+        <v>1.2095824861680085E-2</v>
       </c>
       <c r="W158" cm="1">
         <f t="array" ref="W158:W160">MMULT($A$158:$C$160,V158:V160)</f>
-        <v>3.4812991986408776E-2</v>
+        <v>3.481299198640881E-2</v>
       </c>
       <c r="X158">
         <f>W158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>6.9843010720195492E-3</v>
+        <v>6.9843010720195562E-3</v>
       </c>
       <c r="Y158" cm="1">
         <f t="array" ref="Y158:Y160">MMULT($A$158:$C$160,X158:X160)</f>
-        <v>2.0101516021549849E-2</v>
+        <v>2.0101516021549869E-2</v>
       </c>
       <c r="Z158">
         <f>Y158/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>4.0328346369464564E-3</v>
+        <v>4.0328346369464608E-3</v>
       </c>
       <c r="AA158">
         <f>X158/SUM(X158:X160)</f>
@@ -10368,15 +10424,15 @@
       </c>
     </row>
     <row r="159" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A159">
+      <c r="A159" s="14">
         <f>A78</f>
-        <v>0.91681576858937075</v>
-      </c>
-      <c r="B159">
+        <v>0.91681576858937086</v>
+      </c>
+      <c r="B159" s="14">
         <f>E78</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="14">
         <f>I78</f>
         <v>0.99640046664270443</v>
       </c>
@@ -10398,86 +10454,86 @@
         <v>0.33759312896719768</v>
       </c>
       <c r="K159">
-        <v>0.97164061562083359</v>
+        <v>0.9716406156208337</v>
       </c>
       <c r="L159">
         <f>K159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>0.19493385101595725</v>
+        <v>0.19493385101595728</v>
       </c>
       <c r="M159">
-        <v>0.56103942245631278</v>
+        <v>0.56103942245631289</v>
       </c>
       <c r="N159">
         <f>M159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>0.11255764058534957</v>
+        <v>0.1125576405853496</v>
       </c>
       <c r="O159">
-        <v>0.32395213885289953</v>
+        <v>0.32395213885289964</v>
       </c>
       <c r="P159">
         <f>O159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>6.4992381911806313E-2</v>
+        <v>6.4992381911806341E-2</v>
       </c>
       <c r="Q159">
-        <v>0.18705456625098638</v>
+        <v>0.18705456625098646</v>
       </c>
       <c r="R159">
         <f>Q159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>3.7527524439811465E-2</v>
+        <v>3.7527524439811479E-2</v>
       </c>
       <c r="S159">
-        <v>0.10800796329205062</v>
+        <v>0.10800796329205069</v>
       </c>
       <c r="T159">
         <f>S159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>2.166892561552378E-2</v>
+        <v>2.1668925615523794E-2</v>
       </c>
       <c r="U159">
-        <v>6.2365332041023236E-2</v>
+        <v>6.2365332041023278E-2</v>
       </c>
       <c r="V159">
         <f>U159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>1.2511945413971496E-2</v>
+        <v>1.2511945413971505E-2</v>
       </c>
       <c r="W159">
-        <v>3.601062849471344E-2</v>
+        <v>3.6010628494713467E-2</v>
       </c>
       <c r="X159">
         <f>W159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>7.2245749890706206E-3</v>
+        <v>7.2245749890706267E-3</v>
       </c>
       <c r="Y159">
-        <v>2.079304835146522E-2</v>
+        <v>2.079304835146524E-2</v>
       </c>
       <c r="Z159">
         <f>Y159/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>4.1715722092599689E-3</v>
+        <v>4.1715722092599732E-3</v>
       </c>
       <c r="AC159">
         <f>Z159/SUM($Z$158:$Z$160)</f>
-        <v>0.33759828003515202</v>
+        <v>0.33759828003515208</v>
       </c>
       <c r="AD159">
         <v>0</v>
       </c>
       <c r="AE159">
         <f>AC159</f>
-        <v>0.33759828003515202</v>
+        <v>0.33759828003515208</v>
       </c>
       <c r="AF159">
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A160">
+      <c r="A160" s="14">
         <f>A83</f>
-        <v>0.90301407305509662</v>
-      </c>
-      <c r="B160">
+        <v>0.90301407305509673</v>
+      </c>
+      <c r="B160" s="14">
         <f>E83</f>
         <v>0.99640046664270443</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="14">
         <f>I83</f>
         <v>1</v>
       </c>
@@ -10506,53 +10562,53 @@
         <v>0.19402898458837972</v>
       </c>
       <c r="M160">
-        <v>0.55843521974236232</v>
+        <v>0.55843521974236243</v>
       </c>
       <c r="N160">
         <f>M160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>0.1120351765634723</v>
+        <v>0.11203517656347232</v>
       </c>
       <c r="O160">
-        <v>0.32244843744205803</v>
+        <v>0.32244843744205814</v>
       </c>
       <c r="P160">
         <f>O160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>6.4690704211141065E-2</v>
+        <v>6.4690704211141092E-2</v>
       </c>
       <c r="Q160">
-        <v>0.18618630775234118</v>
+        <v>0.18618630775234127</v>
       </c>
       <c r="R160">
         <f>Q160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>3.7353331461361196E-2</v>
+        <v>3.7353331461361217E-2</v>
       </c>
       <c r="S160">
-        <v>0.10750661850433035</v>
+        <v>0.10750661850433041</v>
       </c>
       <c r="T160">
         <f>S160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>2.1568344115959103E-2</v>
+        <v>2.1568344115959117E-2</v>
       </c>
       <c r="U160">
-        <v>6.2075848440028406E-2</v>
+        <v>6.2075848440028447E-2</v>
       </c>
       <c r="V160">
         <f>U160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>1.2453868227570809E-2</v>
+        <v>1.2453868227570818E-2</v>
       </c>
       <c r="W160">
-        <v>3.5843476551966881E-2</v>
+        <v>3.5843476551966909E-2</v>
       </c>
       <c r="X160">
         <f>W160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>7.1910403967732767E-3</v>
+        <v>7.1910403967732819E-3</v>
       </c>
       <c r="Y160">
-        <v>2.0696532445665904E-2</v>
+        <v>2.0696532445665924E-2</v>
       </c>
       <c r="Z160">
         <f>Y160/SQRT(SUMSQ($G$158:$G$160))</f>
-        <v>4.1522088593759863E-3</v>
+        <v>4.1522088593759906E-3</v>
       </c>
       <c r="AC160">
         <f>Z160/SUM($Z$158:$Z$160)</f>
@@ -10590,7 +10646,7 @@
       </c>
       <c r="L162">
         <f>L158/SUM(L158:L160)</f>
-        <v>0.32637096696279178</v>
+        <v>0.32637096696279183</v>
       </c>
       <c r="N162">
         <f>N158/SUM(N158:N160)</f>
@@ -10598,15 +10654,15 @@
       </c>
       <c r="P162">
         <f>P158/SUM(P158:P160)</f>
-        <v>0.32637048389589829</v>
+        <v>0.32637048389589834</v>
       </c>
       <c r="R162">
         <f>R158/SUM(R158:R160)</f>
-        <v>0.32637048310451328</v>
+        <v>0.32637048310451339</v>
       </c>
       <c r="T162">
         <f>T158/SUM(T158:T160)</f>
-        <v>0.32637048307182698</v>
+        <v>0.32637048307182703</v>
       </c>
       <c r="V162">
         <f>V158/SUM(V158:V160)</f>
@@ -10637,8 +10693,8 @@
         <v>17.1859</v>
       </c>
       <c r="D166" cm="1">
-        <f t="array" ref="D166:D168">B166*AC152:AC154</f>
-        <v>4.950647353569031</v>
+        <f t="array" ref="D166:D168">(B166*_xlfn.ANCHORARRAY(K152))/10</f>
+        <v>8.5080880689142653</v>
       </c>
       <c r="F166" cm="1">
         <f t="array" ref="F166:F168">B166*AC140:AC142</f>
@@ -10653,7 +10709,7 @@
         <v>295.73480000000001</v>
       </c>
       <c r="D167">
-        <v>6.020896167234306</v>
+        <v>10.347294764966923</v>
       </c>
       <c r="F167">
         <v>6.1109772389404702</v>
@@ -10667,7 +10723,7 @@
         <v>0.38030000000000003</v>
       </c>
       <c r="D168">
-        <v>6.2143564791966615</v>
+        <v>10.679759802844073</v>
       </c>
       <c r="F168">
         <v>6.2728362354819156</v>
@@ -10729,7 +10785,7 @@
         <v>8.5345179400000006</v>
       </c>
       <c r="E174">
-        <f t="shared" ref="E174:E176" si="87">C174*$B$166</f>
+        <f t="shared" ref="E174:E176" si="88">C174*$B$166</f>
         <v>11.00585036</v>
       </c>
     </row>
@@ -10744,11 +10800,11 @@
         <v>0.57020000000000004</v>
       </c>
       <c r="D175">
-        <f t="shared" ref="D175:D176" si="88">B175*$B$166</f>
+        <f t="shared" ref="D175:D176" si="89">B175*$B$166</f>
         <v>10.3802836</v>
       </c>
       <c r="E175">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>9.799400180000001</v>
       </c>
     </row>
@@ -10763,11 +10819,11 @@
         <v>0.51449999999999996</v>
       </c>
       <c r="D176">
+        <f t="shared" si="89"/>
+        <v>10.713690059999999</v>
+      </c>
+      <c r="E176">
         <f t="shared" si="88"/>
-        <v>10.713690059999999</v>
-      </c>
-      <c r="E176">
-        <f t="shared" si="87"/>
         <v>8.8421455499999997</v>
       </c>
     </row>
@@ -10796,7 +10852,7 @@
         <v>0.7745966692414834</v>
       </c>
       <c r="K182">
-        <f t="shared" ref="K182:K183" si="89">SQRT(H182)</f>
+        <f t="shared" ref="K182:K183" si="90">SQRT(H182)</f>
         <v>0</v>
       </c>
     </row>
@@ -10821,11 +10877,11 @@
         <v>0.4</v>
       </c>
       <c r="J183">
-        <f t="shared" ref="J183" si="90">SQRT(G183)</f>
+        <f t="shared" ref="J183" si="91">SQRT(G183)</f>
         <v>0</v>
       </c>
       <c r="K183">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.63245553203367588</v>
       </c>
     </row>
@@ -10864,7 +10920,7 @@
         <v>1.9544040000000005</v>
       </c>
       <c r="F188">
-        <f t="shared" ref="F188:F189" si="91">C188^2</f>
+        <f t="shared" ref="F188:F189" si="92">C188^2</f>
         <v>0.77760000000000029</v>
       </c>
       <c r="H188">
@@ -10886,11 +10942,11 @@
         <v>0.56400000000000006</v>
       </c>
       <c r="E189">
-        <f t="shared" ref="E189" si="92">B189^2</f>
+        <f t="shared" ref="E189" si="93">B189^2</f>
         <v>0.77759999999999985</v>
       </c>
       <c r="F189">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.31809600000000005</v>
       </c>
       <c r="J189">
@@ -10925,11 +10981,11 @@
         <v>-0.81323059460401514</v>
       </c>
       <c r="E191">
-        <f t="shared" ref="E191:E192" si="93">B191^2</f>
+        <f t="shared" ref="E191:E192" si="94">B191^2</f>
         <v>3.5268840000000004</v>
       </c>
       <c r="F191">
-        <f t="shared" ref="F191:F192" si="94">C191^2</f>
+        <f t="shared" ref="F191:F192" si="95">C191^2</f>
         <v>0.66134400000000004</v>
       </c>
       <c r="H191">
@@ -10952,11 +11008,11 @@
         <v>0.35600000000000009</v>
       </c>
       <c r="E192">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.66134400000000015</v>
       </c>
       <c r="F192">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.12673600000000007</v>
       </c>
     </row>
@@ -10976,7 +11032,7 @@
         <v>2.6254440000000003</v>
       </c>
       <c r="C194">
-        <f t="shared" ref="C194:C195" si="95">C188*C191</f>
+        <f t="shared" ref="C194:C195" si="96">C188*C191</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="H194">
@@ -10994,11 +11050,11 @@
     </row>
     <row r="195" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B195">
-        <f t="shared" ref="B195" si="96">B189*B192</f>
+        <f t="shared" ref="B195" si="97">B189*B192</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="C195">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.20078400000000007</v>
       </c>
     </row>
@@ -11111,7 +11167,7 @@
         <v>0.7745966692414834</v>
       </c>
       <c r="K208">
-        <f t="shared" ref="K208:K209" si="97">SQRT(H208)</f>
+        <f t="shared" ref="K208:K209" si="98">SQRT(H208)</f>
         <v>0</v>
       </c>
       <c r="O208" cm="1">
@@ -11143,11 +11199,11 @@
         <v>0.4</v>
       </c>
       <c r="J209">
-        <f t="shared" ref="J209" si="98">SQRT(G209)</f>
+        <f t="shared" ref="J209" si="99">SQRT(G209)</f>
         <v>0</v>
       </c>
       <c r="K209">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.63245553203367588</v>
       </c>
       <c r="O209">
@@ -11192,7 +11248,7 @@
         <v>1.9544040000000005</v>
       </c>
       <c r="F214">
-        <f t="shared" ref="F214:F215" si="99">C214^2</f>
+        <f t="shared" ref="F214:F215" si="100">C214^2</f>
         <v>0.77760000000000029</v>
       </c>
       <c r="H214">
@@ -11214,11 +11270,11 @@
         <v>0.56400000000000006</v>
       </c>
       <c r="E215">
-        <f t="shared" ref="E215" si="100">B215^2</f>
+        <f t="shared" ref="E215" si="101">B215^2</f>
         <v>0.77759999999999985</v>
       </c>
       <c r="F215">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.31809600000000005</v>
       </c>
       <c r="J215">
@@ -11253,11 +11309,11 @@
         <v>-0.81323059460401514</v>
       </c>
       <c r="E217">
-        <f t="shared" ref="E217:E218" si="101">B217^2</f>
+        <f t="shared" ref="E217:E218" si="102">B217^2</f>
         <v>3.5268840000000004</v>
       </c>
       <c r="F217">
-        <f t="shared" ref="F217:F218" si="102">C217^2</f>
+        <f t="shared" ref="F217:F218" si="103">C217^2</f>
         <v>0.66134400000000004</v>
       </c>
       <c r="H217">
@@ -11280,11 +11336,11 @@
         <v>0.35600000000000009</v>
       </c>
       <c r="E218">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.66134400000000015</v>
       </c>
       <c r="F218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.12673600000000007</v>
       </c>
     </row>
@@ -11304,7 +11360,7 @@
         <v>2.6254440000000003</v>
       </c>
       <c r="C220">
-        <f t="shared" ref="C220:C221" si="103">C214*C217</f>
+        <f t="shared" ref="C220:C221" si="104">C214*C217</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="H220">
@@ -11322,11 +11378,11 @@
     </row>
     <row r="221" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B221">
-        <f t="shared" ref="B221" si="104">B215*B218</f>
+        <f t="shared" ref="B221" si="105">B215*B218</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="C221">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.20078400000000007</v>
       </c>
     </row>
@@ -11416,6 +11472,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/Olahan Data Sampel.xlsx
+++ b/data/Olahan Data Sampel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D60502B-0101-44EF-9EDC-A34F18D183F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E58320F-2B56-4C6A-A0CD-711AB1F6601F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="1650" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="220">
   <si>
     <t>Data Tahun 2020</t>
   </si>
@@ -630,9 +630,6 @@
   </si>
   <si>
     <t>Gc=∑αGk</t>
-  </si>
-  <si>
-    <t>scaleG1</t>
   </si>
   <si>
     <t>Kuantitas</t>
@@ -7706,7 +7703,7 @@
         <v>0.99640046664270443</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>A71/(SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(I56),_xlfn.MUNIT(4)))*SQRT(SUMPRODUCT(_xlfn.ANCHORARRAY(A46),_xlfn.MUNIT(4))))</f>
         <v>0.90301407305509673</v>
@@ -7720,12 +7717,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>-1.4790127066301544</v>
       </c>
@@ -7753,11 +7750,8 @@
       <c r="K87">
         <v>-1.1698614761101329</v>
       </c>
-      <c r="V87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>0.39523545574314989</v>
       </c>
@@ -7785,12 +7779,8 @@
       <c r="K88">
         <v>0.98117866422162847</v>
       </c>
-      <c r="V88" cm="1">
-        <f t="array" ref="V88">MAX(ABS(_xlfn.ANCHORARRAY(N18)))</f>
-        <v>2.9116248291487659</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1.172515630105323</v>
       </c>
@@ -7818,12 +7808,8 @@
       <c r="K89">
         <v>-0.74538955508466542</v>
       </c>
-      <c r="V89" cm="1">
-        <f t="array" ref="V89">MAX(ABS(_xlfn.ANCHORARRAY(M93)))</f>
-        <v>0.99957362381448789</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>-1.7360166352499051</v>
       </c>
@@ -7854,12 +7840,8 @@
       <c r="M90" t="s">
         <v>169</v>
       </c>
-      <c r="V90">
-        <f>V88/V89</f>
-        <v>2.9128668061864924</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>173</v>
       </c>
@@ -7870,7 +7852,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>178</v>
       </c>
@@ -7890,7 +7872,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="15" cm="1">
         <f t="array" ref="A93:C95">MMULT(MMULT(TRANSPOSE(A87:C90), $N$1:$Q$4), A87:C90)</f>
         <v>1.0000000000000002</v>
@@ -7943,11 +7925,31 @@
         <v>0.50665295375324104</v>
       </c>
       <c r="V93">
-        <f>M93*$V$90</f>
-        <v>2.4193791583338102</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+        <f>M93*$U$3*-1</f>
+        <v>-1.2598290795743905</v>
+      </c>
+      <c r="W93">
+        <f>N93*$U$4</f>
+        <v>0.4656742155612687</v>
+      </c>
+      <c r="Y93">
+        <f t="shared" ref="Y93:Y95" si="16">P93*$U$3*-1</f>
+        <v>-1.3244546770647012</v>
+      </c>
+      <c r="Z93">
+        <f t="shared" ref="Z93:Z95" si="17">Q93*$U$4</f>
+        <v>0.40754422346460728</v>
+      </c>
+      <c r="AB93">
+        <f>S93*$U$3*-1</f>
+        <v>-1.3076976550531543</v>
+      </c>
+      <c r="AC93">
+        <f>T93*$U$4</f>
+        <v>0.42366319992846019</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="15">
         <v>-0.8141372497034659</v>
       </c>
@@ -7993,8 +7995,32 @@
       <c r="T94" s="14">
         <v>6.4519571843513826E-2</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V94">
+        <f>M94*$U$3*-1</f>
+        <v>1.5161532726018152</v>
+      </c>
+      <c r="W94">
+        <f>N94*$U$4</f>
+        <v>2.4157269081460823E-2</v>
+      </c>
+      <c r="Y94">
+        <f t="shared" si="16"/>
+        <v>1.5117821649304171</v>
+      </c>
+      <c r="Z94">
+        <f t="shared" si="17"/>
+        <v>6.7942885358043187E-2</v>
+      </c>
+      <c r="AB94">
+        <f t="shared" ref="AB94:AB95" si="18">S94*$U$3*-1</f>
+        <v>1.5136391660115605</v>
+      </c>
+      <c r="AC94">
+        <f t="shared" ref="AC94:AC95" si="19">T94*$U$4</f>
+        <v>5.3951265975546267E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
         <v>-0.27808203787720759</v>
       </c>
@@ -8040,8 +8066,32 @@
       <c r="T95" s="14">
         <v>-0.41075344784035539</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V95">
+        <f>M95*$U$3*-1</f>
+        <v>-0.46102810193662003</v>
+      </c>
+      <c r="W95">
+        <f>N95*$U$4</f>
+        <v>-0.79662952558371936</v>
+      </c>
+      <c r="Y95">
+        <f t="shared" si="16"/>
+        <v>-1.2633747331457292</v>
+      </c>
+      <c r="Z95">
+        <f t="shared" si="17"/>
+        <v>-0.46274547622497347</v>
+      </c>
+      <c r="AB95">
+        <f t="shared" si="18"/>
+        <v>-1.3829357426769076</v>
+      </c>
+      <c r="AC95">
+        <f t="shared" si="19"/>
+        <v>-0.34347203308410518</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>174</v>
       </c>
@@ -8052,7 +8102,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>175</v>
       </c>
@@ -8071,11 +8121,8 @@
       <c r="S97" t="s">
         <v>172</v>
       </c>
-      <c r="V97" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" cm="1">
         <f t="array" ref="A98:C100">MMULT(_xlfn.ANCHORARRAY(A93),_xlfn.ANCHORARRAY(A93))</f>
         <v>1.7401490811446647</v>
@@ -8127,12 +8174,32 @@
       <c r="T98" s="14">
         <v>-0.30719766301389029</v>
       </c>
-      <c r="V98" cm="1">
-        <f t="array" ref="V98">M98/SUM(ABS(M98:M100))</f>
-        <v>-0.33649376690928745</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V98">
+        <f>M98*$AA$3</f>
+        <v>-0.94161150067190247</v>
+      </c>
+      <c r="W98">
+        <f>N98*$AA$4</f>
+        <v>-0.89716820077411741</v>
+      </c>
+      <c r="Y98">
+        <f t="shared" ref="Y98:Y100" si="20">P98*$AA$3</f>
+        <v>-1.3313358646130087</v>
+      </c>
+      <c r="Z98">
+        <f t="shared" ref="Z98:Z100" si="21">Q98*$AA$4</f>
+        <v>-0.34808240443372601</v>
+      </c>
+      <c r="AB98">
+        <f t="shared" ref="AB98:AB100" si="22">S98*$AA$3</f>
+        <v>-1.3913009987938596</v>
+      </c>
+      <c r="AC98">
+        <f t="shared" ref="AC98:AC100" si="23">T98*$AA$4</f>
+        <v>-0.2580767566979692</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>-1.5361399185743245</v>
       </c>
@@ -8178,12 +8245,32 @@
       <c r="T99" s="14">
         <v>-0.14133997045908686</v>
       </c>
-      <c r="V99" cm="1">
-        <f t="array" ref="V99">M99/SUM(ABS(M99:M101))</f>
-        <v>0.68721784913291939</v>
-      </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V99">
+        <f t="shared" ref="V99:V100" si="24">M99*$AA$3</f>
+        <v>1.2759515044598886</v>
+      </c>
+      <c r="W99">
+        <f t="shared" ref="W99:W100" si="25">N99*$AA$4</f>
+        <v>0.32428565835472301</v>
+      </c>
+      <c r="Y99">
+        <f t="shared" si="20"/>
+        <v>1.5650494853105623</v>
+      </c>
+      <c r="Z99">
+        <f t="shared" si="21"/>
+        <v>-7.0982389750193095E-2</v>
+      </c>
+      <c r="AB99">
+        <f t="shared" si="22"/>
+        <v>1.5949039545105403</v>
+      </c>
+      <c r="AC99">
+        <f t="shared" si="23"/>
+        <v>-0.11873970918267887</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>-0.28642283387397738</v>
       </c>
@@ -8229,17 +8316,37 @@
       <c r="T100" s="14">
         <v>0.39767932104203829</v>
       </c>
-      <c r="V100" t="e" cm="1">
-        <f t="array" ref="V100">M100/SUM(ABS(M100:M102))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V100">
+        <f t="shared" si="24"/>
+        <v>-0.5807399450852444</v>
+      </c>
+      <c r="W100">
+        <f t="shared" si="25"/>
+        <v>0.92138101050367027</v>
+      </c>
+      <c r="Y100">
+        <f t="shared" si="20"/>
+        <v>-1.3424718304274097</v>
+      </c>
+      <c r="Z100">
+        <f t="shared" si="21"/>
+        <v>0.41591467673961457</v>
+      </c>
+      <c r="AB100">
+        <f t="shared" si="22"/>
+        <v>-1.4488057216469639</v>
+      </c>
+      <c r="AC100">
+        <f t="shared" si="23"/>
+        <v>0.33409039760741638</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="X101" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>176</v>
       </c>
@@ -8262,7 +8369,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" cm="1">
         <f t="array" ref="A103:C105">MMULT(_xlfn.ANCHORARRAY(E93),_xlfn.ANCHORARRAY(A93))</f>
         <v>1.5490542552806241</v>
@@ -8294,27 +8401,27 @@
         <v>1.8133534453388238</v>
       </c>
       <c r="M103" s="14">
-        <f t="shared" ref="M103:O105" si="16">$AC$152*A93+$AC$153*E93+$AC$154*I93</f>
+        <f t="shared" ref="M103:O105" si="26">$AC$152*A93+$AC$153*E93+$AC$154*I93</f>
         <v>1</v>
       </c>
       <c r="N103" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>-0.82482658958326927</v>
       </c>
       <c r="O103" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0.2891875079829011</v>
       </c>
       <c r="Q103">
-        <f t="shared" ref="Q103:S105" si="17">$AC$140*A93+$AC$141*E93+$AC$142*I93</f>
+        <f t="shared" ref="Q103:S105" si="27">$AC$140*A93+$AC$141*E93+$AC$142*I93</f>
         <v>1</v>
       </c>
       <c r="R103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>-0.82495938638675614</v>
       </c>
       <c r="S103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>0.29595643853495757</v>
       </c>
       <c r="U103" s="16">
@@ -8334,7 +8441,7 @@
         <v>-0.55783151928606856</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>-1.4014775917870677</v>
       </c>
@@ -8363,27 +8470,27 @@
         <v>-2.2915701630314245</v>
       </c>
       <c r="M104" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>-0.82482658958326938</v>
       </c>
       <c r="N104" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="O104" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>-0.74061368614327694</v>
       </c>
       <c r="Q104">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>-0.82495938638675614</v>
       </c>
       <c r="R104">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="S104">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="U104" s="16">
@@ -8403,7 +8510,7 @@
         <v>2.622433481163558E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>0.89198267448669055</v>
       </c>
@@ -8432,27 +8539,27 @@
         <v>2.0838846526725989</v>
       </c>
       <c r="M105" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0.2891875079829011</v>
       </c>
       <c r="N105" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>-0.74061368614327694</v>
       </c>
       <c r="O105" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="Q105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>0.29595643853495757</v>
       </c>
       <c r="R105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="S105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="U105" s="16">
@@ -8472,7 +8579,7 @@
         <v>0.62761794935667969</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="U106" t="s">
         <v>189</v>
       </c>
@@ -8485,7 +8592,7 @@
         <v>-0.98228900548454134</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>177</v>
       </c>
@@ -8507,7 +8614,7 @@
         <v>4.6178594918020233E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" cm="1">
         <f t="array" ref="A108:C110">MMULT(_xlfn.ANCHORARRAY(I93),_xlfn.ANCHORARRAY(A93))</f>
         <v>1.5131089475069888</v>
@@ -8543,7 +8650,7 @@
         <v>0.85692185000260301</v>
       </c>
       <c r="V108" s="14">
-        <f t="shared" ref="V108:V110" si="18">$AC$152*N93+$AC$153*Q93+$AC$154*T93</f>
+        <f t="shared" ref="V108:V110" si="28">$AC$152*N93+$AC$153*Q93+$AC$154*T93</f>
         <v>0.51437212436558544</v>
       </c>
       <c r="X108" s="18" cm="1">
@@ -8555,7 +8662,7 @@
         <v>1.1051763659515697</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>-1.3814094925825509</v>
       </c>
@@ -8584,15 +8691,15 @@
         <v>-2.3510313539583199</v>
       </c>
       <c r="U109" s="14">
-        <f t="shared" ref="U109:U110" si="19">$AC$152*M94+$AC$153*P94+$AC$154*S94</f>
+        <f t="shared" ref="U109:U110" si="29">$AC$152*M94+$AC$153*P94+$AC$154*S94</f>
         <v>-0.9979646692788755</v>
       </c>
       <c r="V109" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>6.0117780285518056E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1.0621745962568658</v>
       </c>
@@ -8621,15 +8728,15 @@
         <v>2.2107634602498205</v>
       </c>
       <c r="U110" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>0.70904534338822867</v>
       </c>
       <c r="V110" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>-0.61683423249866121</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="U111" s="18" cm="1">
         <f t="array" ref="U111">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U108</f>
         <v>1.5452684095797602</v>
@@ -8639,9 +8746,9 @@
         <v>0.92755598955512264</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="U112" s="18" cm="1">
         <f t="array" ref="U112">(MAX(ABS($AK$24:$AL$27))/MAX(ABS($U$108:$V$110)))*0.8*U109</f>
@@ -8751,7 +8858,7 @@
     </row>
     <row r="139" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AC139" t="s">
         <v>110</v>
@@ -8792,7 +8899,7 @@
         <v>8.047367450037564</v>
       </c>
       <c r="J140">
-        <f t="shared" ref="J140" si="20">I140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="J140" si="30">I140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.27965542240933233</v>
       </c>
       <c r="K140" cm="1">
@@ -8800,7 +8907,7 @@
         <v>4.6726852112206263</v>
       </c>
       <c r="L140">
-        <f t="shared" ref="L140" si="21">K140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="L140" si="31">K140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.16238127122226101</v>
       </c>
       <c r="M140" cm="1">
@@ -8812,7 +8919,7 @@
         <v>45.407360153100647</v>
       </c>
       <c r="O140">
-        <f t="shared" ref="O140" si="22">N140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="O140" si="32">N140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.5779588247891891</v>
       </c>
       <c r="P140" cm="1">
@@ -8820,7 +8927,7 @@
         <v>26.387818919345605</v>
       </c>
       <c r="Q140">
-        <f t="shared" ref="Q140" si="23">P140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Q140" si="33">P140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.91700754217655622</v>
       </c>
       <c r="R140" cm="1">
@@ -8828,7 +8935,7 @@
         <v>15.334895929340741</v>
       </c>
       <c r="S140">
-        <f t="shared" ref="S140" si="24">R140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="S140" si="34">R140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.53290555269759898</v>
       </c>
       <c r="T140" cm="1">
@@ -8840,7 +8947,7 @@
         <v>149.02739472143</v>
       </c>
       <c r="V140">
-        <f t="shared" ref="V140" si="25">U140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="V140" si="35">U140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>5.1788761082593879</v>
       </c>
       <c r="W140" cm="1">
@@ -8848,7 +8955,7 @@
         <v>86.60509727763332</v>
       </c>
       <c r="X140">
-        <f t="shared" ref="X140" si="26">W140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="X140" si="36">W140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>3.0096283303013349</v>
       </c>
       <c r="Y140" cm="1">
@@ -8856,7 +8963,7 @@
         <v>50.329289380114972</v>
       </c>
       <c r="Z140">
-        <f t="shared" ref="Z140" si="27">Y140/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Z140" si="37">Y140/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.7490016168072302</v>
       </c>
       <c r="AA140">
@@ -8912,11 +9019,11 @@
         <v>1</v>
       </c>
       <c r="AU140">
-        <f t="shared" ref="AU140:AU142" si="28">AI140+AM140+AQ140</f>
+        <f t="shared" ref="AU140:AU142" si="38">AI140+AM140+AQ140</f>
         <v>-0.82495938638675614</v>
       </c>
       <c r="AV140">
-        <f t="shared" ref="AV140:AV142" si="29">AJ140+AN140+AR140</f>
+        <f t="shared" ref="AV140:AV142" si="39">AJ140+AN140+AR140</f>
         <v>0.29595643853495757</v>
       </c>
       <c r="AY140">
@@ -8935,7 +9042,7 @@
         <v>1.1978398093026457</v>
       </c>
       <c r="BC140">
-        <f t="shared" ref="BC140" si="30">BB140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BC140" si="40">BB140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>1.2990369496505474</v>
       </c>
       <c r="BD140" cm="1">
@@ -8943,7 +9050,7 @@
         <v>3.0158281988966844</v>
       </c>
       <c r="BE140">
-        <f t="shared" ref="BE140" si="31">BD140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BE140" si="41">BD140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>3.2706145126748045</v>
       </c>
       <c r="BF140" cm="1">
@@ -8951,7 +9058,7 @@
         <v>7.4747387202002393</v>
       </c>
       <c r="BG140">
-        <f t="shared" ref="BG140" si="32">BF140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BG140" si="42">BF140/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>8.1062273194749377</v>
       </c>
       <c r="BJ140">
@@ -8979,21 +9086,21 @@
         <v>17.551428935095586</v>
       </c>
       <c r="H141">
-        <f t="shared" ref="H141:L142" si="33">G141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="H141:L142" si="43">G141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.60993266471367891</v>
       </c>
       <c r="I141">
         <v>10.229522033857513</v>
       </c>
       <c r="J141">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0.35548784409125522</v>
       </c>
       <c r="K141">
         <v>5.9458741523964278</v>
       </c>
       <c r="L141">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0.20662607467655678</v>
       </c>
       <c r="M141">
@@ -9003,21 +9110,21 @@
         <v>57.783893731253237</v>
       </c>
       <c r="O141">
-        <f t="shared" ref="O141" si="34">N141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="O141" si="44">N141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.0080578288734863</v>
       </c>
       <c r="P141">
         <v>33.580269040208748</v>
       </c>
       <c r="Q141">
-        <f t="shared" ref="Q141" si="35">P141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Q141" si="45">P141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.1669535884079416</v>
       </c>
       <c r="R141">
         <v>19.514683744217756</v>
       </c>
       <c r="S141">
-        <f t="shared" ref="S141" si="36">R141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="S141" si="46">R141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.67815806343579765</v>
       </c>
       <c r="T141">
@@ -9027,21 +9134,21 @@
         <v>189.64735688647738</v>
       </c>
       <c r="V141">
-        <f t="shared" ref="V141" si="37">U141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="V141" si="47">U141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>6.5904672587870552</v>
       </c>
       <c r="W141">
         <v>110.21079595728307</v>
       </c>
       <c r="X141">
-        <f t="shared" ref="X141" si="38">W141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="X141" si="48">W141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>3.8299539431816134</v>
       </c>
       <c r="Y141">
         <v>64.047396942089932</v>
       </c>
       <c r="Z141">
-        <f t="shared" ref="Z141" si="39">Y141/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Z141" si="49">Y141/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.2257218844871729</v>
       </c>
       <c r="AC141">
@@ -9086,15 +9193,15 @@
         <v>-0.34176618068564535</v>
       </c>
       <c r="AT141">
-        <f t="shared" ref="AT141:AT142" si="40">AH141+AL141+AP141</f>
+        <f t="shared" ref="AT141:AT142" si="50">AH141+AL141+AP141</f>
         <v>-0.82495938638675614</v>
       </c>
       <c r="AU141">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="AV141">
-        <f t="shared" si="29"/>
+        <f t="shared" si="39"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="AY141">
@@ -9104,28 +9211,28 @@
         <v>-0.5704822406848985</v>
       </c>
       <c r="BA141">
-        <f t="shared" ref="BA141" si="41">AZ141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BA141" si="51">AZ141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-0.61867831075054847</v>
       </c>
       <c r="BB141">
         <v>-1.4850872662922221</v>
       </c>
       <c r="BC141">
-        <f t="shared" ref="BC141" si="42">BB141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BC141" si="52">BB141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-1.6105519430784687</v>
       </c>
       <c r="BD141">
         <v>-3.6599690693111007</v>
       </c>
       <c r="BE141">
-        <f t="shared" ref="BE141" si="43">BD141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BE141" si="53">BD141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-3.9691743576139498</v>
       </c>
       <c r="BF141">
         <v>-9.0092814972132356</v>
       </c>
       <c r="BG141">
-        <f t="shared" ref="BG141" si="44">BF141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BG141" si="54">BF141/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>-9.7704129248271006</v>
       </c>
       <c r="BJ141">
@@ -9153,21 +9260,21 @@
         <v>17.981061150579304</v>
       </c>
       <c r="H142">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0.6248628862361465</v>
       </c>
       <c r="I142">
         <v>10.499121296466662</v>
       </c>
       <c r="J142">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0.36485673349941239</v>
       </c>
       <c r="K142">
         <v>6.1033087321190891</v>
       </c>
       <c r="L142">
-        <f t="shared" si="33"/>
+        <f t="shared" si="43"/>
         <v>0.21209711028758396</v>
       </c>
       <c r="M142">
@@ -9177,21 +9284,21 @@
         <v>59.314390329480474</v>
       </c>
       <c r="O142">
-        <f t="shared" ref="O142" si="45">N142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="O142" si="55">N142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.0612443740798057</v>
       </c>
       <c r="P142">
         <v>34.469696039302661</v>
       </c>
       <c r="Q142">
-        <f t="shared" ref="Q142" si="46">P142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Q142" si="56">P142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>1.1978622159408763</v>
       </c>
       <c r="R142">
         <v>20.031561321394342</v>
       </c>
       <c r="S142">
-        <f t="shared" ref="S142" si="47">R142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="S142" si="57">R142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>0.69612016322515868</v>
       </c>
       <c r="T142">
@@ -9201,21 +9308,21 @@
         <v>194.67047015974859</v>
       </c>
       <c r="V142">
-        <f t="shared" ref="V142" si="48">U142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="V142" si="58">U142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>6.7650263146482388</v>
       </c>
       <c r="W142">
         <v>113.12990498750165</v>
       </c>
       <c r="X142">
-        <f t="shared" ref="X142" si="49">W142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="X142" si="59">W142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>3.9313963930228795</v>
       </c>
       <c r="Y142">
         <v>65.74379458763832</v>
       </c>
       <c r="Z142">
-        <f t="shared" ref="Z142" si="50">Y142/SQRT(SUMSQ($G$140:$G$142))</f>
+        <f t="shared" ref="Z142" si="60">Y142/SQRT(SUMSQ($G$140:$G$142))</f>
         <v>2.2846736849468146</v>
       </c>
       <c r="AC142">
@@ -9260,15 +9367,15 @@
         <v>0.36499899542543113</v>
       </c>
       <c r="AT142">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0.29595643853495757</v>
       </c>
       <c r="AU142">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-0.74552285429814225</v>
       </c>
       <c r="AV142">
-        <f t="shared" si="29"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="AY142">
@@ -9285,21 +9392,21 @@
         <v>1.209345792702718</v>
       </c>
       <c r="BC142">
-        <f t="shared" ref="BC142" si="51">BB142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BC142" si="61">BB142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>1.3115149934279213</v>
       </c>
       <c r="BD142">
         <v>2.8966766241710911</v>
       </c>
       <c r="BE142">
-        <f t="shared" ref="BE142" si="52">BD142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BE142" si="62">BD142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>3.1413966515087903</v>
       </c>
       <c r="BF142">
         <v>7.0684662707961188</v>
       </c>
       <c r="BG142">
-        <f t="shared" ref="BG142" si="53">BF142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
+        <f t="shared" ref="BG142" si="63">BF142/SQRT(SUMSQ($AZ$140:$AZ$142))</f>
         <v>7.6656317412496344</v>
       </c>
       <c r="BJ142">
@@ -9389,7 +9496,7 @@
     </row>
     <row r="145" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AT145" cm="1">
         <f t="array" ref="AT145:AV147">AT140:AV142 - BJ144 * MMULT(BJ140:BJ142, TRANSPOSE(BJ140:BJ142))</f>
@@ -9417,7 +9524,7 @@
         <v>45.004167137490029</v>
       </c>
       <c r="BC145">
-        <f t="shared" ref="BC145" si="54">BB145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BC145" si="64">BB145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>1.3505683961136534</v>
       </c>
       <c r="BD145" cm="1">
@@ -9425,7 +9532,7 @@
         <v>-111.21054372594716</v>
       </c>
       <c r="BE145">
-        <f t="shared" ref="BE145" si="55">BD145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BE145" si="65">BD145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-3.337411960364002</v>
       </c>
       <c r="BF145" cm="1">
@@ -9433,7 +9540,7 @@
         <v>274.8073218656919</v>
       </c>
       <c r="BG145">
-        <f t="shared" ref="BG145" si="56">BF145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BG145" si="66">BF145/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>8.2469270634109453</v>
       </c>
       <c r="BJ145">
@@ -9470,7 +9577,7 @@
         <v>1.5434186437477948</v>
       </c>
       <c r="J146">
-        <f t="shared" ref="J146" si="57">I146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="J146" si="67">I146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.31981097053097252</v>
       </c>
       <c r="K146" cm="1">
@@ -9478,7 +9585,7 @@
         <v>0.89127067879257527</v>
       </c>
       <c r="L146">
-        <f t="shared" ref="L146" si="58">K146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="L146" si="68">K146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.18467973154601167</v>
       </c>
       <c r="M146" cm="1">
@@ -9486,7 +9593,7 @@
         <v>0.51478564613098365</v>
       </c>
       <c r="N146">
-        <f t="shared" ref="N146" si="59">M146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="N146" si="69">M146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.10666846469133749</v>
       </c>
       <c r="O146" cm="1">
@@ -9494,7 +9601,7 @@
         <v>0.29733783140494713</v>
       </c>
       <c r="P146">
-        <f t="shared" ref="P146" si="60">O146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="P146" si="70">O146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.1611216647146763E-2</v>
       </c>
       <c r="Q146" cm="1">
@@ -9502,7 +9609,7 @@
         <v>0.17174117845826059</v>
       </c>
       <c r="R146">
-        <f t="shared" ref="R146" si="61">Q146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="R146" si="71">Q146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.5586399830896655E-2</v>
       </c>
       <c r="S146" cm="1">
@@ -9510,7 +9617,7 @@
         <v>9.9197047927088791E-2</v>
       </c>
       <c r="T146">
-        <f t="shared" ref="T146" si="62">S146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="T146" si="72">S146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>2.0554568457418237E-2</v>
       </c>
       <c r="U146" cm="1">
@@ -9518,7 +9625,7 @@
         <v>5.7295835950954645E-2</v>
       </c>
       <c r="V146">
-        <f t="shared" ref="V146" si="63">U146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="V146" si="73">U146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>1.1872240222758661E-2</v>
       </c>
       <c r="W146" cm="1">
@@ -9526,7 +9633,7 @@
         <v>3.3093855993569496E-2</v>
       </c>
       <c r="X146">
-        <f t="shared" ref="X146" si="64">W146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="X146" si="74">W146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.8573606045186303E-3</v>
       </c>
       <c r="Y146" cm="1">
@@ -9534,7 +9641,7 @@
         <v>1.9114884814763054E-2</v>
       </c>
       <c r="Z146">
-        <f t="shared" ref="Z146:Z148" si="65">Y146/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="Z146:Z148" si="75">Y146/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.9607852924161335E-3</v>
       </c>
       <c r="AA146">
@@ -9578,21 +9685,21 @@
         <v>-54.247807541274952</v>
       </c>
       <c r="BC146">
-        <f t="shared" ref="BC146" si="66">BB146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BC146" si="76">BB146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-1.6279686767643629</v>
       </c>
       <c r="BD146">
         <v>134.04951934355591</v>
       </c>
       <c r="BE146">
-        <f t="shared" ref="BE146" si="67">BD146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BE146" si="77">BD146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>4.0228062389542005</v>
       </c>
       <c r="BF146">
         <v>-331.24374548012474</v>
       </c>
       <c r="BG146">
-        <f t="shared" ref="BG146" si="68">BF146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BG146" si="78">BF146/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-9.9405757846610356</v>
       </c>
       <c r="BJ146">
@@ -9627,63 +9734,63 @@
         <v>1.6510784394907587</v>
       </c>
       <c r="J147">
-        <f t="shared" ref="J147" si="69">I147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="J147" si="79">I147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.34211910054041522</v>
       </c>
       <c r="K147">
         <v>0.95373476848455829</v>
       </c>
       <c r="L147">
-        <f t="shared" ref="L147" si="70">K147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="L147" si="80">K147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.1976228829253539</v>
       </c>
       <c r="M147">
         <v>0.55087700032616083</v>
       </c>
       <c r="N147">
-        <f t="shared" ref="N147" si="71">M147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="N147" si="81">M147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.11414693533162271</v>
       </c>
       <c r="O147">
         <v>0.318184602702002</v>
       </c>
       <c r="P147">
-        <f t="shared" ref="P147" si="72">O147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="P147" si="82">O147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.5930865232419256E-2</v>
       </c>
       <c r="Q147">
         <v>0.18378221783365095</v>
       </c>
       <c r="R147">
-        <f t="shared" ref="R147" si="73">Q147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="R147" si="83">Q147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.8081417306838526E-2</v>
       </c>
       <c r="S147">
         <v>0.10615190732987274</v>
       </c>
       <c r="T147">
-        <f t="shared" ref="T147" si="74">S147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="T147" si="84">S147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>2.1995681239436862E-2</v>
       </c>
       <c r="U147">
         <v>6.1312936223166664E-2</v>
       </c>
       <c r="V147">
-        <f t="shared" ref="V147" si="75">U147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="V147" si="85">U147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>1.2704621470698473E-2</v>
       </c>
       <c r="W147">
         <v>3.5414117768907474E-2</v>
       </c>
       <c r="X147">
-        <f t="shared" ref="X147" si="76">W147/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="X147" si="86">W147/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>7.3381408343433071E-3</v>
       </c>
       <c r="Y147">
         <v>2.0455059153692355E-2</v>
       </c>
       <c r="Z147">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>4.2384821167676476E-3</v>
       </c>
       <c r="AC147">
@@ -9723,21 +9830,21 @@
         <v>42.56603064110454</v>
       </c>
       <c r="BC147">
-        <f t="shared" ref="BC147" si="77">BB147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BC147" si="87">BB147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>1.2774002806507092</v>
       </c>
       <c r="BD147">
         <v>-105.17982934385645</v>
       </c>
       <c r="BE147">
-        <f t="shared" ref="BE147" si="78">BD147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BE147" si="88">BD147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>-3.1564311141779871</v>
       </c>
       <c r="BF147">
         <v>259.90522039121441</v>
       </c>
       <c r="BG147">
-        <f t="shared" ref="BG147" si="79">BF147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
+        <f t="shared" ref="BG147" si="89">BF147/SQRT(SUMSQ($AZ$145:$AZ$147))</f>
         <v>7.7997172033635183</v>
       </c>
       <c r="BJ147">
@@ -9772,63 +9879,63 @@
         <v>1.6315369992862068</v>
       </c>
       <c r="J148">
-        <f t="shared" ref="J148" si="80">I148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="J148" si="90">I148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.33806992892861243</v>
       </c>
       <c r="K148">
         <v>0.94248148869594528</v>
       </c>
       <c r="L148">
-        <f t="shared" ref="L148" si="81">K148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="L148" si="91">K148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.19529109670167979</v>
       </c>
       <c r="M148">
         <v>0.54437863596877545</v>
       </c>
       <c r="N148">
-        <f t="shared" ref="N148" si="82">M148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="N148" si="92">M148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>0.11280041264938219</v>
       </c>
       <c r="O148">
         <v>0.31443123773153231</v>
       </c>
       <c r="P148">
-        <f t="shared" ref="P148" si="83">O148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="P148" si="93">O148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>6.5153132438516947E-2</v>
       </c>
       <c r="Q148">
         <v>0.18161429144485913</v>
       </c>
       <c r="R148">
-        <f t="shared" ref="R148" si="84">Q148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="R148" si="94">Q148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>3.7632202412844727E-2</v>
       </c>
       <c r="S148">
         <v>0.10489972145528234</v>
       </c>
       <c r="T148">
-        <f t="shared" ref="T148" si="85">S148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="T148" si="95">S148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>2.1736216458795421E-2</v>
       </c>
       <c r="U148">
         <v>6.0589678450503101E-2</v>
       </c>
       <c r="V148">
-        <f t="shared" ref="V148" si="86">U148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="V148" si="96">U148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>1.2554755605622529E-2</v>
       </c>
       <c r="W148">
         <v>3.4996366842256793E-2</v>
       </c>
       <c r="X148">
-        <f t="shared" ref="X148" si="87">W148/SQRT(SUMSQ($G$146:$G$148))</f>
+        <f t="shared" ref="X148" si="97">W148/SQRT(SUMSQ($G$146:$G$148))</f>
         <v>7.2515788831620312E-3</v>
       </c>
       <c r="Y148">
         <v>2.0213767814133466E-2</v>
       </c>
       <c r="Z148">
-        <f t="shared" si="65"/>
+        <f t="shared" si="75"/>
         <v>4.1884842644042313E-3</v>
       </c>
       <c r="AC148">
@@ -9928,7 +10035,7 @@
     </row>
     <row r="151" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC151" t="s">
         <v>111</v>
@@ -10305,7 +10412,7 @@
     </row>
     <row r="157" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:62" x14ac:dyDescent="0.25">
@@ -10679,15 +10786,15 @@
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>190</v>
+      </c>
+      <c r="B165" t="s">
         <v>191</v>
-      </c>
-      <c r="B165" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B166">
         <v>17.1859</v>
@@ -10703,7 +10810,7 @@
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B167">
         <v>295.73480000000001</v>
@@ -10717,7 +10824,7 @@
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B168">
         <v>0.38030000000000003</v>
@@ -10731,7 +10838,7 @@
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B169">
         <v>1.2999999999999999E-3</v>
@@ -10739,15 +10846,15 @@
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>196</v>
+      </c>
+      <c r="B170" t="s">
         <v>197</v>
-      </c>
-      <c r="B170" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B171">
         <v>27.883299999999998</v>
@@ -10755,24 +10862,24 @@
     </row>
     <row r="173" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="B173" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B173" s="17" t="s">
+      <c r="C173" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C173" s="17" t="s">
-        <v>207</v>
-      </c>
       <c r="D173" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E173" s="17" t="s">
         <v>211</v>
-      </c>
-      <c r="E173" s="17" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="174" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B174" s="17">
         <v>0.49659999999999999</v>
@@ -10785,13 +10892,13 @@
         <v>8.5345179400000006</v>
       </c>
       <c r="E174">
-        <f t="shared" ref="E174:E176" si="88">C174*$B$166</f>
+        <f t="shared" ref="E174:E176" si="98">C174*$B$166</f>
         <v>11.00585036</v>
       </c>
     </row>
     <row r="175" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B175" s="17">
         <v>0.60399999999999998</v>
@@ -10800,17 +10907,17 @@
         <v>0.57020000000000004</v>
       </c>
       <c r="D175">
-        <f t="shared" ref="D175:D176" si="89">B175*$B$166</f>
+        <f t="shared" ref="D175:D176" si="99">B175*$B$166</f>
         <v>10.3802836</v>
       </c>
       <c r="E175">
-        <f t="shared" si="88"/>
+        <f t="shared" si="98"/>
         <v>9.799400180000001</v>
       </c>
     </row>
     <row r="176" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B176" s="17">
         <v>0.62339999999999995</v>
@@ -10819,11 +10926,11 @@
         <v>0.51449999999999996</v>
       </c>
       <c r="D176">
-        <f t="shared" si="89"/>
+        <f t="shared" si="99"/>
         <v>10.713690059999999</v>
       </c>
       <c r="E176">
-        <f t="shared" si="88"/>
+        <f t="shared" si="98"/>
         <v>8.8421455499999997</v>
       </c>
     </row>
@@ -10852,7 +10959,7 @@
         <v>0.7745966692414834</v>
       </c>
       <c r="K182">
-        <f t="shared" ref="K182:K183" si="90">SQRT(H182)</f>
+        <f t="shared" ref="K182:K183" si="100">SQRT(H182)</f>
         <v>0</v>
       </c>
     </row>
@@ -10877,11 +10984,11 @@
         <v>0.4</v>
       </c>
       <c r="J183">
-        <f t="shared" ref="J183" si="91">SQRT(G183)</f>
+        <f t="shared" ref="J183" si="101">SQRT(G183)</f>
         <v>0</v>
       </c>
       <c r="K183">
-        <f t="shared" si="90"/>
+        <f t="shared" si="100"/>
         <v>0.63245553203367588</v>
       </c>
     </row>
@@ -10920,7 +11027,7 @@
         <v>1.9544040000000005</v>
       </c>
       <c r="F188">
-        <f t="shared" ref="F188:F189" si="92">C188^2</f>
+        <f t="shared" ref="F188:F189" si="102">C188^2</f>
         <v>0.77760000000000029</v>
       </c>
       <c r="H188">
@@ -10942,11 +11049,11 @@
         <v>0.56400000000000006</v>
       </c>
       <c r="E189">
-        <f t="shared" ref="E189" si="93">B189^2</f>
+        <f t="shared" ref="E189" si="103">B189^2</f>
         <v>0.77759999999999985</v>
       </c>
       <c r="F189">
-        <f t="shared" si="92"/>
+        <f t="shared" si="102"/>
         <v>0.31809600000000005</v>
       </c>
       <c r="J189">
@@ -10958,14 +11065,14 @@
     </row>
     <row r="190" spans="2:15" x14ac:dyDescent="0.25">
       <c r="K190" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L190">
         <f>SUMPRODUCT(J188:K189,_xlfn.MUNIT(2))</f>
         <v>8.8040080000000014</v>
       </c>
       <c r="N190" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O190">
         <f>(L190+SQRT(L190^2-4*L191))/2</f>
@@ -10981,11 +11088,11 @@
         <v>-0.81323059460401514</v>
       </c>
       <c r="E191">
-        <f t="shared" ref="E191:E192" si="94">B191^2</f>
+        <f t="shared" ref="E191:E192" si="104">B191^2</f>
         <v>3.5268840000000004</v>
       </c>
       <c r="F191">
-        <f t="shared" ref="F191:F192" si="95">C191^2</f>
+        <f t="shared" ref="F191:F192" si="105">C191^2</f>
         <v>0.66134400000000004</v>
       </c>
       <c r="H191">
@@ -10993,7 +11100,7 @@
         <v>4.9763080000000004</v>
       </c>
       <c r="K191" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L191">
         <f>J188*K189-J189*K188</f>
@@ -11008,11 +11115,11 @@
         <v>0.35600000000000009</v>
       </c>
       <c r="E192">
-        <f t="shared" si="94"/>
+        <f t="shared" si="104"/>
         <v>0.66134400000000015</v>
       </c>
       <c r="F192">
-        <f t="shared" si="95"/>
+        <f t="shared" si="105"/>
         <v>0.12673600000000007</v>
       </c>
     </row>
@@ -11032,7 +11139,7 @@
         <v>2.6254440000000003</v>
       </c>
       <c r="C194">
-        <f t="shared" ref="C194:C195" si="96">C188*C191</f>
+        <f t="shared" ref="C194:C195" si="106">C188*C191</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="H194">
@@ -11050,11 +11157,11 @@
     </row>
     <row r="195" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B195">
-        <f t="shared" ref="B195" si="97">B189*B192</f>
+        <f t="shared" ref="B195" si="107">B189*B192</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="C195">
-        <f t="shared" si="96"/>
+        <f t="shared" si="106"/>
         <v>0.20078400000000007</v>
       </c>
     </row>
@@ -11066,19 +11173,19 @@
     </row>
     <row r="197" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J197" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K197">
         <f>-(J194)/J193</f>
         <v>0.87424605853845416</v>
       </c>
       <c r="L197" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J198" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" spans="2:16" x14ac:dyDescent="0.25">
@@ -11107,7 +11214,7 @@
     </row>
     <row r="203" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J203" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K203">
         <f>1 /( K197^2 + 1)</f>
@@ -11116,7 +11223,7 @@
     </row>
     <row r="204" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J204" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K204">
         <f>SQRT(K203)</f>
@@ -11125,7 +11232,7 @@
     </row>
     <row r="205" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J205" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K205">
         <f>K197*K204</f>
@@ -11167,7 +11274,7 @@
         <v>0.7745966692414834</v>
       </c>
       <c r="K208">
-        <f t="shared" ref="K208:K209" si="98">SQRT(H208)</f>
+        <f t="shared" ref="K208:K209" si="108">SQRT(H208)</f>
         <v>0</v>
       </c>
       <c r="O208" cm="1">
@@ -11199,11 +11306,11 @@
         <v>0.4</v>
       </c>
       <c r="J209">
-        <f t="shared" ref="J209" si="99">SQRT(G209)</f>
+        <f t="shared" ref="J209" si="109">SQRT(G209)</f>
         <v>0</v>
       </c>
       <c r="K209">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>0.63245553203367588</v>
       </c>
       <c r="O209">
@@ -11248,7 +11355,7 @@
         <v>1.9544040000000005</v>
       </c>
       <c r="F214">
-        <f t="shared" ref="F214:F215" si="100">C214^2</f>
+        <f t="shared" ref="F214:F215" si="110">C214^2</f>
         <v>0.77760000000000029</v>
       </c>
       <c r="H214">
@@ -11270,11 +11377,11 @@
         <v>0.56400000000000006</v>
       </c>
       <c r="E215">
-        <f t="shared" ref="E215" si="101">B215^2</f>
+        <f t="shared" ref="E215" si="111">B215^2</f>
         <v>0.77759999999999985</v>
       </c>
       <c r="F215">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>0.31809600000000005</v>
       </c>
       <c r="J215">
@@ -11286,14 +11393,14 @@
     </row>
     <row r="216" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K216" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L216">
         <f>SUMPRODUCT(J214:K215,_xlfn.MUNIT(2))</f>
         <v>8.8040080000000014</v>
       </c>
       <c r="N216" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O216">
         <f>(L216+SQRT(L216^2-4*L217))/2</f>
@@ -11309,11 +11416,11 @@
         <v>-0.81323059460401514</v>
       </c>
       <c r="E217">
-        <f t="shared" ref="E217:E218" si="102">B217^2</f>
+        <f t="shared" ref="E217:E218" si="112">B217^2</f>
         <v>3.5268840000000004</v>
       </c>
       <c r="F217">
-        <f t="shared" ref="F217:F218" si="103">C217^2</f>
+        <f t="shared" ref="F217:F218" si="113">C217^2</f>
         <v>0.66134400000000004</v>
       </c>
       <c r="H217">
@@ -11321,7 +11428,7 @@
         <v>4.9763080000000004</v>
       </c>
       <c r="K217" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L217">
         <f>J214*K215-J215*K214</f>
@@ -11336,11 +11443,11 @@
         <v>0.35600000000000009</v>
       </c>
       <c r="E218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="112"/>
         <v>0.66134400000000015</v>
       </c>
       <c r="F218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>0.12673600000000007</v>
       </c>
     </row>
@@ -11360,7 +11467,7 @@
         <v>2.6254440000000003</v>
       </c>
       <c r="C220">
-        <f t="shared" ref="C220:C221" si="104">C214*C217</f>
+        <f t="shared" ref="C220:C221" si="114">C214*C217</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="H220">
@@ -11378,11 +11485,11 @@
     </row>
     <row r="221" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B221">
-        <f t="shared" ref="B221" si="105">B215*B218</f>
+        <f t="shared" ref="B221" si="115">B215*B218</f>
         <v>0.71712000000000009</v>
       </c>
       <c r="C221">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.20078400000000007</v>
       </c>
     </row>
@@ -11394,19 +11501,19 @@
     </row>
     <row r="223" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J223" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K223">
         <f>-(J220)/J219</f>
         <v>0.87424605853845416</v>
       </c>
       <c r="L223" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="224" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J224" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="225" spans="10:13" x14ac:dyDescent="0.25">
@@ -11435,7 +11542,7 @@
     </row>
     <row r="229" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J229" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K229">
         <f>1 /( K223^2 + 1)</f>
@@ -11444,7 +11551,7 @@
     </row>
     <row r="230" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J230" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K230">
         <f>SQRT(K229)</f>
@@ -11453,7 +11560,7 @@
     </row>
     <row r="231" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J231" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K231">
         <f>K223*K230</f>
